--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1920×1080</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>800×600</t>
+          <t>800x600</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>320×480, 480×320, 1024×768, 768×1024 e 800×600</t>
+          <t>320x480, 480x320, 1024x768, 768x1024 e 800x600</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1920×1080</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>728×90</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1450×250</t>
+          <t>1450x250</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>300×250</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1920×1080</t>
+          <t>1920x1080</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1920×1080, 680x1520</t>
+          <t>1920x1080, 680x1520</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>110×80</t>
+          <t>110x80</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1080 x 1080, 1080x1350 e 1080x566</t>
+          <t>1080x1080, 1080x1350 e 1080x566</t>
         </is>
       </c>
       <c r="H36" s="3" t="n"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>320×480, 480×320, 1024×768 e 768×1024</t>
+          <t>320x480, 480x320, 1024x768 e 768x1024</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>650×350</t>
+          <t>650x350</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>100KB (no caso de imagem JPG), 200KB (no caso de imagem PNG - sem transparência), 300KB (no caso de imagem animada GIF - sem transparência)</t>
+          <t>100 KB (no caso de imagem JPG), 200 KB (no caso de imagem PNG - sem transparência), 300 KB (no caso de imagem animada GIF - sem transparência)</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1140×50</t>
+          <t>1140x50</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Desktop: 1140×220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
+          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>300×600</t>
+          <t>300x600</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>Image up to 2.5 MB, gif/mp4 up to 30MB</t>
+          <t>Image up to 2.5 MB, gif/mp4 up to 30 MB</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>720x1280 (portrait), HD 1280x720 (landscape), HD 1080 x 1080 (square)</t>
+          <t>720x1280 (portrait), HD 1280x720 (landscape), HD 1080x1080 (square)</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>1200 x 800</t>
+          <t>1200x800</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -14667,10 +14667,26 @@
           <t>Prog - Native Ad</t>
         </is>
       </c>
-      <c r="G291" s="3" t="n"/>
-      <c r="H291" s="3" t="n"/>
-      <c r="I291" s="3" t="n"/>
-      <c r="J291" s="3" t="n"/>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+        </is>
+      </c>
+      <c r="I291" s="3" t="inlineStr">
+        <is>
+          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
+        </is>
+      </c>
+      <c r="J291" s="3" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
@@ -15115,9 +15131,21 @@
           <t>Prog - Uber Journey Ad</t>
         </is>
       </c>
-      <c r="G305" s="3" t="n"/>
-      <c r="H305" s="3" t="n"/>
-      <c r="I305" s="3" t="n"/>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="inlineStr">
+        <is>
+          <t>Display: imagens. Video: MP4.</t>
+        </is>
+      </c>
       <c r="J305" s="3" t="n"/>
     </row>
     <row r="306">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J310"/>
+  <dimension ref="A1:K310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -498,15 +498,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Aspect Ratio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Tipo de Ficheiro</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
@@ -548,17 +553,17 @@
           <t>970x250, 320x10</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
@@ -600,17 +605,17 @@
           <t>970x250, 300x250</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>JPG</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/cube.html</t>
         </is>
@@ -652,17 +657,17 @@
           <t>1240x150 ou 1240x120, 320x100 ou 320x50</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>GIF, JPEG ou PNG</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/floorad.html</t>
         </is>
@@ -704,17 +709,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
@@ -752,17 +762,17 @@
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>JPG</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
@@ -804,17 +814,17 @@
           <t>1920x540, 576x100</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>JPG</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/hero.html</t>
         </is>
@@ -856,17 +866,22 @@
           <t>600x300, 320x100</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/in-article.html</t>
         </is>
@@ -908,17 +923,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG ou GIF</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/interscroller.html</t>
         </is>
@@ -960,17 +980,22 @@
           <t>600x400, 320x480</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3:2 ou 2:3</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
@@ -1012,17 +1037,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/mrec.html</t>
         </is>
@@ -1064,17 +1089,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>2 MB</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/mrec_video.html</t>
         </is>
@@ -1116,17 +1141,22 @@
           <t>1920x100, 600x900</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>200 KB, 100 KB</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>JPG</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/pushdown.html</t>
         </is>
@@ -1168,17 +1198,22 @@
           <t>1920x1080, 680x1520</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>200 KB, 150 KB</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>JPG</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
@@ -1220,17 +1255,22 @@
           <t>1280x720</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>8 MB</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/video-instream.html</t>
         </is>
@@ -1272,17 +1312,22 @@
           <t>640x360</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>8 MB</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/video-outstream.html</t>
         </is>
@@ -1324,17 +1369,17 @@
           <t>980x250 ou 970x250</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
@@ -1376,17 +1421,22 @@
           <t>1900x285, 570x285</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/billboard-xl/</t>
         </is>
@@ -1428,17 +1478,22 @@
           <t>320x320</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/carrossel-incontent/</t>
         </is>
@@ -1480,17 +1535,22 @@
           <t>320x320</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/carrossel-top/</t>
         </is>
@@ -1532,17 +1592,22 @@
           <t>1920x1080, 680x1520</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>8 MB</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>JPEG</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/dossier/</t>
         </is>
@@ -1584,17 +1649,22 @@
           <t>1920x1080</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/full-frame/</t>
         </is>
@@ -1636,17 +1706,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
@@ -1688,17 +1763,22 @@
           <t>380x676</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/interscroller/</t>
         </is>
@@ -1740,17 +1820,22 @@
           <t>800x600</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
@@ -1792,17 +1877,17 @@
           <t>320x480, 480x320, 1024x768, 768x1024 e 800x600</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>50 KB, 200 KB (800x600)</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/intro-splash/</t>
         </is>
@@ -1844,17 +1929,22 @@
           <t>1920x1080</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/l-frame/</t>
         </is>
@@ -1896,17 +1986,17 @@
           <t>728x90</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
@@ -1948,17 +2038,17 @@
           <t>1450x250</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Imagens (S, M, L e XL)</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/megabillboard/</t>
         </is>
@@ -2000,17 +2090,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/mrec/</t>
         </is>
@@ -2052,17 +2142,22 @@
           <t>1920x1080</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>8 MB</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>JPEG</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/native/</t>
         </is>
@@ -2104,17 +2199,22 @@
           <t>1920x1080, 680x1520</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
@@ -2152,17 +2252,17 @@
         </is>
       </c>
       <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>3 MB</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/outstream/</t>
         </is>
@@ -2200,17 +2300,17 @@
         </is>
       </c>
       <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>40 KB</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>Imagens</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
@@ -2252,17 +2352,17 @@
           <t>110x80</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>50 KB</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF + Copies</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pop-in/</t>
         </is>
@@ -2304,13 +2404,18 @@
           <t>1080x1080, 1080x1350 e 1080x566</t>
         </is>
       </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1:1 ou 4:5 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/post-social-media/</t>
         </is>
@@ -2352,17 +2457,22 @@
           <t>1280x720</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>6 MB</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
@@ -2404,17 +2514,22 @@
           <t>1080x1920</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>3 MB</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/7668/</t>
         </is>
@@ -2456,17 +2571,22 @@
           <t>1920x600, 600x900 e 1920x100</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>JPG</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/push-down/</t>
         </is>
@@ -2508,17 +2628,22 @@
           <t>1440x2560</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>4 GB</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/reel-social-media/</t>
         </is>
@@ -2560,17 +2685,17 @@
           <t>6x19</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>1 MB</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/side-frame/</t>
         </is>
@@ -2608,13 +2733,13 @@
         </is>
       </c>
       <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="inlineStr">
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>Link post Facebook ou Instagram</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/social-card/</t>
         </is>
@@ -2656,17 +2781,17 @@
           <t>320x480, 480x320, 1024x768 e 768x1024</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>50 KB</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/splash/</t>
         </is>
@@ -2708,17 +2833,22 @@
           <t>1440x2560</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>4 GB</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/story-social-media/</t>
         </is>
@@ -2760,17 +2890,17 @@
           <t>650x350</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
@@ -2812,17 +2942,22 @@
           <t>1450x90, 625x90 e 207x90</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>21:9</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/ticker/</t>
         </is>
@@ -2864,17 +2999,22 @@
           <t>720x1280</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>3 MB</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/vertical-video/</t>
         </is>
@@ -2912,17 +3052,17 @@
         </is>
       </c>
       <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/videowall/</t>
         </is>
@@ -2964,17 +3104,17 @@
           <t>250x300</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>2.5 MB</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>HTML / MP4</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/cornerad/</t>
         </is>
@@ -3016,17 +3156,17 @@
           <t>1240x120, 1280x120</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/floorad/</t>
         </is>
@@ -3068,17 +3208,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>80 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
@@ -3120,17 +3265,22 @@
           <t>640x360</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>1 MB</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/incontent/</t>
         </is>
@@ -3172,17 +3322,22 @@
           <t>800x600, 768x1024</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:4</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>120 KB / 1 MB</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
@@ -3224,17 +3379,17 @@
           <t>600x500</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>120 KB / 1 MB</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/layer/</t>
         </is>
@@ -3276,17 +3431,17 @@
           <t>728x90</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>80 KB</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
@@ -3328,17 +3483,17 @@
           <t>1240x220, 970x250, 1280x220 e 1280x600</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
@@ -3380,17 +3535,17 @@
           <t>1240x120, 320x100 e 728x90</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/masthead-sticky-companion/</t>
         </is>
@@ -3428,17 +3583,17 @@
         </is>
       </c>
       <c r="G58" s="3" t="n"/>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>175 KB</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="K58" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/moldura/</t>
         </is>
@@ -3480,17 +3635,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>75 KB</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/m-rec/</t>
         </is>
@@ -3532,17 +3687,22 @@
           <t>950x700, 390x850 / 640x360</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>500 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
@@ -3584,13 +3744,18 @@
           <t>200x200, 850x650</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>260 KB</t>
         </is>
       </c>
-      <c r="I61" s="3" t="n"/>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
@@ -3632,17 +3797,22 @@
           <t>640x360</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>15 MB</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>MP4 ou FLV</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
@@ -3680,9 +3850,9 @@
         </is>
       </c>
       <c r="G63" s="3" t="n"/>
-      <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/showcase-richmedia/</t>
         </is>
@@ -3720,9 +3890,9 @@
         </is>
       </c>
       <c r="G64" s="3" t="n"/>
-      <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/sideticker/</t>
         </is>
@@ -3760,9 +3930,9 @@
         </is>
       </c>
       <c r="G65" s="3" t="n"/>
-      <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
-      <c r="J65" s="3" t="inlineStr">
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/slash/</t>
         </is>
@@ -3800,9 +3970,9 @@
         </is>
       </c>
       <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/topo-extensivel/</t>
         </is>
@@ -3840,17 +4010,17 @@
         </is>
       </c>
       <c r="G67" s="3" t="n"/>
-      <c r="H67" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>10 MB</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="K67" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/audio-desktop.html</t>
         </is>
@@ -3892,17 +4062,17 @@
           <t>Largura exacta - 900px | Altura variável - 300px (máximo)</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>100 KB (no caso de imagem JPG), 200 KB (no caso de imagem PNG - sem transparência), 300 KB (no caso de imagem animada GIF - sem transparência)</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="K68" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/nl-desktop.html</t>
         </is>
@@ -3944,17 +4114,22 @@
           <t>1080x1080</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="K69" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/carrossel-desktop.html</t>
         </is>
@@ -3996,17 +4171,22 @@
           <t>1280x720</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/compare-desktop.html</t>
         </is>
@@ -4048,17 +4228,22 @@
           <t>1080x1080</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="J71" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
+      <c r="K71" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/flipper-desktop.html</t>
         </is>
@@ -4100,17 +4285,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>100 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="K72" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
@@ -4152,17 +4342,17 @@
           <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>500 KB</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="K73" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
@@ -4204,17 +4394,17 @@
           <t>990x600, 300x480</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>120 KB, 75 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="K74" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
@@ -4256,17 +4446,17 @@
           <t>990x600, 300x480</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>120 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>GIF ou WEBM</t>
         </is>
       </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="K75" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/intro-dinamic-desktop.html</t>
         </is>
@@ -4304,17 +4494,17 @@
         </is>
       </c>
       <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>500 KB</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="K76" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/intro-folheto-desktop.html</t>
         </is>
@@ -4356,17 +4546,17 @@
           <t>1200x220, 970x250</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>120 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I77" s="3" t="inlineStr">
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="K77" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
@@ -4408,17 +4598,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
         <is>
           <t>100 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I78" s="3" t="inlineStr">
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/mrec-desktop.html</t>
         </is>
@@ -4456,17 +4646,17 @@
         </is>
       </c>
       <c r="G79" s="3" t="n"/>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>Máxima resolução</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="K79" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
@@ -4508,17 +4698,22 @@
           <t>640x360</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
         <is>
           <t>10 MB</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J80" s="3" t="inlineStr">
+      <c r="K80" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/outstream-desktop.html</t>
         </is>
@@ -4560,17 +4755,22 @@
           <t>200x200, 850x650px</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
         <is>
           <t>120 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I81" s="3" t="inlineStr">
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="K81" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
@@ -4612,17 +4812,22 @@
           <t>640x360</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
         <is>
           <t>10 MB</t>
         </is>
       </c>
-      <c r="I82" s="3" t="inlineStr">
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr">
+      <c r="K82" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
@@ -4664,17 +4869,17 @@
           <t>Imagem de topo Transparente: 750x200px, Imagem Lateral Direita: 670px altura e Imagem Lateral Esquerda: 670px altura</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
+      <c r="J83" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="K83" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/skin-desktop.html</t>
         </is>
@@ -4716,17 +4921,17 @@
           <t>728x120px (60px de altura + 60px altura transparente) | 375x225px (100px de altura + 125px altura transparente)</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I84" s="3" t="inlineStr">
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr">
+      <c r="K84" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-dynamic-mobile.html</t>
         </is>
@@ -4768,17 +4973,17 @@
           <t>970x90, 728x90</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t>40 KB</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr">
+      <c r="K85" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-footer-desktop.html</t>
         </is>
@@ -4820,17 +5025,22 @@
           <t>970x250 e 3800x1880</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
         <is>
           <t>120 KB / 2 MB</t>
         </is>
       </c>
-      <c r="I86" s="3" t="inlineStr">
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / MP4</t>
         </is>
       </c>
-      <c r="J86" s="3" t="inlineStr">
+      <c r="K86" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-to-intro-desktop.html</t>
         </is>
@@ -4872,17 +5082,22 @@
           <t>Background: 1450x90px, Botão 1: 625x90px, Botão 2: 207x90px</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>21:9</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
         <is>
           <t>500 KB</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr">
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J87" s="3" t="inlineStr">
+      <c r="K87" s="3" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/twinad-desktop.html</t>
         </is>
@@ -4924,17 +5139,22 @@
           <t>1080x1080</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J88" s="3" t="inlineStr">
+      <c r="K88" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/ad-selector.html</t>
         </is>
@@ -4976,17 +5196,17 @@
           <t>1140x50</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I89" s="3" t="inlineStr">
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J89" s="3" t="inlineStr">
+      <c r="K89" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
@@ -5028,17 +5248,17 @@
           <t>1140x50, 1140x450</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>300 KB</t>
         </is>
       </c>
-      <c r="I90" s="3" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="J90" s="3" t="inlineStr">
+      <c r="K90" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/barra-topo-extensivel.html</t>
         </is>
@@ -5080,17 +5300,17 @@
           <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I91" s="3" t="inlineStr">
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="J91" s="3" t="inlineStr">
+      <c r="K91" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
@@ -5132,17 +5352,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="I92" s="3" t="inlineStr">
         <is>
           <t>80 KB</t>
         </is>
       </c>
-      <c r="I92" s="3" t="inlineStr">
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J92" s="3" t="inlineStr">
+      <c r="K92" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/cubo-mrec.html</t>
         </is>
@@ -5184,17 +5404,17 @@
           <t>1140x100</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr">
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="J93" s="3" t="inlineStr">
+      <c r="K93" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/floorad.html</t>
         </is>
@@ -5236,17 +5456,22 @@
           <t>1080x1080</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J94" s="3" t="inlineStr">
+      <c r="K94" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/gallery-flip.html</t>
         </is>
@@ -5288,17 +5513,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
         <is>
           <t>80 KB</t>
         </is>
       </c>
-      <c r="I95" s="3" t="inlineStr">
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="J95" s="3" t="inlineStr">
+      <c r="K95" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
@@ -5340,17 +5570,22 @@
           <t>800x600, 768x1024</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:4</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I96" s="3" t="inlineStr">
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="J96" s="3" t="inlineStr">
+      <c r="K96" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
@@ -5392,17 +5627,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
         <is>
           <t>80 KB</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr">
+      <c r="J97" s="3" t="inlineStr">
         <is>
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="J97" s="3" t="inlineStr">
+      <c r="K97" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/mrec.html</t>
         </is>
@@ -5444,17 +5679,17 @@
           <t>Desktop: 700x200px / Mobile 350x165px</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="I98" s="3" t="inlineStr">
         <is>
           <t>40 KB</t>
         </is>
       </c>
-      <c r="I98" s="3" t="inlineStr">
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J98" s="3" t="inlineStr">
+      <c r="K98" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/newsletter.html</t>
         </is>
@@ -5496,17 +5731,17 @@
           <t>800x900</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
+      <c r="I99" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I99" s="3" t="inlineStr">
+      <c r="J99" s="3" t="inlineStr">
         <is>
           <t>JPG / Video</t>
         </is>
       </c>
-      <c r="J99" s="3" t="inlineStr">
+      <c r="K99" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
@@ -5548,17 +5783,22 @@
           <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I100" s="3" t="inlineStr">
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J100" s="3" t="inlineStr">
+      <c r="K100" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
@@ -5600,17 +5840,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>80 KB</t>
         </is>
       </c>
-      <c r="I101" s="3" t="inlineStr">
+      <c r="J101" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J101" s="3" t="inlineStr">
+      <c r="K101" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/prisma-halfpage.html</t>
         </is>
@@ -5652,17 +5897,22 @@
           <t>1080x1080px (1:1) / 1920x1080px (16:9) / 1080x810px (4:3) / 819x1080px (3:4)</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1:1 ou 16:9 ou 4:3 ou 3:4</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J102" s="3" t="inlineStr">
+      <c r="K102" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/scratch-.html</t>
         </is>
@@ -5704,17 +5954,22 @@
           <t>Capa com 1920x1080px / Produtos com 1080x1080px</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>16:9 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I103" s="3" t="inlineStr">
+      <c r="J103" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J103" s="3" t="inlineStr">
+      <c r="K103" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/shopping-ads-.html</t>
         </is>
@@ -5756,17 +6011,22 @@
           <t>Desktop: 2512x1413px e Mobile: 1000x2100px</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I104" s="3" t="inlineStr">
         <is>
           <t>120 KB</t>
         </is>
       </c>
-      <c r="I104" s="3" t="inlineStr">
+      <c r="J104" s="3" t="inlineStr">
         <is>
           <t>JPG</t>
         </is>
       </c>
-      <c r="J104" s="3" t="inlineStr">
+      <c r="K104" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/slidedoorvideo.html</t>
         </is>
@@ -5808,13 +6068,13 @@
           <t>380x220 (4 imagens)</t>
         </is>
       </c>
-      <c r="H105" s="3" t="n"/>
-      <c r="I105" s="3" t="inlineStr">
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="inlineStr">
         <is>
           <t>JPEG, JPG ou PNG</t>
         </is>
       </c>
-      <c r="J105" s="3" t="inlineStr">
+      <c r="K105" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/slidervideo.html</t>
         </is>
@@ -5856,17 +6116,17 @@
           <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
+      <c r="I106" s="3" t="inlineStr">
         <is>
           <t>500 KB</t>
         </is>
       </c>
-      <c r="I106" s="3" t="inlineStr">
+      <c r="J106" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
-      <c r="J106" s="3" t="inlineStr">
+      <c r="K106" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
@@ -5908,13 +6168,13 @@
           <t>Fundo - Dimensões: 1920x220, Imagens dos Produtos (mín. 5) - Dimensões Máximas: 130x200, Imagens dos Logos (até 2) - Dimensões Máximas: 300x70, Imagens de CTA (até 2) - Dimensões Máximas: 300x70</t>
         </is>
       </c>
-      <c r="H107" s="3" t="n"/>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="I107" s="3" t="n"/>
+      <c r="J107" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J107" s="3" t="inlineStr">
+      <c r="K107" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/galeria_header.html</t>
         </is>
@@ -5956,17 +6216,17 @@
           <t>1140x90</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
+      <c r="I108" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I108" s="3" t="inlineStr">
+      <c r="J108" s="3" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="J108" s="3" t="inlineStr">
+      <c r="K108" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/twinad.html</t>
         </is>
@@ -6008,17 +6268,22 @@
           <t>640x360px com rácio de 16:9</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
         <is>
           <t>10 MB</t>
         </is>
       </c>
-      <c r="I109" s="3" t="inlineStr">
+      <c r="J109" s="3" t="inlineStr">
         <is>
           <t>MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="J109" s="3" t="inlineStr">
+      <c r="K109" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/incontent.html</t>
         </is>
@@ -6060,17 +6325,22 @@
           <t>640x360px com rácio de 16:9</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="inlineStr">
         <is>
           <t>10 MB</t>
         </is>
       </c>
-      <c r="I110" s="3" t="inlineStr">
+      <c r="J110" s="3" t="inlineStr">
         <is>
           <t>MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="J110" s="3" t="inlineStr">
+      <c r="K110" s="3" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
@@ -6112,17 +6382,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I111" s="3" t="inlineStr">
+      <c r="J111" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J111" s="3" t="inlineStr">
+      <c r="K111" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278437-cube-3d-viewable-display</t>
         </is>
@@ -6164,17 +6434,22 @@
           <t>Up to 1200px, in a 1:1 ratio (display size is 300x300px), Logo: Minimum 40x40px, maximum 400x400px, 1:1 ratio</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
         <is>
           <t>2.5 MB</t>
         </is>
       </c>
-      <c r="I112" s="3" t="inlineStr">
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J112" s="3" t="inlineStr">
+      <c r="K112" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-app_install_native_outbrain</t>
         </is>
@@ -6212,17 +6487,17 @@
         </is>
       </c>
       <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="inlineStr">
+      <c r="I113" s="3" t="inlineStr">
         <is>
           <t>50 MB</t>
         </is>
       </c>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="J113" s="3" t="inlineStr">
         <is>
           <t>MPEG, MP3, WAV, ou OGG</t>
         </is>
       </c>
-      <c r="J113" s="3" t="inlineStr">
+      <c r="K113" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/audio-ad-specs/</t>
         </is>
@@ -6260,17 +6535,17 @@
         </is>
       </c>
       <c r="G114" s="3" t="n"/>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="I114" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>MP3</t>
         </is>
       </c>
-      <c r="J114" s="3" t="inlineStr">
+      <c r="K114" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6308,17 +6583,17 @@
         </is>
       </c>
       <c r="G115" s="3" t="n"/>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I115" s="3" t="inlineStr">
+      <c r="J115" s="3" t="inlineStr">
         <is>
           <t>MP3</t>
         </is>
       </c>
-      <c r="J115" s="3" t="inlineStr">
+      <c r="K115" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6356,17 +6631,17 @@
         </is>
       </c>
       <c r="G116" s="3" t="n"/>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="I116" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I116" s="3" t="inlineStr">
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>MP3</t>
         </is>
       </c>
-      <c r="J116" s="3" t="inlineStr">
+      <c r="K116" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6408,17 +6683,17 @@
           <t>1450x250 (4 imagens S, M, L e XL)</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr">
+      <c r="J117" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J117" s="3" t="inlineStr">
+      <c r="K117" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_1a_2a_posicao</t>
         </is>
@@ -6460,17 +6735,22 @@
           <t>Display: 970x250px, Carousel: 5 imagens (250x250px)</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I118" s="3" t="inlineStr">
+      <c r="J118" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J118" s="3" t="inlineStr">
+      <c r="K118" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_carousel</t>
         </is>
@@ -6512,13 +6792,13 @@
           <t>970x250</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I119" s="3" t="n"/>
-      <c r="J119" s="3" t="inlineStr">
+      <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
@@ -6560,17 +6840,17 @@
           <t>1450x250 (4 imagens S, M, L e XL)</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="I120" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I120" s="3" t="inlineStr">
+      <c r="J120" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J120" s="3" t="inlineStr">
+      <c r="K120" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard</t>
         </is>
@@ -6608,9 +6888,9 @@
         </is>
       </c>
       <c r="G121" s="3" t="n"/>
-      <c r="H121" s="3" t="n"/>
       <c r="I121" s="3" t="n"/>
-      <c r="J121" s="3" t="inlineStr">
+      <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-artigos_content_marketing</t>
         </is>
@@ -6652,17 +6932,22 @@
           <t>Display: imagem estática 1518x1926px (evitar logos nos cantos da capa por causa da marca de água SAPO JORNAIS), Companion banners: Mrec, 320x50px, Hp, 320x480px</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>4:5 ou 2:3</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="J122" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J122" s="3" t="inlineStr">
+      <c r="K122" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-capa_falsa</t>
         </is>
@@ -6704,17 +6989,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I123" s="3" t="inlineStr">
+      <c r="J123" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J123" s="3" t="inlineStr">
+      <c r="K123" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206459-carousel-square,  https://support.teads.tv/support/solutions/articles/36000206458-carousel-landscape, https://support.teads.tv/support/solutions/articles/36000552432-carousel-vertical-</t>
         </is>
@@ -6756,17 +7041,17 @@
           <t>1:1 ratio, min 300px, max 1200px</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="I124" s="3" t="inlineStr">
         <is>
           <t>Image up to 2.5 MB, gif/mp4 up to 30 MB</t>
         </is>
       </c>
-      <c r="I124" s="3" t="inlineStr">
+      <c r="J124" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J124" s="3" t="inlineStr">
+      <c r="K124" s="3" t="inlineStr">
         <is>
           <t>https://www.outbrain.com/help/ads-specs/#carousel</t>
         </is>
@@ -6804,9 +7089,9 @@
         </is>
       </c>
       <c r="G125" s="3" t="n"/>
-      <c r="H125" s="3" t="n"/>
       <c r="I125" s="3" t="n"/>
       <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -6840,9 +7125,9 @@
         </is>
       </c>
       <c r="G126" s="3" t="n"/>
-      <c r="H126" s="3" t="n"/>
       <c r="I126" s="3" t="n"/>
       <c r="J126" s="3" t="n"/>
+      <c r="K126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -6880,17 +7165,17 @@
           <t>Display: 728x90px, Mobile: 320x100px ou 320x50px</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr">
+      <c r="J127" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J127" s="3" t="inlineStr">
+      <c r="K127" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-companion_banner_resumo_artigo</t>
         </is>
@@ -6932,17 +7217,22 @@
           <t>HTML a 100% com altura máxima de 150px, Imagem: 1920x1080px</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
         <is>
           <t>1.5 MB</t>
         </is>
       </c>
-      <c r="I128" s="3" t="inlineStr">
+      <c r="J128" s="3" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
       </c>
-      <c r="J128" s="3" t="inlineStr">
+      <c r="K128" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-countdown</t>
         </is>
@@ -6980,9 +7270,9 @@
         </is>
       </c>
       <c r="G129" s="3" t="n"/>
-      <c r="H129" s="3" t="n"/>
       <c r="I129" s="3" t="n"/>
       <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -7016,9 +7306,9 @@
         </is>
       </c>
       <c r="G130" s="3" t="n"/>
-      <c r="H130" s="3" t="n"/>
       <c r="I130" s="3" t="n"/>
       <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -7052,9 +7342,9 @@
         </is>
       </c>
       <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -7092,17 +7382,22 @@
           <t>Display: 300x250px, 300x600px, 728x90px, 320x100px, 970x250px</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I132" s="3" t="inlineStr">
+      <c r="J132" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J132" s="3" t="inlineStr">
+      <c r="K132" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-display_standard_cpc_surf</t>
         </is>
@@ -7144,17 +7439,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="I133" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr">
+      <c r="J133" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J133" s="3" t="inlineStr">
+      <c r="K133" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278434-drag-drop-viewable-display</t>
         </is>
@@ -7196,17 +7491,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="I134" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="J134" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J134" s="3" t="inlineStr">
+      <c r="K134" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552435-flip-flow-viewable-display</t>
         </is>
@@ -7248,17 +7543,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="I135" s="3" t="inlineStr">
         <is>
           <t>100 KB</t>
         </is>
       </c>
-      <c r="I135" s="3" t="inlineStr">
+      <c r="J135" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J135" s="3" t="inlineStr">
+      <c r="K135" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206460-flow-square, https://support.teads.tv/support/solutions/articles/36000206461-flow-landscape</t>
         </is>
@@ -7300,17 +7595,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
         <is>
           <t>200 KB / 3.5 MB</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
+      <c r="J136" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="J136" s="3" t="inlineStr">
+      <c r="K136" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
@@ -7352,17 +7652,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I137" s="3" t="inlineStr">
+      <c r="J137" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J137" s="3" t="inlineStr">
+      <c r="K137" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage_flip</t>
         </is>
@@ -7400,9 +7705,9 @@
         </is>
       </c>
       <c r="G138" s="3" t="n"/>
-      <c r="H138" s="3" t="n"/>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -7436,9 +7741,9 @@
         </is>
       </c>
       <c r="G139" s="3" t="n"/>
-      <c r="H139" s="3" t="n"/>
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -7472,9 +7777,9 @@
         </is>
       </c>
       <c r="G140" s="3" t="n"/>
-      <c r="H140" s="3" t="n"/>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -7508,9 +7813,9 @@
         </is>
       </c>
       <c r="G141" s="3" t="n"/>
-      <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -7544,9 +7849,9 @@
         </is>
       </c>
       <c r="G142" s="3" t="n"/>
-      <c r="H142" s="3" t="n"/>
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -7580,9 +7885,9 @@
         </is>
       </c>
       <c r="G143" s="3" t="n"/>
-      <c r="H143" s="3" t="n"/>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="3" t="n"/>
+      <c r="K143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -7616,9 +7921,9 @@
         </is>
       </c>
       <c r="G144" s="3" t="n"/>
-      <c r="H144" s="3" t="n"/>
       <c r="I144" s="3" t="n"/>
       <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -7656,17 +7961,22 @@
           <t>1200x628 / 1280x720</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 16:9</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
         <is>
           <t>75 MB / 500 MB</t>
         </is>
       </c>
-      <c r="I145" s="3" t="inlineStr">
+      <c r="J145" s="3" t="inlineStr">
         <is>
           <t>JPG / MOV ou MP4</t>
         </is>
       </c>
-      <c r="J145" s="3" t="inlineStr">
+      <c r="K145" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-SG/ad-experiences/display-homepage-takeover-ads-specs/</t>
         </is>
@@ -7708,17 +8018,22 @@
           <t>960x540, 720x720</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>16:9 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I146" s="3" t="inlineStr">
+      <c r="J146" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J146" s="3" t="inlineStr">
+      <c r="K146" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278440-hover-viewable-display</t>
         </is>
@@ -7760,17 +8075,22 @@
           <t>600x600, 600x500</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I147" s="3" t="inlineStr">
         <is>
           <t>75 MB</t>
         </is>
       </c>
-      <c r="I147" s="3" t="inlineStr">
+      <c r="J147" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J147" s="3" t="inlineStr">
+      <c r="K147" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/display-ad-specs/</t>
         </is>
@@ -7808,9 +8128,9 @@
         </is>
       </c>
       <c r="G148" s="3" t="n"/>
-      <c r="H148" s="3" t="n"/>
       <c r="I148" s="3" t="n"/>
-      <c r="J148" s="3" t="inlineStr">
+      <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/in-feed-video-ad-specs/</t>
         </is>
@@ -7852,13 +8172,18 @@
           <t>2560x1440, 1080x1920, 1080x1152 / 1920x1080, 1080x1920</t>
         </is>
       </c>
-      <c r="H149" s="3" t="n"/>
-      <c r="I149" s="3" t="inlineStr">
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="n"/>
+      <c r="J149" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou WEBP / MP4</t>
         </is>
       </c>
-      <c r="J149" s="3" t="inlineStr">
+      <c r="K149" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/inline-midscroll-template</t>
         </is>
@@ -7900,17 +8225,22 @@
           <t>720x1280</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I150" s="3" t="inlineStr">
+      <c r="J150" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J150" s="3" t="inlineStr">
+      <c r="K150" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552431-interscroller-display</t>
         </is>
@@ -7952,17 +8282,22 @@
           <t>720x1280</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
         <is>
           <t>50 MB</t>
         </is>
       </c>
-      <c r="I151" s="3" t="inlineStr">
+      <c r="J151" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J151" s="3" t="inlineStr">
+      <c r="K151" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552411-interscroller-video</t>
         </is>
@@ -8004,17 +8339,22 @@
           <t>800x600px (600x400px recomendado)</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:2</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I152" s="3" t="inlineStr">
+      <c r="J152" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J152" s="3" t="inlineStr">
+      <c r="K152" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
@@ -8056,17 +8396,17 @@
           <t>Full Page Ad: HTML5 responsive enviado em zip, juntamente com editáveis (caso sejam necessário ajustes de última hora). Para desenvolvimento, usar o template disponível abaixo. Tipo ficheiro: HTML5 responsive com recursos em WEBP, Leaderboard: 728x90px, Mobile banner: 320x90px</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="I153" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I153" s="3" t="inlineStr">
+      <c r="J153" s="3" t="inlineStr">
         <is>
           <t>WEBP ou GIF</t>
         </is>
       </c>
-      <c r="J153" s="3" t="inlineStr">
+      <c r="K153" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_plus</t>
         </is>
@@ -8108,17 +8448,17 @@
           <t>Full Page Ad: HTML5 responsive enviado em zip, juntamente com editáveis (caso sejam necessário ajustes de última hora). Para desenvolvimento, usar o template disponível abaixo. Tipo ficheiro: HTML5 responsive com recursos em WEBP, Leaderboard: 728x90px, Mobile banner: 320x90px</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
+      <c r="I154" s="3" t="inlineStr">
         <is>
           <t>3.5 MB</t>
         </is>
       </c>
-      <c r="I154" s="3" t="inlineStr">
+      <c r="J154" s="3" t="inlineStr">
         <is>
           <t>HTML5 responsive com recursos em WEBP e MP4/WEBM, WEBP ou GIF (Leaderboard e Mobile)</t>
         </is>
       </c>
-      <c r="J154" s="3" t="inlineStr">
+      <c r="K154" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_plus_video</t>
         </is>
@@ -8160,17 +8500,22 @@
           <t>Vídeo: 800x600px (600x400px recomendado), Fallback: imagem 300x600px</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:2 ou 1:2</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
         <is>
           <t>3.5 MB</t>
         </is>
       </c>
-      <c r="I155" s="3" t="inlineStr">
+      <c r="J155" s="3" t="inlineStr">
         <is>
           <t>MP4 ou WEBP</t>
         </is>
       </c>
-      <c r="J155" s="3" t="inlineStr">
+      <c r="K155" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_video</t>
         </is>
@@ -8212,17 +8557,22 @@
           <t>720x1280 (portrait), HD 1280x720 (landscape), HD 1080x1080 (square)</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>9:16 ou 16:9 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
         <is>
           <t>500 MB</t>
         </is>
       </c>
-      <c r="I156" s="3" t="inlineStr">
+      <c r="J156" s="3" t="inlineStr">
         <is>
           <t>MP4, WebM, ou MOV</t>
         </is>
       </c>
-      <c r="J156" s="3" t="inlineStr">
+      <c r="K156" s="3" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/in-stream-video-ad-specs/</t>
         </is>
@@ -8260,9 +8610,9 @@
         </is>
       </c>
       <c r="G157" s="3" t="n"/>
-      <c r="H157" s="3" t="n"/>
       <c r="I157" s="3" t="n"/>
-      <c r="J157" s="3" t="inlineStr">
+      <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-microsites_landing_pages</t>
         </is>
@@ -8304,17 +8654,17 @@
           <t>728x90</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
+      <c r="I158" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I158" s="3" t="inlineStr">
+      <c r="J158" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J158" s="3" t="inlineStr">
+      <c r="K158" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
@@ -8352,9 +8702,9 @@
         </is>
       </c>
       <c r="G159" s="3" t="n"/>
-      <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="n"/>
-      <c r="J159" s="3" t="inlineStr">
+      <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-microsites_landing_pages</t>
         </is>
@@ -8396,17 +8746,17 @@
           <t>Display: 320x100px ou 320x50px, Carousel: 5 imagens (176x95px)</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
+      <c r="I160" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I160" s="3" t="inlineStr">
+      <c r="J160" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J160" s="3" t="inlineStr">
+      <c r="K160" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mobile_banner</t>
         </is>
@@ -8448,17 +8798,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
+      <c r="I161" s="3" t="inlineStr">
         <is>
           <t>200 KB / 3.5 MB</t>
         </is>
       </c>
-      <c r="I161" s="3" t="inlineStr">
+      <c r="J161" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF / MP4 ou WEBP</t>
         </is>
       </c>
-      <c r="J161" s="3" t="inlineStr">
+      <c r="K161" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mrec, https://saleshouse.sapo.pt/formatos.html#format-mrec_video</t>
         </is>
@@ -8500,17 +8850,17 @@
           <t>Display: 300x250px, Carousel: 5 imagens (200x120px)</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr">
+      <c r="I162" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I162" s="3" t="inlineStr">
+      <c r="J162" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J162" s="3" t="inlineStr">
+      <c r="K162" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mrec_carousel</t>
         </is>
@@ -8552,17 +8902,22 @@
           <t>960x540, 720x720</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>16:9 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
         <is>
           <t>200 KB / 50 MB</t>
         </is>
       </c>
-      <c r="I163" s="3" t="inlineStr">
+      <c r="J163" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="J163" s="3" t="inlineStr">
+      <c r="K163" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206444-video-overlay</t>
         </is>
@@ -8604,17 +8959,22 @@
           <t>1080x1920</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
         <is>
           <t>200 KB / 50 MB</t>
         </is>
       </c>
-      <c r="I164" s="3" t="inlineStr">
+      <c r="J164" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou WEBP / MP4</t>
         </is>
       </c>
-      <c r="J164" s="3" t="inlineStr">
+      <c r="K164" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/inline-expander-reel-template</t>
         </is>
@@ -8656,17 +9016,22 @@
           <t>960x540, 720x720</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>16:9 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I165" s="3" t="inlineStr">
+      <c r="J165" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J165" s="3" t="inlineStr">
+      <c r="K165" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278439-scratch-viewable-display</t>
         </is>
@@ -8708,17 +9073,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
+      <c r="I166" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I166" s="3" t="inlineStr">
+      <c r="J166" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J166" s="3" t="inlineStr">
+      <c r="K166" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206455-scroller-square, https://support.teads.tv/support/solutions/articles/36000206453-scroller-landscape, https://support.teads.tv/support/solutions/articles/36000206456-scroller-vertical</t>
         </is>
@@ -8760,13 +9125,18 @@
           <t>Carousel Images: 1080x1080, Product Images: 540x540, Logo: 170x170</t>
         </is>
       </c>
-      <c r="H167" s="3" t="n"/>
-      <c r="I167" s="3" t="inlineStr">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="n"/>
+      <c r="J167" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J167" s="3" t="inlineStr">
+      <c r="K167" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000434238-shoppable-carousel</t>
         </is>
@@ -8808,17 +9178,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
+      <c r="I168" s="3" t="inlineStr">
         <is>
           <t>200 KB / 50 MB</t>
         </is>
       </c>
-      <c r="I168" s="3" t="inlineStr">
+      <c r="J168" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="J168" s="3" t="inlineStr">
+      <c r="K168" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206452-shoppable-square, https://support.teads.tv/support/solutions/articles/36000206451-shoppable-landscape, https://support.teads.tv/support/solutions/articles/36000552430-shoppable-vertical</t>
         </is>
@@ -8860,13 +9230,18 @@
           <t>1200x627</t>
         </is>
       </c>
-      <c r="H169" s="3" t="n"/>
-      <c r="I169" s="3" t="inlineStr">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1.91:1</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J169" s="3" t="inlineStr">
+      <c r="K169" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000208421-single-image</t>
         </is>
@@ -8908,13 +9283,13 @@
           <t>16:9</t>
         </is>
       </c>
-      <c r="H170" s="3" t="n"/>
-      <c r="I170" s="3" t="inlineStr">
+      <c r="I170" s="3" t="n"/>
+      <c r="J170" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J170" s="3" t="inlineStr">
+      <c r="K170" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000297712-single-video</t>
         </is>
@@ -8956,9 +9331,9 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H171" s="3" t="n"/>
       <c r="I171" s="3" t="n"/>
-      <c r="J171" s="3" t="inlineStr">
+      <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/fluid-skin-image-video</t>
         </is>
@@ -9000,17 +9375,22 @@
           <t>960x540, 720x720</t>
         </is>
       </c>
-      <c r="H172" s="3" t="inlineStr">
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>16:9 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I172" s="3" t="inlineStr">
+      <c r="J172" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J172" s="3" t="inlineStr">
+      <c r="K172" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278442-slider-viewable-display</t>
         </is>
@@ -9052,17 +9432,22 @@
           <t>960x540</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
         <is>
           <t>200 KB / 4 MB</t>
         </is>
       </c>
-      <c r="I173" s="3" t="inlineStr">
+      <c r="J173" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="J173" s="3" t="inlineStr">
+      <c r="K173" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000366159-inread-smart6</t>
         </is>
@@ -9104,9 +9489,9 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H174" s="3" t="n"/>
       <c r="I174" s="3" t="n"/>
-      <c r="J174" s="3" t="inlineStr">
+      <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000238201-social-video-image-layout-1-, https://support.teads.tv/support/solutions/articles/36000238202-social-video-image-layout-2-</t>
         </is>
@@ -9148,9 +9533,9 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H175" s="3" t="n"/>
       <c r="I175" s="3" t="n"/>
-      <c r="J175" s="3" t="inlineStr">
+      <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000297713-social-layout-1-performance, https://support.teads.tv/support/solutions/articles/36000297714-social-layout-2-performance</t>
         </is>
@@ -9192,9 +9577,9 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H176" s="3" t="n"/>
       <c r="I176" s="3" t="n"/>
-      <c r="J176" s="3" t="inlineStr">
+      <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000238201-social-video-image-layout-1-, https://support.teads.tv/support/solutions/articles/36000238202-social-video-image-layout-2-</t>
         </is>
@@ -9236,17 +9621,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H177" s="3" t="inlineStr">
+      <c r="I177" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I177" s="3" t="inlineStr">
+      <c r="J177" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J177" s="3" t="inlineStr">
+      <c r="K177" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278441-spin-card-viewable-display</t>
         </is>
@@ -9288,17 +9673,17 @@
           <t>Mrec (300x250px), Halfpage, Billboard, Floor-Ad Mobile (320x100px)</t>
         </is>
       </c>
-      <c r="H178" s="3" t="inlineStr">
+      <c r="I178" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I178" s="3" t="inlineStr">
+      <c r="J178" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J178" s="3" t="inlineStr">
+      <c r="K178" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-standard_green_ad</t>
         </is>
@@ -9340,17 +9725,22 @@
           <t>1200x800</t>
         </is>
       </c>
-      <c r="H179" s="3" t="inlineStr">
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="I179" s="3" t="inlineStr">
         <is>
           <t>2.5 MB</t>
         </is>
       </c>
-      <c r="I179" s="3" t="inlineStr">
+      <c r="J179" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J179" s="3" t="inlineStr">
+      <c r="K179" s="3" t="inlineStr">
         <is>
           <t>https://www.outbrain.com/help/ads-specs/#native-image</t>
         </is>
@@ -9392,9 +9782,9 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H180" s="3" t="n"/>
       <c r="I180" s="3" t="n"/>
-      <c r="J180" s="3" t="inlineStr">
+      <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000245892-stories-display-square, https://support.teads.tv/support/solutions/articles/36000245899-stories-display-vertical</t>
         </is>
@@ -9436,9 +9826,9 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H181" s="3" t="n"/>
       <c r="I181" s="3" t="n"/>
-      <c r="J181" s="3" t="inlineStr">
+      <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000245891-stories-video-square, https://support.teads.tv/support/solutions/articles/36000245901-stories-video-vertical</t>
         </is>
@@ -9480,17 +9870,22 @@
           <t>520x520, 720x1280</t>
         </is>
       </c>
-      <c r="H182" s="3" t="inlineStr">
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>1:1 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I182" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I182" s="3" t="inlineStr">
+      <c r="J182" s="3" t="inlineStr">
         <is>
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="J182" s="3" t="inlineStr">
+      <c r="K182" s="3" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278444-swipe-carousel-viewable-display</t>
         </is>
@@ -9532,17 +9927,22 @@
           <t>2560x1440 (16:9), 1080x1920</t>
         </is>
       </c>
-      <c r="H183" s="3" t="inlineStr">
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I183" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I183" s="3" t="inlineStr">
+      <c r="J183" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou WEBP</t>
         </is>
       </c>
-      <c r="J183" s="3" t="inlineStr">
+      <c r="K183" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-desktop-image</t>
         </is>
@@ -9584,9 +9984,9 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H184" s="3" t="n"/>
       <c r="I184" s="3" t="n"/>
-      <c r="J184" s="3" t="inlineStr">
+      <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/fluid-product-carousel, https://www.adnami.io/specs/dynamic-hybrid-carousel, https://www.adnami.io/specs/product-lightbox</t>
         </is>
@@ -9628,17 +10028,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H185" s="3" t="inlineStr">
+      <c r="I185" s="3" t="inlineStr">
         <is>
           <t>3.5 MB</t>
         </is>
       </c>
-      <c r="I185" s="3" t="inlineStr">
+      <c r="J185" s="3" t="inlineStr">
         <is>
           <t>JPG ou WEBP</t>
         </is>
       </c>
-      <c r="J185" s="3" t="inlineStr">
+      <c r="K185" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-expand-template-image-desktop, https://www.adnami.io/specs/topscroll-expand-template-image-mobile</t>
         </is>
@@ -9680,17 +10080,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H186" s="3" t="inlineStr">
+      <c r="I186" s="3" t="inlineStr">
         <is>
           <t>3.5 MB</t>
         </is>
       </c>
-      <c r="I186" s="3" t="inlineStr">
+      <c r="J186" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J186" s="3" t="inlineStr">
+      <c r="K186" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-expand-template-desktop, https://www.adnami.io/specs/topscroll-expand-template-mobile</t>
         </is>
@@ -9732,17 +10132,17 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H187" s="3" t="inlineStr">
+      <c r="I187" s="3" t="inlineStr">
         <is>
           <t>3.5 MB</t>
         </is>
       </c>
-      <c r="I187" s="3" t="inlineStr">
+      <c r="J187" s="3" t="inlineStr">
         <is>
           <t>JPG ou WEBP</t>
         </is>
       </c>
-      <c r="J187" s="3" t="inlineStr">
+      <c r="K187" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/prismo</t>
         </is>
@@ -9784,9 +10184,9 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="H188" s="3" t="n"/>
       <c r="I188" s="3" t="n"/>
-      <c r="J188" s="3" t="inlineStr">
+      <c r="J188" s="3" t="n"/>
+      <c r="K188" s="3" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-desktop-video, https://www.adnami.io/specs/topscroll-mobile-video</t>
         </is>
@@ -9828,17 +10228,17 @@
           <t>Super Leaderboard: 1376x90px: dependendo das dimensões de ecrã, a criatividade vai sendo cortada do lado direito para o esquerdo. A informação principal deverá estar sempre do lado esquerdo.</t>
         </is>
       </c>
-      <c r="H189" s="3" t="inlineStr">
+      <c r="I189" s="3" t="inlineStr">
         <is>
           <t>200 KB</t>
         </is>
       </c>
-      <c r="I189" s="3" t="inlineStr">
+      <c r="J189" s="3" t="inlineStr">
         <is>
           <t>WEBP</t>
         </is>
       </c>
-      <c r="J189" s="3" t="inlineStr">
+      <c r="K189" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-twin_ad</t>
         </is>
@@ -9880,17 +10280,22 @@
           <t>640x360px (16:9)</t>
         </is>
       </c>
-      <c r="H190" s="3" t="inlineStr">
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I190" s="3" t="inlineStr">
         <is>
           <t>3.5 MB</t>
         </is>
       </c>
-      <c r="I190" s="3" t="inlineStr">
+      <c r="J190" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J190" s="3" t="inlineStr">
+      <c r="K190" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
@@ -9932,17 +10337,22 @@
           <t>640x360px (16:9)</t>
         </is>
       </c>
-      <c r="H191" s="3" t="inlineStr">
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I191" s="3" t="inlineStr">
         <is>
           <t>3.5 MB</t>
         </is>
       </c>
-      <c r="I191" s="3" t="inlineStr">
+      <c r="J191" s="3" t="inlineStr">
         <is>
           <t>MP4</t>
         </is>
       </c>
-      <c r="J191" s="3" t="inlineStr">
+      <c r="K191" s="3" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
@@ -9984,17 +10394,17 @@
           <t>Imagem do artigo/newsletter (conteúdo orgânico)</t>
         </is>
       </c>
-      <c r="H192" s="3" t="inlineStr">
+      <c r="I192" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I192" s="3" t="inlineStr">
+      <c r="J192" s="3" t="inlineStr">
         <is>
           <t>Post/artigo ou newsletter já publicado no LinkedIn</t>
         </is>
       </c>
-      <c r="J192" s="3" t="n"/>
+      <c r="K192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -10032,17 +10442,22 @@
           <t>1080x1080 recomendado; máx. 4320x4320</t>
         </is>
       </c>
-      <c r="H193" s="3" t="inlineStr">
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I193" s="3" t="inlineStr">
         <is>
           <t>10 MB por cartão</t>
         </is>
       </c>
-      <c r="I193" s="3" t="inlineStr">
+      <c r="J193" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF não animado</t>
         </is>
       </c>
-      <c r="J193" s="3" t="n"/>
+      <c r="K193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -10080,17 +10495,22 @@
           <t>1920x1080 recomendado; 1280x720 aceite</t>
         </is>
       </c>
-      <c r="H194" s="3" t="inlineStr">
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I194" s="3" t="inlineStr">
         <is>
           <t>500 MB</t>
         </is>
       </c>
-      <c r="I194" s="3" t="inlineStr">
+      <c r="J194" s="3" t="inlineStr">
         <is>
           <t>MP4 (H.264)</t>
         </is>
       </c>
-      <c r="J194" s="3" t="n"/>
+      <c r="K194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -10128,17 +10548,22 @@
           <t>250x250 imagem; banner opcional máx. 300x250</t>
         </is>
       </c>
-      <c r="H195" s="3" t="inlineStr">
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I195" s="3" t="inlineStr">
         <is>
           <t>5 MB imagem; 2 MB banner</t>
         </is>
       </c>
-      <c r="I195" s="3" t="inlineStr">
+      <c r="J195" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J195" s="3" t="n"/>
+      <c r="K195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -10176,17 +10601,17 @@
           <t>Sem dimensão fixa; layouts standard (A4, Letter, etc.)</t>
         </is>
       </c>
-      <c r="H196" s="3" t="inlineStr">
+      <c r="I196" s="3" t="inlineStr">
         <is>
           <t>100 MB</t>
         </is>
       </c>
-      <c r="I196" s="3" t="inlineStr">
+      <c r="J196" s="3" t="inlineStr">
         <is>
           <t>PDF, PPT, PPTX, DOC, DOCX</t>
         </is>
       </c>
-      <c r="J196" s="3" t="n"/>
+      <c r="K196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -10224,17 +10649,17 @@
           <t>Usa imagem do evento LinkedIn</t>
         </is>
       </c>
-      <c r="H197" s="3" t="inlineStr">
+      <c r="I197" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I197" s="3" t="inlineStr">
+      <c r="J197" s="3" t="inlineStr">
         <is>
           <t>Evento publicado no LinkedIn</t>
         </is>
       </c>
-      <c r="J197" s="3" t="n"/>
+      <c r="K197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -10272,17 +10697,22 @@
           <t>Logo: 100x100 recomendado</t>
         </is>
       </c>
-      <c r="H198" s="3" t="inlineStr">
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
         <is>
           <t>2 MB</t>
         </is>
       </c>
-      <c r="I198" s="3" t="inlineStr">
+      <c r="J198" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J198" s="3" t="n"/>
+      <c r="K198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -10320,17 +10750,17 @@
           <t>Dinâmico; usa logo/elementos da Page e vaga</t>
         </is>
       </c>
-      <c r="H199" s="3" t="inlineStr">
+      <c r="I199" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I199" s="3" t="inlineStr">
+      <c r="J199" s="3" t="inlineStr">
         <is>
           <t>Vaga + Page LinkedIn</t>
         </is>
       </c>
-      <c r="J199" s="3" t="n"/>
+      <c r="K199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -10368,17 +10798,17 @@
           <t>Sem asset gráfico próprio; associado ao anúncio</t>
         </is>
       </c>
-      <c r="H200" s="3" t="inlineStr">
+      <c r="I200" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I200" s="3" t="inlineStr">
+      <c r="J200" s="3" t="inlineStr">
         <is>
           <t>Formulário criado no Campaign Manager</t>
         </is>
       </c>
-      <c r="J200" s="3" t="n"/>
+      <c r="K200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -10416,17 +10846,17 @@
           <t>Banner opcional 300x250</t>
         </is>
       </c>
-      <c r="H201" s="3" t="inlineStr">
+      <c r="I201" s="3" t="inlineStr">
         <is>
           <t>2 MB</t>
         </is>
       </c>
-      <c r="I201" s="3" t="inlineStr">
+      <c r="J201" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J201" s="3" t="n"/>
+      <c r="K201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -10464,17 +10894,22 @@
           <t>1200x628 (1.91:1); 1200x1200 (1:1); 720x900 (4:5)</t>
         </is>
       </c>
-      <c r="H202" s="3" t="inlineStr">
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I202" s="3" t="inlineStr">
+      <c r="J202" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="J202" s="3" t="inlineStr">
+      <c r="K202" s="3" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/single-image-ads-specs</t>
         </is>
@@ -10516,17 +10951,22 @@
           <t>1920x1080 / 720x900 / 720x1280; conforme rácio</t>
         </is>
       </c>
-      <c r="H203" s="3" t="inlineStr">
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>16:9 ou 4:5 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr">
         <is>
           <t>75 KB–500 MB</t>
         </is>
       </c>
-      <c r="I203" s="3" t="inlineStr">
+      <c r="J203" s="3" t="inlineStr">
         <is>
           <t>MP4; thumbnail JPG/PNG opcional</t>
         </is>
       </c>
-      <c r="J203" s="3" t="n"/>
+      <c r="K203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -10564,17 +11004,22 @@
           <t>Logo 100x100; background opcional 300x250</t>
         </is>
       </c>
-      <c r="H204" s="3" t="inlineStr">
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
         <is>
           <t>2 MB</t>
         </is>
       </c>
-      <c r="I204" s="3" t="inlineStr">
+      <c r="J204" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J204" s="3" t="n"/>
+      <c r="K204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -10612,17 +11057,22 @@
           <t>100x100</t>
         </is>
       </c>
-      <c r="H205" s="3" t="inlineStr">
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr">
         <is>
           <t>2 MB</t>
         </is>
       </c>
-      <c r="I205" s="3" t="inlineStr">
+      <c r="J205" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J205" s="3" t="n"/>
+      <c r="K205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -10660,17 +11110,17 @@
           <t>Depende do post original (imagem/vídeo/documento/etc.)</t>
         </is>
       </c>
-      <c r="H206" s="3" t="inlineStr">
+      <c r="I206" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I206" s="3" t="inlineStr">
+      <c r="J206" s="3" t="inlineStr">
         <is>
           <t>Post orgânico elegível de membro/Page</t>
         </is>
       </c>
-      <c r="J206" s="3" t="n"/>
+      <c r="K206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -10708,17 +11158,22 @@
           <t>1080x1080 recomendado (1:1); placement pode variar</t>
         </is>
       </c>
-      <c r="H207" s="3" t="inlineStr">
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
         <is>
           <t>Imagem 30 MB; vídeo 4 GB</t>
         </is>
       </c>
-      <c r="I207" s="3" t="inlineStr">
+      <c r="J207" s="3" t="inlineStr">
         <is>
           <t>JPG/PNG ou MP4/MOV por cartão</t>
         </is>
       </c>
-      <c r="J207" s="3" t="inlineStr">
+      <c r="K207" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -10760,17 +11215,22 @@
           <t>1080x1080 recomendado; capa pode ser imagem ou vídeo</t>
         </is>
       </c>
-      <c r="H208" s="3" t="inlineStr">
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr">
         <is>
           <t>Imagem 30 MB; vídeo 4 GB</t>
         </is>
       </c>
-      <c r="I208" s="3" t="inlineStr">
+      <c r="J208" s="3" t="inlineStr">
         <is>
           <t>JPG/PNG ou MP4/MOV + catálogo/Instant Experience</t>
         </is>
       </c>
-      <c r="J208" s="3" t="inlineStr">
+      <c r="K208" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -10812,17 +11272,22 @@
           <t>1080x1080 (1:1) ou 1080x1350 (4:5) recomendado; placement pode variar</t>
         </is>
       </c>
-      <c r="H209" s="3" t="inlineStr">
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>1:1 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr">
         <is>
           <t>30 MB</t>
         </is>
       </c>
-      <c r="I209" s="3" t="inlineStr">
+      <c r="J209" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J209" s="3" t="inlineStr">
+      <c r="K209" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -10864,17 +11329,22 @@
           <t>1080x1920 (9:16) Stories/Reels; 1080x1350 (4:5) Feed recomendado</t>
         </is>
       </c>
-      <c r="H210" s="3" t="inlineStr">
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>9:16 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr">
         <is>
           <t>4 GB</t>
         </is>
       </c>
-      <c r="I210" s="3" t="inlineStr">
+      <c r="J210" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J210" s="3" t="inlineStr">
+      <c r="K210" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -10916,17 +11386,22 @@
           <t>1080x1080 recomendado (1:1); placement pode variar</t>
         </is>
       </c>
-      <c r="H211" s="3" t="inlineStr">
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr">
         <is>
           <t>Imagem 30 MB; vídeo 4 GB</t>
         </is>
       </c>
-      <c r="I211" s="3" t="inlineStr">
+      <c r="J211" s="3" t="inlineStr">
         <is>
           <t>JPG/PNG ou MP4/MOV por cartão</t>
         </is>
       </c>
-      <c r="J211" s="3" t="inlineStr">
+      <c r="K211" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -10968,17 +11443,22 @@
           <t>1080x1080 recomendado; capa pode ser imagem ou vídeo</t>
         </is>
       </c>
-      <c r="H212" s="3" t="inlineStr">
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr">
         <is>
           <t>Imagem 30 MB; vídeo 4 GB</t>
         </is>
       </c>
-      <c r="I212" s="3" t="inlineStr">
+      <c r="J212" s="3" t="inlineStr">
         <is>
           <t>JPG/PNG ou MP4/MOV + catálogo/Instant Experience</t>
         </is>
       </c>
-      <c r="J212" s="3" t="inlineStr">
+      <c r="K212" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -11020,17 +11500,22 @@
           <t>1080x1080 (1:1) ou 1080x1350 (4:5) recomendado; placement pode variar</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr">
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>1:1 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="inlineStr">
         <is>
           <t>30 MB</t>
         </is>
       </c>
-      <c r="I213" s="3" t="inlineStr">
+      <c r="J213" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J213" s="3" t="inlineStr">
+      <c r="K213" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -11072,17 +11557,22 @@
           <t>1080x1920 (9:16) Stories/Reels; 1080x1350 (4:5) Feed recomendado</t>
         </is>
       </c>
-      <c r="H214" s="3" t="inlineStr">
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>9:16 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="inlineStr">
         <is>
           <t>4 GB</t>
         </is>
       </c>
-      <c r="I214" s="3" t="inlineStr">
+      <c r="J214" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J214" s="3" t="inlineStr">
+      <c r="K214" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -11124,17 +11614,22 @@
           <t>1080x1080 recomendado (1:1); placement pode variar</t>
         </is>
       </c>
-      <c r="H215" s="3" t="inlineStr">
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="inlineStr">
         <is>
           <t>Imagem 30 MB; vídeo 4 GB</t>
         </is>
       </c>
-      <c r="I215" s="3" t="inlineStr">
+      <c r="J215" s="3" t="inlineStr">
         <is>
           <t>JPG/PNG ou MP4/MOV por cartão</t>
         </is>
       </c>
-      <c r="J215" s="3" t="inlineStr">
+      <c r="K215" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -11176,17 +11671,22 @@
           <t>1080x1080 recomendado; capa pode ser imagem ou vídeo</t>
         </is>
       </c>
-      <c r="H216" s="3" t="inlineStr">
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr">
         <is>
           <t>Imagem 30 MB; vídeo 4 GB</t>
         </is>
       </c>
-      <c r="I216" s="3" t="inlineStr">
+      <c r="J216" s="3" t="inlineStr">
         <is>
           <t>JPG/PNG ou MP4/MOV + catálogo/Instant Experience</t>
         </is>
       </c>
-      <c r="J216" s="3" t="inlineStr">
+      <c r="K216" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -11228,17 +11728,22 @@
           <t>1080x1080 (1:1) ou 1080x1350 (4:5) recomendado; placement pode variar</t>
         </is>
       </c>
-      <c r="H217" s="3" t="inlineStr">
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>1:1 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
         <is>
           <t>30 MB</t>
         </is>
       </c>
-      <c r="I217" s="3" t="inlineStr">
+      <c r="J217" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J217" s="3" t="inlineStr">
+      <c r="K217" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -11280,17 +11785,22 @@
           <t>1080x1920 (9:16) Stories/Reels; 1080x1350 (4:5) Feed recomendado</t>
         </is>
       </c>
-      <c r="H218" s="3" t="inlineStr">
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>9:16 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr">
         <is>
           <t>4 GB</t>
         </is>
       </c>
-      <c r="I218" s="3" t="inlineStr">
+      <c r="J218" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J218" s="3" t="inlineStr">
+      <c r="K218" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide</t>
         </is>
@@ -11332,17 +11842,22 @@
           <t>1:1 ou 2:3; 1000x1000 / 1000x1500 recomendado</t>
         </is>
       </c>
-      <c r="H219" s="3" t="inlineStr">
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>1:1 ou 2:3</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
         <is>
           <t>20 MB por imagem</t>
         </is>
       </c>
-      <c r="I219" s="3" t="inlineStr">
+      <c r="J219" s="3" t="inlineStr">
         <is>
           <t>PNG, JPEG; 2–5 imagens (non-Sales)</t>
         </is>
       </c>
-      <c r="J219" s="3" t="inlineStr">
+      <c r="K219" s="3" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11384,17 +11899,17 @@
           <t>Hero 1:1 ou 2:3; assets secundários via catálogo</t>
         </is>
       </c>
-      <c r="H220" s="3" t="inlineStr">
+      <c r="I220" s="3" t="inlineStr">
         <is>
           <t>Imagem 20 MB; vídeo até 2 GB</t>
         </is>
       </c>
-      <c r="I220" s="3" t="inlineStr">
+      <c r="J220" s="3" t="inlineStr">
         <is>
           <t>PNG, JPEG, MP4/MOV/M4V + catálogo</t>
         </is>
       </c>
-      <c r="J220" s="3" t="inlineStr">
+      <c r="K220" s="3" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11436,17 +11951,22 @@
           <t>1000x1500 recomendado (2:3)</t>
         </is>
       </c>
-      <c r="H221" s="3" t="inlineStr">
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
         <is>
           <t>20 MB</t>
         </is>
       </c>
-      <c r="I221" s="3" t="inlineStr">
+      <c r="J221" s="3" t="inlineStr">
         <is>
           <t>PNG, JPEG</t>
         </is>
       </c>
-      <c r="J221" s="3" t="inlineStr">
+      <c r="K221" s="3" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11488,17 +12008,22 @@
           <t>1000x1500 (2:3), 1080x1920 (9:16) ou square conforme placement</t>
         </is>
       </c>
-      <c r="H222" s="3" t="inlineStr">
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2:3 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr">
         <is>
           <t>2 GB</t>
         </is>
       </c>
-      <c r="I222" s="3" t="inlineStr">
+      <c r="J222" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV, M4V</t>
         </is>
       </c>
-      <c r="J222" s="3" t="inlineStr">
+      <c r="K222" s="3" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11540,17 +12065,22 @@
           <t>2–6 cartões; 1080x1080 recomendado</t>
         </is>
       </c>
-      <c r="H223" s="3" t="inlineStr">
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
         <is>
           <t>20 MB por imagem; GIF 3 MB</t>
         </is>
       </c>
-      <c r="I223" s="3" t="inlineStr">
+      <c r="J223" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="J223" s="3" t="inlineStr">
+      <c r="K223" s="3" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types/carousel-ads</t>
         </is>
@@ -11592,17 +12122,22 @@
           <t>Imagem: 1200x1200 (1:1) ou 1920x1080/1440x1080; vídeo conforme asset</t>
         </is>
       </c>
-      <c r="H224" s="3" t="inlineStr">
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="inlineStr">
         <is>
           <t>Imagem ≤20 MB; vídeo ≤1 GB</t>
         </is>
       </c>
-      <c r="I224" s="3" t="inlineStr">
+      <c r="J224" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF, MP4, MOV + rich text</t>
         </is>
       </c>
-      <c r="J224" s="3" t="inlineStr">
+      <c r="K224" s="3" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types/free-form</t>
         </is>
@@ -11644,17 +12179,22 @@
           <t>1080x1080 (1:1); 1080x1350 (4:5); 1440x1080 (4:3); 1920x1080 (16:9)</t>
         </is>
       </c>
-      <c r="H225" s="3" t="inlineStr">
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>1:1 ou 4:5 ou 4:3 ou 16:9</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
         <is>
           <t>3 MB</t>
         </is>
       </c>
-      <c r="I225" s="3" t="inlineStr">
+      <c r="J225" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF (estático)</t>
         </is>
       </c>
-      <c r="J225" s="3" t="inlineStr">
+      <c r="K225" s="3" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/learning-hub/articles/reddit-image-ad-specs</t>
         </is>
@@ -11696,17 +12236,17 @@
           <t>Depende do asset do catálogo/underlying ad type</t>
         </is>
       </c>
-      <c r="H226" s="3" t="inlineStr">
+      <c r="I226" s="3" t="inlineStr">
         <is>
           <t>Depende do asset</t>
         </is>
       </c>
-      <c r="I226" s="3" t="inlineStr">
+      <c r="J226" s="3" t="inlineStr">
         <is>
           <t>Catálogo de produtos + JPG/PNG ou vídeo conforme configuração</t>
         </is>
       </c>
-      <c r="J226" s="3" t="inlineStr">
+      <c r="K226" s="3" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types</t>
         </is>
@@ -11748,17 +12288,17 @@
           <t>1:1 / 4:5 / 16:9; 1080p recomendado</t>
         </is>
       </c>
-      <c r="H227" s="3" t="inlineStr">
+      <c r="I227" s="3" t="inlineStr">
         <is>
           <t>1 GB</t>
         </is>
       </c>
-      <c r="I227" s="3" t="inlineStr">
+      <c r="J227" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J227" s="3" t="inlineStr">
+      <c r="K227" s="3" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types/video-ads</t>
         </is>
@@ -11800,17 +12340,17 @@
           <t>Filter estático 945x2048; animado 720x1560</t>
         </is>
       </c>
-      <c r="H228" s="3" t="inlineStr">
+      <c r="I228" s="3" t="inlineStr">
         <is>
           <t>Varia por asset AR</t>
         </is>
       </c>
-      <c r="I228" s="3" t="inlineStr">
+      <c r="J228" s="3" t="inlineStr">
         <is>
           <t>PNG (filtro estático), GIF (animado); Lens assets conforme Lens Studio</t>
         </is>
       </c>
-      <c r="J228" s="3" t="inlineStr">
+      <c r="K228" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11852,17 +12392,22 @@
           <t>720x1280 (9:16) por asset recomendado</t>
         </is>
       </c>
-      <c r="H229" s="3" t="inlineStr">
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I229" s="3" t="inlineStr">
         <is>
           <t>Varia por asset</t>
         </is>
       </c>
-      <c r="I229" s="3" t="inlineStr">
+      <c r="J229" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
-      <c r="J229" s="3" t="inlineStr">
+      <c r="K229" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11904,17 +12449,22 @@
           <t>720x1280 (9:16)</t>
         </is>
       </c>
-      <c r="H230" s="3" t="inlineStr">
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I230" s="3" t="inlineStr">
         <is>
           <t>Varia por asset</t>
         </is>
       </c>
-      <c r="I230" s="3" t="inlineStr">
+      <c r="J230" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
         </is>
       </c>
-      <c r="J230" s="3" t="inlineStr">
+      <c r="K230" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11956,17 +12506,22 @@
           <t>720x1280 (9:16)</t>
         </is>
       </c>
-      <c r="H231" s="3" t="inlineStr">
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I231" s="3" t="inlineStr">
         <is>
           <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
-      <c r="I231" s="3" t="inlineStr">
+      <c r="J231" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV (H.264)</t>
         </is>
       </c>
-      <c r="J231" s="3" t="inlineStr">
+      <c r="K231" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -12008,17 +12563,22 @@
           <t>720x1280 (9:16)</t>
         </is>
       </c>
-      <c r="H232" s="3" t="inlineStr">
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I232" s="3" t="inlineStr">
         <is>
           <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
-      <c r="I232" s="3" t="inlineStr">
+      <c r="J232" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J232" s="3" t="inlineStr">
+      <c r="K232" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -12060,17 +12620,22 @@
           <t>720x1280 (9:16)</t>
         </is>
       </c>
-      <c r="H233" s="3" t="inlineStr">
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I233" s="3" t="inlineStr">
         <is>
           <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
-      <c r="I233" s="3" t="inlineStr">
+      <c r="J233" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J233" s="3" t="inlineStr">
+      <c r="K233" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -12112,17 +12677,22 @@
           <t>720x1280 (9:16)</t>
         </is>
       </c>
-      <c r="H234" s="3" t="inlineStr">
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I234" s="3" t="inlineStr">
         <is>
           <t>Varia por asset</t>
         </is>
       </c>
-      <c r="I234" s="3" t="inlineStr">
+      <c r="J234" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
-      <c r="J234" s="3" t="inlineStr">
+      <c r="K234" s="3" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -12164,17 +12734,22 @@
           <t>Ícone 162x162 (safe 144x144); restantes assets conforme template</t>
         </is>
       </c>
-      <c r="H235" s="3" t="inlineStr">
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I235" s="3" t="inlineStr">
         <is>
           <t>Ícone &lt;60 KB; restantes conforme template</t>
         </is>
       </c>
-      <c r="I235" s="3" t="inlineStr">
+      <c r="J235" s="3" t="inlineStr">
         <is>
           <t>PNG + assets de efeito conforme template</t>
         </is>
       </c>
-      <c r="J235" s="3" t="inlineStr">
+      <c r="K235" s="3" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
         </is>
@@ -12216,17 +12791,17 @@
           <t>Criativo final segue In-Feed/Spark Ads (vertical 9:16 recomendado)</t>
         </is>
       </c>
-      <c r="H236" s="3" t="inlineStr">
+      <c r="I236" s="3" t="inlineStr">
         <is>
           <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
-      <c r="I236" s="3" t="inlineStr">
+      <c r="J236" s="3" t="inlineStr">
         <is>
           <t>Vídeo de creator elegível / Spark Ads</t>
         </is>
       </c>
-      <c r="J236" s="3" t="inlineStr">
+      <c r="K236" s="3" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
         </is>
@@ -12268,17 +12843,22 @@
           <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
         </is>
       </c>
-      <c r="H237" s="3" t="inlineStr">
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I237" s="3" t="inlineStr">
         <is>
           <t>100 KB sugerido por imagem; música até 10 MB</t>
         </is>
       </c>
-      <c r="I237" s="3" t="inlineStr">
+      <c r="J237" s="3" t="inlineStr">
         <is>
           <t>JPG/JPEG, PNG + MP3</t>
         </is>
       </c>
-      <c r="J237" s="3" t="inlineStr">
+      <c r="K237" s="3" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
         </is>
@@ -12320,17 +12900,22 @@
           <t>Vertical 9:16 recomendado; ≥540x960 recomendado</t>
         </is>
       </c>
-      <c r="H238" s="3" t="inlineStr">
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I238" s="3" t="inlineStr">
         <is>
           <t>Até 500 MB (reservation); limites podem variar em auction</t>
         </is>
       </c>
-      <c r="I238" s="3" t="inlineStr">
+      <c r="J238" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
-      <c r="J238" s="3" t="inlineStr">
+      <c r="K238" s="3" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12372,17 +12957,17 @@
           <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
         </is>
       </c>
-      <c r="H239" s="3" t="inlineStr">
+      <c r="I239" s="3" t="inlineStr">
         <is>
           <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
-      <c r="I239" s="3" t="inlineStr">
+      <c r="J239" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
-      <c r="J239" s="3" t="inlineStr">
+      <c r="K239" s="3" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
         </is>
@@ -12424,17 +13009,22 @@
           <t>Usa vídeo orgânico; para push, 9:16 ≥540x960 recomendado</t>
         </is>
       </c>
-      <c r="H240" s="3" t="inlineStr">
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I240" s="3" t="inlineStr">
         <is>
           <t>Até 500 MB para push</t>
         </is>
       </c>
-      <c r="I240" s="3" t="inlineStr">
+      <c r="J240" s="3" t="inlineStr">
         <is>
           <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
         </is>
       </c>
-      <c r="J240" s="3" t="inlineStr">
+      <c r="K240" s="3" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12476,17 +13066,17 @@
           <t>Segue criativo In-Feed; vertical 9:16 recomendado</t>
         </is>
       </c>
-      <c r="H241" s="3" t="inlineStr">
+      <c r="I241" s="3" t="inlineStr">
         <is>
           <t>Conforme In-Feed</t>
         </is>
       </c>
-      <c r="I241" s="3" t="inlineStr">
+      <c r="J241" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
-      <c r="J241" s="3" t="inlineStr">
+      <c r="K241" s="3" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
@@ -12528,17 +13118,22 @@
           <t>9:16; ≥540x960</t>
         </is>
       </c>
-      <c r="H242" s="3" t="inlineStr">
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I242" s="3" t="inlineStr">
         <is>
           <t>500 MB</t>
         </is>
       </c>
-      <c r="I242" s="3" t="inlineStr">
+      <c r="J242" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
-      <c r="J242" s="3" t="inlineStr">
+      <c r="K242" s="3" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12580,17 +13175,17 @@
           <t>16:9 recomendado; vídeo HD</t>
         </is>
       </c>
-      <c r="H243" s="3" t="inlineStr">
+      <c r="I243" s="3" t="inlineStr">
         <is>
           <t>1 GB recomendado/limite conforme placement</t>
         </is>
       </c>
-      <c r="I243" s="3" t="inlineStr">
+      <c r="J243" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J243" s="3" t="inlineStr">
+      <c r="K243" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12632,17 +13227,22 @@
           <t>800x800 (1:1) ou 800x418 (1.91:1) recomendado</t>
         </is>
       </c>
-      <c r="H244" s="3" t="inlineStr">
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I244" s="3" t="inlineStr">
         <is>
           <t>5 MB por imagem; vídeo conforme specs</t>
         </is>
       </c>
-      <c r="I244" s="3" t="inlineStr">
+      <c r="J244" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG; MP4/MOV para video carousel</t>
         </is>
       </c>
-      <c r="J244" s="3" t="inlineStr">
+      <c r="K244" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12684,17 +13284,22 @@
           <t>Hero 800x800 (1:1) recomendado + thumbnails de produtos</t>
         </is>
       </c>
-      <c r="H245" s="3" t="inlineStr">
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I245" s="3" t="inlineStr">
         <is>
           <t>5 MB por imagem</t>
         </is>
       </c>
-      <c r="I245" s="3" t="inlineStr">
+      <c r="J245" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG + catálogo</t>
         </is>
       </c>
-      <c r="J245" s="3" t="inlineStr">
+      <c r="K245" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12736,17 +13341,17 @@
           <t>Assets provenientes do catálogo; 1:1 recomendado</t>
         </is>
       </c>
-      <c r="H246" s="3" t="inlineStr">
+      <c r="I246" s="3" t="inlineStr">
         <is>
           <t>Conforme catálogo</t>
         </is>
       </c>
-      <c r="I246" s="3" t="inlineStr">
+      <c r="J246" s="3" t="inlineStr">
         <is>
           <t>Feed/catálogo + JPG/PNG</t>
         </is>
       </c>
-      <c r="J246" s="3" t="inlineStr">
+      <c r="K246" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12788,17 +13393,22 @@
           <t>1200x1200 (1:1) ou 1200x628 (1.91:1) recomendado</t>
         </is>
       </c>
-      <c r="H247" s="3" t="inlineStr">
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I247" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I247" s="3" t="inlineStr">
+      <c r="J247" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J247" s="3" t="inlineStr">
+      <c r="K247" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12840,17 +13450,17 @@
           <t>Depende do produto (Timeline/Trend Takeover); assets conforme ficha X</t>
         </is>
       </c>
-      <c r="H248" s="3" t="inlineStr">
+      <c r="I248" s="3" t="inlineStr">
         <is>
           <t>Conforme formato</t>
         </is>
       </c>
-      <c r="I248" s="3" t="inlineStr">
+      <c r="J248" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, MP4/MOV conforme takeover</t>
         </is>
       </c>
-      <c r="J248" s="3" t="inlineStr">
+      <c r="K248" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12892,17 +13502,17 @@
           <t>Sem asset gráfico obrigatório</t>
         </is>
       </c>
-      <c r="H249" s="3" t="inlineStr">
+      <c r="I249" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I249" s="3" t="inlineStr">
+      <c r="J249" s="3" t="inlineStr">
         <is>
           <t>Texto/post + URL opcional</t>
         </is>
       </c>
-      <c r="J249" s="3" t="inlineStr">
+      <c r="K249" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12944,17 +13554,22 @@
           <t>1200x1200 (1:1) ou 1920x1080 (16:9) recomendado</t>
         </is>
       </c>
-      <c r="H250" s="3" t="inlineStr">
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>1:1 ou 16:9</t>
+        </is>
+      </c>
+      <c r="I250" s="3" t="inlineStr">
         <is>
           <t>1 GB</t>
         </is>
       </c>
-      <c r="I250" s="3" t="inlineStr">
+      <c r="J250" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J250" s="3" t="inlineStr">
+      <c r="K250" s="3" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12996,17 +13611,17 @@
           <t>300x250</t>
         </is>
       </c>
-      <c r="H251" s="3" t="inlineStr">
+      <c r="I251" s="3" t="inlineStr">
         <is>
           <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
         </is>
       </c>
-      <c r="I251" s="3" t="inlineStr">
+      <c r="J251" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="J251" s="3" t="inlineStr">
+      <c r="K251" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13048,17 +13663,17 @@
           <t>336x280</t>
         </is>
       </c>
-      <c r="H252" s="3" t="inlineStr">
+      <c r="I252" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I252" s="3" t="inlineStr">
+      <c r="J252" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="J252" s="3" t="inlineStr">
+      <c r="K252" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13100,17 +13715,17 @@
           <t>728x90</t>
         </is>
       </c>
-      <c r="H253" s="3" t="inlineStr">
+      <c r="I253" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I253" s="3" t="inlineStr">
+      <c r="J253" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="J253" s="3" t="inlineStr">
+      <c r="K253" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13152,17 +13767,22 @@
           <t>300x600</t>
         </is>
       </c>
-      <c r="H254" s="3" t="inlineStr">
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I254" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I254" s="3" t="inlineStr">
+      <c r="J254" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="J254" s="3" t="inlineStr">
+      <c r="K254" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13204,17 +13824,17 @@
           <t>320x50</t>
         </is>
       </c>
-      <c r="H255" s="3" t="inlineStr">
+      <c r="I255" s="3" t="inlineStr">
         <is>
           <t>150 KB</t>
         </is>
       </c>
-      <c r="I255" s="3" t="inlineStr">
+      <c r="J255" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="J255" s="3" t="inlineStr">
+      <c r="K255" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13256,17 +13876,22 @@
           <t>Landscape 1200x628 (1.91:1, mín. 600x314); Square 1200x1200 (1:1, mín. 300x300); Portrait 1200x1500 (4:5, opcional)</t>
         </is>
       </c>
-      <c r="H256" s="3" t="inlineStr">
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I256" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I256" s="3" t="inlineStr">
+      <c r="J256" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
-      <c r="J256" s="3" t="inlineStr">
+      <c r="K256" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13308,17 +13933,22 @@
           <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
         </is>
       </c>
-      <c r="H257" s="3" t="inlineStr">
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="I257" s="3" t="inlineStr">
         <is>
           <t>150 KB (dentro do HTML5)</t>
         </is>
       </c>
-      <c r="I257" s="3" t="inlineStr">
+      <c r="J257" s="3" t="inlineStr">
         <is>
           <t>ZIP HTML5</t>
         </is>
       </c>
-      <c r="J257" s="3" t="inlineStr">
+      <c r="K257" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13360,17 +13990,22 @@
           <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
-      <c r="H258" s="3" t="inlineStr">
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
-      <c r="I258" s="3" t="inlineStr">
+      <c r="J258" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="J258" s="3" t="inlineStr">
+      <c r="K258" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13412,17 +14047,22 @@
           <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
         </is>
       </c>
-      <c r="H259" s="3" t="inlineStr">
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I259" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="I259" s="3" t="inlineStr">
+      <c r="J259" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J259" s="3" t="inlineStr">
+      <c r="K259" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13464,17 +14104,22 @@
           <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
         </is>
       </c>
-      <c r="H260" s="3" t="inlineStr">
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="I260" s="3" t="inlineStr">
+      <c r="J260" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J260" s="3" t="inlineStr">
+      <c r="K260" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13516,17 +14161,17 @@
           <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
-      <c r="H261" s="3" t="inlineStr">
+      <c r="I261" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="I261" s="3" t="inlineStr">
+      <c r="J261" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J261" s="3" t="inlineStr">
+      <c r="K261" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13568,17 +14213,17 @@
           <t>Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original</t>
         </is>
       </c>
-      <c r="H262" s="3" t="inlineStr">
+      <c r="I262" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="I262" s="3" t="inlineStr">
+      <c r="J262" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J262" s="3" t="inlineStr">
+      <c r="K262" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13620,17 +14265,17 @@
           <t>9:16 vertical</t>
         </is>
       </c>
-      <c r="H263" s="3" t="inlineStr">
+      <c r="I263" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="I263" s="3" t="inlineStr">
+      <c r="J263" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J263" s="3" t="inlineStr">
+      <c r="K263" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13672,17 +14317,22 @@
           <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
-      <c r="H264" s="3" t="inlineStr">
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I264" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="I264" s="3" t="inlineStr">
+      <c r="J264" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J264" s="3" t="inlineStr">
+      <c r="K264" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13724,17 +14374,22 @@
           <t>Landscape 1200x628 (1.91:1); Square 1200x1200 (1:1); Portrait 1200x1500 (4:5, opcional) — enviar pelo menos landscape + square</t>
         </is>
       </c>
-      <c r="H265" s="3" t="inlineStr">
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I265" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I265" s="3" t="inlineStr">
+      <c r="J265" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
-      <c r="J265" s="3" t="inlineStr">
+      <c r="K265" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -13776,17 +14431,17 @@
           <t>16:9, 1:1 ou 9:16; duração mínima 10s (in-feed) ou 6s (estilo bumper)</t>
         </is>
       </c>
-      <c r="H266" s="3" t="inlineStr">
+      <c r="I266" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="I266" s="3" t="inlineStr">
+      <c r="J266" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J266" s="3" t="inlineStr">
+      <c r="K266" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -13828,17 +14483,17 @@
           <t>2 a 10 cartões, todos com a mesma proporção (1:1 ou 1.91:1); cada cartão com título até 40 caracteres</t>
         </is>
       </c>
-      <c r="H267" s="3" t="inlineStr">
+      <c r="I267" s="3" t="inlineStr">
         <is>
           <t>5 MB por imagem</t>
         </is>
       </c>
-      <c r="I267" s="3" t="inlineStr">
+      <c r="J267" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J267" s="3" t="inlineStr">
+      <c r="K267" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -13880,17 +14535,17 @@
           <t>Várias proporções (paisagem, quadrado, retrato) conforme o placement</t>
         </is>
       </c>
-      <c r="H268" s="3" t="inlineStr">
+      <c r="I268" s="3" t="inlineStr">
         <is>
           <t>5 MB</t>
         </is>
       </c>
-      <c r="I268" s="3" t="inlineStr">
+      <c r="J268" s="3" t="inlineStr">
         <is>
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="J268" s="3" t="inlineStr">
+      <c r="K268" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
@@ -13932,17 +14587,17 @@
           <t>Várias proporções conforme o placement; obrigatório estar alojado no YouTube</t>
         </is>
       </c>
-      <c r="H269" s="3" t="inlineStr">
+      <c r="I269" s="3" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="I269" s="3" t="inlineStr">
+      <c r="J269" s="3" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="J269" s="3" t="inlineStr">
+      <c r="K269" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
@@ -13984,17 +14639,17 @@
           <t>Pacote HTML5, até 512 ficheiros dentro do ZIP</t>
         </is>
       </c>
-      <c r="H270" s="3" t="inlineStr">
+      <c r="I270" s="3" t="inlineStr">
         <is>
           <t>5 MB (ZIP)</t>
         </is>
       </c>
-      <c r="I270" s="3" t="inlineStr">
+      <c r="J270" s="3" t="inlineStr">
         <is>
           <t>ZIP HTML5</t>
         </is>
       </c>
-      <c r="J270" s="3" t="inlineStr">
+      <c r="K270" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/9948381</t>
         </is>
@@ -14028,9 +14683,9 @@
         </is>
       </c>
       <c r="G271" s="3" t="n"/>
-      <c r="H271" s="3" t="n"/>
       <c r="I271" s="3" t="n"/>
       <c r="J271" s="3" t="n"/>
+      <c r="K271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -14060,9 +14715,9 @@
         </is>
       </c>
       <c r="G272" s="3" t="n"/>
-      <c r="H272" s="3" t="n"/>
       <c r="I272" s="3" t="n"/>
       <c r="J272" s="3" t="n"/>
+      <c r="K272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -14092,9 +14747,9 @@
         </is>
       </c>
       <c r="G273" s="3" t="n"/>
-      <c r="H273" s="3" t="n"/>
       <c r="I273" s="3" t="n"/>
       <c r="J273" s="3" t="n"/>
+      <c r="K273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
@@ -14124,9 +14779,9 @@
         </is>
       </c>
       <c r="G274" s="3" t="n"/>
-      <c r="H274" s="3" t="n"/>
       <c r="I274" s="3" t="n"/>
       <c r="J274" s="3" t="n"/>
+      <c r="K274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -14156,9 +14811,9 @@
         </is>
       </c>
       <c r="G275" s="3" t="n"/>
-      <c r="H275" s="3" t="n"/>
       <c r="I275" s="3" t="n"/>
       <c r="J275" s="3" t="n"/>
+      <c r="K275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -14188,9 +14843,9 @@
         </is>
       </c>
       <c r="G276" s="3" t="n"/>
-      <c r="H276" s="3" t="n"/>
       <c r="I276" s="3" t="n"/>
       <c r="J276" s="3" t="n"/>
+      <c r="K276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -14220,9 +14875,9 @@
         </is>
       </c>
       <c r="G277" s="3" t="n"/>
-      <c r="H277" s="3" t="n"/>
       <c r="I277" s="3" t="n"/>
       <c r="J277" s="3" t="n"/>
+      <c r="K277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -14252,9 +14907,9 @@
         </is>
       </c>
       <c r="G278" s="3" t="n"/>
-      <c r="H278" s="3" t="n"/>
       <c r="I278" s="3" t="n"/>
       <c r="J278" s="3" t="n"/>
+      <c r="K278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -14284,9 +14939,9 @@
         </is>
       </c>
       <c r="G279" s="3" t="n"/>
-      <c r="H279" s="3" t="n"/>
       <c r="I279" s="3" t="n"/>
       <c r="J279" s="3" t="n"/>
+      <c r="K279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
@@ -14316,9 +14971,9 @@
         </is>
       </c>
       <c r="G280" s="3" t="n"/>
-      <c r="H280" s="3" t="n"/>
       <c r="I280" s="3" t="n"/>
       <c r="J280" s="3" t="n"/>
+      <c r="K280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -14348,9 +15003,9 @@
         </is>
       </c>
       <c r="G281" s="3" t="n"/>
-      <c r="H281" s="3" t="n"/>
       <c r="I281" s="3" t="n"/>
       <c r="J281" s="3" t="n"/>
+      <c r="K281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -14380,9 +15035,9 @@
         </is>
       </c>
       <c r="G282" s="3" t="n"/>
-      <c r="H282" s="3" t="n"/>
       <c r="I282" s="3" t="n"/>
       <c r="J282" s="3" t="n"/>
+      <c r="K282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -14412,9 +15067,9 @@
         </is>
       </c>
       <c r="G283" s="3" t="n"/>
-      <c r="H283" s="3" t="n"/>
       <c r="I283" s="3" t="n"/>
       <c r="J283" s="3" t="n"/>
+      <c r="K283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -14444,9 +15099,9 @@
         </is>
       </c>
       <c r="G284" s="3" t="n"/>
-      <c r="H284" s="3" t="n"/>
       <c r="I284" s="3" t="n"/>
       <c r="J284" s="3" t="n"/>
+      <c r="K284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -14476,9 +15131,9 @@
         </is>
       </c>
       <c r="G285" s="3" t="n"/>
-      <c r="H285" s="3" t="n"/>
       <c r="I285" s="3" t="n"/>
       <c r="J285" s="3" t="n"/>
+      <c r="K285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -14508,9 +15163,9 @@
         </is>
       </c>
       <c r="G286" s="3" t="n"/>
-      <c r="H286" s="3" t="n"/>
       <c r="I286" s="3" t="n"/>
       <c r="J286" s="3" t="n"/>
+      <c r="K286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
@@ -14540,9 +15195,9 @@
         </is>
       </c>
       <c r="G287" s="3" t="n"/>
-      <c r="H287" s="3" t="n"/>
       <c r="I287" s="3" t="n"/>
       <c r="J287" s="3" t="n"/>
+      <c r="K287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
@@ -14572,9 +15227,9 @@
         </is>
       </c>
       <c r="G288" s="3" t="n"/>
-      <c r="H288" s="3" t="n"/>
       <c r="I288" s="3" t="n"/>
       <c r="J288" s="3" t="n"/>
+      <c r="K288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -14604,9 +15259,9 @@
         </is>
       </c>
       <c r="G289" s="3" t="n"/>
-      <c r="H289" s="3" t="n"/>
       <c r="I289" s="3" t="n"/>
       <c r="J289" s="3" t="n"/>
+      <c r="K289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
@@ -14636,9 +15291,9 @@
         </is>
       </c>
       <c r="G290" s="3" t="n"/>
-      <c r="H290" s="3" t="n"/>
       <c r="I290" s="3" t="n"/>
       <c r="J290" s="3" t="n"/>
+      <c r="K290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -14672,17 +15327,22 @@
           <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
         </is>
       </c>
-      <c r="H291" s="3" t="inlineStr">
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I291" s="3" t="inlineStr">
         <is>
           <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
         </is>
       </c>
-      <c r="I291" s="3" t="inlineStr">
+      <c r="J291" s="3" t="inlineStr">
         <is>
           <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
         </is>
       </c>
-      <c r="J291" s="3" t="inlineStr">
+      <c r="K291" s="3" t="inlineStr">
         <is>
           <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
         </is>
@@ -14716,9 +15376,9 @@
         </is>
       </c>
       <c r="G292" s="3" t="n"/>
-      <c r="H292" s="3" t="n"/>
       <c r="I292" s="3" t="n"/>
       <c r="J292" s="3" t="n"/>
+      <c r="K292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -14748,9 +15408,9 @@
         </is>
       </c>
       <c r="G293" s="3" t="n"/>
-      <c r="H293" s="3" t="n"/>
       <c r="I293" s="3" t="n"/>
       <c r="J293" s="3" t="n"/>
+      <c r="K293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
@@ -14780,9 +15440,9 @@
         </is>
       </c>
       <c r="G294" s="3" t="n"/>
-      <c r="H294" s="3" t="n"/>
       <c r="I294" s="3" t="n"/>
       <c r="J294" s="3" t="n"/>
+      <c r="K294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -14812,9 +15472,9 @@
         </is>
       </c>
       <c r="G295" s="3" t="n"/>
-      <c r="H295" s="3" t="n"/>
       <c r="I295" s="3" t="n"/>
       <c r="J295" s="3" t="n"/>
+      <c r="K295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
@@ -14844,9 +15504,9 @@
         </is>
       </c>
       <c r="G296" s="3" t="n"/>
-      <c r="H296" s="3" t="n"/>
       <c r="I296" s="3" t="n"/>
       <c r="J296" s="3" t="n"/>
+      <c r="K296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -14876,9 +15536,9 @@
         </is>
       </c>
       <c r="G297" s="3" t="n"/>
-      <c r="H297" s="3" t="n"/>
       <c r="I297" s="3" t="n"/>
       <c r="J297" s="3" t="n"/>
+      <c r="K297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -14908,9 +15568,9 @@
         </is>
       </c>
       <c r="G298" s="3" t="n"/>
-      <c r="H298" s="3" t="n"/>
       <c r="I298" s="3" t="n"/>
       <c r="J298" s="3" t="n"/>
+      <c r="K298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -14940,9 +15600,9 @@
         </is>
       </c>
       <c r="G299" s="3" t="n"/>
-      <c r="H299" s="3" t="n"/>
       <c r="I299" s="3" t="n"/>
       <c r="J299" s="3" t="n"/>
+      <c r="K299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -14972,9 +15632,9 @@
         </is>
       </c>
       <c r="G300" s="3" t="n"/>
-      <c r="H300" s="3" t="n"/>
       <c r="I300" s="3" t="n"/>
       <c r="J300" s="3" t="n"/>
+      <c r="K300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -15004,9 +15664,9 @@
         </is>
       </c>
       <c r="G301" s="3" t="n"/>
-      <c r="H301" s="3" t="n"/>
       <c r="I301" s="3" t="n"/>
       <c r="J301" s="3" t="n"/>
+      <c r="K301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
@@ -15036,9 +15696,9 @@
         </is>
       </c>
       <c r="G302" s="3" t="n"/>
-      <c r="H302" s="3" t="n"/>
       <c r="I302" s="3" t="n"/>
       <c r="J302" s="3" t="n"/>
+      <c r="K302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -15068,9 +15728,9 @@
         </is>
       </c>
       <c r="G303" s="3" t="n"/>
-      <c r="H303" s="3" t="n"/>
       <c r="I303" s="3" t="n"/>
       <c r="J303" s="3" t="n"/>
+      <c r="K303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
@@ -15100,9 +15760,9 @@
         </is>
       </c>
       <c r="G304" s="3" t="n"/>
-      <c r="H304" s="3" t="n"/>
       <c r="I304" s="3" t="n"/>
       <c r="J304" s="3" t="n"/>
+      <c r="K304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -15136,17 +15796,22 @@
           <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
         </is>
       </c>
-      <c r="H305" s="3" t="inlineStr">
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>1:1 ou 3:4</t>
+        </is>
+      </c>
+      <c r="I305" s="3" t="inlineStr">
         <is>
           <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
         </is>
       </c>
-      <c r="I305" s="3" t="inlineStr">
+      <c r="J305" s="3" t="inlineStr">
         <is>
           <t>Display: imagens. Video: MP4.</t>
         </is>
       </c>
-      <c r="J305" s="3" t="n"/>
+      <c r="K305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
@@ -15176,9 +15841,9 @@
         </is>
       </c>
       <c r="G306" s="3" t="n"/>
-      <c r="H306" s="3" t="n"/>
       <c r="I306" s="3" t="n"/>
       <c r="J306" s="3" t="n"/>
+      <c r="K306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -15208,9 +15873,9 @@
         </is>
       </c>
       <c r="G307" s="3" t="n"/>
-      <c r="H307" s="3" t="n"/>
       <c r="I307" s="3" t="n"/>
       <c r="J307" s="3" t="n"/>
+      <c r="K307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -15240,9 +15905,9 @@
         </is>
       </c>
       <c r="G308" s="3" t="n"/>
-      <c r="H308" s="3" t="n"/>
       <c r="I308" s="3" t="n"/>
       <c r="J308" s="3" t="n"/>
+      <c r="K308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
@@ -15272,9 +15937,9 @@
         </is>
       </c>
       <c r="G309" s="3" t="n"/>
-      <c r="H309" s="3" t="n"/>
       <c r="I309" s="3" t="n"/>
       <c r="J309" s="3" t="n"/>
+      <c r="K309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -15304,9 +15969,9 @@
         </is>
       </c>
       <c r="G310" s="3" t="n"/>
-      <c r="H310" s="3" t="n"/>
       <c r="I310" s="3" t="n"/>
       <c r="J310" s="3" t="n"/>
+      <c r="K310" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K345"/>
+  <dimension ref="A1:K351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -14905,9 +14905,39 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Open Door</t>
+        </is>
+      </c>
       <c r="F283" t="inlineStr">
         <is>
           <t>Prog - YouTube Masthead</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -15070,9 +15100,39 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
       <c r="F288" t="inlineStr">
         <is>
           <t>Prog - YouTube Select</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -15097,9 +15157,39 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
       <c r="F289" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Ad Sequence</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -15178,9 +15268,39 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
       <c r="F292" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Non-Skippable</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -15306,9 +15426,39 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
       <c r="F296" t="inlineStr">
         <is>
           <t>Prog - YouTube VVC</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -15333,9 +15483,39 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
       <c r="F297" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Efficient Reach</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -15360,9 +15540,39 @@
           <t>YouTube</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
       <c r="F298" t="inlineStr">
         <is>
           <t>Prog - YouTube VRC Target Frequency</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -17842,6 +18052,338 @@
       <c r="F345" t="inlineStr">
         <is>
           <t>Prog - CTV First Screen (Sapo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Skippable In-Stream</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Non-skippable In-Stream (standard)</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Bumper</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>In-Feed Video</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>In-Feed Video Ad (ex-Discovery)</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Vertical Video</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>YouTube Shorts Ads</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>9:16 vertical</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Open Door</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Masthead</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -15280,17 +15280,13 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>Mistura de formatos: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -15495,17 +15491,13 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>Mistura de formatos (o Google escolhe consoante o inventário disponível): BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -15552,17 +15544,13 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
+          <t>Mistura de formatos: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; NON-SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -15280,10 +15280,9 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Mistura de formatos: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr"/>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+        </is>
+      </c>
       <c r="I292" t="inlineStr">
         <is>
           <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
@@ -15491,10 +15490,9 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Mistura de formatos (o Google escolhe consoante o inventário disponível): BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr"/>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+        </is>
+      </c>
       <c r="I297" t="inlineStr">
         <is>
           <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
@@ -15544,10 +15542,9 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Mistura de formatos: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; NON-SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr"/>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; NON-SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+        </is>
+      </c>
       <c r="I298" t="inlineStr">
         <is>
           <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
@@ -18071,7 +18068,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Skippable In-Stream</t>
+          <t>Skippable in-stream ads</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -18128,7 +18125,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Non-skippable In-Stream (standard)</t>
+          <t>Non-skippable in-stream ads</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -18185,7 +18182,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Bumper</t>
+          <t>Bumper ads</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -18242,7 +18239,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>In-Feed Video Ad (ex-Discovery)</t>
+          <t>In-feed ads</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -18294,7 +18291,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>YouTube Shorts Ads</t>
+          <t>Shorts ads</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -18346,7 +18343,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Masthead</t>
+          <t>Masthead ads</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K351"/>
+  <dimension ref="A1:K343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11253,32 +11253,32 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>1080x1080 recomendado (1:1); placement pode variar</t>
+          <t>1:1 ou 2:3; 1000x1000 / 1000x1500 recomendado</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1 ou 2:3</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Imagem 30 MB; vídeo 4 GB</t>
+          <t>20 MB por imagem</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>JPG/PNG ou MP4/MOV por cartão</t>
+          <t>PNG, JPEG; 2–5 imagens (non-Sales)</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -11295,12 +11295,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11315,27 +11315,22 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>1080x1080 recomendado; capa pode ser imagem ou vídeo</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>Hero 1:1 ou 2:3; assets secundários via catálogo</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Imagem 30 MB; vídeo 4 GB</t>
+          <t>Imagem 20 MB; vídeo até 2 GB</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>JPG/PNG ou MP4/MOV + catálogo/Instant Experience</t>
+          <t>PNG, JPEG, MP4/MOV/M4V + catálogo</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -11352,12 +11347,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11367,32 +11362,32 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Image Pin</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>1080x1080 (1:1) ou 1080x1350 (4:5) recomendado; placement pode variar</t>
+          <t>1000x1500 recomendado (2:3)</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>1:1 ou 4:5</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>30 MB</t>
+          <t>20 MB</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>PNG, JPEG</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -11409,12 +11404,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -11424,32 +11419,32 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>1080x1920 (9:16) Stories/Reels; 1080x1350 (4:5) Feed recomendado</t>
+          <t>1000x1500 (2:3), 1080x1920 (9:16) ou square conforme placement</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>9:16 ou 4:5</t>
+          <t>2:3 ou 9:16</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>2 GB</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV, M4V</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -11466,12 +11461,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -11481,12 +11476,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>1080x1080 recomendado (1:1); placement pode variar</t>
+          <t>2–6 cartões; 1080x1080 recomendado</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -11496,17 +11491,17 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Imagem 30 MB; vídeo 4 GB</t>
+          <t>20 MB por imagem; GIF 3 MB</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>JPG/PNG ou MP4/MOV por cartão</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://www.business.reddit.com/advertise/ad-types/carousel-ads</t>
         </is>
       </c>
     </row>
@@ -11523,27 +11518,27 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Free-form Ad</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>1080x1080 recomendado; capa pode ser imagem ou vídeo</t>
+          <t>Imagem: 1200x1200 (1:1) ou 1920x1080/1440x1080; vídeo conforme asset</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -11553,17 +11548,17 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Imagem 30 MB; vídeo 4 GB</t>
+          <t>Imagem ≤20 MB; vídeo ≤1 GB</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>JPG/PNG ou MP4/MOV + catálogo/Instant Experience</t>
+          <t>JPG, PNG, GIF, MP4, MOV + rich text</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://www.business.reddit.com/advertise/ad-types/free-form</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11575,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -11595,32 +11590,32 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Image Ad</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>1080x1080 (1:1) ou 1080x1350 (4:5) recomendado; placement pode variar</t>
+          <t>1080x1080 (1:1); 1080x1350 (4:5); 1440x1080 (4:3); 1920x1080 (16:9)</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>1:1 ou 4:5</t>
+          <t>1:1 ou 4:5 ou 4:3 ou 16:9</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>30 MB</t>
+          <t>3 MB</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, PNG, GIF (estático)</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://www.business.reddit.com/learning-hub/articles/reddit-image-ad-specs</t>
         </is>
       </c>
     </row>
@@ -11637,47 +11632,42 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Catalog Ad</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>1080x1920 (9:16) Stories/Reels; 1080x1350 (4:5) Feed recomendado</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>9:16 ou 4:5</t>
+          <t>Depende do asset do catálogo/underlying ad type</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>Depende do asset</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>Catálogo de produtos + JPG/PNG ou vídeo conforme configuração</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://www.business.reddit.com/advertise/ad-types</t>
         </is>
       </c>
     </row>
@@ -11694,47 +11684,42 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Carousel Ad</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>1:1 ou 2:3; 1000x1000 / 1000x1500 recomendado</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>1:1 ou 2:3</t>
+          <t>1:1 / 4:5 / 16:9; 1080p recomendado</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>20 MB por imagem</t>
+          <t>1 GB</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>PNG, JPEG; 2–5 imagens (non-Sales)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://www.business.reddit.com/advertise/ad-types/video-ads</t>
         </is>
       </c>
     </row>
@@ -11751,42 +11736,42 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>AR Lenses Filters</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hero 1:1 ou 2:3; assets secundários via catálogo</t>
+          <t>Filter estático 945x2048; animado 720x1560</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Imagem 20 MB; vídeo até 2 GB</t>
+          <t>Varia por asset AR</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>PNG, JPEG, MP4/MOV/M4V + catálogo</t>
+          <t>PNG (filtro estático), GIF (animado); Lens assets conforme Lens Studio</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -11803,47 +11788,47 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Image Pin</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>1000x1500 recomendado (2:3)</t>
+          <t>720x1280 (9:16) por asset recomendado</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>20 MB</t>
+          <t>Varia por asset</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>PNG, JPEG</t>
+          <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -11860,47 +11845,47 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>1000x1500 (2:3), 1080x1920 (9:16) ou square conforme placement</t>
+          <t>720x1280 (9:16)</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2:3 ou 9:16</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2 GB</t>
+          <t>Varia por asset</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>MP4, MOV, M4V</t>
+          <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -11917,47 +11902,47 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Carousel Ad</t>
+          <t>Commercial Ad</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2–6 cartões; 1080x1080 recomendado</t>
+          <t>720x1280 (9:16)</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>20 MB por imagem; GIF 3 MB</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV (H.264)</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/carousel-ads</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -11974,47 +11959,47 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Free-form Ad</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Imagem: 1200x1200 (1:1) ou 1920x1080/1440x1080; vídeo conforme asset</t>
+          <t>720x1280 (9:16)</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Imagem ≤20 MB; vídeo ≤1 GB</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF, MP4, MOV + rich text</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/free-form</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -12031,47 +12016,47 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Image Ad</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>1080x1080 (1:1); 1080x1350 (4:5); 1440x1080 (4:3); 1920x1080 (16:9)</t>
+          <t>720x1280 (9:16)</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>1:1 ou 4:5 ou 4:3 ou 16:9</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>3 MB</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (estático)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/learning-hub/articles/reddit-image-ad-specs</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -12088,42 +12073,47 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Catalog Ad</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Depende do asset do catálogo/underlying ad type</t>
+          <t>720x1280 (9:16)</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Depende do asset</t>
+          <t>Varia por asset</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Catálogo de produtos + JPG/PNG ou vídeo conforme configuração</t>
+          <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -12140,42 +12130,47 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Branded Effect</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>1:1 / 4:5 / 16:9; 1080p recomendado</t>
+          <t>Ícone 162x162 (safe 144x144); restantes assets conforme template</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>Ícone &lt;60 KB; restantes conforme template</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>PNG + assets de efeito conforme template</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/video-ads</t>
+          <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
         </is>
       </c>
     </row>
@@ -12192,42 +12187,42 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Branded Effects</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>AR Lenses Filters</t>
+          <t>Branded Mission</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Filter estático 945x2048; animado 720x1560</t>
+          <t>Criativo final segue In-Feed/Spark Ads (vertical 9:16 recomendado)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Varia por asset AR</t>
+          <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>PNG (filtro estático), GIF (animado); Lens assets conforme Lens Studio</t>
+          <t>Vídeo de creator elegível / Spark Ads</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12244,12 +12239,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -12259,32 +12254,32 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Carousel Ads</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>720x1280 (9:16) por asset recomendado</t>
+          <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1.91:1 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>100 KB sugerido por imagem; música até 10 MB</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV</t>
+          <t>JPG/JPEG, PNG + MP3</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12301,27 +12296,27 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>In-Feed (Standard Feed)</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>Vertical 9:16 recomendado; ≥540x960 recomendado</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -12331,17 +12326,17 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>Até 500 MB (reservation); limites podem variar em auction</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
+          <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12358,47 +12353,42 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Commercial Ad</t>
+          <t>Pulse</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>MP4, MOV (H.264)</t>
+          <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
         </is>
       </c>
     </row>
@@ -12415,27 +12405,27 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Spark Ads</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>Usa vídeo orgânico; para push, 9:16 ≥540x960 recomendado</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -12445,17 +12435,17 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Até 500 MB para push</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12472,47 +12462,42 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Top Feed</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Segue criativo In-Feed; vertical 9:16 recomendado</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Conforme In-Feed</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12529,27 +12514,27 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>TopView</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>9:16; ≥540x960</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -12559,17 +12544,17 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>500 MB</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV</t>
+          <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12586,47 +12571,42 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Branded Effects</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Branded Effect</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Ícone 162x162 (safe 144x144); restantes assets conforme template</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>16:9 recomendado; vídeo HD</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Ícone &lt;60 KB; restantes conforme template</t>
+          <t>1 GB recomendado/limite conforme placement</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>PNG + assets de efeito conforme template</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12643,42 +12623,47 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Branded Mission</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Criativo final segue In-Feed/Spark Ads (vertical 9:16 recomendado)</t>
+          <t>800x800 (1:1) ou 800x418 (1.91:1) recomendado</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Conforme vídeo In-Feed/Spark</t>
+          <t>5 MB por imagem; vídeo conforme specs</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Vídeo de creator elegível / Spark Ads</t>
+          <t>JPG, PNG; MP4/MOV para video carousel</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12695,47 +12680,47 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Carousel Ads</t>
+          <t>Collection Ad</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
+          <t>Hero 800x800 (1:1) recomendado + thumbnails de produtos</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 9:16</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>100 KB sugerido por imagem; música até 10 MB</t>
+          <t>5 MB por imagem</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>JPG/JPEG, PNG + MP3</t>
+          <t>JPG, PNG + catálogo</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12752,47 +12737,42 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Catalog Ad</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>In-Feed (Standard Feed)</t>
+          <t>Dynamic Product Ads</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Vertical 9:16 recomendado; ≥540x960 recomendado</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Assets provenientes do catálogo; 1:1 recomendado</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Até 500 MB (reservation); limites podem variar em auction</t>
+          <t>Conforme catálogo</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>MP4, MOV, MPEG, 3GP</t>
+          <t>Feed/catálogo + JPG/PNG</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12809,42 +12789,47 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pulse</t>
+          <t>Image Ad</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
+          <t>1200x1200 (1:1) ou 1200x628 (1.91:1) recomendado</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Conforme vídeo In-Feed/Spark</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>MP4, MOV / Spark Ads</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12861,47 +12846,42 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Spark Ads</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Usa vídeo orgânico; para push, 9:16 ≥540x960 recomendado</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Depende do produto (Timeline/Trend Takeover); assets conforme ficha X</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Até 500 MB para push</t>
+          <t>Conforme formato</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
+          <t>JPG, PNG, MP4/MOV conforme takeover</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12918,42 +12898,42 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Top Feed</t>
+          <t>Text Ad</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Segue criativo In-Feed; vertical 9:16 recomendado</t>
+          <t>Sem asset gráfico obrigatório</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Conforme In-Feed</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>MP4, MOV / Spark Ads</t>
+          <t>Texto/post + URL opcional</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12970,47 +12950,47 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>TopView</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>9:16; ≥540x960</t>
+          <t>1200x1200 (1:1) ou 1920x1080 (16:9) recomendado</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1:1 ou 16:9</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>500 MB</t>
+          <t>1 GB</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>MP4, MOV, MPEG, 3GP</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -13022,47 +13002,47 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Medium Rectangle</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>16:9 recomendado; vídeo HD</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1 GB recomendado/limite conforme placement</t>
+          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13074,52 +13054,47 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Carousel Ad</t>
+          <t>Large Rectangle</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>800x800 (1:1) ou 800x418 (1.91:1) recomendado</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>336x280</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>5 MB por imagem; vídeo conforme specs</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>JPG, PNG; MP4/MOV para video carousel</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13131,52 +13106,47 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Collection Ad</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hero 800x800 (1:1) recomendado + thumbnails de produtos</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>5 MB por imagem</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>JPG, PNG + catálogo</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13188,47 +13158,52 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Catalog Ad</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Dynamic Product Ads</t>
+          <t>Half Page</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Assets provenientes do catálogo; 1:1 recomendado</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Conforme catálogo</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Feed/catálogo + JPG/PNG</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13240,52 +13215,47 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Image Ad</t>
+          <t>Mobile Banner</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>1200x1200 (1:1) ou 1200x628 (1.91:1) recomendado</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>320x50</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13297,47 +13267,52 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Responsive Display Ads (imagem)</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Depende do produto (Timeline/Trend Takeover); assets conforme ficha X</t>
+          <t>Landscape 1200x628 (1.91:1, mín. 600x314); Square 1200x1200 (1:1, mín. 300x300); Portrait 1200x1500 (4:5, opcional)</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Conforme formato</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4/MOV conforme takeover</t>
+          <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13349,47 +13324,52 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Text Ad</t>
+          <t>HTML5 Display</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Sem asset gráfico obrigatório</t>
+          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>150 KB (dentro do HTML5)</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Texto/post + URL opcional</t>
+          <t>ZIP HTML5</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13401,52 +13381,52 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Skippable In-Stream</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>1200x1200 (1:1) ou 1920x1080 (16:9) recomendado</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>1:1 ou 16:9</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13468,37 +13448,42 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Medium Rectangle</t>
+          <t>Non-skippable In-Stream (standard)</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13520,37 +13505,42 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Large Rectangle</t>
+          <t>Bumper</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>336x280</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13572,37 +13562,37 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Non-skippable 30s (Connected TV)</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13624,42 +13614,37 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Half Page</t>
+          <t>In-Feed Video Ad (ex-Discovery)</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13681,37 +13666,37 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Mobile Banner</t>
+          <t>YouTube Shorts Ads</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>320x50</t>
+          <t>9:16 vertical</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13733,42 +13718,42 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Responsive Display Ads (imagem)</t>
+          <t>Masthead</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Landscape 1200x628 (1.91:1, mín. 600x314); Square 1200x1200 (1:1, mín. 300x300); Portrait 1200x1500 (4:5, opcional)</t>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (não animado)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13790,42 +13775,42 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>HTML5 Display</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
+          <t>Landscape 1200x628 (1.91:1); Square 1200x1200 (1:1); Portrait 1200x1500 (4:5, opcional) — enviar pelo menos landscape + square</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1.91:1 ou 1:1</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>150 KB (dentro do HTML5)</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>ZIP HTML5</t>
+          <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -13847,42 +13832,37 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Skippable In-Stream</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>16:9, 1:1 ou 9:16; duração mínima 10s (in-feed) ou 6s (estilo bumper)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -13904,42 +13884,37 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Non-skippable In-Stream (standard)</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>2 a 10 cartões, todos com a mesma proporção (1:1 ou 1.91:1); cada cartão com título até 40 caracteres</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB por imagem</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -13961,42 +13936,37 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns / Performance Max</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Bumper</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Várias proporções (paisagem, quadrado, retrato) conforme o placement</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
@@ -14018,22 +13988,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns / Performance Max</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Non-skippable 30s (Connected TV)</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
+          <t>Várias proporções conforme o placement; obrigatório estar alojado no YouTube</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -14048,7 +14018,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
@@ -14070,463 +14040,283 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns / Performance Max</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>In-Feed Video Ad (ex-Discovery)</t>
+          <t>HTML5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original</t>
+          <t>Pacote HTML5, até 512 ficheiros dentro do ZIP</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB (ZIP)</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>ZIP HTML5</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/9948381</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>YouTube Shorts Ads</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>9:16 vertical</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - App Install</t>
         </is>
       </c>
     </row>
     <row r="264" ht="25" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>Open Door</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Masthead</t>
+          <t>Prog - Audio Ad</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>MP3</t>
         </is>
       </c>
     </row>
     <row r="265" ht="25" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>Single Image</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Imagem</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Landscape 1200x628 (1.91:1); Square 1200x1200 (1:1); Portrait 1200x1500 (4:5, opcional) — enviar pelo menos landscape + square</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>1.91:1 ou 1:1</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>5 MB</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>JPG, PNG, GIF (não animado)</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>Prog - Audio Ingame</t>
         </is>
       </c>
     </row>
     <row r="266" ht="25" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>Single Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Prog - Banner</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>16:9, 1:1 ou 9:16; duração mínima 10s (in-feed) ou 6s (estilo bumper)</t>
+          <t>300x250, 300x600, 728x90, 320x50</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
     </row>
     <row r="267" ht="25" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Carousel</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Carousel</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>2 a 10 cartões, todos com a mesma proporção (1:1 ou 1.91:1); cada cartão com título até 40 caracteres</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>5 MB por imagem</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>Prog - Banner Ingame</t>
         </is>
       </c>
     </row>
     <row r="268" ht="37.5" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Google App Campaigns / Performance Max</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Single Image</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Imagem</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Várias proporções (paisagem, quadrado, retrato) conforme o placement</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>5 MB</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>Prog - Banner Mobile</t>
         </is>
       </c>
     </row>
     <row r="269" ht="37.5" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Google App Campaigns / Performance Max</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>Single Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>Várias proporções conforme o placement; obrigatório estar alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>Prog - Conversational Display</t>
         </is>
       </c>
     </row>
     <row r="270" ht="37.5" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Google App Campaigns / Performance Max</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>HTML5</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Pacote HTML5, até 512 ficheiros dentro do ZIP</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>5 MB (ZIP)</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>ZIP HTML5</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/9948381</t>
+          <t>Prog - Demand Gen</t>
         </is>
       </c>
     </row>
@@ -14548,12 +14338,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>DOOH</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Prog - App Install</t>
+          <t>Prog - DOOH</t>
         </is>
       </c>
     </row>
@@ -14580,22 +14370,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Prog - Audio Ad</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>1 MB</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>MP3</t>
+          <t>Prog - Expositor</t>
         </is>
       </c>
     </row>
@@ -14622,7 +14397,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Prog - Audio Ingame</t>
+          <t>Prog - In Content</t>
         </is>
       </c>
     </row>
@@ -14649,22 +14424,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Prog - Banner</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>300x250, 300x600, 728x90, 320x50</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>Prog - inRead Carousel</t>
         </is>
       </c>
     </row>
@@ -14686,12 +14446,42 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Prog - Banner Ingame</t>
+          <t>Prog - YouTube Masthead</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14508,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Prog - Banner Mobile</t>
+          <t>Prog - M-Rec</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>300x250</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14540,32 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Prog - Conversational Display</t>
+          <t>Prog - Native Ad</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
         </is>
       </c>
     </row>
@@ -14772,7 +14592,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Prog - Demand Gen</t>
+          <t>Prog - Rewarded Video</t>
         </is>
       </c>
     </row>
@@ -14794,12 +14614,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>DOOH</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Prog - DOOH</t>
+          <t>Prog - Rich Media</t>
         </is>
       </c>
     </row>
@@ -14821,12 +14641,42 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Prog - Expositor</t>
+          <t>Prog - YouTube Select</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14848,12 +14698,42 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Prog - In Content</t>
+          <t>Prog - YouTube VRC Ad Sequence</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14880,7 +14760,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Prog - inRead Carousel</t>
+          <t>Prog - Skyscraper</t>
         </is>
       </c>
     </row>
@@ -14902,42 +14782,12 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Open Door</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Prog - YouTube Masthead</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - Social Display</t>
         </is>
       </c>
     </row>
@@ -14959,17 +14809,37 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Prog - M-Rec</t>
+          <t>Prog - YouTube VRC Non-Skippable</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14991,37 +14861,32 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Prog - Native Ad</t>
+          <t>Prog - Uber Journey Ad</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>1:1 ou 3:4</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
+          <t>Display: imagens. Video: MP4.</t>
         </is>
       </c>
     </row>
@@ -15043,12 +14908,12 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Prog - Rewarded Video</t>
+          <t>Prog - Spotify Video Takeover</t>
         </is>
       </c>
     </row>
@@ -15075,7 +14940,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Prog - Rich Media</t>
+          <t>Prog - Wallpaper</t>
         </is>
       </c>
     </row>
@@ -15107,7 +14972,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Prog - YouTube Select</t>
+          <t>Prog - YouTube VVC</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -15164,17 +15029,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Ad Sequence</t>
+          <t>Prog - YouTube VRC Efficient Reach</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -15184,12 +15044,12 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -15211,12 +15071,37 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Prog - Skyscraper</t>
+          <t>Prog - YouTube VRC Target Frequency</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; NON-SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -15238,12 +15123,37 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Prog - Social Display</t>
+          <t>Prog - Billboard (Impresa)</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>970x250, 320x10</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>200 KB</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
       </c>
     </row>
@@ -15265,37 +15175,37 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Non-Skippable</t>
+          <t>Prog - Billboard (Media Capital)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+          <t>980x250 ou 970x250</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
       </c>
     </row>
@@ -15317,32 +15227,37 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Observador</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Prog - Uber Journey Ad</t>
+          <t>Prog - Billboard (Observador)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>1:1 ou 3:4</t>
+          <t>1200x220, 970x250</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Display: imagens. Video: MP4.</t>
+          <t>JPG, PNG ou GIF / HTML</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15364,12 +15279,37 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Prog - Spotify Video Takeover</t>
+          <t>Prog - Billboard (Público)</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>120 KB</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
       </c>
     </row>
@@ -15391,12 +15331,32 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Sapo</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Prog - Wallpaper</t>
+          <t>Prog - Billboard (Sapo)</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>970x250</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>200 KB</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
       </c>
     </row>
@@ -15418,42 +15378,42 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Prog - YouTube VVC</t>
+          <t>Prog - Half-Page (Impresa)</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>300x600</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15475,37 +15435,42 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Efficient Reach</t>
+          <t>Prog - Half-Page (Media Capital)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
       </c>
     </row>
@@ -15527,37 +15492,42 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Target Frequency</t>
+          <t>Prog - Half-Page (Media Livre)</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; NON-SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>80 KB / 2 MB</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
       </c>
     </row>
@@ -15579,37 +15549,42 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Impresa)</t>
+          <t>Prog - Half-Page (Observador)</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>970x250, 320x10</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>100 KB / 2 MB</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
+          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15631,37 +15606,42 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Media Capital)</t>
+          <t>Prog - Half-Page (Público)</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>980x250 ou 970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15683,37 +15663,42 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Observador)</t>
+          <t>Prog - Half-Page (Sapo)</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>1200x220, 970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>200 KB / 3.5 MB</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/manchete-desktop.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
       </c>
     </row>
@@ -15735,37 +15720,42 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Público)</t>
+          <t>Prog - Half-Page (Google)</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -15787,32 +15777,32 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Sapo)</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>970x250</t>
+          <t>Prog - Header XL (Impresa)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>150 KB</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>JPG</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
       </c>
     </row>
@@ -15834,32 +15824,27 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Impresa)</t>
+          <t>Prog - Header XL (Media Livre)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -15869,7 +15854,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
       </c>
     </row>
@@ -15891,42 +15876,37 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Capital)</t>
+          <t>Prog - Header XL (Observador)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
+          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15948,42 +15928,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Livre)</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>80 KB / 2 MB</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>HTML, JPEG, PNG ou GIF / MP4</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
+          <t>Prog - Header XL (Sapo)</t>
         </is>
       </c>
     </row>
@@ -16005,42 +15960,42 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Observador)</t>
+          <t>Prog - Intro (Impresa)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>600x400, 320x480</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>3:2 ou 2:3</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>100 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>JPG ou PNG</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -16062,42 +16017,42 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Público)</t>
+          <t>Prog - Intro (Media Capital)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>800x600</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>4:3</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
+          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
       </c>
     </row>
@@ -16119,42 +16074,42 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Sapo)</t>
+          <t>Prog - Intro (Media Livre)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>800x600, 768x1024</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>200 KB / 3.5 MB</t>
+          <t>120 KB / 1 MB</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
       </c>
     </row>
@@ -16176,42 +16131,37 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Google)</t>
+          <t>Prog - Intro (Observador)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>990x600, 300x480</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>120 KB, 75 KB / 2 MB</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16233,32 +16183,42 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Impresa)</t>
+          <t>Prog - Intro (Público)</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>800x600, 768x1024</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -16280,37 +16240,42 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Media Livre)</t>
+          <t>Prog - Intro (Sapo)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
+          <t>800x600px (600x400px recomendado)</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:2</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
       </c>
     </row>
@@ -16332,37 +16297,37 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Observador)</t>
+          <t>Prog - Leaderboard (Media Capital)</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>500 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -16384,17 +16349,37 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Sapo)</t>
+          <t>Prog - Leaderboard (Media Livre)</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>728x90</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>80 KB</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>HTML, JPEG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -16416,42 +16401,37 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Prog - Intro (Impresa)</t>
+          <t>Prog - Leaderboard (Público)</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>600x400, 320x480</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>3:2 ou 2:3</t>
+          <t>1140x50</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
       </c>
     </row>
@@ -16473,42 +16453,37 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Capital)</t>
+          <t>Prog - Leaderboard (Sapo)</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>800x600</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>4:3</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>WEBP</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
       </c>
     </row>
@@ -16530,42 +16505,37 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Livre)</t>
+          <t>Prog - Leaderboard (Google)</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>120 KB / 1 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -16587,37 +16557,42 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Prog - Intro (Observador)</t>
+          <t>Prog - Open Door (Impresa)</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>990x600, 300x480</t>
+          <t>1920x1080, 680x1520</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>120 KB, 75 KB / 2 MB</t>
+          <t>200 KB, 150 KB</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16639,42 +16614,42 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Prog - Intro (Público)</t>
+          <t>Prog - Open Door (Media Capital)</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
+          <t>1920x1080, 680x1520</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>4:3 ou 3:4</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
+          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
       </c>
     </row>
@@ -16696,42 +16671,42 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Prog - Intro (Sapo)</t>
+          <t>Prog - Open Door (Media Livre)</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>800x600px (600x400px recomendado)</t>
+          <t>950x700, 390x850 / 640x360</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>4:3 ou 3:2</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>500 KB / 2 MB</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
       </c>
     </row>
@@ -16753,37 +16728,32 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Capital)</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>728x90</t>
+          <t>Prog - Open Door (Observador)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Máxima resolução</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
+          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16805,37 +16775,37 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Livre)</t>
+          <t>Prog - Open Door (Público)</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>800x900</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF</t>
+          <t>JPG / Video</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16857,37 +16827,42 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Público)</t>
+          <t>Prog - Open Door (Google)</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>1140x50</t>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -16909,37 +16884,42 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Parallax</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Sapo)</t>
+          <t>Prog - Parallax (Público)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>WEBP</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
       </c>
     </row>
@@ -16961,37 +16941,32 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Google)</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>728x90</t>
+          <t>Prog - Peel off (Media Capital)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>Imagens</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
       </c>
     </row>
@@ -17013,42 +16988,37 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Impresa)</t>
+          <t>Prog - Peel off (Media Livre)</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>1920x1080, 680x1520</t>
+          <t>200x200, 850x650</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>200 KB, 150 KB</t>
-        </is>
-      </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>JPG</t>
+          <t>260 KB</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
       </c>
     </row>
@@ -17070,42 +17040,42 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Capital)</t>
+          <t>Prog - Peel off (Observador)</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>1920x1080, 680x1520</t>
+          <t>200x200, 850x650px</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
+          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
       </c>
     </row>
@@ -17127,22 +17097,22 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Livre)</t>
+          <t>Prog - Pre-Roll (Media Capital)</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>950x700, 390x850 / 640x360</t>
+          <t>1280x720</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -17152,17 +17122,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>500 KB / 2 MB</t>
+          <t>6 MB</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG / MP4</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
+          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -17184,32 +17154,42 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Observador)</t>
+          <t>Prog - Pre-Roll (Media Livre)</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>640x360</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Máxima resolução</t>
+          <t>15 MB</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>MP4 ou FLV</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -17231,37 +17211,42 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Público)</t>
+          <t>Prog - Pre-Roll (Observador)</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>800x900</t>
+          <t>640x360</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>JPG / Video</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
+          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
       </c>
     </row>
@@ -17283,22 +17268,22 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Google)</t>
+          <t>Prog - Pre-Roll (Público)</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>640x360px com rácio de 16:9</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -17308,17 +17293,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
       </c>
     </row>
@@ -17340,42 +17325,42 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Parallax</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Prog - Parallax (Público)</t>
+          <t>Prog - Pre-Roll (Sapo)</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
+          <t>640x360px (16:9)</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>3.5 MB</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
       </c>
     </row>
@@ -17402,27 +17387,32 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Capital)</t>
+          <t>Prog - Takeover (Media Capital)</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>650x350</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Imagens</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
+          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
       </c>
     </row>
@@ -17444,37 +17434,37 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Livre)</t>
+          <t>Prog - Takeover (Público)</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>200x200, 850x650</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>260 KB</t>
+          <t>500 KB</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
       </c>
     </row>
@@ -17496,42 +17486,17 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Observador)</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>200x200, 850x650px</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>120 KB / 2 MB</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
+          <t>Prog - Connected TV (Sapo)</t>
         </is>
       </c>
     </row>
@@ -17553,42 +17518,37 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Capital)</t>
+          <t>Prog - Connected TV (Google)</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>1280x720</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>6 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -17610,79 +17570,54 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Livre)</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>640x360</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>15 MB</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>MP4 ou FLV</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
+          <t>Prog - CTV First Screen (Sapo)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Observador)</t>
+          <t>Skippable in-stream ads</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>640x360</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -17692,54 +17627,54 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Público)</t>
+          <t>Non-skippable in-stream ads</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>640x360px com rácio de 16:9</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -17749,54 +17684,54 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>MP4 ou WEBM</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Sapo)</t>
+          <t>Bumper ads</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>640x360px (16:9)</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -17806,567 +17741,176 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>3.5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Media Capital)</t>
+          <t>In-feed ads</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>650x350</t>
+          <t>Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Público)</t>
+          <t>Shorts ads</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
+          <t>9:16 vertical</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>500 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / Video para a área expandida</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Sapo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>Prog - Connected TV (Google)</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr">
+          <t>Masthead ads</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
         <is>
           <t>Alojado no YouTube</t>
         </is>
       </c>
-      <c r="J344" t="inlineStr">
+      <c r="J343" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>Sapo</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>Prog - CTV First Screen (Sapo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>Skippable in-stream ads</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
-        </is>
-      </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>MP4, MOV (upload via YouTube)</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Non-skippable in-stream ads</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>Bumper ads</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>In-Feed Video</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>In-feed ads</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>Shorts ads</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>9:16 vertical</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>Masthead ads</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
+      <c r="K343" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K343"/>
+  <dimension ref="A1:K351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -13292,12 +13292,12 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Landscape 1200x628 (1.91:1, mín. 600x314); Square 1200x1200 (1:1, mín. 300x300); Portrait 1200x1500 (4:5, opcional)</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 600x600 (mín. 300x300); Logo 1:1: 1200x1200 (mín. 128x128, opcional); Logo 4:1: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal 16:9, Square 1:1, Vertical 2:3; qualquer duração (recomendado 30s).</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>1.91:1 ou 1:1 ou 4:1</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (não animado)</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -13629,7 +13629,12 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original</t>
+          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; 15 segundos recomendado. Texto — Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -13681,7 +13686,12 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>9:16 vertical</t>
+          <t>9:16 vertical: 1080x1920; 6 a 60 segundos</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -13790,12 +13800,12 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Landscape 1200x628 (1.91:1); Square 1200x1200 (1:1); Portrait 1200x1500 (4:5, opcional) — enviar pelo menos landscape + square</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Logo 1:1: 1200x1200 (mín. 144x144); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional)</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1</t>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -13847,7 +13857,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>16:9, 1:1 ou 9:16; duração mínima 10s (in-feed) ou 6s (estilo bumper)</t>
+          <t>Horizontal 16:9, Vertical 9:16 ou 4:5, Square 1:1; 10 a 60 segundos (opcional)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -13921,156 +13931,96 @@
     <row r="260" ht="25" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Google App Campaigns / Performance Max</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>Single Image</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Imagem</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>Várias proporções (paisagem, quadrado, retrato) conforme o placement</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>5 MB</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>Prog - App Install</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Google App Campaigns / Performance Max</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Single Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Prog - Audio Ad</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Várias proporções conforme o placement; obrigatório estar alojado no YouTube</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>MP3</t>
         </is>
       </c>
     </row>
     <row r="262" ht="25" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Google App Campaigns / Performance Max</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Rich Media</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>HTML5</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Pacote HTML5, até 512 ficheiros dentro do ZIP</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>5 MB (ZIP)</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>ZIP HTML5</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/9948381</t>
+          <t>Prog - Audio Ingame</t>
         </is>
       </c>
     </row>
@@ -14097,7 +14047,22 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Prog - App Install</t>
+          <t>Prog - Banner</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>300x250, 300x600, 728x90, 320x50</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>200 KB</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
     </row>
@@ -14124,22 +14089,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Prog - Audio Ad</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>1 MB</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>MP3</t>
+          <t>Prog - Banner Ingame</t>
         </is>
       </c>
     </row>
@@ -14166,7 +14116,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Prog - Audio Ingame</t>
+          <t>Prog - Banner Mobile</t>
         </is>
       </c>
     </row>
@@ -14193,22 +14143,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Prog - Banner</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>300x250, 300x600, 728x90, 320x50</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>Prog - Conversational Display</t>
         </is>
       </c>
     </row>
@@ -14235,7 +14170,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Prog - Banner Ingame</t>
+          <t>Prog - Demand Gen</t>
         </is>
       </c>
     </row>
@@ -14257,12 +14192,12 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>DOOH</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Prog - Banner Mobile</t>
+          <t>Prog - DOOH</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14224,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Prog - Conversational Display</t>
+          <t>Prog - Expositor</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14251,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Prog - Demand Gen</t>
+          <t>Prog - In Content</t>
         </is>
       </c>
     </row>
@@ -14338,12 +14273,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DOOH</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Prog - DOOH</t>
+          <t>Prog - inRead Carousel</t>
         </is>
       </c>
     </row>
@@ -14365,12 +14300,42 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Prog - Expositor</t>
+          <t>Prog - YouTube Masthead</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14397,7 +14362,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Prog - In Content</t>
+          <t>Prog - M-Rec</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>300x250</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14394,32 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Prog - inRead Carousel</t>
+          <t>Prog - Native Ad</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
         </is>
       </c>
     </row>
@@ -14446,42 +14441,12 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>Open Door</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Prog - YouTube Masthead</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - Rewarded Video</t>
         </is>
       </c>
     </row>
@@ -14508,12 +14473,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Prog - M-Rec</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>300x250</t>
+          <t>Prog - Rich Media</t>
         </is>
       </c>
     </row>
@@ -14535,37 +14495,42 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Prog - Native Ad</t>
+          <t>Prog - YouTube Select</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14587,12 +14552,42 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Prog - Rewarded Video</t>
+          <t>Prog - YouTube VRC Ad Sequence</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14614,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Prog - Rich Media</t>
+          <t>Prog - Skyscraper</t>
         </is>
       </c>
     </row>
@@ -14641,42 +14636,12 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Prog - YouTube Select</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>MP4, MOV (upload via YouTube)</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - Social Display</t>
         </is>
       </c>
     </row>
@@ -14708,17 +14673,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Ad Sequence</t>
+          <t>Prog - YouTube VRC Non-Skippable</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14728,12 +14688,12 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14755,12 +14715,32 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Prog - Skyscraper</t>
+          <t>Prog - Uber Journey Ad</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>1:1 ou 3:4</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Display: imagens. Video: MP4.</t>
         </is>
       </c>
     </row>
@@ -14782,12 +14762,12 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Prog - Social Display</t>
+          <t>Prog - Spotify Video Takeover</t>
         </is>
       </c>
     </row>
@@ -14809,37 +14789,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Non-Skippable</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>Prog - Wallpaper</t>
         </is>
       </c>
     </row>
@@ -14861,32 +14816,42 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Prog - Uber Journey Ad</t>
+          <t>Prog - YouTube VVC</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>1:1 ou 3:4</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Display: imagens. Video: MP4.</t>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14908,12 +14873,37 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Prog - Spotify Video Takeover</t>
+          <t>Prog - YouTube VRC Efficient Reach</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal 16:9: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical 9:16: 1080x1920, 6 a 60 segundos (Shorts); Square 1:1: 1080x1080, 6 a 60 segundos.</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14935,12 +14925,37 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Prog - Wallpaper</t>
+          <t>Prog - YouTube VRC Target Frequency</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal 16:9: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14962,42 +14977,37 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Prog - YouTube VVC</t>
+          <t>Prog - Billboard (Impresa)</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>970x250, 320x10</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>JPG ou PNG</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
       </c>
     </row>
@@ -15019,37 +15029,37 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Efficient Reach</t>
+          <t>Prog - Billboard (Media Capital)</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+          <t>980x250 ou 970x250</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
       </c>
     </row>
@@ -15071,37 +15081,37 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Target Frequency</t>
+          <t>Prog - Billboard (Observador)</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa; NON-SKIPPABLE IN-STREAM — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; IN-FEED — Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original; SHORTS — 9:16 vertical.</t>
+          <t>1200x220, 970x250</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15123,7 +15133,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -15133,27 +15143,27 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Impresa)</t>
+          <t>Prog - Billboard (Público)</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>970x250, 320x10</t>
+          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15185,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -15185,27 +15195,22 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Media Capital)</t>
+          <t>Prog - Billboard (Sapo)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>980x250 ou 970x250</t>
+          <t>970x250</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>100 KB</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
       </c>
     </row>
@@ -15227,37 +15232,42 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Observador)</t>
+          <t>Prog - Half-Page (Impresa)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>1200x220, 970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/manchete-desktop.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15279,37 +15289,42 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Público)</t>
+          <t>Prog - Half-Page (Media Capital)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
+          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
       </c>
     </row>
@@ -15331,32 +15346,42 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Sapo)</t>
+          <t>Prog - Half-Page (Media Livre)</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>80 KB / 2 MB</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15403,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -15388,7 +15413,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Impresa)</t>
+          <t>Prog - Half-Page (Observador)</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -15403,17 +15428,17 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>100 KB / 2 MB</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
+          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15435,7 +15460,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -15445,7 +15470,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Capital)</t>
+          <t>Prog - Half-Page (Público)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -15460,17 +15485,17 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15517,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -15502,7 +15527,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Livre)</t>
+          <t>Prog - Half-Page (Sapo)</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -15517,17 +15542,17 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>80 KB / 2 MB</t>
+          <t>200 KB / 3.5 MB</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF / MP4</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
       </c>
     </row>
@@ -15549,7 +15574,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -15559,7 +15584,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Observador)</t>
+          <t>Prog - Half-Page (Google)</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -15574,17 +15599,17 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>100 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -15606,42 +15631,32 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Público)</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>Prog - Header XL (Impresa)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
       </c>
     </row>
@@ -15663,42 +15678,37 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Sapo)</t>
+          <t>Prog - Header XL (Media Livre)</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>200 KB / 3.5 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
       </c>
     </row>
@@ -15720,42 +15730,37 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Google)</t>
+          <t>Prog - Header XL (Observador)</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15782,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -15787,22 +15792,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Impresa)</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>JPG</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
+          <t>Prog - Header XL (Sapo)</t>
         </is>
       </c>
     </row>
@@ -15824,22 +15814,27 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Media Livre)</t>
+          <t>Prog - Intro (Impresa)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
+          <t>600x400, 320x480</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>3:2 ou 2:3</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -15849,12 +15844,12 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>JPG ou PNG</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -15876,37 +15871,42 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Observador)</t>
+          <t>Prog - Intro (Media Capital)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
+          <t>800x600</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>4:3</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>500 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
       </c>
     </row>
@@ -15928,17 +15928,42 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Sapo)</t>
+          <t>Prog - Intro (Media Livre)</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>800x600, 768x1024</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:4</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>120 KB / 1 MB</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
       </c>
     </row>
@@ -15960,7 +15985,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -15970,32 +15995,27 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Prog - Intro (Impresa)</t>
+          <t>Prog - Intro (Observador)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>600x400, 320x480</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>3:2 ou 2:3</t>
+          <t>990x600, 300x480</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>120 KB, 75 KB / 2 MB</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
+          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16037,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16027,32 +16047,32 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Capital)</t>
+          <t>Prog - Intro (Público)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>800x600</t>
+          <t>800x600, 768x1024</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>4:3</t>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16094,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -16084,32 +16104,32 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Livre)</t>
+          <t>Prog - Intro (Sapo)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
+          <t>800x600px (600x400px recomendado)</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>4:3 ou 3:4</t>
+          <t>4:3 ou 3:2</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>120 KB / 1 MB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
       </c>
     </row>
@@ -16131,37 +16151,37 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Prog - Intro (Observador)</t>
+          <t>Prog - Leaderboard (Media Capital)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>990x600, 300x480</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>120 KB, 75 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -16183,42 +16203,37 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Prog - Intro (Público)</t>
+          <t>Prog - Leaderboard (Media Livre)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -16240,27 +16255,22 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Prog - Intro (Sapo)</t>
+          <t>Prog - Leaderboard (Público)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>800x600px (600x400px recomendado)</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:2</t>
+          <t>1140x50</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -16270,12 +16280,12 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
       </c>
     </row>
@@ -16297,7 +16307,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -16307,7 +16317,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Capital)</t>
+          <t>Prog - Leaderboard (Sapo)</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -16317,17 +16327,17 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>WEBP</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
       </c>
     </row>
@@ -16349,7 +16359,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -16359,7 +16369,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Livre)</t>
+          <t>Prog - Leaderboard (Google)</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -16369,17 +16379,17 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -16401,37 +16411,42 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Público)</t>
+          <t>Prog - Open Door (Impresa)</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>1140x50</t>
+          <t>1920x1080, 680x1520</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>200 KB, 150 KB</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16453,37 +16468,42 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Sapo)</t>
+          <t>Prog - Open Door (Media Capital)</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>1920x1080, 680x1520</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>WEBP</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
+          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
       </c>
     </row>
@@ -16505,37 +16525,42 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Google)</t>
+          <t>Prog - Open Door (Media Livre)</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>950x700, 390x850 / 640x360</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>500 KB / 2 MB</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
       </c>
     </row>
@@ -16557,7 +16582,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -16567,32 +16592,22 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Impresa)</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>1920x1080, 680x1520</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Prog - Open Door (Observador)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>200 KB, 150 KB</t>
+          <t>Máxima resolução</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
+          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16629,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -16624,32 +16639,27 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Capital)</t>
+          <t>Prog - Open Door (Público)</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>1920x1080, 680x1520</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>800x900</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG / Video</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16681,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -16681,12 +16691,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Livre)</t>
+          <t>Prog - Open Door (Google)</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>950x700, 390x850 / 640x360</t>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -16696,17 +16706,17 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>500 KB / 2 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG / MP4</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -16728,32 +16738,42 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Parallax</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Observador)</t>
+          <t>Prog - Parallax (Público)</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Máxima resolução</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
       </c>
     </row>
@@ -16775,37 +16795,32 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Público)</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>800x900</t>
+          <t>Prog - Peel off (Media Capital)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>JPG / Video</t>
+          <t>Imagens</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
+          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
       </c>
     </row>
@@ -16827,42 +16842,37 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Google)</t>
+          <t>Prog - Peel off (Media Livre)</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>200x200, 850x650</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
+          <t>260 KB</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
       </c>
     </row>
@@ -16884,32 +16894,32 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Parallax</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Prog - Parallax (Público)</t>
+          <t>Prog - Peel off (Observador)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
+          <t>200x200, 850x650px</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -16919,7 +16929,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
+          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16946,27 +16956,37 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Capital)</t>
+          <t>Prog - Pre-Roll (Media Capital)</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>1280x720</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>6 MB</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>Imagens</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
+          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -16993,32 +17013,37 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Livre)</t>
+          <t>Prog - Pre-Roll (Media Livre)</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>200x200, 850x650</t>
+          <t>640x360</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>260 KB</t>
+          <t>15 MB</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>MP4 ou FLV</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -17045,37 +17070,37 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Observador)</t>
+          <t>Prog - Pre-Roll (Observador)</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>200x200, 850x650px</t>
+          <t>640x360</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
+          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
       </c>
     </row>
@@ -17097,7 +17122,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -17107,12 +17132,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Capital)</t>
+          <t>Prog - Pre-Roll (Público)</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>1280x720</t>
+          <t>640x360px com rácio de 16:9</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -17122,17 +17147,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>6 MB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17179,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -17164,12 +17189,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Livre)</t>
+          <t>Prog - Pre-Roll (Sapo)</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>640x360</t>
+          <t>640x360px (16:9)</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -17179,17 +17204,17 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>15 MB</t>
+          <t>3.5 MB</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>MP4 ou FLV</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
       </c>
     </row>
@@ -17211,42 +17236,37 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Observador)</t>
+          <t>Prog - Takeover (Media Capital)</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>640x360</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>650x350</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
       </c>
     </row>
@@ -17273,37 +17293,32 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Público)</t>
+          <t>Prog - Takeover (Público)</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>640x360px com rácio de 16:9</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>MP4 ou WEBM</t>
+          <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
       </c>
     </row>
@@ -17330,37 +17345,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Sapo)</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>640x360px (16:9)</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>3.5 MB</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
+          <t>Prog - Connected TV (Sapo)</t>
         </is>
       </c>
     </row>
@@ -17382,37 +17372,37 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Media Capital)</t>
+          <t>Prog - Connected TV (Google)</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>650x350</t>
+          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -17434,106 +17424,116 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Público)</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>500 KB</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF / Video para a área expandida</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
+          <t>Prog - CTV First Screen (Sapo)</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Sapo)</t>
+          <t>Skippable in-stream ads</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Google)</t>
+          <t>Non-skippable in-stream ads</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -17555,32 +17555,57 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Prog - CTV First Screen (Sapo)</t>
+          <t>Bumper ads</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -17607,32 +17632,32 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Skippable in-stream ads</t>
+          <t>In-feed ads</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; 15 segundos recomendado. Texto — Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -17664,22 +17689,22 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Non-skippable in-stream ads</t>
+          <t>Shorts ads</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+          <t>9:16 vertical: 1080x1920; 6 a 60 segundos</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -17694,7 +17719,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -17721,17 +17746,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Bumper ads</t>
+          <t>Masthead ads</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -17751,7 +17776,7 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -17763,47 +17788,52 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>In-feed ads</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Miniatura + até 2 linhas de texto; o vídeo mantém a proporção original</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Vertical 4:5: 1200x1500 (mín. 320x400); Square 1:1: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
@@ -17815,32 +17845,37 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Vertical Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Shorts ads</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>9:16 vertical</t>
+          <t>Horizontal 16:9, Vertical 9:16, Square 1:1; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -17855,7 +17890,7 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
@@ -17867,50 +17902,501 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Google Performance Max</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Single Image</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Imagem</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>5120 KB</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Google Performance Max</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Logo quadrado 1:1: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal 4:1: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>1:1 ou 4:1</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>5120 KB</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Google Performance Max</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Single Video</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Horizontal 16:9, Square 1:1, Vertical 9:16; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>16:9 ou 1:1 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Google Search</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Business Information (Logo)</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Logo 1:1: 1200x1200 (mín. 128x128)</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>não especificado</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Google Search</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Ad Assets</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Ad Assets (Imagens)</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Square 1:1: 1200x1200 (mín. 300x300), obrigatório; Horizontal 1.91:1: 1200x628 (mín. 600x314), opcional</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>não especificado</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Google Search</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Responsive Search Ad</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Responsive Search Ads</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Só texto (sem imagem) — Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>N/A (texto)</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/7684791</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Video Action Campaigns</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; mín. 10 segundos. Texto — Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/12066387</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>Masthead ads</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Thumbnail</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Thumbnail (vídeo)</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>16:9: 1280x720 (mín. 1280x640)</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>JPG, GIF ou PNG</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Companion Banner</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Companion Banner</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>5:1: 300x60 (só em desktop)</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>&lt; 150 KB</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>JPG, GIF ou PNG</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -13007,7 +13007,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -17850,7 +17850,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -18192,7 +18192,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -18358,7 +18358,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Vídeo</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K351"/>
+  <dimension ref="A1:K345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Google Vídeo</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Google Vídeo</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Google Vídeo</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Google Vídeo</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -13609,7 +13609,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Google Vídeo</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Google Vídeo</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Google Vídeo</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -17446,52 +17446,52 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Skippable in-stream ads</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Vertical 4:5: 1200x1500 (mín. 320x400); Square 1:1: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1.91:1 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
@@ -17503,37 +17503,37 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Non-skippable in-stream ads</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+          <t>Horizontal 16:9, Vertical 9:16, Square 1:1; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -17548,7 +17548,7 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
@@ -17560,52 +17560,52 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Bumper ads</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5120 KB</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -17617,52 +17617,52 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>In-feed ads</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; 15 segundos recomendado. Texto — Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
+          <t>Logo quadrado 1:1: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal 4:1: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>1:1 ou 4:1</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5120 KB</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -17674,37 +17674,37 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Vertical Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Shorts ads</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>9:16 vertical: 1080x1920; 6 a 60 segundos</t>
+          <t>Horizontal 16:9, Square 1:1, Vertical 9:16; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>16:9 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -17731,52 +17731,52 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Masthead ads</t>
+          <t>Business Information (Logo)</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Logo 1:1: 1200x1200 (mín. 128x128)</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
@@ -17793,37 +17793,37 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Ad Assets</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Ad Assets (Imagens)</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Vertical 4:5: 1200x1500 (mín. 320x400); Square 1:1: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+          <t>Square 1:1: 1200x1200 (mín. 300x300), obrigatório; Horizontal 1.91:1: 1200x628 (mín. 600x314), opcional</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>1.91:1 ou 4:5 ou 1:1</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
@@ -17850,47 +17850,42 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Responsive Search Ad</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Responsive Search Ads</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Horizontal 16:9, Vertical 9:16, Square 1:1; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>Só texto (sem imagem) — Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>N/A (texto)</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>https://support.google.com/google-ads/answer/7684791</t>
         </is>
       </c>
     </row>
@@ -17907,47 +17902,47 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Video Action Campaigns</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; mín. 10 segundos. Texto — Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>5120 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/12066387</t>
         </is>
       </c>
     </row>
@@ -17964,47 +17959,47 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Thumbnail</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Thumbnail (vídeo)</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Logo quadrado 1:1: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal 4:1: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
+          <t>16:9: 1280x720 (mín. 1280x640)</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>1:1 ou 4:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>5120 KB</t>
+          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -18021,382 +18016,45 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Horizontal 16:9, Square 1:1, Vertical 9:16; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+          <t>5:1: 300x60 (só em desktop)</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>16:9 ou 1:1 ou 9:16</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>&lt; 150 KB</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>Logo</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>Business Information (Logo)</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>Logo 1:1: 1200x1200 (mín. 128x128)</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>não especificado</t>
-        </is>
-      </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>Ad Assets</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Ad Assets (Imagens)</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>Square 1:1: 1200x1200 (mín. 300x300), obrigatório; Horizontal 1.91:1: 1200x628 (mín. 600x314), opcional</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>não especificado</t>
-        </is>
-      </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>Responsive Search Ad</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>Responsive Search Ads</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>Só texto (sem imagem) — Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>N/A (texto)</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/7684791</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Google Vídeo</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>Video Action Campaigns</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; mín. 10 segundos. Texto — Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/12066387</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Google Vídeo</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>Thumbnail</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>Thumbnail (vídeo)</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>16:9: 1280x720 (mín. 1280x640)</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Google Vídeo</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>5:1: 300x60 (só em desktop)</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>&lt; 150 KB</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -11144,12 +11144,12 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>1080x1080 (1:1) ou 1080x1350 (4:5) recomendado; placement pode variar</t>
+          <t>FACEBOOK — Feed: 4:5, 1440x1800 (mín. 600px largura, mín. 750px altura), tolerância 3%, texto principal 50-150c, título 27c; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 125c, título 40c; Reels: 9:16, 1440x2560 (mín. 600x600px), tolerância 3%, texto principal 40c, título 55c. INSTAGRAM — Feed: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%, texto principal 125c, título 40c, máx. 30 hashtags; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 125c; Reels: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 44c; Explorar: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%, texto principal 125c, título 40c, máx. 30 hashtags.</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>1:1 ou 4:5</t>
+          <t>4:5 ou 9:16</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -11164,7 +11164,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -11201,12 +11201,12 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>1080x1920 (9:16) Stories/Reels; 1080x1350 (4:5) Feed recomendado</t>
+          <t>FACEBOOK — Feed: 4:5, 1440x1800 (mín. 120x120px), 1s a 241min, texto principal 50-150c, título 27c; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 3min, texto principal 125c, título 40c; Reels: 9:16 recomendado, 1440x2560, sem duração máxima, texto principal 40c, título 55c (sem legendas automáticas). INSTAGRAM — Feed: 9:16, 1080x1920 (mín. 250px largura), tolerância 1%, 1s a 60min, texto principal 125c, máx. 30 hashtags; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 60min, texto principal 125c; Reels: 9:16, 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s), texto principal 44c. Todos: compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>9:16 ou 4:5</t>
+          <t>4:5 ou 9:16</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -11216,12 +11216,12 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV ou GIF (Reels do Instagram: só MP4 ou MOV)</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -11030,27 +11030,27 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>1080x1080 recomendado (1:1); placement pode variar</t>
+          <t>FACEBOOK — Feed: 1:1, 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 3%, texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: 1:1 recomendado, 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px, texto principal 125c, título 40c, URL obrigatório; Reels: 9:16, 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px, tolerância 1%, texto principal 40c. INSTAGRAM — Feed: 4:5 (carrosséis só de imagem) ou 1:1 (se tiver vídeo), 1080x1080 mín., 2 a 10 cartões, tolerância 1%, texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: 9:16, 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 1%, texto principal 125c, título 40c, URL obrigatório; Reels: 9:16, 1080x1080 mín. (só imagem), 2 a 10 cartões, tolerância 1%.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1 ou 4:5 ou 9:16</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Imagem 30 MB; vídeo 4 GB</t>
+          <t>Imagem: 30 MB por cartão (todos os placements). Vídeo (só Feed do Facebook e Instagram, e Stories do Instagram): 4 GB por cartão; duração — Feed Facebook 1s-240min, Feed Instagram 1s-2min, Stories Instagram 1s-15s.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>JPG/PNG ou MP4/MOV por cartão</t>
+          <t>JPG ou PNG (todos os placements); MP4/MOV/GIF também aceite em Feed Facebook, Feed Instagram e Stories Instagram</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K345"/>
+  <dimension ref="A1:K349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -11010,12 +11010,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11025,32 +11025,32 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>FACEBOOK — Feed: 1:1, 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 3%, texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: 1:1 recomendado, 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px, texto principal 125c, título 40c, URL obrigatório; Reels: 9:16, 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px, tolerância 1%, texto principal 40c. INSTAGRAM — Feed: 4:5 (carrosséis só de imagem) ou 1:1 (se tiver vídeo), 1080x1080 mín., 2 a 10 cartões, tolerância 1%, texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: 9:16, 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 1%, texto principal 125c, título 40c, URL obrigatório; Reels: 9:16, 1080x1080 mín. (só imagem), 2 a 10 cartões, tolerância 1%.</t>
+          <t>1:1 ou 2:3; 1000x1000 / 1000x1500 recomendado</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>1:1 ou 4:5 ou 9:16</t>
+          <t>1:1 ou 2:3</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB por cartão (todos os placements). Vídeo (só Feed do Facebook e Instagram, e Stories do Instagram): 4 GB por cartão; duração — Feed Facebook 1s-240min, Feed Instagram 1s-2min, Stories Instagram 1s-15s.</t>
+          <t>20 MB por imagem</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>JPG ou PNG (todos os placements); MP4/MOV/GIF também aceite em Feed Facebook, Feed Instagram e Stories Instagram</t>
+          <t>PNG, JPEG; 2–5 imagens (non-Sales)</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -11067,12 +11067,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11087,27 +11087,22 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>1080x1080 recomendado; capa pode ser imagem ou vídeo</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>Hero 1:1 ou 2:3; assets secundários via catálogo</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Imagem 30 MB; vídeo 4 GB</t>
+          <t>Imagem 20 MB; vídeo até 2 GB</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>JPG/PNG ou MP4/MOV + catálogo/Instant Experience</t>
+          <t>PNG, JPEG, MP4/MOV/M4V + catálogo</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11119,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -11139,32 +11134,32 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Image Pin</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>FACEBOOK — Feed: 4:5, 1440x1800 (mín. 600px largura, mín. 750px altura), tolerância 3%, texto principal 50-150c, título 27c; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 125c, título 40c; Reels: 9:16, 1440x2560 (mín. 600x600px), tolerância 3%, texto principal 40c, título 55c. INSTAGRAM — Feed: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%, texto principal 125c, título 40c, máx. 30 hashtags; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 125c; Reels: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 44c; Explorar: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%, texto principal 125c, título 40c, máx. 30 hashtags.</t>
+          <t>1000x1500 recomendado (2:3)</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>4:5 ou 9:16</t>
+          <t>2:3</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>30 MB</t>
+          <t>20 MB</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>PNG, JPEG</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -11181,12 +11176,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -11196,32 +11191,32 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>FACEBOOK — Feed: 4:5, 1440x1800 (mín. 120x120px), 1s a 241min, texto principal 50-150c, título 27c; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 3min, texto principal 125c, título 40c; Reels: 9:16 recomendado, 1440x2560, sem duração máxima, texto principal 40c, título 55c (sem legendas automáticas). INSTAGRAM — Feed: 9:16, 1080x1920 (mín. 250px largura), tolerância 1%, 1s a 60min, texto principal 125c, máx. 30 hashtags; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 60min, texto principal 125c; Reels: 9:16, 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s), texto principal 44c. Todos: compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>1000x1500 (2:3), 1080x1920 (9:16) ou square conforme placement</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>4:5 ou 9:16</t>
+          <t>2:3 ou 9:16</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>2 GB</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF (Reels do Instagram: só MP4 ou MOV)</t>
+          <t>MP4, MOV, M4V</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -11238,12 +11233,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11258,27 +11253,27 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>1:1 ou 2:3; 1000x1000 / 1000x1500 recomendado</t>
+          <t>2–6 cartões; 1080x1080 recomendado</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>1:1 ou 2:3</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>20 MB por imagem</t>
+          <t>20 MB por imagem; GIF 3 MB</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PNG, JPEG; 2–5 imagens (non-Sales)</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://www.business.reddit.com/advertise/ad-types/carousel-ads</t>
         </is>
       </c>
     </row>
@@ -11295,42 +11290,47 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Free-form Ad</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hero 1:1 ou 2:3; assets secundários via catálogo</t>
+          <t>Imagem: 1200x1200 (1:1) ou 1920x1080/1440x1080; vídeo conforme asset</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Imagem 20 MB; vídeo até 2 GB</t>
+          <t>Imagem ≤20 MB; vídeo ≤1 GB</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>PNG, JPEG, MP4/MOV/M4V + catálogo</t>
+          <t>JPG, PNG, GIF, MP4, MOV + rich text</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://www.business.reddit.com/advertise/ad-types/free-form</t>
         </is>
       </c>
     </row>
@@ -11347,12 +11347,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -11362,32 +11362,32 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Image Pin</t>
+          <t>Image Ad</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>1000x1500 recomendado (2:3)</t>
+          <t>1080x1080 (1:1); 1080x1350 (4:5); 1440x1080 (4:3); 1920x1080 (16:9)</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>1:1 ou 4:5 ou 4:3 ou 16:9</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>20 MB</t>
+          <t>3 MB</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>PNG, JPEG</t>
+          <t>JPG, PNG, GIF (estático)</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://www.business.reddit.com/learning-hub/articles/reddit-image-ad-specs</t>
         </is>
       </c>
     </row>
@@ -11404,47 +11404,42 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Catalog Ad</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Product Ad</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>1000x1500 (2:3), 1080x1920 (9:16) ou square conforme placement</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>2:3 ou 9:16</t>
+          <t>Depende do asset do catálogo/underlying ad type</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2 GB</t>
+          <t>Depende do asset</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>MP4, MOV, M4V</t>
+          <t>Catálogo de produtos + JPG/PNG ou vídeo conforme configuração</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://www.business.reddit.com/advertise/ad-types</t>
         </is>
       </c>
     </row>
@@ -11471,37 +11466,32 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Carousel Ad</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2–6 cartões; 1080x1080 recomendado</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>1:1 / 4:5 / 16:9; 1080p recomendado</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>20 MB por imagem; GIF 3 MB</t>
+          <t>1 GB</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/carousel-ads</t>
+          <t>https://www.business.reddit.com/advertise/ad-types/video-ads</t>
         </is>
       </c>
     </row>
@@ -11518,47 +11508,42 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Free-form Ad</t>
+          <t>AR Lenses Filters</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Imagem: 1200x1200 (1:1) ou 1920x1080/1440x1080; vídeo conforme asset</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>Filter estático 945x2048; animado 720x1560</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Imagem ≤20 MB; vídeo ≤1 GB</t>
+          <t>Varia por asset AR</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF, MP4, MOV + rich text</t>
+          <t>PNG (filtro estático), GIF (animado); Lens assets conforme Lens Studio</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/free-form</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -11575,47 +11560,47 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Image Ad</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>1080x1080 (1:1); 1080x1350 (4:5); 1440x1080 (4:3); 1920x1080 (16:9)</t>
+          <t>720x1280 (9:16) por asset recomendado</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>1:1 ou 4:5 ou 4:3 ou 16:9</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>3 MB</t>
+          <t>Varia por asset</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (estático)</t>
+          <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/learning-hub/articles/reddit-image-ad-specs</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -11632,42 +11617,47 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Catalog Ad</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Product Ad</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Depende do asset do catálogo/underlying ad type</t>
+          <t>720x1280 (9:16)</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Depende do asset</t>
+          <t>Varia por asset</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Catálogo de produtos + JPG/PNG ou vídeo conforme configuração</t>
+          <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -11684,12 +11674,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -11699,27 +11689,32 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Commercial Ad</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>1:1 / 4:5 / 16:9; 1080p recomendado</t>
+          <t>720x1280 (9:16)</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (H.264)</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/video-ads</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -11746,27 +11741,32 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Branded Effects</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>AR Lenses Filters</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Filter estático 945x2048; animado 720x1560</t>
+          <t>720x1280 (9:16)</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Varia por asset AR</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>PNG (filtro estático), GIF (animado); Lens assets conforme Lens Studio</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -11798,17 +11798,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>720x1280 (9:16) por asset recomendado</t>
+          <t>720x1280 (9:16)</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
+          <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -11902,47 +11902,47 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Commercial Ad</t>
+          <t>Branded Effect</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>Ícone 162x162 (safe 144x144); restantes assets conforme template</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Ícone &lt;60 KB; restantes conforme template</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>MP4, MOV (H.264)</t>
+          <t>PNG + assets de efeito conforme template</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
         </is>
       </c>
     </row>
@@ -11959,47 +11959,42 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Branded Mission</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Criativo final segue In-Feed/Spark Ads (vertical 9:16 recomendado)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>Vídeo de creator elegível / Spark Ads</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12016,47 +12011,47 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel Ads</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1.91:1 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>100 KB sugerido por imagem; música até 10 MB</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG/JPEG, PNG + MP3</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12073,27 +12068,27 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>In-Feed (Standard Feed)</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>Vertical 9:16 recomendado; ≥540x960 recomendado</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -12103,17 +12098,17 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>Até 500 MB (reservation); limites podem variar em auction</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV</t>
+          <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12140,37 +12135,32 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Branded Effects</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Branded Effect</t>
+          <t>Pulse</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Ícone 162x162 (safe 144x144); restantes assets conforme template</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Ícone &lt;60 KB; restantes conforme template</t>
+          <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>PNG + assets de efeito conforme template</t>
+          <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
+          <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
         </is>
       </c>
     </row>
@@ -12197,32 +12187,37 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Branded Mission</t>
+          <t>Spark Ads</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Criativo final segue In-Feed/Spark Ads (vertical 9:16 recomendado)</t>
+          <t>Usa vídeo orgânico; para push, 9:16 ≥540x960 recomendado</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Conforme vídeo In-Feed/Spark</t>
+          <t>Até 500 MB para push</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Vídeo de creator elegível / Spark Ads</t>
+          <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12249,37 +12244,32 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Carousel Ads</t>
+          <t>Top Feed</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>1.91:1 ou 1:1 ou 9:16</t>
+          <t>Segue criativo In-Feed; vertical 9:16 recomendado</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>100 KB sugerido por imagem; música até 10 MB</t>
+          <t>Conforme In-Feed</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>JPG/JPEG, PNG + MP3</t>
+          <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12311,12 +12301,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>In-Feed (Standard Feed)</t>
+          <t>TopView</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Vertical 9:16 recomendado; ≥540x960 recomendado</t>
+          <t>9:16; ≥540x960</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -12326,7 +12316,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Até 500 MB (reservation); limites podem variar em auction</t>
+          <t>500 MB</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -12353,42 +12343,42 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Pulse</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
+          <t>16:9 recomendado; vídeo HD</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Conforme vídeo In-Feed/Spark</t>
+          <t>1 GB recomendado/limite conforme placement</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>MP4, MOV / Spark Ads</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12405,47 +12395,47 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Spark Ads</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Usa vídeo orgânico; para push, 9:16 ≥540x960 recomendado</t>
+          <t>800x800 (1:1) ou 800x418 (1.91:1) recomendado</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Até 500 MB para push</t>
+          <t>5 MB por imagem; vídeo conforme specs</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
+          <t>JPG, PNG; MP4/MOV para video carousel</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12462,42 +12452,47 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Top Feed</t>
+          <t>Collection Ad</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Segue criativo In-Feed; vertical 9:16 recomendado</t>
+          <t>Hero 800x800 (1:1) recomendado + thumbnails de produtos</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Conforme In-Feed</t>
+          <t>5 MB por imagem</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>MP4, MOV / Spark Ads</t>
+          <t>JPG, PNG + catálogo</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12514,47 +12509,42 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Catalog Ad</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>TopView</t>
+          <t>Dynamic Product Ads</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>9:16; ≥540x960</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Assets provenientes do catálogo; 1:1 recomendado</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>500 MB</t>
+          <t>Conforme catálogo</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>MP4, MOV, MPEG, 3GP</t>
+          <t>Feed/catálogo + JPG/PNG</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12581,27 +12571,32 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Image Ad</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>16:9 recomendado; vídeo HD</t>
+          <t>1200x1200 (1:1) ou 1200x628 (1.91:1) recomendado</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>1 GB recomendado/limite conforme placement</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -12633,32 +12628,27 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Carousel Ad</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>800x800 (1:1) ou 800x418 (1.91:1) recomendado</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>Depende do produto (Timeline/Trend Takeover); assets conforme ficha X</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>5 MB por imagem; vídeo conforme specs</t>
+          <t>Conforme formato</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>JPG, PNG; MP4/MOV para video carousel</t>
+          <t>JPG, PNG, MP4/MOV conforme takeover</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -12690,32 +12680,27 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Collection Ad</t>
+          <t>Text Ad</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hero 800x800 (1:1) recomendado + thumbnails de produtos</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>Sem asset gráfico obrigatório</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>5 MB por imagem</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>JPG, PNG + catálogo</t>
+          <t>Texto/post + URL opcional</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -12747,27 +12732,32 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Catalog Ad</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Dynamic Product Ads</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Assets provenientes do catálogo; 1:1 recomendado</t>
+          <t>1200x1200 (1:1) ou 1920x1080 (16:9) recomendado</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>1:1 ou 16:9</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Conforme catálogo</t>
+          <t>1 GB</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Feed/catálogo + JPG/PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -12784,52 +12774,47 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Image Ad</t>
+          <t>Medium Rectangle</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>1200x1200 (1:1) ou 1200x628 (1.91:1) recomendado</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -12841,47 +12826,47 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Large Rectangle</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Depende do produto (Timeline/Trend Takeover); assets conforme ficha X</t>
+          <t>336x280</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Conforme formato</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4/MOV conforme takeover</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -12893,47 +12878,47 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Text Ad</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Sem asset gráfico obrigatório</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Texto/post + URL opcional</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -12945,52 +12930,52 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Half Page</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>1200x1200 (1:1) ou 1920x1080 (16:9) recomendado</t>
+          <t>300x600</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>1:1 ou 16:9</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13017,22 +13002,22 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Medium Rectangle</t>
+          <t>Mobile Banner</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>320x50</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -13069,27 +13054,32 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Large Rectangle</t>
+          <t>Responsive Display Ads (imagem)</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>336x280</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 600x600 (mín. 300x300); Logo 1:1: 1200x1200 (mín. 128x128, opcional); Logo 4:1: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal 16:9, Square 1:1, Vertical 2:3; qualquer duração (recomendado 30s).</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 4:1</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -13121,27 +13111,32 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>HTML5 Display</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>150 KB (dentro do HTML5)</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>ZIP HTML5</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -13163,47 +13158,47 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Half Page</t>
+          <t>Skippable In-Stream</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13220,42 +13215,47 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Mobile Banner</t>
+          <t>Non-skippable In-Stream (standard)</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>320x50</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13272,47 +13272,47 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Responsive Display Ads (imagem)</t>
+          <t>Bumper</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 600x600 (mín. 300x300); Logo 1:1: 1200x1200 (mín. 128x128, opcional); Logo 4:1: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal 16:9, Square 1:1, Vertical 2:3; qualquer duração (recomendado 30s).</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13329,47 +13329,42 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>HTML5 Display</t>
+          <t>Non-skippable 30s (Connected TV)</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>150 KB (dentro do HTML5)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>ZIP HTML5</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13396,32 +13391,32 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Skippable In-Stream</t>
+          <t>In-Feed Video Ad (ex-Discovery)</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; 15 segundos recomendado. Texto — Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -13453,22 +13448,22 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Non-skippable In-Stream (standard)</t>
+          <t>YouTube Shorts Ads</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+          <t>9:16 vertical: 1080x1920; 6 a 60 segundos</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -13483,7 +13478,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13510,17 +13505,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Bumper</t>
+          <t>Masthead</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -13540,7 +13535,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13557,42 +13552,47 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Non-skippable 30s (Connected TV)</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Logo 1:1: 1200x1200 (mín. 144x144); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional)</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -13609,32 +13609,27 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>In-Feed Video Ad (ex-Discovery)</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; 15 segundos recomendado. Texto — Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>Horizontal 16:9, Vertical 9:16 ou 4:5, Square 1:1; 10 a 60 segundos (opcional)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -13649,7 +13644,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -13666,265 +13661,180 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Vertical Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>YouTube Shorts Ads</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>9:16 vertical: 1080x1920; 6 a 60 segundos</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>2 a 10 cartões, todos com a mesma proporção (1:1 ou 1.91:1); cada cartão com título até 40 caracteres</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB por imagem</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
     <row r="256" ht="25" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>Open Door</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Masthead</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - App Install</t>
         </is>
       </c>
     </row>
     <row r="257" ht="25" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>Single Image</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Prog - Audio Ad</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Logo 1:1: 1200x1200 (mín. 144x144); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional)</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (não animado)</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>MP3</t>
         </is>
       </c>
     </row>
     <row r="258" ht="25" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Single Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Horizontal 16:9, Vertical 9:16 ou 4:5, Square 1:1; 10 a 60 segundos (opcional)</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>Prog - Audio Ingame</t>
         </is>
       </c>
     </row>
     <row r="259" ht="25" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>Carousel</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Prog - Banner</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2 a 10 cartões, todos com a mesma proporção (1:1 ou 1.91:1); cada cartão com título até 40 caracteres</t>
+          <t>300x250, 300x600, 728x90, 320x50</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>5 MB por imagem</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
     </row>
@@ -13951,7 +13861,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Prog - App Install</t>
+          <t>Prog - Banner Ingame</t>
         </is>
       </c>
     </row>
@@ -13978,22 +13888,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Prog - Audio Ad</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>1 MB</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>MP3</t>
+          <t>Prog - Banner Mobile</t>
         </is>
       </c>
     </row>
@@ -14020,7 +13915,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Prog - Audio Ingame</t>
+          <t>Prog - Conversational Display</t>
         </is>
       </c>
     </row>
@@ -14047,22 +13942,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Prog - Banner</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>300x250, 300x600, 728x90, 320x50</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>Prog - Demand Gen</t>
         </is>
       </c>
     </row>
@@ -14084,12 +13964,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>DOOH</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Prog - Banner Ingame</t>
+          <t>Prog - DOOH</t>
         </is>
       </c>
     </row>
@@ -14116,7 +13996,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Prog - Banner Mobile</t>
+          <t>Prog - Expositor</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14023,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Prog - Conversational Display</t>
+          <t>Prog - In Content</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14050,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Prog - Demand Gen</t>
+          <t>Prog - inRead Carousel</t>
         </is>
       </c>
     </row>
@@ -14192,12 +14072,42 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>DOOH</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Prog - DOOH</t>
+          <t>Prog - YouTube Masthead</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14134,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Prog - Expositor</t>
+          <t>Prog - M-Rec</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>300x250</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14166,32 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Prog - In Content</t>
+          <t>Prog - Native Ad</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
         </is>
       </c>
     </row>
@@ -14278,7 +14218,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Prog - inRead Carousel</t>
+          <t>Prog - Rewarded Video</t>
         </is>
       </c>
     </row>
@@ -14300,42 +14240,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>Open Door</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Prog - YouTube Masthead</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - Rich Media</t>
         </is>
       </c>
     </row>
@@ -14357,17 +14267,42 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Prog - M-Rec</t>
+          <t>Prog - YouTube Select</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14389,37 +14324,42 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Prog - Native Ad</t>
+          <t>Prog - YouTube VRC Ad Sequence</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14386,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Prog - Rewarded Video</t>
+          <t>Prog - Skyscraper</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14413,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Prog - Rich Media</t>
+          <t>Prog - Social Display</t>
         </is>
       </c>
     </row>
@@ -14505,17 +14445,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Prog - YouTube Select</t>
+          <t>Prog - YouTube VRC Non-Skippable</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -14525,12 +14460,12 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14552,42 +14487,32 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Ad Sequence</t>
+          <t>Prog - Uber Journey Ad</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1 ou 3:4</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Display: imagens. Video: MP4.</t>
         </is>
       </c>
     </row>
@@ -14609,12 +14534,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Prog - Skyscraper</t>
+          <t>Prog - Spotify Video Takeover</t>
         </is>
       </c>
     </row>
@@ -14641,7 +14566,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Prog - Social Display</t>
+          <t>Prog - Wallpaper</t>
         </is>
       </c>
     </row>
@@ -14673,12 +14598,17 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Non-Skippable</t>
+          <t>Prog - YouTube VVC</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14688,12 +14618,12 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14715,32 +14645,37 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Prog - Uber Journey Ad</t>
+          <t>Prog - YouTube VRC Efficient Reach</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>1:1 ou 3:4</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal 16:9: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical 9:16: 1080x1920, 6 a 60 segundos (Shorts); Square 1:1: 1080x1080, 6 a 60 segundos.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Display: imagens. Video: MP4.</t>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14762,12 +14697,37 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Prog - Spotify Video Takeover</t>
+          <t>Prog - YouTube VRC Target Frequency</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal 16:9: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14789,12 +14749,37 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Prog - Wallpaper</t>
+          <t>Prog - Billboard (Impresa)</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>970x250, 320x10</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>200 KB</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
       </c>
     </row>
@@ -14816,42 +14801,37 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Prog - YouTube VVC</t>
+          <t>Prog - Billboard (Media Capital)</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>980x250 ou 970x250</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
       </c>
     </row>
@@ -14873,37 +14853,37 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Efficient Reach</t>
+          <t>Prog - Billboard (Observador)</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal 16:9: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical 9:16: 1080x1920, 6 a 60 segundos (Shorts); Square 1:1: 1080x1080, 6 a 60 segundos.</t>
+          <t>1200x220, 970x250</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
       </c>
     </row>
@@ -14925,37 +14905,37 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Target Frequency</t>
+          <t>Prog - Billboard (Público)</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal 16:9: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14957,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -14987,12 +14967,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Impresa)</t>
+          <t>Prog - Billboard (Sapo)</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>970x250, 320x10</t>
+          <t>970x250</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -15000,14 +14980,9 @@
           <t>200 KB</t>
         </is>
       </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
       </c>
     </row>
@@ -15029,37 +15004,42 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Media Capital)</t>
+          <t>Prog - Half-Page (Impresa)</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>980x250 ou 970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15081,37 +15061,42 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Observador)</t>
+          <t>Prog - Half-Page (Media Capital)</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>1200x220, 970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/manchete-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
       </c>
     </row>
@@ -15133,37 +15118,42 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Público)</t>
+          <t>Prog - Half-Page (Media Livre)</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>80 KB / 2 MB</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
       </c>
     </row>
@@ -15185,32 +15175,42 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Sapo)</t>
+          <t>Prog - Half-Page (Observador)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>100 KB / 2 MB</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
+          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Impresa)</t>
+          <t>Prog - Half-Page (Público)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -15257,17 +15257,17 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Capital)</t>
+          <t>Prog - Half-Page (Sapo)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -15314,17 +15314,17 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB / 3.5 MB</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Livre)</t>
+          <t>Prog - Half-Page (Google)</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -15371,17 +15371,17 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>80 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF / MP4</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -15403,42 +15403,32 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Observador)</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>Prog - Header XL (Impresa)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>100 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
       </c>
     </row>
@@ -15460,42 +15450,37 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Público)</t>
+          <t>Prog - Header XL (Media Livre)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
       </c>
     </row>
@@ -15517,42 +15502,37 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Sapo)</t>
+          <t>Prog - Header XL (Observador)</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>200 KB / 3.5 MB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
+          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15574,42 +15554,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Google)</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>JPG, PNG, GIF</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>Prog - Header XL (Sapo)</t>
         </is>
       </c>
     </row>
@@ -15636,12 +15591,22 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Impresa)</t>
+          <t>Prog - Intro (Impresa)</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>600x400, 320x480</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>3:2 ou 2:3</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -15651,12 +15616,12 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>JPG ou PNG</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -15678,22 +15643,27 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Media Livre)</t>
+          <t>Prog - Intro (Media Capital)</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
+          <t>800x600</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>4:3</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -15703,12 +15673,12 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
+          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
       </c>
     </row>
@@ -15730,37 +15700,42 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Observador)</t>
+          <t>Prog - Intro (Media Livre)</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
+          <t>800x600, 768x1024</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>500 KB</t>
+          <t>120 KB / 1 MB</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
       </c>
     </row>
@@ -15782,17 +15757,37 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Sapo)</t>
+          <t>Prog - Intro (Observador)</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>990x600, 300x480</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>120 KB, 75 KB / 2 MB</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF / HTML</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15809,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -15824,32 +15819,32 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Prog - Intro (Impresa)</t>
+          <t>Prog - Intro (Público)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>600x400, 320x480</t>
+          <t>800x600, 768x1024</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>3:2 ou 2:3</t>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -15871,7 +15866,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -15881,32 +15876,32 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Capital)</t>
+          <t>Prog - Intro (Sapo)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>800x600</t>
+          <t>800x600px (600x400px recomendado)</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>4:3</t>
+          <t>4:3 ou 3:2</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
       </c>
     </row>
@@ -15928,42 +15923,37 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Livre)</t>
+          <t>Prog - Leaderboard (Media Capital)</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>120 KB / 1 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
+          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -15985,37 +15975,37 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Prog - Intro (Observador)</t>
+          <t>Prog - Leaderboard (Media Livre)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>990x600, 300x480</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>120 KB, 75 KB / 2 MB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -16042,37 +16032,32 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Prog - Intro (Público)</t>
+          <t>Prog - Leaderboard (Público)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
+          <t>1140x50</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
       </c>
     </row>
@@ -16099,22 +16084,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Prog - Intro (Sapo)</t>
+          <t>Prog - Leaderboard (Sapo)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>800x600px (600x400px recomendado)</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:2</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -16124,12 +16104,12 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>WEBP</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16131,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -16161,7 +16141,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Capital)</t>
+          <t>Prog - Leaderboard (Google)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -16176,12 +16156,12 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -16203,37 +16183,42 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Livre)</t>
+          <t>Prog - Open Door (Impresa)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>1920x1080, 680x1520</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>200 KB, 150 KB</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16255,37 +16240,42 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Público)</t>
+          <t>Prog - Open Door (Media Capital)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>1140x50</t>
+          <t>1920x1080, 680x1520</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
+          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
       </c>
     </row>
@@ -16307,37 +16297,42 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Sapo)</t>
+          <t>Prog - Open Door (Media Livre)</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>950x700, 390x850 / 640x360</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>500 KB / 2 MB</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>WEBP</t>
+          <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
       </c>
     </row>
@@ -16359,37 +16354,32 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Google)</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>728x90</t>
+          <t>Prog - Open Door (Observador)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Máxima resolução</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16411,7 +16401,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -16421,32 +16411,27 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Impresa)</t>
+          <t>Prog - Open Door (Público)</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>1920x1080, 680x1520</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>800x900</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>200 KB, 150 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>JPG / Video</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16453,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -16478,12 +16463,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Capital)</t>
+          <t>Prog - Open Door (Google)</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>1920x1080, 680x1520</t>
+          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -16493,17 +16478,17 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -16525,42 +16510,42 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Parallax</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Livre)</t>
+          <t>Prog - Parallax (Público)</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>950x700, 390x850 / 640x360</t>
+          <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>500 KB / 2 MB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG / MP4</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
       </c>
     </row>
@@ -16582,32 +16567,32 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Observador)</t>
+          <t>Prog - Peel off (Media Capital)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Máxima resolução</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>Imagens</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
       </c>
     </row>
@@ -16629,37 +16614,37 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Público)</t>
+          <t>Prog - Peel off (Media Livre)</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>800x900</t>
+          <t>200x200, 850x650</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>JPG / Video</t>
+          <t>260 KB</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
       </c>
     </row>
@@ -16681,42 +16666,42 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Google)</t>
+          <t>Prog - Peel off (Observador)</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>200x200, 850x650px</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16738,42 +16723,42 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Parallax</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Prog - Parallax (Público)</t>
+          <t>Prog - Pre-Roll (Media Capital)</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
+          <t>1280x720</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>6 MB</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
+          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -16795,32 +16780,42 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Capital)</t>
+          <t>Prog - Pre-Roll (Media Livre)</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>640x360</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>15 MB</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Imagens</t>
+          <t>MP4 ou FLV</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -16842,37 +16837,42 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Livre)</t>
+          <t>Prog - Pre-Roll (Observador)</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>200x200, 850x650</t>
+          <t>640x360</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>260 KB</t>
+          <t>10 MB</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>MP4</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
+          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16894,42 +16894,42 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Observador)</t>
+          <t>Prog - Pre-Roll (Público)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>200x200, 850x650px</t>
+          <t>640x360px com rácio de 16:9</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>MP4 ou WEBM</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
       </c>
     </row>
@@ -16951,7 +16951,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Capital)</t>
+          <t>Prog - Pre-Roll (Sapo)</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>1280x720</t>
+          <t>640x360px (16:9)</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>6 MB</t>
+          <t>3.5 MB</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
       </c>
     </row>
@@ -17008,42 +17008,37 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Livre)</t>
+          <t>Prog - Takeover (Media Capital)</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>640x360</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>650x350</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>15 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>MP4 ou FLV</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
+          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
       </c>
     </row>
@@ -17065,42 +17060,37 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Observador)</t>
+          <t>Prog - Takeover (Público)</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>640x360</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
       </c>
     </row>
@@ -17122,42 +17112,17 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Público)</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>640x360px com rácio de 16:9</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>10 MB</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>MP4 ou WEBM</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
+          <t>Prog - Connected TV (Sapo)</t>
         </is>
       </c>
     </row>
@@ -17179,42 +17144,37 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Sapo)</t>
+          <t>Prog - Connected TV (Google)</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>640x360px (16:9)</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>3.5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -17236,205 +17196,245 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Media Capital)</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>650x350</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
+          <t>Prog - CTV First Screen (Sapo)</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Público)</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Vertical 4:5: 1200x1500 (mín. 320x400); Square 1:1: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>500 KB</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / Video para a área expandida</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Sapo)</t>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Horizontal 16:9, Vertical 9:16, Square 1:1; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Google)</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
+          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5120 KB</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Prog - CTV First Screen (Sapo)</t>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Logo quadrado 1:1: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal 4:1: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>1:1 ou 4:1</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>5120 KB</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -17451,47 +17451,47 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Vertical 4:5: 1200x1500 (mín. 320x400); Square 1:1: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+          <t>Horizontal 16:9, Square 1:1, Vertical 9:16; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>1.91:1 ou 4:5 ou 1:1</t>
+          <t>16:9 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -17508,47 +17508,47 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Business Information (Logo)</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Horizontal 16:9, Vertical 9:16, Square 1:1; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+          <t>Logo 1:1: 1200x1200 (mín. 128x128)</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
@@ -17565,37 +17565,37 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Ad Assets</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Ad Assets (Imagens)</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+          <t>Square 1:1: 1200x1200 (mín. 300x300), obrigatório; Horizontal 1.91:1: 1200x628 (mín. 600x314), opcional</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>5120 KB</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
@@ -17622,47 +17622,42 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Responsive Search Ad</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Responsive Search Ads</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Logo quadrado 1:1: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal 4:1: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>1:1 ou 4:1</t>
+          <t>Só texto (sem imagem) — Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>5120 KB</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>N/A (texto)</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/7684791</t>
         </is>
       </c>
     </row>
@@ -17679,32 +17674,32 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Video Action Campaigns</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Horizontal 16:9, Square 1:1, Vertical 9:16; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; mín. 10 segundos. Texto — Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>16:9 ou 1:1 ou 9:16</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -17719,7 +17714,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/12066387</t>
         </is>
       </c>
     </row>
@@ -17736,47 +17731,47 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Thumbnail</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Business Information (Logo)</t>
+          <t>Thumbnail (vídeo)</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Logo 1:1: 1200x1200 (mín. 128x128)</t>
+          <t>16:9: 1280x720 (mín. 1280x640)</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>não especificado</t>
+          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -17793,47 +17788,47 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Ad Assets</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Ad Assets (Imagens)</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Square 1:1: 1200x1200 (mín. 300x300), obrigatório; Horizontal 1.91:1: 1200x628 (mín. 600x314), opcional</t>
+          <t>5:1: 300x60 (só em desktop)</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>não especificado</t>
+          <t>&lt; 150 KB</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -17845,47 +17840,52 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Responsive Search Ad</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Responsive Search Ads</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Só texto (sem imagem) — Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+          <t>Feed: 4:5, 1440x1800 (mín. 600px largura, mín. 750px altura), tolerância 3%, texto principal 50-150c, título 27c; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 125c, título 40c; Reels: 9:16, 1440x2560 (mín. 600x600px), tolerância 3%, texto principal 40c, título 55c.</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>4:5 ou 9:16</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>30 MB</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>N/A (texto)</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/7684791</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -17897,52 +17897,52 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Video Action Campaigns</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; mín. 10 segundos. Texto — Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
+          <t>Feed: 4:5, 1440x1800 (mín. 120x120px), 1s a 241min, texto principal 50-150c, título 27c; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 3min, texto principal 125c, título 40c; Reels: 9:16 recomendado, 1440x2560, sem duração máxima, texto principal 40c, título 55c (sem legendas automáticas). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>4:5 ou 9:16</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12066387</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -17954,52 +17954,52 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Thumbnail</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Thumbnail (vídeo)</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>16:9: 1280x720 (mín. 1280x640)</t>
+          <t>Feed: 1:1, 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 3%, texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: 1:1 recomendado, 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px, texto principal 125c, título 40c, URL obrigatório; Reels: 9:16, 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px, tolerância 1%, texto principal 40c.</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
+          <t>Imagem: 30 MB por cartão</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -18011,52 +18011,280 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>5:1: 300x60 (só em desktop)</t>
+          <t>Feed: 1.91:1 até 1:1, 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto; Experiência Instantânea obrigatória; texto principal 125c, título 40c, URL obrigatório; Reels: 9:16 até 1:1, 1080x1080 mín.; requer Catálogo Advantage+ como fonte de conteúdo; texto principal 72c, título 10c, URL obrigatório; Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>1.91:1 até 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>&lt; 150 KB</t>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG, PNG, MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Single Image</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Single Image</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Feed: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%, texto principal 125c, título 40c, máx. 30 hashtags; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 125c; Reels: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 44c; Explorar: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%, texto principal 125c, título 40c, máx. 30 hashtags.</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>4:5 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>30 MB</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Single Video</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Single Video</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Feed: 9:16, 1080x1920 (mín. 250px largura), tolerância 1%, 1s a 60min, texto principal 125c, máx. 30 hashtags; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 60min, texto principal 125c; Reels: 9:16, 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s), texto principal 44c. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>4 GB</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV)</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Feed: 4:5 (carrosséis só de imagem) ou 1:1 (se tiver vídeo), 1080x1080 mín., 2 a 10 cartões, tolerância 1%, texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: 9:16, 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 1%, texto principal 125c, título 40c, URL obrigatório; Reels: 9:16, 1080x1080 mín. (só imagem), 2 a 10 cartões, tolerância 1%.</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>4:5 ou 1:1 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Imagem: 30 MB por cartão</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Feed: 1.91:1 até 1:1, 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto; Experiência Instantânea obrigatória; texto principal 125c, título 40c, URL obrigatório; Stories: 1.91:1 até 1:1, 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto; Experiência Instantânea obrigatória; texto principal 125c, URL obrigatório; Reels: 9:16 (imagem de produto 1:1), mín. 500x888, capa + até 3 imagens de produto; Experiência Instantânea obrigatória.</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>1.91:1 até 1:1 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>JPG, PNG, MP4 ou MOV</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K349"/>
+  <dimension ref="A1:L349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -513,6 +513,11 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Copies</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Link</t>
         </is>
       </c>
@@ -563,7 +568,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
@@ -615,7 +620,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/cube.html</t>
         </is>
@@ -667,7 +672,7 @@
           <t>GIF, JPEG ou PNG</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/floorad.html</t>
         </is>
@@ -724,7 +729,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
@@ -771,7 +776,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
@@ -823,7 +828,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/hero.html</t>
         </is>
@@ -880,7 +885,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/in-article.html</t>
         </is>
@@ -937,7 +942,7 @@
           <t>HTML, JPG ou GIF</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/interscroller.html</t>
         </is>
@@ -994,7 +999,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
@@ -1046,7 +1051,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/mrec.html</t>
         </is>
@@ -1098,7 +1103,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/mrec_video.html</t>
         </is>
@@ -1155,7 +1160,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/pushdown.html</t>
         </is>
@@ -1212,7 +1217,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
@@ -1269,7 +1274,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/video-instream.html</t>
         </is>
@@ -1326,7 +1331,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/video-outstream.html</t>
         </is>
@@ -1378,7 +1383,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
@@ -1435,7 +1440,7 @@
           <t>PNG</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/billboard-xl/</t>
         </is>
@@ -1492,7 +1497,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/carrossel-incontent/</t>
         </is>
@@ -1549,7 +1554,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/carrossel-top/</t>
         </is>
@@ -1606,7 +1611,7 @@
           <t>JPEG</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/dossier/</t>
         </is>
@@ -1663,7 +1668,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/full-frame/</t>
         </is>
@@ -1720,7 +1725,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
@@ -1777,7 +1782,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/interscroller/</t>
         </is>
@@ -1834,7 +1839,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
@@ -1886,7 +1891,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/intro-splash/</t>
         </is>
@@ -1943,7 +1948,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/l-frame/</t>
         </is>
@@ -1995,7 +2000,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
@@ -2047,7 +2052,7 @@
           <t>Imagens (S, M, L e XL)</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/megabillboard/</t>
         </is>
@@ -2099,7 +2104,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/mrec/</t>
         </is>
@@ -2156,7 +2161,7 @@
           <t>JPEG</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/native/</t>
         </is>
@@ -2213,7 +2218,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
@@ -2260,7 +2265,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/outstream/</t>
         </is>
@@ -2307,7 +2312,7 @@
           <t>Imagens</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
@@ -2359,7 +2364,7 @@
           <t>JPEG, PNG ou GIF + Copies</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pop-in/</t>
         </is>
@@ -2411,7 +2416,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/post-social-media/</t>
         </is>
@@ -2468,7 +2473,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
@@ -2525,7 +2530,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/7668/</t>
         </is>
@@ -2582,7 +2587,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/push-down/</t>
         </is>
@@ -2639,7 +2644,7 @@
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/reel-social-media/</t>
         </is>
@@ -2691,7 +2696,7 @@
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/side-frame/</t>
         </is>
@@ -2733,7 +2738,7 @@
           <t>Link post Facebook ou Instagram</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/social-card/</t>
         </is>
@@ -2785,7 +2790,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/splash/</t>
         </is>
@@ -2842,7 +2847,7 @@
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/story-social-media/</t>
         </is>
@@ -2894,7 +2899,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
@@ -2951,7 +2956,7 @@
           <t>PNG</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/ticker/</t>
         </is>
@@ -3008,7 +3013,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/vertical-video/</t>
         </is>
@@ -3055,7 +3060,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/videowall/</t>
         </is>
@@ -3107,7 +3112,7 @@
           <t>HTML / MP4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/cornerad/</t>
         </is>
@@ -3159,7 +3164,7 @@
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/floorad/</t>
         </is>
@@ -3216,7 +3221,7 @@
           <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
@@ -3273,7 +3278,7 @@
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/incontent/</t>
         </is>
@@ -3330,7 +3335,7 @@
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
@@ -3382,7 +3387,7 @@
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/layer/</t>
         </is>
@@ -3434,7 +3439,7 @@
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
@@ -3486,7 +3491,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
@@ -3538,7 +3543,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/masthead-sticky-companion/</t>
         </is>
@@ -3585,7 +3590,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/moldura/</t>
         </is>
@@ -3637,7 +3642,7 @@
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/m-rec/</t>
         </is>
@@ -3694,7 +3699,7 @@
           <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
@@ -3746,7 +3751,7 @@
           <t>260 KB</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
@@ -3803,7 +3808,7 @@
           <t>MP4 ou FLV</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
@@ -3840,7 +3845,7 @@
           <t>Showcase Rich Media</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/showcase-richmedia/</t>
         </is>
@@ -3877,7 +3882,7 @@
           <t>Sideticker</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/sideticker/</t>
         </is>
@@ -3914,7 +3919,7 @@
           <t>Slash</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/slash/</t>
         </is>
@@ -3951,7 +3956,7 @@
           <t>Topo Extensivel</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/topo-extensivel/</t>
         </is>
@@ -3998,7 +4003,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/audio-desktop.html</t>
         </is>
@@ -4050,7 +4055,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/nl-desktop.html</t>
         </is>
@@ -4107,7 +4112,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/carrossel-desktop.html</t>
         </is>
@@ -4164,7 +4169,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/compare-desktop.html</t>
         </is>
@@ -4221,7 +4226,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/flipper-desktop.html</t>
         </is>
@@ -4278,7 +4283,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
@@ -4330,7 +4335,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
@@ -4382,7 +4387,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
@@ -4434,7 +4439,7 @@
           <t>GIF ou WEBM</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/intro-dinamic-desktop.html</t>
         </is>
@@ -4481,7 +4486,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/intro-folheto-desktop.html</t>
         </is>
@@ -4533,7 +4538,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
@@ -4585,7 +4590,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/mrec-desktop.html</t>
         </is>
@@ -4632,7 +4637,7 @@
           <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
@@ -4689,7 +4694,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/outstream-desktop.html</t>
         </is>
@@ -4746,7 +4751,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
@@ -4803,7 +4808,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
@@ -4855,7 +4860,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/skin-desktop.html</t>
         </is>
@@ -4907,7 +4912,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-dynamic-mobile.html</t>
         </is>
@@ -4959,7 +4964,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-footer-desktop.html</t>
         </is>
@@ -5016,7 +5021,7 @@
           <t>JPG, PNG ou GIF / MP4</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-to-intro-desktop.html</t>
         </is>
@@ -5073,7 +5078,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/twinad-desktop.html</t>
         </is>
@@ -5130,7 +5135,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/ad-selector.html</t>
         </is>
@@ -5182,7 +5187,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
@@ -5234,7 +5239,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/barra-topo-extensivel.html</t>
         </is>
@@ -5286,7 +5291,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
@@ -5338,7 +5343,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/cubo-mrec.html</t>
         </is>
@@ -5390,7 +5395,7 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/floorad.html</t>
         </is>
@@ -5447,7 +5452,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/gallery-flip.html</t>
         </is>
@@ -5504,7 +5509,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
@@ -5561,7 +5566,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
@@ -5613,7 +5618,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/mrec.html</t>
         </is>
@@ -5665,7 +5670,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/newsletter.html</t>
         </is>
@@ -5717,7 +5722,7 @@
           <t>JPG / Video</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
@@ -5774,7 +5779,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
@@ -5831,7 +5836,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/prisma-halfpage.html</t>
         </is>
@@ -5888,7 +5893,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/scratch-.html</t>
         </is>
@@ -5945,7 +5950,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/shopping-ads-.html</t>
         </is>
@@ -6002,7 +6007,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/slidedoorvideo.html</t>
         </is>
@@ -6049,7 +6054,7 @@
           <t>JPEG, JPG ou PNG</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/slidervideo.html</t>
         </is>
@@ -6101,7 +6106,7 @@
           <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
@@ -6148,7 +6153,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/galeria_header.html</t>
         </is>
@@ -6200,7 +6205,7 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/twinad.html</t>
         </is>
@@ -6257,7 +6262,7 @@
           <t>MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/incontent.html</t>
         </is>
@@ -6314,7 +6319,7 @@
           <t>MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
@@ -6366,7 +6371,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278437-cube-3d-viewable-display</t>
         </is>
@@ -6423,7 +6428,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-app_install_native_outbrain</t>
         </is>
@@ -6470,7 +6475,7 @@
           <t>MPEG, MP3, WAV, ou OGG</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/audio-ad-specs/</t>
         </is>
@@ -6517,7 +6522,7 @@
           <t>MP3</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6564,7 +6569,7 @@
           <t>MP3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6611,7 +6616,7 @@
           <t>MP3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6663,7 +6668,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_1a_2a_posicao</t>
         </is>
@@ -6720,7 +6725,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_carousel</t>
         </is>
@@ -6767,7 +6772,7 @@
           <t>200 KB</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
@@ -6819,7 +6824,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard</t>
         </is>
@@ -6856,7 +6861,7 @@
           <t>Branded Content</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-artigos_content_marketing</t>
         </is>
@@ -6913,7 +6918,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-capa_falsa</t>
         </is>
@@ -6965,7 +6970,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206459-carousel-square,  https://support.teads.tv/support/solutions/articles/36000206458-carousel-landscape, https://support.teads.tv/support/solutions/articles/36000552432-carousel-vertical-</t>
         </is>
@@ -7017,7 +7022,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>https://www.outbrain.com/help/ads-specs/#carousel</t>
         </is>
@@ -7133,7 +7138,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-companion_banner_resumo_artigo</t>
         </is>
@@ -7190,7 +7195,7 @@
           <t>PNG</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-countdown</t>
         </is>
@@ -7343,7 +7348,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-display_standard_cpc_surf</t>
         </is>
@@ -7395,7 +7400,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278434-drag-drop-viewable-display</t>
         </is>
@@ -7447,7 +7452,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552435-flip-flow-viewable-display</t>
         </is>
@@ -7499,7 +7504,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206460-flow-square, https://support.teads.tv/support/solutions/articles/36000206461-flow-landscape</t>
         </is>
@@ -7556,7 +7561,7 @@
           <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
@@ -7613,7 +7618,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage_flip</t>
         </is>
@@ -7894,7 +7899,7 @@
           <t>JPG / MOV ou MP4</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-SG/ad-experiences/display-homepage-takeover-ads-specs/</t>
         </is>
@@ -7951,7 +7956,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278440-hover-viewable-display</t>
         </is>
@@ -8008,7 +8013,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/display-ad-specs/</t>
         </is>
@@ -8045,7 +8050,7 @@
           <t>In-feed Video (Spotify)</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/in-feed-video-ad-specs/</t>
         </is>
@@ -8097,7 +8102,7 @@
           <t>JPG, PNG ou WEBP / MP4</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/inline-midscroll-template</t>
         </is>
@@ -8154,7 +8159,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552431-interscroller-display</t>
         </is>
@@ -8211,7 +8216,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552411-interscroller-video</t>
         </is>
@@ -8268,7 +8273,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
@@ -8320,7 +8325,7 @@
           <t>WEBP ou GIF</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_plus</t>
         </is>
@@ -8372,7 +8377,7 @@
           <t>HTML5 responsive com recursos em WEBP e MP4/WEBM, WEBP ou GIF (Leaderboard e Mobile)</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_plus_video</t>
         </is>
@@ -8429,7 +8434,7 @@
           <t>MP4 ou WEBP</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_video</t>
         </is>
@@ -8486,7 +8491,7 @@
           <t>MP4, WebM, ou MOV</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/in-stream-video-ad-specs/</t>
         </is>
@@ -8523,7 +8528,7 @@
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-microsites_landing_pages</t>
         </is>
@@ -8575,7 +8580,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
@@ -8612,7 +8617,7 @@
           <t>Microsite</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-microsites_landing_pages</t>
         </is>
@@ -8664,7 +8669,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mobile_banner</t>
         </is>
@@ -8716,7 +8721,7 @@
           <t>JPG, PNG ou GIF / MP4 ou WEBP</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mrec, https://saleshouse.sapo.pt/formatos.html#format-mrec_video</t>
         </is>
@@ -8768,7 +8773,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mrec_carousel</t>
         </is>
@@ -8825,7 +8830,7 @@
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206444-video-overlay</t>
         </is>
@@ -8882,7 +8887,7 @@
           <t>JPG, PNG ou WEBP / MP4</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/inline-expander-reel-template</t>
         </is>
@@ -8939,7 +8944,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278439-scratch-viewable-display</t>
         </is>
@@ -8991,7 +8996,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206455-scroller-square, https://support.teads.tv/support/solutions/articles/36000206453-scroller-landscape, https://support.teads.tv/support/solutions/articles/36000206456-scroller-vertical</t>
         </is>
@@ -9043,7 +9048,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000434238-shoppable-carousel</t>
         </is>
@@ -9095,7 +9100,7 @@
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206452-shoppable-square, https://support.teads.tv/support/solutions/articles/36000206451-shoppable-landscape, https://support.teads.tv/support/solutions/articles/36000552430-shoppable-vertical</t>
         </is>
@@ -9147,7 +9152,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000208421-single-image</t>
         </is>
@@ -9194,7 +9199,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000297712-single-video</t>
         </is>
@@ -9236,7 +9241,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/fluid-skin-image-video</t>
         </is>
@@ -9293,7 +9298,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278442-slider-viewable-display</t>
         </is>
@@ -9350,7 +9355,7 @@
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000366159-inread-smart6</t>
         </is>
@@ -9392,7 +9397,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000238201-social-video-image-layout-1-, https://support.teads.tv/support/solutions/articles/36000238202-social-video-image-layout-2-</t>
         </is>
@@ -9434,7 +9439,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000297713-social-layout-1-performance, https://support.teads.tv/support/solutions/articles/36000297714-social-layout-2-performance</t>
         </is>
@@ -9476,7 +9481,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000238201-social-video-image-layout-1-, https://support.teads.tv/support/solutions/articles/36000238202-social-video-image-layout-2-</t>
         </is>
@@ -9528,7 +9533,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278441-spin-card-viewable-display</t>
         </is>
@@ -9580,7 +9585,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-standard_green_ad</t>
         </is>
@@ -9637,7 +9642,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t>https://www.outbrain.com/help/ads-specs/#native-image</t>
         </is>
@@ -9679,7 +9684,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000245892-stories-display-square, https://support.teads.tv/support/solutions/articles/36000245899-stories-display-vertical</t>
         </is>
@@ -9721,7 +9726,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000245891-stories-video-square, https://support.teads.tv/support/solutions/articles/36000245901-stories-video-vertical</t>
         </is>
@@ -9778,7 +9783,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278444-swipe-carousel-viewable-display</t>
         </is>
@@ -9835,7 +9840,7 @@
           <t>JPG, PNG ou WEBP</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-desktop-image</t>
         </is>
@@ -9877,7 +9882,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/fluid-product-carousel, https://www.adnami.io/specs/dynamic-hybrid-carousel, https://www.adnami.io/specs/product-lightbox</t>
         </is>
@@ -9929,7 +9934,7 @@
           <t>JPG ou WEBP</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-expand-template-image-desktop, https://www.adnami.io/specs/topscroll-expand-template-image-mobile</t>
         </is>
@@ -9981,7 +9986,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-expand-template-desktop, https://www.adnami.io/specs/topscroll-expand-template-mobile</t>
         </is>
@@ -10033,7 +10038,7 @@
           <t>JPG ou WEBP</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/prismo</t>
         </is>
@@ -10075,7 +10080,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-desktop-video, https://www.adnami.io/specs/topscroll-mobile-video</t>
         </is>
@@ -10127,7 +10132,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-twin_ad</t>
         </is>
@@ -10184,7 +10189,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
@@ -10241,7 +10246,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
@@ -10788,7 +10793,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/single-image-ads-specs</t>
         </is>
@@ -11048,7 +11053,7 @@
           <t>PNG, JPEG; 2–5 imagens (non-Sales)</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11100,7 +11105,7 @@
           <t>PNG, JPEG, MP4/MOV/M4V + catálogo</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11157,7 +11162,7 @@
           <t>PNG, JPEG</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11214,7 +11219,7 @@
           <t>MP4, MOV, M4V</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11271,7 +11276,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types/carousel-ads</t>
         </is>
@@ -11328,7 +11333,7 @@
           <t>JPG, PNG, GIF, MP4, MOV + rich text</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types/free-form</t>
         </is>
@@ -11385,7 +11390,7 @@
           <t>JPG, PNG, GIF (estático)</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/learning-hub/articles/reddit-image-ad-specs</t>
         </is>
@@ -11437,7 +11442,7 @@
           <t>Catálogo de produtos + JPG/PNG ou vídeo conforme configuração</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types</t>
         </is>
@@ -11489,7 +11494,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types/video-ads</t>
         </is>
@@ -11541,7 +11546,7 @@
           <t>PNG (filtro estático), GIF (animado); Lens assets conforme Lens Studio</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11598,7 +11603,7 @@
           <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11655,7 +11660,7 @@
           <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11712,7 +11717,7 @@
           <t>MP4, MOV (H.264)</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11769,7 +11774,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11826,7 +11831,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11883,7 +11888,7 @@
           <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11940,7 +11945,7 @@
           <t>PNG + assets de efeito conforme template</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
         </is>
@@ -11992,7 +11997,7 @@
           <t>Vídeo de creator elegível / Spark Ads</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="L224" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
         </is>
@@ -12049,7 +12054,7 @@
           <t>JPG/JPEG, PNG + MP3</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="L225" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
         </is>
@@ -12106,7 +12111,7 @@
           <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12158,7 +12163,7 @@
           <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="L227" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
         </is>
@@ -12215,7 +12220,7 @@
           <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12267,7 +12272,7 @@
           <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
@@ -12324,7 +12329,7 @@
           <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12376,7 +12381,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="L231" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12433,7 +12438,7 @@
           <t>JPG, PNG; MP4/MOV para video carousel</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="L232" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12490,7 +12495,7 @@
           <t>JPG, PNG + catálogo</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="L233" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12542,7 +12547,7 @@
           <t>Feed/catálogo + JPG/PNG</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="L234" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12599,7 +12604,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12651,7 +12656,7 @@
           <t>JPG, PNG, MP4/MOV conforme takeover</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="L236" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12703,7 +12708,7 @@
           <t>Texto/post + URL opcional</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="L237" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12760,7 +12765,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="L238" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12812,7 +12817,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="L239" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -12864,7 +12869,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="L240" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -12916,7 +12921,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
+      <c r="L241" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -12973,7 +12978,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13025,7 +13030,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="L243" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13082,7 +13087,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
+      <c r="L244" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13139,7 +13144,7 @@
           <t>ZIP HTML5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
+      <c r="L245" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13196,7 +13201,7 @@
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="L246" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13253,7 +13258,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
+      <c r="L247" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13310,7 +13315,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
+      <c r="L248" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13362,7 +13367,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="L249" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13401,7 +13406,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; 15 segundos recomendado. Texto — Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
+          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; 15 segundos recomendado.</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -13420,6 +13425,11 @@
         </is>
       </c>
       <c r="K250" t="inlineStr">
+        <is>
+          <t>Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13476,7 +13486,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="L251" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13533,7 +13543,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="L252" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13590,7 +13600,7 @@
           <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -13642,7 +13652,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
+      <c r="L254" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -13681,7 +13691,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2 a 10 cartões, todos com a mesma proporção (1:1 ou 1.91:1); cada cartão com título até 40 caracteres</t>
+          <t>2 a 10 cartões, todos com a mesma proporção (1:1 ou 1.91:1)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -13695,6 +13705,11 @@
         </is>
       </c>
       <c r="K255" t="inlineStr">
+        <is>
+          <t>Título por cartão: até 40 caracteres</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -14105,7 +14120,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
+      <c r="L268" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -14171,7 +14186,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível. COPY (igual para imagem e vídeo) — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível.</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -14190,6 +14205,11 @@
         </is>
       </c>
       <c r="K270" t="inlineStr">
+        <is>
+          <t>Igual para imagem e vídeo — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
         <is>
           <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
         </is>
@@ -14300,7 +14320,7 @@
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="L273" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -14357,7 +14377,7 @@
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="L274" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -14463,7 +14483,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
+      <c r="L277" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -14497,7 +14517,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c; Espera: 420x420 ou 314x420, máx 1 imagem, copy: título máx 25c, CTA máx 15c; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes), copy: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg, copy: título máx 25c, corpo máx 52c; Espera: 6 a 60 seg, copy: título máx 25c, CTA máx 15c; Viagem: 6 a 60 seg, copy: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (Click Tag só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -14513,6 +14533,11 @@
       <c r="J278" t="inlineStr">
         <is>
           <t>Display: imagens. Video: MP4.</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14646,7 @@
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
+      <c r="L281" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -14673,7 +14698,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="L282" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -14725,7 +14750,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
+      <c r="L283" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -14777,7 +14802,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
+      <c r="L284" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
@@ -14829,7 +14854,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="L285" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
@@ -14881,7 +14906,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
+      <c r="L286" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
@@ -14933,7 +14958,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="L287" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
@@ -14980,7 +15005,7 @@
           <t>200 KB</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
+      <c r="L288" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
@@ -15037,7 +15062,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
+      <c r="L289" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
@@ -15094,7 +15119,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
+      <c r="L290" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
@@ -15151,7 +15176,7 @@
           <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
+      <c r="L291" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
@@ -15208,7 +15233,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
+      <c r="L292" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
@@ -15265,7 +15290,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
+      <c r="L293" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
@@ -15322,7 +15347,7 @@
           <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
+      <c r="L294" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
@@ -15379,7 +15404,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
+      <c r="L295" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -15426,7 +15451,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
+      <c r="L296" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
@@ -15478,7 +15503,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
+      <c r="L297" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
@@ -15530,7 +15555,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
+      <c r="L298" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
@@ -15619,7 +15644,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
+      <c r="L300" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
@@ -15676,7 +15701,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
+      <c r="L301" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
@@ -15733,7 +15758,7 @@
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
+      <c r="L302" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
@@ -15785,7 +15810,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
+      <c r="L303" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
@@ -15842,7 +15867,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
+      <c r="L304" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
@@ -15899,7 +15924,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
+      <c r="L305" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
@@ -15951,7 +15976,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
+      <c r="L306" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
@@ -16003,7 +16028,7 @@
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
+      <c r="L307" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
@@ -16055,7 +16080,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
+      <c r="L308" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
@@ -16107,7 +16132,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
+      <c r="L309" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
@@ -16159,7 +16184,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
+      <c r="L310" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -16216,7 +16241,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
+      <c r="L311" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
@@ -16273,7 +16298,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
+      <c r="L312" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
@@ -16330,7 +16355,7 @@
           <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
+      <c r="L313" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
@@ -16377,7 +16402,7 @@
           <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
+      <c r="L314" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
@@ -16429,7 +16454,7 @@
           <t>JPG / Video</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
+      <c r="L315" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
@@ -16486,7 +16511,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
+      <c r="L316" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -16543,7 +16568,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
+      <c r="L317" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
@@ -16590,7 +16615,7 @@
           <t>Imagens</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
+      <c r="L318" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
@@ -16642,7 +16667,7 @@
           <t>260 KB</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
+      <c r="L319" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
@@ -16699,7 +16724,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
+      <c r="L320" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
@@ -16756,7 +16781,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
+      <c r="L321" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
@@ -16813,7 +16838,7 @@
           <t>MP4 ou FLV</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
+      <c r="L322" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
@@ -16870,7 +16895,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
+      <c r="L323" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
@@ -16927,7 +16952,7 @@
           <t>MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
+      <c r="L324" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
@@ -16984,7 +17009,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="L325" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
@@ -17036,7 +17061,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
+      <c r="L326" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
@@ -17088,7 +17113,7 @@
           <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
+      <c r="L327" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
@@ -17172,7 +17197,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
+      <c r="L329" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -17261,7 +17286,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="L331" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
@@ -17318,7 +17343,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
+      <c r="L332" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
@@ -17375,7 +17400,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
+      <c r="L333" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
@@ -17432,7 +17457,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
+      <c r="L334" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
@@ -17489,7 +17514,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
+      <c r="L335" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
@@ -17546,7 +17571,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
+      <c r="L336" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
@@ -17603,7 +17628,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
+      <c r="L337" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
@@ -17642,7 +17667,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Só texto (sem imagem) — Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+          <t>N/A (só texto, sem imagem)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -17656,6 +17681,11 @@
         </is>
       </c>
       <c r="K338" t="inlineStr">
+        <is>
+          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/7684791</t>
         </is>
@@ -17694,7 +17724,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; mín. 10 segundos. Texto — Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
+          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; mín. 10 segundos.</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -17713,6 +17743,11 @@
         </is>
       </c>
       <c r="K339" t="inlineStr">
+        <is>
+          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/12066387</t>
         </is>
@@ -17769,7 +17804,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr">
+      <c r="L340" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -17826,7 +17861,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr">
+      <c r="L341" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -17865,7 +17900,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Feed: 4:5, 1440x1800 (mín. 600px largura, mín. 750px altura), tolerância 3%, texto principal 50-150c, título 27c; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 125c, título 40c; Reels: 9:16, 1440x2560 (mín. 600x600px), tolerância 3%, texto principal 40c, título 55c.</t>
+          <t>Feed: 4:5, 1440x1800 (mín. 600px largura, mín. 750px altura), tolerância 3%; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%; Reels: 9:16, 1440x2560 (mín. 600x600px), tolerância 3%.</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -17884,6 +17919,11 @@
         </is>
       </c>
       <c r="K342" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -17922,7 +17962,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Feed: 4:5, 1440x1800 (mín. 120x120px), 1s a 241min, texto principal 50-150c, título 27c; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 3min, texto principal 125c, título 40c; Reels: 9:16 recomendado, 1440x2560, sem duração máxima, texto principal 40c, título 55c (sem legendas automáticas). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>Feed: 4:5, 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 3min; Reels: 9:16 recomendado, 1440x2560, sem duração máxima.</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -17937,10 +17977,15 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF</t>
+          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -17979,7 +18024,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Feed: 1:1, 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 3%, texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: 1:1 recomendado, 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px, texto principal 125c, título 40c, URL obrigatório; Reels: 9:16, 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px, tolerância 1%, texto principal 40c.</t>
+          <t>Feed: 1:1, 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 3%; Stories: 1:1 recomendado, 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 9:16, 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px, tolerância 1%.</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -17998,6 +18043,11 @@
         </is>
       </c>
       <c r="K344" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -18036,7 +18086,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1, 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto; Experiência Instantânea obrigatória; texto principal 125c, título 40c, URL obrigatório; Reels: 9:16 até 1:1, 1080x1080 mín.; requer Catálogo Advantage+ como fonte de conteúdo; texto principal 72c, título 10c, URL obrigatório; Experiência Instantânea obrigatória.</t>
+          <t>Feed: 1.91:1 até 1:1, 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 9:16 até 1:1, 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -18055,6 +18105,11 @@
         </is>
       </c>
       <c r="K345" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -18093,7 +18148,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Feed: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%, texto principal 125c, título 40c, máx. 30 hashtags; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 125c; Reels: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%, texto principal 44c; Explorar: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%, texto principal 125c, título 40c, máx. 30 hashtags.</t>
+          <t>Feed: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%; Reels: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%; Explorar: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%.</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -18112,6 +18167,11 @@
         </is>
       </c>
       <c r="K346" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -18150,7 +18210,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Feed: 9:16, 1080x1920 (mín. 250px largura), tolerância 1%, 1s a 60min, texto principal 125c, máx. 30 hashtags; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 60min, texto principal 125c; Reels: 9:16, 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s), texto principal 44c. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>Feed: 9:16, 1080x1920 (mín. 250px largura), tolerância 1%, 1s a 60min; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 60min; Reels: 9:16, 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -18165,10 +18225,15 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV)</t>
+          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -18207,7 +18272,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Feed: 4:5 (carrosséis só de imagem) ou 1:1 (se tiver vídeo), 1080x1080 mín., 2 a 10 cartões, tolerância 1%, texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: 9:16, 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 1%, texto principal 125c, título 40c, URL obrigatório; Reels: 9:16, 1080x1080 mín. (só imagem), 2 a 10 cartões, tolerância 1%.</t>
+          <t>Feed: 4:5 (carrosséis só de imagem) ou 1:1 (se tiver vídeo), 1080x1080 mín., 2 a 10 cartões, tolerância 1%; Stories: 9:16, 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 1%; Reels: 9:16, 1080x1080 mín. (só imagem), 2 a 10 cartões, tolerância 1%.</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -18226,6 +18291,11 @@
         </is>
       </c>
       <c r="K348" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -18264,7 +18334,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1, 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto; Experiência Instantânea obrigatória; texto principal 125c, título 40c, URL obrigatório; Stories: 1.91:1 até 1:1, 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto; Experiência Instantânea obrigatória; texto principal 125c, URL obrigatório; Reels: 9:16 (imagem de produto 1:1), mín. 500x888, capa + até 3 imagens de produto; Experiência Instantânea obrigatória.</t>
+          <t>Feed: 1.91:1 até 1:1, 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1.91:1 até 1:1, 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: 9:16 (imagem de produto 1:1), mín. 500x888, capa + até 3 imagens de produto, Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -18283,6 +18353,11 @@
         </is>
       </c>
       <c r="K349" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -17900,12 +17900,12 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Feed: 4:5, 1440x1800 (mín. 600px largura, mín. 750px altura), tolerância 3%; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%; Reels: 9:16, 1440x2560 (mín. 600x600px), tolerância 3%.</t>
+          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura), tolerância 3%; Stories: 1440x2560 (mín. 500px largura), tolerância 1%; Reels: 1440x2560 (mín. 600x600px), tolerância 3%.</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>4:5 ou 9:16</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -17962,12 +17962,12 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Feed: 4:5, 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 3min; Reels: 9:16 recomendado, 1440x2560, sem duração máxima.</t>
+          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>4:5 ou 9:16</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Feed: 1:1, 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 3%; Stories: 1:1 recomendado, 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 9:16, 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px, tolerância 1%.</t>
+          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 3%; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px, tolerância 1%.</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>1:1 ou 9:16</t>
+          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -18086,12 +18086,12 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1, 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 9:16 até 1:1, 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
+          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>1.91:1 até 1:1 ou 9:16</t>
+          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -18148,12 +18148,12 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Feed: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%; Stories: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%; Reels: 9:16, 1440x2560 (mín. 500px largura), tolerância 1%; Explorar: 4:5, 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%.</t>
+          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%; Stories: 1440x2560 (mín. 500px largura), tolerância 1%; Reels: 1440x2560 (mín. 500px largura), tolerância 1%; Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%.</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>4:5 ou 9:16</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -18210,12 +18210,12 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Feed: 9:16, 1080x1920 (mín. 250px largura), tolerância 1%, 1s a 60min; Stories: 9:16, 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 60min; Reels: 9:16, 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
+          <t>Feed: 1080x1920 (mín. 250px largura), tolerância 1%, 1s a 60min; Stories: 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -18272,12 +18272,12 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Feed: 4:5 (carrosséis só de imagem) ou 1:1 (se tiver vídeo), 1080x1080 mín., 2 a 10 cartões, tolerância 1%; Stories: 9:16, 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 1%; Reels: 9:16, 1080x1080 mín. (só imagem), 2 a 10 cartões, tolerância 1%.</t>
+          <t>Feed: 1080x1080 mín., 2 a 10 cartões, tolerância 1%; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 1%; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões, tolerância 1%.</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>4:5 ou 1:1 ou 9:16</t>
+          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -18334,12 +18334,12 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1, 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1.91:1 até 1:1, 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: 9:16 (imagem de produto 1:1), mín. 500x888, capa + até 3 imagens de produto, Experiência Instantânea obrigatória.</t>
+          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888 (imagem de produto 1:1), capa + até 3 imagens de produto, Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>1.91:1 até 1:1 ou 9:16</t>
+          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -17900,7 +17900,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura), tolerância 3%; Stories: 1440x2560 (mín. 500px largura), tolerância 1%; Reels: 1440x2560 (mín. 600x600px), tolerância 3%.</t>
+          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
+          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 3%; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px, tolerância 1%.</t>
+          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%; Stories: 1440x2560 (mín. 500px largura), tolerância 1%; Reels: 1440x2560 (mín. 500px largura), tolerância 1%; Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100), tolerância 1%.</t>
+          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Feed: 1080x1920 (mín. 250px largura), tolerância 1%, 1s a 60min; Stories: 1440x2560 (mín. 250px largura), tolerância 1%, 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
+          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -18272,7 +18272,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín., 2 a 10 cartões, tolerância 1%; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões, tolerância 1%; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões, tolerância 1%.</t>
+          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -10285,7 +10285,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Imagem do artigo/newsletter (conteúdo orgânico)</t>
+          <t>Imagem do artigo/newsletter (conteúdo orgânico) — specs iguais ao Single Image.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10296,6 +10296,11 @@
       <c r="J192" t="inlineStr">
         <is>
           <t>Post/artigo ou newsletter já publicado no LinkedIn</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Sem título/texto introdutório editável — o criativo é o artigo/newsletter orgânico original.</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10337,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>1080x1080 recomendado; máx. 4320x4320</t>
+          <t>Recomendado mín. 1080x1080 (não suporta vídeo).</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -10347,7 +10352,12 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF não animado</t>
+          <t>JPG ou PNG; 2 a 10 cartões</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Nome do anúncio (opcional): 255c; Título do cartão: 45c; Texto introdutório: 255c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10394,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>1920x1080 recomendado; 1280x720 aceite</t>
+          <t>1920x1080 recomendado (ou 1280x720); duração 6 a 60s (recomendado 6, 15, 30, 45 ou 60s).</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -10399,7 +10409,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>MP4 (H.264)</t>
+          <t>MP4, codec H.264, bitrate mín. 12 Mbps (recomendado 15–40 Mbps), frame rate constante (23,98/24/25/29,97/30 fps), áudio 2 canais -23 LUFS integrado, PCM (16/24 bit) ou AAC ≥192 Kbps, 48 kHz, chroma 4:2:0 (recomendado 4:2:2).</t>
         </is>
       </c>
     </row>
@@ -10436,22 +10446,22 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>250x250 imagem; banner opcional máx. 300x250</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>Banner opcional: máx. 300x250 (só desktop); imagem do remetente = foto de perfil LinkedIn do remetente definido.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>5 MB imagem; 2 MB banner</t>
+          <t>Banner: máx. 2 MB</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>Banner: JPG ou PNG (opcional)</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Nome do anúncio (opcional): 255c; Texto da mensagem: máx. 8000c; Rodapé personalizado: máx. 20000c; CTA: máx. 25c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10498,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sem dimensão fixa; layouts standard (A4, Letter, etc.)</t>
+          <t>Sem dimensão fixa em píxeis — layouts standard (A4, Letter, Legal, etc.); recomendado até 10 páginas (máx. 300 páginas ou 1M palavras).</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -10498,7 +10508,12 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>PDF, PPT, PPTX, DOC, DOCX</t>
+          <t>PDF, DOC, DOCX, PPT, PPTX</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Nome do anúncio (opcional): 255c; Título: 70c; Texto introdutório: 150c.</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10550,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Usa imagem do evento LinkedIn</t>
+          <t>Imagem retirada automaticamente da página do Evento.</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>4:1</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -10545,7 +10565,12 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Evento publicado no LinkedIn</t>
+          <t>Evento já publicado no LinkedIn</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Nome do evento (opcional): 255c; Texto introdutório: 600c; Event URL: obrigatório, só páginas de Evento do LinkedIn.</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10607,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Logo: 100x100 recomendado</t>
+          <t>Logo da empresa: 100x100.</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -10597,7 +10622,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Título: 50c; Descrição: 70c; Nome da empresa: 25c.</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10664,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dinâmico; usa logo/elementos da Page e vaga</t>
+          <t>Dinâmico; usa logo/elementos da Page e vaga.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -10645,6 +10675,11 @@
       <c r="J199" t="inlineStr">
         <is>
           <t>Vaga + Page LinkedIn</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Texto introdutório: até 150c.</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10716,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Sem asset gráfico próprio; associado ao anúncio</t>
+          <t>Sem asset gráfico próprio; associado ao anúncio.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10692,6 +10727,11 @@
       <c r="J200" t="inlineStr">
         <is>
           <t>Formulário criado no Campaign Manager</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Nome do formulário: 256c; Título da oferta: 60c; Detalhe da oferta (opcional): 160c; Política de privacidade: 2000c; CTA: 20c; Mensagem de confirmação: 300c; Perguntas personalizadas: até 3, 100c cada; campos recomendados: 3-4 (máx. 12).</t>
         </is>
       </c>
     </row>
@@ -10728,17 +10768,22 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Banner opcional 300x250</t>
+          <t>Banner opcional: máx. 300x250 (só desktop); imagem do remetente = foto de perfil LinkedIn do remetente definido.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2 MB</t>
+          <t>Banner: máx. 2 MB</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>Banner: JPG ou PNG (opcional)</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Nome do anúncio (opcional): 255c; Texto da mensagem: máx. 8000c; Rodapé personalizado: máx. 20000c; CTA: máx. 25c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
     </row>
@@ -10775,12 +10820,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>1200x628 (1.91:1); 1200x1200 (1:1); 720x900 (4:5)</t>
+          <t>Horizontal: 1200x628 recomendado (mín. 640x360, máx. 7680x4320); Quadrado: 1200x1200 recomendado (mín. 360x360, máx. 4320x4320); Vertical: 720x900 recomendado (mín. 360x640, máx. 2430x4320).</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>1,91:1 (horizontal) ou 1:1 (quadrado) ou 4:5 (vertical, recomendado)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10790,7 +10835,12 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPG, PNG ou GIF (GIF animado até 250 frames)</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Nome do anúncio (opcional): 255c; Título: 70c; Texto introdutório: 150c (máx. 3000c); Descrição (só LAN): 70c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -10832,22 +10882,27 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>1920x1080 / 720x900 / 720x1280; conforme rácio</t>
+          <t>Landscape: 1920x1080 recomendado (mín. 640x360, máx. 1920x1080); Square: mín. 360x360, máx. 1920x1920; Vertical 4:5: mín. 360x450, máx. 1080x1350; Vertical 9:16: 720x1280 recomendado (mín. 360x640, máx. 1080x1920). Duração: 3s a 30min (in-stream em streaming até 90s).</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>16:9 ou 4:5 ou 9:16</t>
+          <t>16:9 ou 1:1 ou 4:5 ou 9:16</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>75 KB–500 MB</t>
+          <t>75 KB a 500 MB</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>MP4; thumbnail JPG/PNG opcional</t>
+          <t>MP4, codec H.264 ou VP8, áudio AAC ou MPEG4 (&lt;64 KHz), 30 fps recomendado; thumbnail opcional JPG/PNG máx. 2 MB (rácio igual ao vídeo)</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Nome do anúncio (opcional): 255c; Título: 70c (máx. 200c); Texto introdutório: 150c (máx. 600c).</t>
         </is>
       </c>
     </row>
@@ -10884,22 +10939,27 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Logo 100x100; background opcional 300x250</t>
+          <t>Logo da empresa: 100x100; Imagem de fundo opcional: 300x250.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>Logo: 1:1</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2 MB</t>
+          <t>Logo: 2 MB; Imagem de fundo: 2 MB</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Título: 50c; Descrição: 70c; Nome da empresa: 25c; CTA: 18c; Landing page URL: máx. 500c.</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10996,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>100x100</t>
+          <t>Logo: 100x100.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -10951,7 +11011,12 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Título: 25c; Descrição: 75c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
     </row>
@@ -10988,7 +11053,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Depende do post original (imagem/vídeo/documento/etc.)</t>
+          <t>Depende do post original (imagem/vídeo/documento/etc.) — specs iguais ao formato do post.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10999,6 +11064,11 @@
       <c r="J206" t="inlineStr">
         <is>
           <t>Post orgânico elegível de membro/Page</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Sem título/texto introdutório editável — o criativo é o post orgânico original; sem CTA.</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -10303,6 +10303,11 @@
           <t>Sem título/texto introdutório editável — o criativo é o artigo/newsletter orgânico original.</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-content/articles-and-newsletters-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10360,6 +10365,11 @@
           <t>Nome do anúncio (opcional): 255c; Título do cartão: 45c; Texto introdutório: 255c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-content/carousel-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10412,6 +10422,11 @@
           <t>MP4, codec H.264, bitrate mín. 12 Mbps (recomendado 15–40 Mbps), frame rate constante (23,98/24/25/29,97/30 fps), áudio 2 canais -23 LUFS integrado, PCM (16/24 bit) ou AAC ≥192 Kbps, 48 kHz, chroma 4:2:0 (recomendado 4:2:2).</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-content/connected-tv-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10464,6 +10479,11 @@
           <t>Nome do anúncio (opcional): 255c; Texto da mensagem: máx. 8000c; Rodapé personalizado: máx. 20000c; CTA: máx. 25c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-messaging/conversation-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10516,6 +10536,11 @@
           <t>Nome do anúncio (opcional): 255c; Título: 70c; Texto introdutório: 150c.</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-content/document-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10573,6 +10598,11 @@
           <t>Nome do evento (opcional): 255c; Texto introdutório: 600c; Event URL: obrigatório, só páginas de Evento do LinkedIn.</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-content/event-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10630,6 +10660,11 @@
           <t>Título: 50c; Descrição: 70c; Nome da empresa: 25c.</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/dynamic-ads/follower-ads</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10682,6 +10717,11 @@
           <t>Texto introdutório: até 150c.</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/ads-guide</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10734,6 +10774,11 @@
           <t>Nome do formulário: 256c; Título da oferta: 60c; Detalhe da oferta (opcional): 160c; Política de privacidade: 2000c; CTA: 20c; Mensagem de confirmação: 300c; Perguntas personalizadas: até 3, 100c cada; campos recomendados: 3-4 (máx. 12).</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-content/lead-gen-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10786,6 +10831,11 @@
           <t>Nome do anúncio (opcional): 255c; Texto da mensagem: máx. 8000c; Rodapé personalizado: máx. 20000c; CTA: máx. 25c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-messaging/message-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10905,6 +10955,11 @@
           <t>Nome do anúncio (opcional): 255c; Título: 70c (máx. 200c); Texto introdutório: 150c (máx. 600c).</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-content/video-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10962,6 +11017,11 @@
           <t>Título: 50c; Descrição: 70c; Nome da empresa: 25c; CTA: 18c; Landing page URL: máx. 500c.</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/dynamic-ads/spotlight-ads</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11019,6 +11079,11 @@
           <t>Título: 25c; Descrição: 75c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/text-ads/specs</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11069,6 +11134,11 @@
       <c r="K206" t="inlineStr">
         <is>
           <t>Sem título/texto introdutório editável — o criativo é o post orgânico original; sem CTA.</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>https://business.linkedin.com/advertise/ads/sponsored-content/thought-leader-ads/specs</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L349"/>
+  <dimension ref="A1:L352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -11175,22 +11175,27 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>1:1 ou 2:3; 1000x1000 / 1000x1500 recomendado</t>
+          <t>Standard: 2 a 5 imagens, 1:1 ou 2:3; Sales (catálogo): 2 a 10 imagens/vídeos, dimensões herdadas do catálogo.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>1:1 ou 2:3</t>
+          <t>1:1 ou 2:3 (Standard); N/A no Sales (herdado do catálogo)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>20 MB por imagem</t>
+          <t>Standard: 20 MB por imagem; Sales: N/A (herdado do catálogo)</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>PNG, JPEG; 2–5 imagens (non-Sales)</t>
+          <t>PNG ou JPEG (Standard); imagem ou vídeo via catálogo (Sales)</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: até 800c.</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -11232,17 +11237,27 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hero 1:1 ou 2:3; assets secundários via catálogo</t>
+          <t>Hero: 1:1 ou 2:3 (pode diferir dos secundários); Secundários: mín. 3 recomendado, máx. 24, todos com o mesmo rácio entre si (1:1 ou 2:3); Hero em vídeo: duração mín. 4s, máx. 15min, rácio mais estreito que 1:2 e mais largo que 1,91:1 (recomendado 1:1, 2:3 ou 9:16).</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Hero: 1:1 ou 2:3; Secundários: 1:1 ou 2:3 (recomendado 1:1)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Imagem 20 MB; vídeo até 2 GB</t>
+          <t>Imagem: 10 MB; Vídeo: até 2 GB</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>PNG, JPEG, MP4/MOV/M4V + catálogo</t>
+          <t>PNG ou JPEG (imagem); MP4, MOV ou M4V, codec H.264 ou H.265 (vídeo hero)</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: só aparece em Pins de Collection orgânicos vistos de perto, não em ads promovidos.</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -11284,22 +11299,27 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>1000x1500 recomendado (2:3)</t>
+          <t>Recomendado 1000x1500 (2:3). Pins com rácio superior a 2:3 podem ficar cortados no feed.</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2:3</t>
+          <t>2:3 (recomendado)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>20 MB</t>
+          <t>Desktop: 20 MB; In-app: 32 MB</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PNG, JPEG</t>
+          <t>PNG ou JPEG</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: até 800c.</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -11341,22 +11361,27 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>1000x1500 (2:3), 1080x1920 (9:16) ou square conforme placement</t>
+          <t>Duração: mín. 4s, máx. 15min (recomendado 6-15s para ads). Rácio: mais estreito que 1:2, mais largo que 1,91:1; recomendado quadrado (1:1) ou vertical (2:3, 4:5 ou 9:16).</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2:3 ou 9:16</t>
+          <t>1:1, 2:3, 4:5 ou 9:16 (recomendado); aceite entre 1:2 e 1,91:1</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2 GB</t>
+          <t>Até 2 GB</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>MP4, MOV, M4V</t>
+          <t>MP4, MOV ou M4V; codec H.264 ou H.265</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: até 800c.</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -18500,6 +18525,192 @@
       <c r="L349" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Idea Ad</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>9:16 (recomendado, sem restrição rígida)</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Título: até 100c; Texto na página: até 250c.</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Showcase Ad</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Até 32 MB</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Quiz Ad</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>Title Pin: 2:3; Results Pin: 2:3</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Até 32 MB</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -11423,27 +11423,32 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2–6 cartões; 1080x1080 recomendado</t>
+          <t>2 a 6 imagens (mesmo rácio recomendado em todas). Cross-device recomendado: 1200x1500 (4:5), 1440x1080 (4:3) ou 1920x1080 (16:9). Mobile: 1200x1200 (1:1), 1080x1440 (3:4), 900x1200 (4:5), 1440x1080 (4:3), 1920x1080 (16:9). Desktop: 1200x1500 (4:5), 1440x1080 (4:3), 1920x1080 (16:9). Qualquer rácio é aceite mas pode causar letterboxing. GIF: duração recomendada 3-10s. Thumbnail (compact view, gerado automaticamente a partir da 1ª imagem ou substituível): recomendado 400x300 (4:3); aceite 300x300 (1:1).</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1, 3:4, 4:5, 4:3 ou 16:9 (qualquer rácio aceite; mesmo rácio recomendado em todas as imagens)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>20 MB por imagem; GIF 3 MB</t>
+          <t>GIF: 3 MB; Outros tipos: 20 MB; Thumbnail: 3 MB</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Título: até 300c, 1 (recomendado ≤100c, mais seguro ≤80c); URL de destino: até 268c, 1 por imagem; Legenda: até 50c, 1 por imagem; URL de exibição: até 100c, 1 por imagem (tem de corresponder ao domínio do destino); CTA: à escolha.</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/carousel-ads</t>
+          <t>https://business.reddithelp.com/s/article/carousel-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -11480,27 +11485,32 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Imagem: 1200x1200 (1:1) ou 1920x1080/1440x1080; vídeo conforme asset</t>
+          <t>Imagem (opcional): até 20 ficheiros, largura mín. recomendada 1000px; resoluções recomendadas 1200x1200 (1:1), 1440x1080 (4:3) ou 1920x1080 (16:9). Vídeo (opcional): até 5 ficheiros; duração recomendada 5-30s; resoluções recomendadas 1200x1200 (1:1), 1200x1500 (4:5), 1440x1080 (4:3) ou 1920x1080 (16:9). Thumbnail (opcional, NÃO gerado automaticamente — sem thumbnail não aparece media no feed): recomendado 400x300 ou 300x300 (1:1).</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1, 4:5, 4:3 ou 16:9 (qualquer rácio aceite)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Imagem ≤20 MB; vídeo ≤1 GB</t>
+          <t>Imagem: 10 MB; Vídeo: até 1 GB (recomendado 50-100 MB); Thumbnail: 3 MB</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF, MP4, MOV + rich text</t>
+          <t>Imagem: JPG, PNG ou GIF; Vídeo: MP4 ou MOV (ProRes não suportado), frame rate máx. 30 FPS; Thumbnail: JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Título: até 300c, 1 (recomendado ≤100c, mais seguro ≤80c); Corpo: até 40.000c, 1 (recomendado 3-6 linhas em texto simples no feed); Legenda: até 50c, 1 por imagem/vídeo.</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/free-form</t>
+          <t>https://business.reddithelp.com/s/article/free-form-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -11537,27 +11547,32 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>1080x1080 (1:1); 1080x1350 (4:5); 1440x1080 (4:3); 1920x1080 (16:9)</t>
+          <t>Imagem — Cross-device recomendado: 1440x1080 (4:3). Mobile: 1080x1080 (1:1), 1080x1440 (3:4), 1080x1350 (4:5), 1440x1080 (4:3), 1920x1080 (16:9). Desktop: 1440x1080, 1920x1080 (16:9). Qualquer rácio é aceite mas pode causar letterboxing. Thumbnail (só conversation/compact view, gerado automaticamente ou substituível): recomendado 400x300 (4:3); aceite 300x300 (1:1) ou 400x225 (16:9).</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>1:1 ou 4:5 ou 4:3 ou 16:9</t>
+          <t>1:1, 3:4, 4:5, 4:3 ou 16:9 (qualquer rácio aceite; recomendado 4:3 cross-device)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>3 MB</t>
+          <t>Imagem: 3 MB; Thumbnail: 3 MB</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (estático)</t>
+          <t>JPG, PNG ou GIF (thumbnail: GIF convertido para imagem estática)</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Título: até 300c (recomendado ≤100c, mais seguro ≤80c); URL de destino: até 268c; URL de exibição: até 100c (tem de corresponder ao domínio do destino); CTA: à escolha.</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/learning-hub/articles/reddit-image-ad-specs</t>
+          <t>https://business.reddithelp.com/s/article/image-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -11646,22 +11661,32 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>1:1 / 4:5 / 16:9; 1080p recomendado</t>
+          <t>Vídeo — Cross-device recomendado: 1440x1080 (4:3) ou 1920x1080 (16:9). Mobile: 1200x1200 (1:1), 900x1200 (3:4), 1200x1500 (4:5), 1440x1080 (4:3), 1920x1080 (16:9). Desktop: 1440x1080 (4:3), 1920x1080 (16:9). Qualquer rácio é aceite mas pode causar letterboxing. Duração: 2s a 15min (recomendado 5-30s). Thumbnail: resolução a acompanhar o rácio do vídeo (gerado automaticamente ou substituível).</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>1:1, 3:4, 4:5, 4:3 ou 16:9 (qualquer rácio aceite)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>Vídeo: até 1 GB; Thumbnail: 3 MB</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4 ou MOV (ProRes não suportado); frame rate máx. 30 FPS; thumbnail: JPG, PNG ou GIF</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Título: até 300c (recomendado ≤100c, mais seguro ≤80c); URL de destino: até 268c; URL de exibição: até 100c (tem de corresponder ao domínio do destino); CTA: à escolha.</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>https://www.business.reddit.com/advertise/ad-types/video-ads</t>
+          <t>https://business.reddithelp.com/s/article/video-ad-specifications</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -5761,7 +5761,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
+          <t>Landscape: 1280x720px, Portrait: 720x1280px</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1080x1080px (1:1) / 1920x1080px (16:9) / 1080x810px (4:3) / 819x1080px (3:4)</t>
+          <t>1080x1080px / 1920x1080px / 1080x810px / 819x1080px</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>640x360px com rácio de 16:9</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>640x360px com rácio de 16:9</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Up to 1200px, in a 1:1 ratio (display size is 300x300px), Logo: Minimum 40x40px, maximum 400x400px, 1:1 ratio</t>
+          <t>Up to 1200px (display size is 300x300px); Logo: minimum 40x40px, maximum 400x400px</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7009,7 +7009,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1:1 ratio, min 300px, max 1200px</t>
+          <t>Min 300px, max 1200px</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9189,7 +9194,8 @@
           <t>Single Video</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
         <is>
           <t>16:9</t>
         </is>
@@ -9822,7 +9828,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2560x1440 (16:9), 1080x1920</t>
+          <t>2560x1440, 1080x1920</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -10171,7 +10177,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>640x360px (16:9)</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -10228,7 +10234,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>640x360px (16:9)</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -10932,12 +10938,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Landscape: 1920x1080 recomendado (mín. 640x360, máx. 1920x1080); Square: mín. 360x360, máx. 1920x1920; Vertical 4:5: mín. 360x450, máx. 1080x1350; Vertical 9:16: 720x1280 recomendado (mín. 360x640, máx. 1080x1920). Duração: 3s a 30min (in-stream em streaming até 90s).</t>
+          <t>Landscape: 1920x1080 recomendado (mín. 640x360, máx. 1920x1080); Square: mín. 360x360, máx. 1920x1920; Vertical: mín. 360x450, máx. 1080x1350; Vertical: 720x1280 recomendado (mín. 360x640, máx. 1080x1920). Duração: 3s a 30min (in-stream em streaming até 90s).</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>16:9 ou 1:1 ou 4:5 ou 9:16</t>
+          <t>Landscape: 16:9; Square: 1:1; Vertical: 4:5; Vertical: 9:16</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11175,7 +11181,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Standard: 2 a 5 imagens, 1:1 ou 2:3; Sales (catálogo): 2 a 10 imagens/vídeos, dimensões herdadas do catálogo.</t>
+          <t>Standard: 2 a 5 imagens; Sales (catálogo): 2 a 10 imagens/vídeos, dimensões herdadas do catálogo.</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -11237,12 +11243,12 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hero: 1:1 ou 2:3 (pode diferir dos secundários); Secundários: mín. 3 recomendado, máx. 24, todos com o mesmo rácio entre si (1:1 ou 2:3); Hero em vídeo: duração mín. 4s, máx. 15min, rácio mais estreito que 1:2 e mais largo que 1,91:1 (recomendado 1:1, 2:3 ou 9:16).</t>
+          <t>Hero: pode diferir dos secundários; Secundários: mín. 3 recomendado, máx. 24, todos com o mesmo rácio entre si; Hero em vídeo: duração mín. 4s, máx. 15min.</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Hero: 1:1 ou 2:3; Secundários: 1:1 ou 2:3 (recomendado 1:1)</t>
+          <t>Hero: 1:1 ou 2:3; Hero vídeo: recomendado 1:1, 2:3 ou 9:16 (aceite entre 1:2 e 1,91:1); Secundários: 1:1 ou 2:3 (recomendado 1:1)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -11299,7 +11305,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Recomendado 1000x1500 (2:3). Pins com rácio superior a 2:3 podem ficar cortados no feed.</t>
+          <t>Recomendado 1000x1500. Pins com rácio superior ao recomendado podem ficar cortados no feed.</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -11361,7 +11367,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Duração: mín. 4s, máx. 15min (recomendado 6-15s para ads). Rácio: mais estreito que 1:2, mais largo que 1,91:1; recomendado quadrado (1:1) ou vertical (2:3, 4:5 ou 9:16).</t>
+          <t>Duração: mín. 4s, máx. 15min (recomendado 6-15s para ads).</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -11423,7 +11429,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2 a 6 imagens (mesmo rácio recomendado em todas). Cross-device recomendado: 1200x1500 (4:5), 1440x1080 (4:3) ou 1920x1080 (16:9). Mobile: 1200x1200 (1:1), 1080x1440 (3:4), 900x1200 (4:5), 1440x1080 (4:3), 1920x1080 (16:9). Desktop: 1200x1500 (4:5), 1440x1080 (4:3), 1920x1080 (16:9). Qualquer rácio é aceite mas pode causar letterboxing. GIF: duração recomendada 3-10s. Thumbnail (compact view, gerado automaticamente a partir da 1ª imagem ou substituível): recomendado 400x300 (4:3); aceite 300x300 (1:1).</t>
+          <t>2 a 6 imagens (mesmo rácio recomendado em todas). Cross-device recomendado: 1200x1500, 1440x1080 ou 1920x1080. Mobile: 1200x1200, 1080x1440, 900x1200, 1440x1080, 1920x1080. Desktop: 1200x1500, 1440x1080, 1920x1080. Qualquer rácio é aceite mas pode causar letterboxing. GIF: duração recomendada 3-10s. Thumbnail (compact view, gerado automaticamente a partir da 1ª imagem ou substituível): recomendado 400x300; aceite 300x300.</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -11485,7 +11491,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Imagem (opcional): até 20 ficheiros, largura mín. recomendada 1000px; resoluções recomendadas 1200x1200 (1:1), 1440x1080 (4:3) ou 1920x1080 (16:9). Vídeo (opcional): até 5 ficheiros; duração recomendada 5-30s; resoluções recomendadas 1200x1200 (1:1), 1200x1500 (4:5), 1440x1080 (4:3) ou 1920x1080 (16:9). Thumbnail (opcional, NÃO gerado automaticamente — sem thumbnail não aparece media no feed): recomendado 400x300 ou 300x300 (1:1).</t>
+          <t>Imagem (opcional): até 20 ficheiros, largura mín. recomendada 1000px; resoluções recomendadas 1200x1200, 1440x1080 ou 1920x1080. Vídeo (opcional): até 5 ficheiros; duração recomendada 5-30s; resoluções recomendadas 1200x1200, 1200x1500, 1440x1080 ou 1920x1080. Thumbnail (opcional, NÃO gerado automaticamente — sem thumbnail não aparece media no feed): recomendado 400x300 ou 300x300.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -11547,7 +11553,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Imagem — Cross-device recomendado: 1440x1080 (4:3). Mobile: 1080x1080 (1:1), 1080x1440 (3:4), 1080x1350 (4:5), 1440x1080 (4:3), 1920x1080 (16:9). Desktop: 1440x1080, 1920x1080 (16:9). Qualquer rácio é aceite mas pode causar letterboxing. Thumbnail (só conversation/compact view, gerado automaticamente ou substituível): recomendado 400x300 (4:3); aceite 300x300 (1:1) ou 400x225 (16:9).</t>
+          <t>Imagem — Cross-device recomendado: 1440x1080. Mobile: 1080x1080, 1080x1440, 1080x1350, 1440x1080, 1920x1080. Desktop: 1440x1080, 1920x1080. Qualquer rácio é aceite mas pode causar letterboxing. Thumbnail (só conversation/compact view, gerado automaticamente ou substituível): recomendado 400x300; aceite 300x300 ou 400x225.</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -11661,7 +11667,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Vídeo — Cross-device recomendado: 1440x1080 (4:3) ou 1920x1080 (16:9). Mobile: 1200x1200 (1:1), 900x1200 (3:4), 1200x1500 (4:5), 1440x1080 (4:3), 1920x1080 (16:9). Desktop: 1440x1080 (4:3), 1920x1080 (16:9). Qualquer rácio é aceite mas pode causar letterboxing. Duração: 2s a 15min (recomendado 5-30s). Thumbnail: resolução a acompanhar o rácio do vídeo (gerado automaticamente ou substituível).</t>
+          <t>Vídeo — Cross-device recomendado: 1440x1080 ou 1920x1080. Mobile: 1200x1200, 900x1200, 1200x1500, 1440x1080, 1920x1080. Desktop: 1440x1080, 1920x1080. Qualquer rácio é aceite mas pode causar letterboxing. Duração: 2s a 15min (recomendado 5-30s). Thumbnail: resolução a acompanhar o rácio do vídeo (gerado automaticamente ou substituível).</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -11775,7 +11781,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>720x1280 (9:16) por asset recomendado</t>
+          <t>720x1280 por asset recomendado</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -11832,7 +11838,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>720x1280</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -11889,7 +11895,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>720x1280</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -11946,7 +11952,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>720x1280</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -12003,7 +12009,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>720x1280</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -12060,7 +12066,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>720x1280 (9:16)</t>
+          <t>720x1280</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -12174,7 +12180,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Criativo final segue In-Feed/Spark Ads (vertical 9:16 recomendado)</t>
+          <t>Criativo final segue In-Feed/Spark Ads</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12283,7 +12294,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Vertical 9:16 recomendado; ≥540x960 recomendado</t>
+          <t>Vertical recomendado; ≥540x960 recomendado</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -12392,7 +12403,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Usa vídeo orgânico; para push, 9:16 ≥540x960 recomendado</t>
+          <t>Usa vídeo orgânico; para push, ≥540x960 recomendado</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -12449,7 +12460,12 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Segue criativo In-Feed; vertical 9:16 recomendado</t>
+          <t>Segue criativo In-Feed</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -12501,7 +12517,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>9:16; ≥540x960</t>
+          <t>≥540x960</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -12558,7 +12574,12 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>16:9 recomendado; vídeo HD</t>
+          <t>Vídeo HD</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -12610,7 +12631,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>800x800 (1:1) ou 800x418 (1.91:1) recomendado</t>
+          <t>800x800 ou 800x418 recomendado</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -12667,7 +12688,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hero 800x800 (1:1) recomendado + thumbnails de produtos</t>
+          <t>Hero 800x800 recomendado + thumbnails de produtos</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -12724,7 +12745,12 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Assets provenientes do catálogo; 1:1 recomendado</t>
+          <t>Assets provenientes do catálogo</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -12776,7 +12802,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>1200x1200 (1:1) ou 1200x628 (1.91:1) recomendado</t>
+          <t>1200x1200 ou 1200x628 recomendado</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -12937,7 +12963,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>1200x1200 (1:1) ou 1920x1080 (16:9) recomendado</t>
+          <t>1200x1200 ou 1920x1080 recomendado</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -13259,12 +13285,12 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 600x600 (mín. 300x300); Logo 1:1: 1200x1200 (mín. 128x128, opcional); Logo 4:1: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal 16:9, Square 1:1, Vertical 2:3; qualquer duração (recomendado 30s).</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical; qualquer duração (recomendado 30s).</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:1</t>
+          <t>Imagem — Horizontal: 1.91:1; Square: 1:1; Logo quadrado: 1:1; Logo horizontal: 4:1. Vídeo — Horizontal: 16:9; Square: 1:1; Vertical: 2:3.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -13373,12 +13399,12 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -13430,12 +13456,12 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+          <t>Recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -13487,12 +13513,12 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+          <t>Recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13544,7 +13570,12 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
+          <t>16 a 30 segundos; formato específico para Connected TV</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13596,7 +13627,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; 15 segundos recomendado.</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; 15 segundos recomendado.</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -13658,7 +13689,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>9:16 vertical: 1080x1920; 6 a 60 segundos</t>
+          <t>Vertical: 1080x1920; 6 a 60 segundos</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -13715,7 +13746,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -13772,7 +13803,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Logo 1:1: 1200x1200 (mín. 144x144); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional)</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Logo: 1200x1200 (mín. 144x144); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional)</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -13829,7 +13860,12 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Horizontal 16:9, Vertical 9:16 ou 4:5, Square 1:1; 10 a 60 segundos (opcional)</t>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos (opcional)</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -13881,7 +13917,12 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2 a 10 cartões, todos com a mesma proporção (1:1 ou 1.91:1)</t>
+          <t>2 a 10 cartões, todos com a mesma proporção entre si</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -14292,7 +14333,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -14376,12 +14417,12 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>IMAGEM — Logo: 100x100 a 2000x2000px (1:1); Imagem: 1200x627 a 2000x1047px (1.91:1); Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px (1:1). VÍDEO — Logo: 100x100 a 2000x2000px (1:1); Cover image: altura mín 627px, máx 2000x1047px (1.91:1 recomendado — para mais inventário, criar criativos adicionais com 16:9, 4:3 ou 1:1); Vídeo: ficheiro fonte com a maior qualidade disponível.</t>
+          <t>IMAGEM — Logo: 100x100 a 2000x2000px; Imagem: 1200x627 a 2000x1047px; Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px. VÍDEO — Logo: 100x100 a 2000x2000px; Cover image: altura mín 627px, máx 2000x1047px (recomendado; para mais inventário, criar criativos adicionais com outros rácios); Vídeo: ficheiro fonte com a maior qualidade disponível.</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>Logo: 1:1; Imagem: 1.91:1; Imagem quadrada: 1:1; Cover image: 1.91:1 (recomendado), 16:9, 4:3 ou 1:1 (adicionais para mais inventário)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -14492,12 +14533,12 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -14549,12 +14590,12 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -14660,7 +14701,12 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — 16:9 ou 9:16; recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — 16:9 ou 9:16; recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -14707,12 +14753,12 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, 16:9, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>1:1 ou 3:4</t>
+          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -14818,12 +14864,12 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16; recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14875,7 +14921,12 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal 16:9: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical 9:16: 1080x1920, 6 a 60 segundos (Shorts); Square 1:1: 1080x1080, 6 a 60 segundos.</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -14927,7 +14978,12 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal 16:9: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -16683,7 +16739,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>16:9, recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -16740,7 +16796,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Landscape – 16:9 (1280x720px), Portrait – 9:16 (720x1280px)</t>
+          <t>Landscape: 1280x720px, Portrait: 720x1280px</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -17124,7 +17180,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>640x360px com rácio de 16:9</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -17181,7 +17237,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>640x360px (16:9)</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -17374,7 +17430,12 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>16:9; 16 a 30 segundos; formato específico para Connected TV</t>
+          <t>16 a 30 segundos; formato específico para Connected TV</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -17458,7 +17519,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Vertical 4:5: 1200x1500 (mín. 320x400); Square 1:1: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -17515,7 +17576,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Horizontal 16:9, Vertical 9:16, Square 1:1; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -17572,7 +17633,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Horizontal 1.91:1: 1200x628 (mín. 600x314); Square 1:1: 1200x1200 (mín. 300x300); Vertical 4:5: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -17629,7 +17690,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Logo quadrado 1:1: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal 4:1: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
+          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -17686,7 +17747,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Horizontal 16:9, Square 1:1, Vertical 9:16; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -17743,7 +17804,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Logo 1:1: 1200x1200 (mín. 128x128)</t>
+          <t>Logo: 1200x1200 (mín. 128x128)</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -17800,7 +17861,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Square 1:1: 1200x1200 (mín. 300x300), obrigatório; Horizontal 1.91:1: 1200x628 (mín. 600x314), opcional</t>
+          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -17914,7 +17975,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Horizontal 16:9: 1920x1080; Vertical 9:16: 1080x1920; Square 1:1: 1080x1080; mín. 10 segundos.</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -17976,7 +18037,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>16:9: 1280x720 (mín. 1280x640)</t>
+          <t>1280x720 (mín. 1280x640)</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -18033,7 +18094,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>5:1: 300x60 (só em desktop)</t>
+          <t>300x60 (só em desktop)</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -18524,7 +18585,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888 (imagem de produto 1:1), capa + até 3 imagens de produto, Experiência Instantânea obrigatória.</t>
+          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L352"/>
+  <dimension ref="A1:L354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -9194,7 +9194,6 @@
           <t>Single Video</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>16:9</t>
@@ -11724,24 +11723,26 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AR Lenses Filters</t>
+          <t>AR Filters</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Filter estático 945x2048; animado 720x1560</t>
-        </is>
-      </c>
+          <t>Estático: 945x2048; Animado: 720x1560, duração 1 a 3 seg.</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Varia por asset AR</t>
+          <t>Varia por asset</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>PNG (filtro estático), GIF (animado); Lens assets conforme Lens Studio</t>
-        </is>
-      </c>
+          <t>PNG (estático), GIF (animado)</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
@@ -11838,7 +11839,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>720x1280</t>
+          <t>720x1280; duração de vídeo 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -11854,6 +11855,11 @@
       <c r="J218" t="inlineStr">
         <is>
           <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -11895,7 +11901,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>720x1280</t>
+          <t>720x1280. Standard: 3 a 6 seg, não saltável; Extended Play: 7 a 180 seg, só os primeiros 6 seg não saltáveis.</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -11910,7 +11916,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>MP4, MOV (H.264)</t>
+          <t>MP4 ou MOV (H.264)</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -11970,6 +11976,11 @@
           <t>JPG, PNG</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
@@ -12009,7 +12020,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>720x1280</t>
+          <t>720x1280; duração 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -12025,6 +12036,11 @@
       <c r="J221" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -12066,7 +12082,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>720x1280</t>
+          <t>720x1280; duração de vídeo 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -12082,6 +12098,11 @@
       <c r="J222" t="inlineStr">
         <is>
           <t>JPG, PNG, MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -18797,6 +18818,126 @@
       <c r="L352" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Snapchat</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Snapchat</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Branded Effects</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>AR Lenses</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Varia por asset AR</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Snapchat</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Snapchat</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Sponsored Snap</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Varia; validar no Ads Manager</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>MP4, MOV, JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L354"/>
+  <dimension ref="A1:L353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -11731,7 +11731,6 @@
           <t>Estático: 945x2048; Animado: 720x1560, duração 1 a 3 seg.</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Varia por asset</t>
@@ -11742,7 +11741,6 @@
           <t>PNG (estático), GIF (animado)</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
@@ -11772,17 +11770,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>720x1280 por asset recomendado</t>
+          <t>720x1280; duração de vídeo 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -11797,7 +11795,12 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV</t>
+          <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -11829,17 +11832,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Commercial Ad</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>720x1280; duração de vídeo 3 a 180 seg.</t>
+          <t>720x1280. Standard: 3 a 6 seg, não saltável; Extended Play: 7 a 180 seg, só os primeiros 6 seg não saltáveis.</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -11849,17 +11852,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV + catálogo/produtos</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
+          <t>MP4 ou MOV (H.264)</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -11891,17 +11889,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Commercial Ad</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>720x1280. Standard: 3 a 6 seg, não saltável; Extended Play: 7 a 180 seg, só os primeiros 6 seg não saltáveis.</t>
+          <t>720x1280</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -11916,7 +11914,12 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>MP4 ou MOV (H.264)</t>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -11948,17 +11951,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>720x1280</t>
+          <t>720x1280; duração 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -11973,7 +11976,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -12010,17 +12013,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>720x1280; duração 3 a 180 seg.</t>
+          <t>720x1280; duração de vídeo 3 a 180 seg.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -12030,12 +12033,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Varia; validar no Ads Manager</t>
+          <t>Varia por asset</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, MP4, MOV</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -12062,52 +12065,47 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Branded Effect</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>720x1280; duração de vídeo 3 a 180 seg.</t>
+          <t>Ícone 162x162 (safe 144x144); restantes assets conforme template</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Varia por asset</t>
+          <t>Ícone &lt;60 KB; restantes conforme template</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
+          <t>PNG + assets de efeito conforme template</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
         </is>
       </c>
     </row>
@@ -12134,37 +12132,37 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Branded Effects</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Branded Effect</t>
+          <t>Branded Mission</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Ícone 162x162 (safe 144x144); restantes assets conforme template</t>
+          <t>Criativo final segue In-Feed/Spark Ads</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Ícone &lt;60 KB; restantes conforme template</t>
+          <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>PNG + assets de efeito conforme template</t>
+          <t>Vídeo de creator elegível / Spark Ads</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
+          <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12191,37 +12189,37 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Branded Mission</t>
+          <t>Carousel Ads</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Criativo final segue In-Feed/Spark Ads</t>
+          <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1.91:1 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Conforme vídeo In-Feed/Spark</t>
+          <t>100 KB sugerido por imagem; música até 10 MB</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Vídeo de creator elegível / Spark Ads</t>
+          <t>JPG/JPEG, PNG + MP3</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12248,37 +12246,37 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Carousel Ads</t>
+          <t>In-Feed (Standard Feed)</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>1200x628 horizontal; 640x640 square; 720x1280 vertical</t>
+          <t>Vertical recomendado; ≥540x960 recomendado</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 9:16</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>100 KB sugerido por imagem; música até 10 MB</t>
+          <t>Até 500 MB (reservation); limites podem variar em auction</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>JPG/JPEG, PNG + MP3</t>
+          <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12310,32 +12308,27 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>In-Feed (Standard Feed)</t>
+          <t>Pulse</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Vertical recomendado; ≥540x960 recomendado</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>9:16</t>
+          <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Até 500 MB (reservation); limites podem variar em auction</t>
+          <t>Conforme vídeo In-Feed/Spark</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>MP4, MOV, MPEG, 3GP</t>
+          <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
         </is>
       </c>
     </row>
@@ -12367,27 +12360,32 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pulse</t>
+          <t>Spark Ads</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Segue especificações de vídeo In-Feed/Spark Ads</t>
+          <t>Usa vídeo orgânico; para push, ≥540x960 recomendado</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Conforme vídeo In-Feed/Spark</t>
+          <t>Até 500 MB para push</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>MP4, MOV / Spark Ads</t>
+          <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12419,12 +12417,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spark Ads</t>
+          <t>Top Feed</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Usa vídeo orgânico; para push, ≥540x960 recomendado</t>
+          <t>Segue criativo In-Feed</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -12434,17 +12432,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Até 500 MB para push</t>
+          <t>Conforme In-Feed</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
+          <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12476,12 +12474,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Top Feed</t>
+          <t>TopView</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Segue criativo In-Feed</t>
+          <t>≥540x960</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -12491,17 +12489,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Conforme In-Feed</t>
+          <t>500 MB</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>MP4, MOV / Spark Ads</t>
+          <t>MP4, MOV, MPEG, 3GP</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
+          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
       </c>
     </row>
@@ -12518,47 +12516,47 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>TopView</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>≥540x960</t>
+          <t>Vídeo HD</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>500 MB</t>
+          <t>1 GB recomendado/limite conforme placement</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>MP4, MOV, MPEG, 3GP</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
@@ -12585,32 +12583,32 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Vídeo HD</t>
+          <t>800x800 ou 800x418 recomendado</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>1 GB recomendado/limite conforme placement</t>
+          <t>5 MB por imagem; vídeo conforme specs</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG; MP4/MOV para video carousel</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -12642,32 +12640,32 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Carousel Ad</t>
+          <t>Collection Ad</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>800x800 ou 800x418 recomendado</t>
+          <t>Hero 800x800 recomendado + thumbnails de produtos</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>5 MB por imagem; vídeo conforme specs</t>
+          <t>5 MB por imagem</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>JPG, PNG; MP4/MOV para video carousel</t>
+          <t>JPG, PNG + catálogo</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -12699,17 +12697,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Catalog Ad</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Collection Ad</t>
+          <t>Dynamic Product Ads</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hero 800x800 recomendado + thumbnails de produtos</t>
+          <t>Assets provenientes do catálogo</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -12719,12 +12717,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>5 MB por imagem</t>
+          <t>Conforme catálogo</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>JPG, PNG + catálogo</t>
+          <t>Feed/catálogo + JPG/PNG</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -12756,32 +12754,32 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Catalog Ad</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dynamic Product Ads</t>
+          <t>Image Ad</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Assets provenientes do catálogo</t>
+          <t>1200x1200 ou 1200x628 recomendado</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Conforme catálogo</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Feed/catálogo + JPG/PNG</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -12813,32 +12811,27 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Image Ad</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>1200x1200 ou 1200x628 recomendado</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>Depende do produto (Timeline/Trend Takeover); assets conforme ficha X</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Conforme formato</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, PNG, MP4/MOV conforme takeover</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -12870,27 +12863,27 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Text Ad</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Depende do produto (Timeline/Trend Takeover); assets conforme ficha X</t>
+          <t>Sem asset gráfico obrigatório</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Conforme formato</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4/MOV conforme takeover</t>
+          <t>Texto/post + URL opcional</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -12922,27 +12915,32 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Text Ad</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Sem asset gráfico obrigatório</t>
+          <t>1200x1200 ou 1920x1080 recomendado</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>1:1 ou 16:9</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1 GB</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Texto/post + URL opcional</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -12959,52 +12957,47 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Medium Rectangle</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>1200x1200 ou 1920x1080 recomendado</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>1:1 ou 16:9</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -13036,17 +13029,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Medium Rectangle</t>
+          <t>Large Rectangle</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>336x280</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -13083,17 +13076,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Large Rectangle</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>336x280</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -13135,17 +13128,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Half Page</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -13187,22 +13185,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Half Page</t>
+          <t>Mobile Banner</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>320x50</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -13244,27 +13237,32 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Mobile Banner</t>
+          <t>Responsive Display Ads (imagem)</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>320x50</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical; qualquer duração (recomendado 30s).</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Imagem — Horizontal: 1.91:1; Square: 1:1; Logo quadrado: 1:1; Logo horizontal: 4:1. Vídeo — Horizontal: 16:9; Square: 1:1; Vertical: 2:3.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -13296,32 +13294,32 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Responsive Display Ads (imagem)</t>
+          <t>HTML5 Display</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical; qualquer duração (recomendado 30s).</t>
+          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Imagem — Horizontal: 1.91:1; Square: 1:1; Logo quadrado: 1:1; Logo horizontal: 4:1. Vídeo — Horizontal: 16:9; Square: 1:1; Vertical: 2:3.</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>150 KB (dentro do HTML5)</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>ZIP HTML5</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -13343,47 +13341,47 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>HTML5 Display</t>
+          <t>Skippable In-Stream</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>150 KB (dentro do HTML5)</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>ZIP HTML5</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13415,12 +13413,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Skippable In-Stream</t>
+          <t>Non-skippable In-Stream (standard)</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -13430,17 +13428,17 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13472,12 +13470,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Non-skippable In-Stream (standard)</t>
+          <t>Bumper</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+          <t>Recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -13524,22 +13522,22 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Bumper</t>
+          <t>Non-skippable 30s (Connected TV)</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+          <t>16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13581,22 +13579,22 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Non-skippable 30s (Connected TV)</t>
+          <t>In-Feed Video Ad (ex-Discovery)</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>16 a 30 segundos; formato específico para Connected TV</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; 15 segundos recomendado.</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13609,9 +13607,14 @@
           <t>MP4, MOV</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13638,22 +13641,22 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>In-Feed Video Ad (ex-Discovery)</t>
+          <t>YouTube Shorts Ads</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; 15 segundos recomendado.</t>
+          <t>Vertical: 1080x1920; 6 a 60 segundos</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -13664,11 +13667,6 @@
       <c r="J250" t="inlineStr">
         <is>
           <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -13700,22 +13698,22 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Vertical Video</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>YouTube Shorts Ads</t>
+          <t>Masthead</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Vertical: 1080x1920; 6 a 60 segundos</t>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -13747,47 +13745,47 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Masthead</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Logo: 1200x1200 (mín. 144x144); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional)</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -13814,32 +13812,32 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Logo: 1200x1200 (mín. 144x144); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional)</t>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos (opcional)</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>16:9 ou 9:16 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (não animado)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -13871,32 +13869,37 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos (opcional)</t>
+          <t>2 a 10 cartões, todos com a mesma proporção entre si</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 4:5 ou 1:1</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB por imagem</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Título por cartão: até 40 caracteres</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -13908,62 +13911,27 @@
     <row r="255" ht="25" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>Carousel</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Carousel</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>2 a 10 cartões, todos com a mesma proporção entre si</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>5 MB por imagem</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Título por cartão: até 40 caracteres</t>
-        </is>
-      </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>Prog - App Install</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13958,22 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Prog - App Install</t>
+          <t>Prog - Audio Ad</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>1 MB</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>MP3</t>
         </is>
       </c>
     </row>
@@ -14017,22 +14000,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Prog - Audio Ad</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>1 MB</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>MP3</t>
+          <t>Prog - Audio Ingame</t>
         </is>
       </c>
     </row>
@@ -14059,7 +14027,22 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Prog - Audio Ingame</t>
+          <t>Prog - Banner</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>300x250, 300x600, 728x90, 320x50</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>200 KB</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
     </row>
@@ -14086,22 +14069,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Prog - Banner</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>300x250, 300x600, 728x90, 320x50</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>Prog - Banner Ingame</t>
         </is>
       </c>
     </row>
@@ -14128,7 +14096,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Prog - Banner Ingame</t>
+          <t>Prog - Banner Mobile</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14123,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Prog - Banner Mobile</t>
+          <t>Prog - Conversational Display</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14150,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Prog - Conversational Display</t>
+          <t>Prog - Demand Gen</t>
         </is>
       </c>
     </row>
@@ -14204,12 +14172,12 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>DOOH</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Prog - Demand Gen</t>
+          <t>Prog - DOOH</t>
         </is>
       </c>
     </row>
@@ -14231,12 +14199,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DOOH</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Prog - DOOH</t>
+          <t>Prog - Expositor</t>
         </is>
       </c>
     </row>
@@ -14263,7 +14231,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Prog - Expositor</t>
+          <t>Prog - In Content</t>
         </is>
       </c>
     </row>
@@ -14290,7 +14258,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Prog - In Content</t>
+          <t>Prog - inRead Carousel</t>
         </is>
       </c>
     </row>
@@ -14312,12 +14280,42 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Prog - inRead Carousel</t>
+          <t>Prog - YouTube Masthead</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14339,42 +14337,17 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Open Door</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Prog - YouTube Masthead</t>
+          <t>Prog - M-Rec</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>300x250</t>
         </is>
       </c>
     </row>
@@ -14401,12 +14374,37 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Prog - M-Rec</t>
+          <t>Prog - Native Ad</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>IMAGEM — Logo: 100x100 a 2000x2000px; Imagem: 1200x627 a 2000x1047px; Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px. VÍDEO — Logo: 100x100 a 2000x2000px; Cover image: altura mín 627px, máx 2000x1047px (recomendado; para mais inventário, criar criativos adicionais com outros rácios); Vídeo: ficheiro fonte com a maior qualidade disponível.</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Logo: 1:1; Imagem: 1.91:1; Imagem quadrada: 1:1; Cover image: 1.91:1 (recomendado), 16:9, 4:3 ou 1:1 (adicionais para mais inventário)</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Igual para imagem e vídeo — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
         </is>
       </c>
     </row>
@@ -14433,37 +14431,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Prog - Native Ad</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>IMAGEM — Logo: 100x100 a 2000x2000px; Imagem: 1200x627 a 2000x1047px; Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px. VÍDEO — Logo: 100x100 a 2000x2000px; Cover image: altura mín 627px, máx 2000x1047px (recomendado; para mais inventário, criar criativos adicionais com outros rácios); Vídeo: ficheiro fonte com a maior qualidade disponível.</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Logo: 1:1; Imagem: 1.91:1; Imagem quadrada: 1:1; Cover image: 1.91:1 (recomendado), 16:9, 4:3 ou 1:1 (adicionais para mais inventário)</t>
-        </is>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>Igual para imagem e vídeo — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
+          <t>Prog - Rewarded Video</t>
         </is>
       </c>
     </row>
@@ -14490,7 +14458,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Prog - Rewarded Video</t>
+          <t>Prog - Rich Media</t>
         </is>
       </c>
     </row>
@@ -14512,12 +14480,42 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Prog - Rich Media</t>
+          <t>Prog - YouTube Select</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14547,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Prog - YouTube Select</t>
+          <t>Prog - YouTube VRC Ad Sequence</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -14596,42 +14594,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Ad Sequence</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>MP4, MOV (upload via YouTube)</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - Skyscraper</t>
         </is>
       </c>
     </row>
@@ -14658,7 +14626,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Prog - Skyscraper</t>
+          <t>Prog - Social Display</t>
         </is>
       </c>
     </row>
@@ -14680,12 +14648,42 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Prog - Social Display</t>
+          <t>Prog - YouTube VRC Non-Skippable</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14707,42 +14705,37 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Non-Skippable</t>
+          <t>Prog - Uber Journey Ad</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>Display: imagens. Video: MP4.</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
         </is>
       </c>
     </row>
@@ -14764,37 +14757,12 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Prog - Uber Journey Ad</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>Display: imagens. Video: MP4.</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+          <t>Prog - Spotify Video Takeover</t>
         </is>
       </c>
     </row>
@@ -14816,12 +14784,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Prog - Spotify Video Takeover</t>
+          <t>Prog - Wallpaper</t>
         </is>
       </c>
     </row>
@@ -14843,12 +14811,42 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Prog - Wallpaper</t>
+          <t>Prog - YouTube VVC</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14880,17 +14878,17 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Prog - YouTube VVC</t>
+          <t>Prog - YouTube VRC Efficient Reach</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14900,12 +14898,12 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14937,17 +14935,17 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Efficient Reach</t>
+          <t>Prog - YouTube VRC Target Frequency</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -14984,42 +14982,37 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Target Frequency</t>
+          <t>Prog - Billboard (Impresa)</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>970x250, 320x10</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG ou PNG</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15034,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -15051,27 +15044,27 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Impresa)</t>
+          <t>Prog - Billboard (Media Capital)</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>970x250, 320x10</t>
+          <t>980x250 ou 970x250</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
+          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15086,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -15103,27 +15096,27 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Media Capital)</t>
+          <t>Prog - Billboard (Observador)</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>980x250 ou 970x250</t>
+          <t>1200x220, 970x250</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
+          <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15145,7 +15138,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -15155,27 +15148,27 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Observador)</t>
+          <t>Prog - Billboard (Público)</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>1200x220, 970x250</t>
+          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/manchete-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
       </c>
     </row>
@@ -15197,7 +15190,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -15207,27 +15200,22 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Público)</t>
+          <t>Prog - Billboard (Sapo)</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
+          <t>970x250</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>120 KB</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
       </c>
     </row>
@@ -15249,22 +15237,27 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Sapo)</t>
+          <t>Prog - Half-Page (Impresa)</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -15272,9 +15265,14 @@
           <t>200 KB</t>
         </is>
       </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>HTML, JPG, PNG ou GIF</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15294,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -15306,7 +15304,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Impresa)</t>
+          <t>Prog - Half-Page (Media Capital)</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -15321,17 +15319,17 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
+          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15351,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -15363,7 +15361,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Capital)</t>
+          <t>Prog - Half-Page (Media Livre)</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -15378,17 +15376,17 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>80 KB / 2 MB</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
       </c>
     </row>
@@ -15410,7 +15408,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -15420,7 +15418,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Livre)</t>
+          <t>Prog - Half-Page (Observador)</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -15435,17 +15433,17 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>80 KB / 2 MB</t>
+          <t>100 KB / 2 MB</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF / MP4</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
+          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15467,7 +15465,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -15477,7 +15475,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Observador)</t>
+          <t>Prog - Half-Page (Público)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -15492,17 +15490,17 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>100 KB / 2 MB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15522,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -15534,7 +15532,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Público)</t>
+          <t>Prog - Half-Page (Sapo)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -15549,17 +15547,17 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>200 KB / 3.5 MB</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15579,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -15591,7 +15589,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Sapo)</t>
+          <t>Prog - Half-Page (Google)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -15606,17 +15604,17 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>200 KB / 3.5 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -15638,27 +15636,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Google)</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>Prog - Header XL (Impresa)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -15668,12 +15656,12 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15683,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -15705,7 +15693,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Impresa)</t>
+          <t>Prog - Header XL (Media Livre)</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -15715,12 +15708,12 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15735,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -15752,27 +15745,27 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Media Livre)</t>
+          <t>Prog - Header XL (Observador)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
+          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
+          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15787,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -15804,27 +15797,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Observador)</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>500 KB</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
+          <t>Prog - Header XL (Sapo)</t>
         </is>
       </c>
     </row>
@@ -15846,17 +15819,42 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Sapo)</t>
+          <t>Prog - Intro (Impresa)</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>600x400, 320x480</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>3:2 ou 2:3</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>150 KB</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -15878,7 +15876,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -15888,17 +15886,17 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Prog - Intro (Impresa)</t>
+          <t>Prog - Intro (Media Capital)</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>600x400, 320x480</t>
+          <t>800x600</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>3:2 ou 2:3</t>
+          <t>4:3</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -15908,12 +15906,12 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
+          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15933,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -15945,32 +15943,32 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Capital)</t>
+          <t>Prog - Intro (Media Livre)</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>800x600</t>
+          <t>800x600, 768x1024</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>4:3</t>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>120 KB / 1 MB</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15990,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -16002,32 +16000,27 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Livre)</t>
+          <t>Prog - Intro (Observador)</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
+          <t>990x600, 300x480</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>120 KB / 1 MB</t>
+          <t>120 KB, 75 KB / 2 MB</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
+          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16042,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -16059,27 +16052,32 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Prog - Intro (Observador)</t>
+          <t>Prog - Intro (Público)</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>990x600, 300x480</t>
+          <t>800x600, 768x1024</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>120 KB, 75 KB / 2 MB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16099,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -16111,32 +16109,32 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Prog - Intro (Público)</t>
+          <t>Prog - Intro (Sapo)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
+          <t>800x600px (600x400px recomendado)</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>4:3 ou 3:4</t>
+          <t>4:3 ou 3:2</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
       </c>
     </row>
@@ -16158,42 +16156,37 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Prog - Intro (Sapo)</t>
+          <t>Prog - Leaderboard (Media Capital)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>800x600px (600x400px recomendado)</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:2</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
+          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -16215,7 +16208,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -16225,7 +16218,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Capital)</t>
+          <t>Prog - Leaderboard (Media Livre)</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -16235,17 +16228,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -16267,7 +16260,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -16277,27 +16270,27 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Livre)</t>
+          <t>Prog - Leaderboard (Público)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>1140x50</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16312,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -16329,12 +16322,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Público)</t>
+          <t>Prog - Leaderboard (Sapo)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>1140x50</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -16344,12 +16337,12 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>WEBP</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16364,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -16381,7 +16374,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Sapo)</t>
+          <t>Prog - Leaderboard (Google)</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -16391,17 +16384,17 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>WEBP</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -16423,37 +16416,42 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Google)</t>
+          <t>Prog - Open Door (Impresa)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>1920x1080, 680x1520</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB, 150 KB</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16473,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -16485,7 +16483,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Impresa)</t>
+          <t>Prog - Open Door (Media Capital)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -16500,17 +16498,17 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>200 KB, 150 KB</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
+          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16530,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -16542,12 +16540,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Capital)</t>
+          <t>Prog - Open Door (Media Livre)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>1920x1080, 680x1520</t>
+          <t>950x700, 390x850 / 640x360</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -16557,17 +16555,17 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>500 KB / 2 MB</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
       </c>
     </row>
@@ -16589,7 +16587,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -16599,32 +16597,22 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Livre)</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>950x700, 390x850 / 640x360</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Prog - Open Door (Observador)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>500 KB / 2 MB</t>
+          <t>Máxima resolução</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG / MP4</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
+          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16646,7 +16634,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -16656,22 +16644,27 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Observador)</t>
+          <t>Prog - Open Door (Público)</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>800x900</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Máxima resolução</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPG / Video</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16693,7 +16686,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -16703,27 +16696,32 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Público)</t>
+          <t>Prog - Open Door (Google)</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>800x900</t>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>JPG / Video</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -16745,42 +16743,42 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Parallax</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Google)</t>
+          <t>Prog - Parallax (Público)</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Landscape: 1280x720px, Portrait: 720x1280px</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
       </c>
     </row>
@@ -16802,42 +16800,32 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Parallax</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Prog - Parallax (Público)</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>Landscape: 1280x720px, Portrait: 720x1280px</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16</t>
+          <t>Prog - Peel off (Media Capital)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>Imagens</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
+          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16847,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -16869,22 +16857,27 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Capital)</t>
+          <t>Prog - Peel off (Media Livre)</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>200x200, 850x650</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>40 KB</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>Imagens</t>
+          <t>260 KB</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
       </c>
     </row>
@@ -16906,7 +16899,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -16916,12 +16909,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Livre)</t>
+          <t>Prog - Peel off (Observador)</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>200x200, 850x650</t>
+          <t>200x200, 850x650px</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -16931,12 +16924,17 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>260 KB</t>
+          <t>120 KB / 2 MB</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
+          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16958,42 +16956,42 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Observador)</t>
+          <t>Prog - Pre-Roll (Media Capital)</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>200x200, 850x650px</t>
+          <t>1280x720</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>6 MB</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17013,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -17025,12 +17023,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Capital)</t>
+          <t>Prog - Pre-Roll (Media Livre)</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>1280x720</t>
+          <t>640x360</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -17040,17 +17038,17 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>6 MB</t>
+          <t>15 MB</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>MP4 ou FLV</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -17072,7 +17070,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -17082,7 +17080,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Livre)</t>
+          <t>Prog - Pre-Roll (Observador)</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -17097,17 +17095,17 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>15 MB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>MP4 ou FLV</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
+          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
       </c>
     </row>
@@ -17129,7 +17127,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -17139,12 +17137,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Observador)</t>
+          <t>Prog - Pre-Roll (Público)</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>640x360</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -17159,12 +17157,12 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>MP4 ou WEBM</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
       </c>
     </row>
@@ -17186,7 +17184,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -17196,7 +17194,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Público)</t>
+          <t>Prog - Pre-Roll (Sapo)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -17211,17 +17209,17 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>3.5 MB</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>MP4 ou WEBM</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
       </c>
     </row>
@@ -17243,42 +17241,37 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Sapo)</t>
+          <t>Prog - Takeover (Media Capital)</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>640x360px</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>650x350</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>3.5 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
+          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17293,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -17310,27 +17303,27 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Media Capital)</t>
+          <t>Prog - Takeover (Público)</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>650x350</t>
+          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
       </c>
     </row>
@@ -17352,37 +17345,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Público)</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>500 KB</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF / Video para a área expandida</t>
-        </is>
-      </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
+          <t>Prog - Connected TV (Sapo)</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17377,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -17414,7 +17387,32 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Sapo)</t>
+          <t>Prog - Connected TV (Google)</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>16 a 30 segundos; formato específico para Connected TV</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -17436,7 +17434,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -17446,64 +17444,64 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Google)</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>16 a 30 segundos; formato específico para Connected TV</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>Prog - CTV First Screen (Sapo)</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Prog - CTV First Screen (Sapo)</t>
+          <t>Imagem</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 4:5 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>5 MB</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
@@ -17530,32 +17528,32 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>1.91:1 ou 4:5 ou 1:1</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -17577,47 +17575,47 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5120 KB</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -17644,22 +17642,22 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>1:1 ou 4:1</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -17701,32 +17699,32 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
+          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>1:1 ou 4:1</t>
+          <t>16:9 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>5120 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -17748,47 +17746,47 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Business Information (Logo)</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+          <t>Logo: 1200x1200 (mín. 128x128)</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>16:9 ou 1:1 ou 9:16</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
@@ -17815,22 +17813,22 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Ad Assets</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Business Information (Logo)</t>
+          <t>Ad Assets (Imagens)</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Logo: 1200x1200 (mín. 128x128)</t>
+          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -17872,37 +17870,37 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Ad Assets</t>
+          <t>Responsive Search Ad</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Ad Assets (Imagens)</t>
+          <t>Responsive Search Ads</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>N/A (só texto, sem imagem)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>não especificado</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>N/A (texto)</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
+          <t>https://support.google.com/google-ads/answer/7684791</t>
         </is>
       </c>
     </row>
@@ -17919,47 +17917,52 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Responsive Search Ad</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Responsive Search Ads</t>
+          <t>Video Action Campaigns</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>N/A (só texto, sem imagem)</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>N/A (texto)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/7684791</t>
+          <t>https://support.google.com/google-ads/answer/12066387</t>
         </is>
       </c>
     </row>
@@ -17986,42 +17989,37 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Thumbnail</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Video Action Campaigns</t>
+          <t>Thumbnail (vídeo)</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
+          <t>1280x720 (mín. 1280x640)</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12066387</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -18048,27 +18046,27 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Thumbnail</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Thumbnail (vídeo)</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>1280x720 (mín. 1280x640)</t>
+          <t>300x60 (só em desktop)</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
+          <t>&lt; 150 KB</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
@@ -18090,52 +18088,57 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>300x60 (só em desktop)</t>
+          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>&lt; 150 KB</t>
+          <t>30 MB</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -18162,17 +18165,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
+          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -18182,17 +18185,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>30 MB</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -18224,37 +18227,37 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
+          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
+          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>Imagem: 30 MB por cartão</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
+          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -18286,37 +18289,37 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
+          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
+          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB por cartão</t>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
+          <t>JPG, PNG, MP4, MOV ou GIF</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -18338,47 +18341,47 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
+          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
+          <t>30 MB</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV ou GIF</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
+          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -18410,37 +18413,37 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
+          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
+          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>30 MB</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
+          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -18472,37 +18475,37 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
+          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
+          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>Imagem: 30 MB por cartão</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
+          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -18534,37 +18537,37 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
+          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
+          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB por cartão</t>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
+          <t>JPG, PNG, MP4 ou MOV</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -18586,52 +18589,52 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Idea Ad</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
+          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
+          <t>9:16 (recomendado, sem restrição rígida)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
+          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4 ou MOV</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
+          <t>Título: até 100c; Texto na página: até 250c.</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -18663,32 +18666,32 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Idea Ad</t>
+          <t>Showcase Ad</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
+          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>9:16 (recomendado, sem restrição rígida)</t>
+          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
+          <t>Até 32 MB</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Título: até 100c; Texto na página: até 250c.</t>
+          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -18725,17 +18728,17 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Showcase Ad</t>
+          <t>Quiz Ad</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
+          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
+          <t>Title Pin: 2:3; Results Pin: 2:3</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -18750,7 +18753,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
+          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -18772,52 +18775,47 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Quiz Ad</t>
+          <t>AR Lenses</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>Title Pin: 2:3; Results Pin: 2:3</t>
+          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>Até 32 MB</t>
+          <t>Varia por asset AR</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
+          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
+          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -18844,98 +18842,40 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Branded Effects</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>AR Lenses</t>
+          <t>Sponsored Snap</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr"/>
+          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>9:16</t>
+        </is>
+      </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>Varia por asset AR</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
+          <t>MP4, MOV, JPG ou PNG</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
+          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
-        <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>Sponsored Snap</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>Varia; validar no Ads Manager</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>MP4, MOV, JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
-        </is>
-      </c>
-      <c r="L354" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L353"/>
+  <dimension ref="A1:L350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -12526,32 +12526,37 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Vídeo HD</t>
+          <t>2 a 6 slides (imagens ou vídeos). Image Carousels: 800x800 recomendado; Video Carousels: 800x450 recomendado. Rácio único em todos os slides do carrossel; conteúdo misto tem de manter o mesmo rácio entre asset de imagem e de vídeo.</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1, 1.91:1, 4:5, 2:3, 16:9 ou 9:16 (rácio único por carrossel)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>1 GB recomendado/limite conforme placement</t>
+          <t>Imagem: até 5 MB; Vídeo: até 1 GB (recomendado &lt;30 MB)</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG (image carousel); MP4, MOV (video carousel)</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>1 destino (Carousel de destino único) ou até 6 destinos únicos (Carousel multi-destino).</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -12583,17 +12588,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Carousel Ad</t>
+          <t>Image Ad</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>800x800 ou 800x418 recomendado</t>
+          <t>1200x1200 ou 1200x628 recomendado</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -12603,12 +12608,17 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>5 MB por imagem; vídeo conforme specs</t>
+          <t>Máx. 5 MB</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>JPG, PNG; MP4/MOV para video carousel</t>
+          <t>PNG ou JPEG recomendado (BMP e TIFF não aceites; GIF carregado é convertido em imagem estática)</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -12640,32 +12650,32 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Collection Ad</t>
+          <t>Text Ad</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hero 800x800 recomendado + thumbnails de produtos</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>1:1</t>
+          <t>Sem asset gráfico obrigatório</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>5 MB por imagem</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>JPG, PNG + catálogo</t>
+          <t>Texto/post + URL opcional</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -12697,32 +12707,37 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Catalog Ad</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Dynamic Product Ads</t>
+          <t>Video Ad</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Assets provenientes do catálogo</t>
+          <t>1200x1200 ou 1920x1080 recomendado. Duração recomendada ≤15s (até 2:20 suportado; alguns anunciantes elegíveis para até 10min, recomendado não ultrapassar 9:55). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (até 60 FPS aceite, não fazer upsample). Thumbnail: rácio igual ao do vídeo, máx. 5 MB. Loop automático se duração &lt;60s. Branding (logo) recomendado persistente no canto superior esquerdo; legendas/closed captions fortemente recomendadas.</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1 ou 16:9</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Conforme catálogo</t>
+          <t>Máx. 1 GB (recomendado manter abaixo de 30 MB para melhor desempenho)</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Feed/catálogo + JPG/PNG</t>
+          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC; thumbnail PNG ou JPEG</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -12739,52 +12754,47 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Image Ad</t>
+          <t>Medium Rectangle</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>1200x1200 ou 1200x628 recomendado</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>300x250</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -12796,47 +12806,47 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Mrec</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Large Rectangle</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Depende do produto (Timeline/Trend Takeover); assets conforme ficha X</t>
+          <t>336x280</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Conforme formato</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4/MOV conforme takeover</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -12848,47 +12858,47 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Text Ad</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Sem asset gráfico obrigatório</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Texto/post + URL opcional</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -12900,52 +12910,52 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Paid Social</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Google Display Network</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Video Ad</t>
+          <t>Half Page</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>1200x1200 ou 1920x1080 recomendado</t>
+          <t>300x600</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>1:1 ou 16:9</t>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>1 GB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -12972,22 +12982,22 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Medium Rectangle</t>
+          <t>Mobile Banner</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>320x50</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>150 KB (imagem estática); até 5 MB em Responsive/Performance Max</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -13024,27 +13034,32 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mrec</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Large Rectangle</t>
+          <t>Responsive Display Ads (imagem)</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>336x280</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical; qualquer duração (recomendado 30s).</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Imagem — Horizontal: 1.91:1; Square: 1:1; Logo quadrado: 1:1; Logo horizontal: 4:1. Vídeo — Horizontal: 16:9; Square: 1:1; Vertical: 2:3.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -13076,27 +13091,32 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Rich Media</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>HTML5 Display</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>150 KB (dentro do HTML5)</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>ZIP HTML5</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -13118,47 +13138,47 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Half Page</t>
+          <t>Skippable In-Stream</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13175,42 +13195,47 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Mobile Banner</t>
+          <t>Non-skippable In-Stream (standard)</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>320x50</t>
+          <t>Recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13227,47 +13252,47 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Responsive Display Ads (imagem)</t>
+          <t>Bumper</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Square: 600x600 (mín. 300x300); Logo quadrado: 1200x1200 (mín. 128x128, opcional); Logo horizontal: 1200x300 (mín. 512x128, opcional). VÍDEO (opcional) — Horizontal, Square, Vertical; qualquer duração (recomendado 30s).</t>
+          <t>Recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Imagem — Horizontal: 1.91:1; Square: 1:1; Logo quadrado: 1:1; Logo horizontal: 4:1. Vídeo — Horizontal: 16:9; Square: 1:1; Vertical: 2:3.</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13284,47 +13309,47 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Google Display Network</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Rich Media</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>HTML5 Display</t>
+          <t>Non-skippable 30s (Connected TV)</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Tamanhos standard (ex.: 300x250, 728x90, 300x600) dentro do pacote</t>
+          <t>16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>150 KB (dentro do HTML5)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>ZIP HTML5</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13351,32 +13376,37 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>In-Feed Video</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Skippable In-Stream</t>
+          <t>In-Feed Video Ad (ex-Discovery)</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; 15 segundos recomendado.</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -13408,22 +13438,22 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Non-skippable In-Stream (standard)</t>
+          <t>YouTube Shorts Ads</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; 7 a 15 segundos; não saltável</t>
+          <t>Vertical: 1080x1920; 6 a 60 segundos</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -13438,7 +13468,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13465,22 +13495,22 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Bumper</t>
+          <t>Masthead</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável</t>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -13495,7 +13525,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13512,47 +13542,47 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Non-skippable 30s (Connected TV)</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>16 a 30 segundos; formato específico para Connected TV</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Logo: 1200x1200 (mín. 144x144); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional)</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -13569,32 +13599,32 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>In-Feed Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>In-Feed Video Ad (ex-Discovery)</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; 15 segundos recomendado.</t>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos (opcional)</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>16:9 ou 9:16 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13607,14 +13637,9 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
@@ -13631,280 +13656,190 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Demand Gen</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Vertical Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>YouTube Shorts Ads</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Vertical: 1080x1920; 6 a 60 segundos</t>
+          <t>2 a 10 cartões, todos com a mesma proporção entre si</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5 MB por imagem</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Título por cartão: até 40 caracteres</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
       </c>
     </row>
     <row r="251" ht="37.5" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Open Door</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Masthead</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - App Install</t>
         </is>
       </c>
     </row>
     <row r="252" ht="25" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>Single Image</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Prog - Audio Ad</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Logo: 1200x1200 (mín. 144x144); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional)</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>1 MB</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF (não animado)</t>
-        </is>
-      </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>MP3</t>
         </is>
       </c>
     </row>
     <row r="253" ht="25" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>Single Video</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos (opcional)</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16 ou 4:5 ou 1:1</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>Prog - Audio Ingame</t>
         </is>
       </c>
     </row>
     <row r="254" ht="25" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>INTERNET</t>
+          <t>PROGRAMÁTICO</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Programático</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Google Demand Gen</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>Carousel</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Prog - Banner</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2 a 10 cartões, todos com a mesma proporção entre si</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>300x250, 300x600, 728x90, 320x50</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>5 MB por imagem</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>Título por cartão: até 40 caracteres</t>
-        </is>
-      </c>
-      <c r="L254" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13704860</t>
+          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
     </row>
@@ -13931,7 +13866,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Prog - App Install</t>
+          <t>Prog - Banner Ingame</t>
         </is>
       </c>
     </row>
@@ -13958,22 +13893,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Prog - Audio Ad</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>1 MB</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>MP3</t>
+          <t>Prog - Banner Mobile</t>
         </is>
       </c>
     </row>
@@ -14000,7 +13920,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Prog - Audio Ingame</t>
+          <t>Prog - Conversational Display</t>
         </is>
       </c>
     </row>
@@ -14027,22 +13947,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Prog - Banner</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>300x250, 300x600, 728x90, 320x50</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>Prog - Demand Gen</t>
         </is>
       </c>
     </row>
@@ -14064,12 +13969,12 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>DOOH</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Prog - Banner Ingame</t>
+          <t>Prog - DOOH</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14001,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Prog - Banner Mobile</t>
+          <t>Prog - Expositor</t>
         </is>
       </c>
     </row>
@@ -14123,7 +14028,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Prog - Conversational Display</t>
+          <t>Prog - In Content</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14055,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Prog - Demand Gen</t>
+          <t>Prog - inRead Carousel</t>
         </is>
       </c>
     </row>
@@ -14172,12 +14077,42 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>DOOH</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Prog - DOOH</t>
+          <t>Prog - YouTube Masthead</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14139,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Prog - Expositor</t>
+          <t>Prog - M-Rec</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>300x250</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14171,37 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Prog - In Content</t>
+          <t>Prog - Native Ad</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>IMAGEM — Logo: 100x100 a 2000x2000px; Imagem: 1200x627 a 2000x1047px; Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px. VÍDEO — Logo: 100x100 a 2000x2000px; Cover image: altura mín 627px, máx 2000x1047px (recomendado; para mais inventário, criar criativos adicionais com outros rácios); Vídeo: ficheiro fonte com a maior qualidade disponível.</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Logo: 1:1; Imagem: 1.91:1; Imagem quadrada: 1:1; Cover image: 1.91:1 (recomendado), 16:9, 4:3 ou 1:1 (adicionais para mais inventário)</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Igual para imagem e vídeo — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14228,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Prog - inRead Carousel</t>
+          <t>Prog - Rewarded Video</t>
         </is>
       </c>
     </row>
@@ -14280,42 +14250,12 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Open Door</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Prog - YouTube Masthead</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Prog - Rich Media</t>
         </is>
       </c>
     </row>
@@ -14337,17 +14277,42 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Prog - M-Rec</t>
+          <t>Prog - YouTube Select</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14369,42 +14334,42 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Prog - Native Ad</t>
+          <t>Prog - YouTube VRC Ad Sequence</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>IMAGEM — Logo: 100x100 a 2000x2000px; Imagem: 1200x627 a 2000x1047px; Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px. VÍDEO — Logo: 100x100 a 2000x2000px; Cover image: altura mín 627px, máx 2000x1047px (recomendado; para mais inventário, criar criativos adicionais com outros rácios); Vídeo: ficheiro fonte com a maior qualidade disponível.</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Logo: 1:1; Imagem: 1.91:1; Imagem quadrada: 1:1; Cover image: 1.91:1 (recomendado), 16:9, 4:3 ou 1:1 (adicionais para mais inventário)</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Igual para imagem e vídeo — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14431,7 +14396,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Prog - Rewarded Video</t>
+          <t>Prog - Skyscraper</t>
         </is>
       </c>
     </row>
@@ -14458,7 +14423,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Prog - Rich Media</t>
+          <t>Prog - Social Display</t>
         </is>
       </c>
     </row>
@@ -14490,12 +14455,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Prog - YouTube Select</t>
+          <t>Prog - YouTube VRC Non-Skippable</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -14510,12 +14475,12 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14537,42 +14502,37 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Ad Sequence</t>
+          <t>Prog - Uber Journey Ad</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
-        </is>
-      </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>Display: imagens. Video: MP4.</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
         </is>
       </c>
     </row>
@@ -14594,12 +14554,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Prog - Skyscraper</t>
+          <t>Prog - Spotify Video Takeover</t>
         </is>
       </c>
     </row>
@@ -14626,7 +14586,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Prog - Social Display</t>
+          <t>Prog - Wallpaper</t>
         </is>
       </c>
     </row>
@@ -14658,12 +14618,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Non-Skippable</t>
+          <t>Prog - YouTube VVC</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -14678,12 +14638,12 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -14705,37 +14665,42 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Prog - Uber Journey Ad</t>
+          <t>Prog - YouTube VRC Efficient Reach</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Display: imagens. Video: MP4.</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14757,12 +14722,42 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Prog - Spotify Video Takeover</t>
+          <t>Prog - YouTube VRC Target Frequency</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -14784,12 +14779,37 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Impresa</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Prog - Wallpaper</t>
+          <t>Prog - Billboard (Impresa)</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>970x250, 320x10</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>200 KB</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
       </c>
     </row>
@@ -14811,42 +14831,37 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Prog - YouTube VVC</t>
+          <t>Prog - Billboard (Media Capital)</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16</t>
+          <t>980x250 ou 970x250</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
       </c>
     </row>
@@ -14868,42 +14883,37 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Efficient Reach</t>
+          <t>Prog - Billboard (Observador)</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>1200x220, 970x250</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
       </c>
     </row>
@@ -14925,42 +14935,37 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Billboard</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Target Frequency</t>
+          <t>Prog - Billboard (Público)</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14987,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -14992,12 +14997,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Impresa)</t>
+          <t>Prog - Billboard (Sapo)</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>970x250, 320x10</t>
+          <t>970x250</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -15005,14 +15010,9 @@
           <t>200 KB</t>
         </is>
       </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
       </c>
     </row>
@@ -15034,37 +15034,42 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Media Capital)</t>
+          <t>Prog - Half-Page (Impresa)</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>980x250 ou 970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15086,37 +15091,42 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Observador)</t>
+          <t>Prog - Half-Page (Media Capital)</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>1200x220, 970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/manchete-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
       </c>
     </row>
@@ -15138,37 +15148,42 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Público)</t>
+          <t>Prog - Half-Page (Media Livre)</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>80 KB / 2 MB</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
       </c>
     </row>
@@ -15190,32 +15205,42 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Halfpage</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Sapo)</t>
+          <t>Prog - Half-Page (Observador)</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>970x250</t>
+          <t>300x600</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>1:2</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>100 KB / 2 MB</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
+          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15237,7 +15262,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -15247,7 +15272,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Impresa)</t>
+          <t>Prog - Half-Page (Público)</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -15262,17 +15287,17 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15319,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -15304,7 +15329,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Capital)</t>
+          <t>Prog - Half-Page (Sapo)</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -15319,17 +15344,17 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB / 3.5 MB</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
       </c>
     </row>
@@ -15351,7 +15376,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -15361,7 +15386,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Livre)</t>
+          <t>Prog - Half-Page (Google)</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -15376,17 +15401,17 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>80 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF / MP4</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -15408,42 +15433,32 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Observador)</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>Prog - Header XL (Impresa)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>100 KB / 2 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
       </c>
     </row>
@@ -15465,42 +15480,37 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Público)</t>
+          <t>Prog - Header XL (Media Livre)</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
       </c>
     </row>
@@ -15522,42 +15532,37 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Sapo)</t>
+          <t>Prog - Header XL (Observador)</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>200 KB / 3.5 MB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
+          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15579,42 +15584,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Header XL</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Google)</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>JPG, PNG, GIF</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>Prog - Header XL (Sapo)</t>
         </is>
       </c>
     </row>
@@ -15641,12 +15621,22 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Impresa)</t>
+          <t>Prog - Intro (Impresa)</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>600x400, 320x480</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>3:2 ou 2:3</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -15656,12 +15646,12 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>JPG ou PNG</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -15683,22 +15673,27 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Media Livre)</t>
+          <t>Prog - Intro (Media Capital)</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
+          <t>800x600</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>4:3</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -15708,12 +15703,12 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
+          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
       </c>
     </row>
@@ -15735,37 +15730,42 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Observador)</t>
+          <t>Prog - Intro (Media Livre)</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
+          <t>800x600, 768x1024</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>500 KB</t>
+          <t>120 KB / 1 MB</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
       </c>
     </row>
@@ -15787,17 +15787,37 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Intro</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Sapo)</t>
+          <t>Prog - Intro (Observador)</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>990x600, 300x480</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>120 KB, 75 KB / 2 MB</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF / HTML</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15839,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -15829,32 +15849,32 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Prog - Intro (Impresa)</t>
+          <t>Prog - Intro (Público)</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>600x400, 320x480</t>
+          <t>800x600, 768x1024</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>3:2 ou 2:3</t>
+          <t>4:3 ou 3:4</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15896,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -15886,32 +15906,32 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Capital)</t>
+          <t>Prog - Intro (Sapo)</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>800x600</t>
+          <t>800x600px (600x400px recomendado)</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>4:3</t>
+          <t>4:3 ou 3:2</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
       </c>
     </row>
@@ -15933,42 +15953,37 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Livre)</t>
+          <t>Prog - Leaderboard (Media Capital)</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>120 KB / 1 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>HTML + Imagens</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
+          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -15990,37 +16005,37 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Prog - Intro (Observador)</t>
+          <t>Prog - Leaderboard (Media Livre)</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>990x600, 300x480</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>120 KB, 75 KB / 2 MB</t>
+          <t>80 KB</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
       </c>
     </row>
@@ -16047,37 +16062,32 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Prog - Intro (Público)</t>
+          <t>Prog - Leaderboard (Público)</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
+          <t>1140x50</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
       </c>
     </row>
@@ -16104,22 +16114,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Leaderboard</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Prog - Intro (Sapo)</t>
+          <t>Prog - Leaderboard (Sapo)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>800x600px (600x400px recomendado)</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:2</t>
+          <t>728x90</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -16129,12 +16134,12 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>WEBP</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
       </c>
     </row>
@@ -16156,7 +16161,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -16166,7 +16171,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Capital)</t>
+          <t>Prog - Leaderboard (Google)</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -16181,12 +16186,12 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>JPG, PNG, GIF</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
+          <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
       </c>
     </row>
@@ -16208,37 +16213,42 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Impresa</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Media Livre)</t>
+          <t>Prog - Open Door (Impresa)</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>1920x1080, 680x1520</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>200 KB, 150 KB</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
+          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16260,37 +16270,42 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Público)</t>
+          <t>Prog - Open Door (Media Capital)</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>1140x50</t>
+          <t>1920x1080, 680x1520</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>100 KB</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
+          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
       </c>
     </row>
@@ -16312,37 +16327,42 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Sapo)</t>
+          <t>Prog - Open Door (Media Livre)</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>728x90</t>
+          <t>950x700, 390x850 / 640x360</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>500 KB / 2 MB</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>WEBP</t>
+          <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
       </c>
     </row>
@@ -16364,37 +16384,32 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Leaderboard</t>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Prog - Leaderboard (Google)</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>728x90</t>
+          <t>Prog - Open Door (Observador)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Máxima resolução</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16431,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -16426,32 +16441,27 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Impresa)</t>
+          <t>Prog - Open Door (Público)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>1920x1080, 680x1520</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>800x900</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>200 KB, 150 KB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>JPG / Video</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16483,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -16483,12 +16493,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Capital)</t>
+          <t>Prog - Open Door (Google)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>1920x1080, 680x1520</t>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -16498,17 +16508,17 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -16530,42 +16540,42 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Parallax</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Media Livre)</t>
+          <t>Prog - Parallax (Público)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>950x700, 390x850 / 640x360</t>
+          <t>Landscape: 1280x720px, Portrait: 720x1280px</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>500 KB / 2 MB</t>
+          <t>120 KB</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG / MP4</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
       </c>
     </row>
@@ -16587,32 +16597,32 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Observador)</t>
+          <t>Prog - Peel off (Media Capital)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Máxima resolução</t>
+          <t>40 KB</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>Imagens</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
+          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
       </c>
     </row>
@@ -16634,37 +16644,37 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Público)</t>
+          <t>Prog - Peel off (Media Livre)</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>800x900</t>
+          <t>200x200, 850x650</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>JPG / Video</t>
+          <t>260 KB</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
       </c>
     </row>
@@ -16686,42 +16696,42 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Peel Off</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Prog - Open Door (Google)</t>
+          <t>Prog - Peel off (Observador)</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>200x200, 850x650px</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>120 KB / 2 MB</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG ou GIF</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16743,42 +16753,42 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Parallax</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Prog - Parallax (Público)</t>
+          <t>Prog - Pre-Roll (Media Capital)</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Landscape: 1280x720px, Portrait: 720x1280px</t>
+          <t>1280x720</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>6 MB</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>MP4</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
+          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -16800,32 +16810,42 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Media Livre</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Capital)</t>
+          <t>Prog - Pre-Roll (Media Livre)</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>640x360</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>40 KB</t>
+          <t>15 MB</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Imagens</t>
+          <t>MP4 ou FLV</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
+          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
       </c>
     </row>
@@ -16847,37 +16867,42 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Observador</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Media Livre)</t>
+          <t>Prog - Pre-Roll (Observador)</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>200x200, 850x650</t>
+          <t>640x360</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>260 KB</t>
+          <t>10 MB</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>MP4</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
+          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
       </c>
     </row>
@@ -16899,42 +16924,42 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Peel Off</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Prog - Peel off (Observador)</t>
+          <t>Prog - Pre-Roll (Público)</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>200x200, 850x650px</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>MP4 ou WEBM</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
       </c>
     </row>
@@ -16956,7 +16981,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -16966,12 +16991,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Capital)</t>
+          <t>Prog - Pre-Roll (Sapo)</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>1280x720</t>
+          <t>640x360px</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -16981,7 +17006,7 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>6 MB</t>
+          <t>3.5 MB</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
@@ -16991,7 +17016,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
+          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
       </c>
     </row>
@@ -17013,42 +17038,37 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>Media Capital</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Media Livre)</t>
+          <t>Prog - Takeover (Media Capital)</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>640x360</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>650x350</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>15 MB</t>
+          <t>150 KB</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>MP4 ou FLV</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
+          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
       </c>
     </row>
@@ -17070,42 +17090,37 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Observador)</t>
+          <t>Prog - Takeover (Público)</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>640x360</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>16:9</t>
+          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>10 MB</t>
+          <t>500 KB</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
+          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
       </c>
     </row>
@@ -17127,42 +17142,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Público)</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>640x360px</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>10 MB</t>
-        </is>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>MP4 ou WEBM</t>
-        </is>
-      </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
+          <t>Prog - Connected TV (Sapo)</t>
         </is>
       </c>
     </row>
@@ -17184,22 +17174,22 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Pre-Roll</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Prog - Pre-Roll (Sapo)</t>
+          <t>Prog - Connected TV (Google)</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>640x360px</t>
+          <t>16 a 30 segundos; formato específico para Connected TV</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -17209,17 +17199,17 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>3.5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>MP4</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -17241,210 +17231,245 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Sapo</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Media Capital)</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>650x350</t>
-        </is>
-      </c>
-      <c r="I325" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="L325" t="inlineStr">
-        <is>
-          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
+          <t>Prog - CTV First Screen (Sapo)</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Takeover</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Prog - Takeover (Público)</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 4:5 ou 1:1</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>500 KB</t>
+          <t>5 MB</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / Video para a área expandida</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Sapo)</t>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Prog - Connected TV (Google)</t>
+          <t>Imagem</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>16 a 30 segundos; formato específico para Connected TV</t>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5120 KB</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>CTV</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Prog - CTV First Screen (Sapo)</t>
+          <t>Logo</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>1:1 ou 4:1</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>5120 KB</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -17461,47 +17486,47 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>1.91:1 ou 4:5 ou 1:1</t>
+          <t>16:9 ou 1:1 ou 9:16</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>5 MB</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>MP4, MOV</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
@@ -17518,47 +17543,47 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Google App Campaigns</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Business Information (Logo)</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+          <t>Logo: 1200x1200 (mín. 128x128)</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
@@ -17575,37 +17600,37 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Ad Assets</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Imagem</t>
+          <t>Ad Assets (Imagens)</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
+          <t>1:1 ou 1.91:1</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>5120 KB</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
@@ -17615,7 +17640,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
@@ -17632,47 +17657,47 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Responsive Search Ad</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Responsive Search Ads</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>1:1 ou 4:1</t>
+          <t>N/A (só texto, sem imagem)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>5120 KB</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>N/A (texto)</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/7684791</t>
         </is>
       </c>
     </row>
@@ -17689,32 +17714,32 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Google Performance Max</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Vídeo</t>
+          <t>Video Action Campaigns</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>16:9 ou 1:1 ou 9:16</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -17727,9 +17752,14 @@
           <t>MP4, MOV</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
+          <t>https://support.google.com/google-ads/answer/12066387</t>
         </is>
       </c>
     </row>
@@ -17746,47 +17776,47 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Thumbnail</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Business Information (Logo)</t>
+          <t>Thumbnail (vídeo)</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Logo: 1200x1200 (mín. 128x128)</t>
+          <t>1280x720 (mín. 1280x640)</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>não especificado</t>
+          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -17803,47 +17833,47 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Ad Assets</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Ad Assets (Imagens)</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
+          <t>300x60 (só em desktop)</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>1:1 ou 1.91:1</t>
+          <t>5:1</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>não especificado</t>
+          <t>&lt; 150 KB</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -17855,52 +17885,57 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Google Search</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Responsive Search Ad</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Responsive Search Ads</t>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>N/A (só texto, sem imagem)</t>
+          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>30 MB</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>N/A (texto)</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/7684791</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -17912,57 +17947,57 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Video Action Campaigns</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
+          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/12066387</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -17974,52 +18009,57 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Thumbnail</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Thumbnail (vídeo)</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>1280x720 (mín. 1280x640)</t>
+          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
+          <t>Imagem: 30 MB por cartão</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -18031,52 +18071,57 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Google Vídeo/YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Companion Banner</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>300x60 (só em desktop)</t>
+          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>5:1</t>
+          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>&lt; 150 KB</t>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>JPG, PNG, MP4, MOV ou GIF</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
@@ -18093,12 +18138,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -18113,12 +18158,12 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
+          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -18133,7 +18178,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
+          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -18155,12 +18200,12 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -18175,12 +18220,12 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
+          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
+          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -18190,12 +18235,12 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
+          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -18217,12 +18262,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -18237,12 +18282,12 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
+          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
+          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -18252,12 +18297,12 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
+          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
+          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -18279,12 +18324,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -18299,12 +18344,12 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
+          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
+          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -18314,12 +18359,12 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4, MOV ou GIF</t>
+          <t>JPG, PNG, MP4 ou MOV</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -18341,52 +18386,52 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Single Image</t>
+          <t>Idea Ad</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
+          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
+          <t>9:16 (recomendado, sem restrição rígida)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>30 MB</t>
+          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>JPG, PNG</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
+          <t>Título: até 100c; Texto na página: até 250c.</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -18403,52 +18448,52 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Single Video</t>
+          <t>Showcase Ad</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
+          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
+          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>4 GB</t>
+          <t>Até 32 MB</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
+          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -18465,52 +18510,52 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Quiz Ad</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
+          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
+          <t>Title Pin: 2:3; Results Pin: 2:3</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB por cartão</t>
+          <t>Até 32 MB</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
+          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
@@ -18527,52 +18572,47 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>AR Lenses</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
+          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
+          <t>Varia por asset AR</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>JPG, PNG, MP4 ou MOV</t>
+          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
+          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -18589,12 +18629,12 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -18604,37 +18644,37 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Idea Ad</t>
+          <t>Sponsored Snap</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
+          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>9:16 (recomendado, sem restrição rígida)</t>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
+          <t>Varia; validar no Ads Manager</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
+          <t>MP4, MOV, JPG ou PNG</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>Título: até 100c; Texto na página: até 250c.</t>
+          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
@@ -18651,233 +18691,44 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Native</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Showcase Ad</t>
+          <t>Vertical Video Ad</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
+          <t>Recomendado até 1080x1920, mín. 720x1280. Duração recomendada &lt;15s (até 2:20 suportado). Frame rate máx. 60 fps. Bitrate máx. 25 Mbps (alvo 5-10 Mbps).</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>Até 32 MB</t>
-        </is>
-      </c>
+          <t>9:16 (recomendado); também aceites 4:5, 2:3, 1:1, 1.91:1 ou 16:9</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
-        </is>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
-        </is>
-      </c>
+          <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>Quiz Ad</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>Title Pin: 2:3; Results Pin: 2:3</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>Até 32 MB</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>Branded Effects</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>AR Lenses</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>Varia por asset AR</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
-        </is>
-      </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>Sponsored Snap</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>Varia; validar no Ads Manager</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>MP4, MOV, JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
+          <t>https://business.x.com/en/products/vertical-video-ads</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L350"/>
+  <dimension ref="A1:L358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -18719,16 +18719,454 @@
           <t>9:16 (recomendado); também aceites 4:5, 2:3, 1:1, 1.91:1 ou 16:9</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr">
         <is>
           <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
           <t>https://business.x.com/en/products/vertical-video-ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Single Video</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Amplify Pre-roll</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Recomendado 1200x1200 (mín. 600x600 para 1:1); se não for 1:1, mín. 640x360. Duração recomendada ≤15s (máx. 2:20). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (superior aceite, não fazer upsample).</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>1:1 (recomendado — ocupa sempre espaço quadrado em desktop/mobile/timeline/perfil) ou 9:16 (vertical, ocupa o mesmo espaço); o anúncio é automaticamente combinado com conteúdo de rácio semelhante do publisher</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Máx. 1 GB</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>URL (opcional): tem de começar por http:// ou https://. Branding e legendas/closed captions fortemente recomendados.</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>https://business.x.com/en/advertising/campaign-types/amplify-pre-roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>X Live</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Resolução: 1280x720 recomendado, 1920x1080 máximo. Frame rate: 30 fps recomendado, 60 fps máximo. Keyframe interval: OBS a cada 3s; Wirecast varia por frame rate (24fps→72 frames, 30fps→90, 50fps→150, 60fps→180).</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Bitrate de vídeo: 9 Mbps recomendado, 12 Mbps máximo. Bitrate de áudio: máx. 128 bps.</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Protocolo RTMP; codec de vídeo H.264/AVC; codec de áudio AAC-LC. Encoders suportados: OBS, Wirecast, Restream, Golightstream, Socialive, Teradek, Elemental, Vmix, StreamYard, Streamlabs.</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Descrição da página do evento: até 280c (pode incluir links externos). Carousel do evento: até 5 vídeos (live, VOD, GIFs ou fotos — investimento adicional). Timeline post: até 5 termos específicos (palavras-chave, nomes).</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Takeover</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Timeline Takeover</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Sem specs próprias — usa as specs do formato subjacente escolhido: Image Ads, Video Ads, Carousel Ads, X Live, Promoted Ads com Conversation Button/Polls, ou Branded Notifications.</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Conforme o formato subjacente escolhido</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Takeover</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Spotlight Takeover</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Recomendado 1280x720. Companion Promoted Ads: 3 a 6 anúncios obrigatórios (imagem, vídeo, GIF, etc.) para apoiar o trend.</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 5 MB; GIF: máx. 15 MB</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>Vídeo MP4 ou imagem estática (ou GIF); entrega via darkpost, só media (cartões não aceites)</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Nome do trend (obrigatório): máx. 20c; Descrição do trend (opcional, muito recomendado): máx. 30c — evitar frases tipo clickbait ('50% off', 'compre um leve dois').</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Branded Notifications</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Segue as specs standard dos formatos suportados: Standalone Image/Video Ads; Image/Video Ads com botão Web ou App; Image/Video Carousel Ads com botão Web ou App (destino único); Image/Video Ads com Conversation Button; Moment Ads.</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow.</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>https://business.x.com/en/advertising/branded-notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Catalog Ad</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Dynamic Product Ads</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Criativo gerado dinamicamente a partir do catálogo de produtos (X Shopping Manager, até 1M produtos ou feed de 8GB, sincronização agendada).</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters)</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Conversation Button</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Feature adicionada a Image Ads ou Video Ads (tem de estar associada a media)</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Conversation Card (post original): texto até 280c, hashtag até 21c (incl. o caracter #). Post pré-preenchido (após clique no CTA): texto até 256c, título até 23c. Thank You post: texto até 23c, URL opcional até 23c.</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#conversation</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Polls</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Duração: mín. 5 min, máx. 7 dias (conta a partir da criação do post, não da promoção). Pode ter ou não media associada (imagem ou vídeo).</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Feature adicionada a um post, com ou sem media</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Texto do post: até 280c; 2 a 4 opções de resposta, até 25c cada (não conta para os 280c do post).</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#polls</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L358"/>
+  <dimension ref="A1:L359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>≥540x960</t>
+          <t>Spark Ads Pull: sem duração mínima/máxima (usa o vídeo orgânico tal como publicado). Non-Spark Ads e Spark Ads Push: vertical, ≥540x960px; duração 5-60s (recomendado 9-15s).</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -12489,12 +12489,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>500 MB</t>
+          <t>Non-Spark Ads e Spark Ads Push: ≤500 MB, bitrate ≥2.500kbps. Spark Ads Pull: sem limite próprio (usa o vídeo já publicado).</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>MP4, MOV, MPEG, 3GP</t>
+          <t>Spark Ads Pull: .mp4 ou .mov (normalmente). Non-Spark Ads e Spark Ads Push: .mp4, .mov, .mpeg, .3gp.</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Foto de perfil: quadrada, 98x98px, &lt;50 KB, .jpg/.jpeg/.png (elemento-chave centrado numa área de 66x66px); em Spark Ads usa a foto de perfil da conta do vídeo. Nome da conta: 1 linha, máx. 10c (CN/JP/KR) ou 20c (outras línguas), sem emojis nem '{ }'. Legenda do anúncio: Spark Ads Pull até 100c (extraída do vídeo orgânico, pode ser vazia); Non-Spark/Spark Push até 100c, máx. 4 linhas visíveis (recomendado ≤50c CN/JP/KR ou ≤100c outras línguas para não ser coberta por 'Ver mais'), sem '{ }', emojis só a partir da versão 11. Máx. 20 anúncios por ad group.</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -18828,7 +18833,6 @@
           <t>Resolução: 1280x720 recomendado, 1920x1080 máximo. Frame rate: 30 fps recomendado, 60 fps máximo. Keyframe interval: OBS a cada 3s; Wirecast varia por frame rate (24fps→72 frames, 30fps→90, 50fps→150, 60fps→180).</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr">
         <is>
           <t>Bitrate de vídeo: 9 Mbps recomendado, 12 Mbps máximo. Bitrate de áudio: máx. 128 bps.</t>
@@ -18886,14 +18890,11 @@
           <t>Sem specs próprias — usa as specs do formato subjacente escolhido: Image Ads, Video Ads, Carousel Ads, X Live, Promoted Ads com Conversation Button/Polls, ou Branded Notifications.</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr">
         <is>
           <t>Conforme o formato subjacente escolhido</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
@@ -18998,8 +18999,6 @@
           <t>Segue as specs standard dos formatos suportados: Standalone Image/Video Ads; Image/Video Ads com botão Web ou App; Image/Video Carousel Ads com botão Web ou App (destino único); Image/Video Ads com Conversation Button; Moment Ads.</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr">
         <is>
           <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
@@ -19052,14 +19051,11 @@
           <t>Criativo gerado dinamicamente a partir do catálogo de produtos (X Shopping Manager, até 1M produtos ou feed de 8GB, sincronização agendada).</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr">
         <is>
           <t>Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters)</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
@@ -19097,9 +19093,6 @@
           <t>Conversation Button</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr">
         <is>
           <t>Feature adicionada a Image Ads ou Video Ads (tem de estar associada a media)</t>
@@ -19152,8 +19145,6 @@
           <t>Duração: mín. 5 min, máx. 7 dias (conta a partir da criação do post, não da promoção). Pode ter ou não media associada (imagem ou vídeo).</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr">
         <is>
           <t>Feature adicionada a um post, com ou sem media</t>
@@ -19167,6 +19158,60 @@
       <c r="L358" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#polls</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Paid Social</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>TopReach</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Combina os placements TopView (primeiro conteúdo ao abrir a app) e Top Feed (primeiro anúncio in-feed no For You), por 1 dia (24h). Sem dayparting. Frequência: 1 impressão por utilizador, por placement (alcance único garantido de frequência 1).</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Suporta Spark Ads e Non-Spark Ads (recomendado 1-2 criativos por campanha); Duet/Stitch: Spark Ads segue os toggles do vídeo original, Non-Spark Ads não suportado.</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Objetivo: Reach. Targeting disponível: idade (18+) e localização (país). Tracking de terceiros suportado (impressões e cliques). Landing page: webview standard (HTTPS) ou páginas internas TikTok (Branded Hashtag Challenge, Effect, TikTok Shop) — não suporta redirecionamento automático para app store nem link de TopView para LIVE. Música: mesma política dos in-feed ads reservation (Commercial Music Library ou faixas próprias autorizadas). Permite desativar comentários e download do vídeo. Add-ons: só os disponíveis em ambos os placements (TopView + Top Feed). Som: sempre ativo. Watermark: pode pedir vídeo descarregável sem marca de água.</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
       </c>
     </row>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -12142,27 +12142,32 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Criativo final segue In-Feed/Spark Ads</t>
+          <t>ÍCONE DA MISSION: 240x240px. VÍDEO DE EXEMPLO (obrigatório, 1 a 10 vídeos): 9:16, ≥720x1280px, duração recomendada 12-15s. MÚSICA OFICIAL (opcional): capa 300x300 (elementos-chave centrados num diâmetro de 260px), duração 15s-1min (recomendado 15s). LOGO DA MARCA (opcional): imagem principal + até 4 secundárias, mín. 1000x1000px. QUICK EFFECT (opcional): 1 a 10 imagens, 100x100 a 1000x1000px. BRAND SAFETY — competitor exclusion (até 5 concorrentes) / negative content: logos da marca/concorrentes.</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>9:16 (vídeo de exemplo)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Conforme vídeo In-Feed/Spark</t>
+          <t>Ícone: ≤500 KB. Vídeo de exemplo: ≤100 MB, bitrate &gt;2.500kbps. Capa da música: ≤1 MB. Logo principal/secundário: ≤10 MB cada. Logos de brand safety (concorrentes/marca): ≤1024 KB cada.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Vídeo de creator elegível / Spark Ads</t>
+          <t>Ícone: PNG, JPG ou JPEG. Vídeo de exemplo: MP4, MPEG, 3GP, AVI, MOV. Música: MP3. Logos: JPG/JPEG/PNG (recomendado PNG).</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Nome do anunciante: até 24c (sem espaços/emojis/caracteres especiais, exceto '&amp;'). Nome da Mission: até 70c (recomendado ≤18c para caber numa linha; sem espaços/emojis/caracteres especiais como &lt; &gt; " &amp;). Descrição da Mission: até 300c (recomendado ≤150c). Legenda do vídeo de exemplo: até 150c (recomendado 4-60c, sem quebras de linha). Nome da música: até 60c (recomendado ≤12c); nome do artista sem limite (recomendado ≤12c). Nome do logo: até 20c. Nome de concorrente/marca (brand safety): até 20c cada. Requisitos: pelo menos 1 requisito geral obrigatório (música oficial, hashtag oficial, mencionar conta oficial, usar/acionar Branded Effect, ou Duet); até 3 requisitos específicos opcionais (dançar, lip-sync, mudar de roupa, mostrar a cara); requisitos de marca opcionais (revelar logo &gt;1s, usar Quick Effect).</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>https://ads.tiktok.com/resources/help/article/about-branded-mission?lang=pt</t>
+          <t>https://ads.tiktok.com/help/article/about-branded-mission</t>
         </is>
       </c>
     </row>
@@ -12256,22 +12261,27 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Vertical recomendado; ≥540x960 recomendado</t>
+          <t>Vertical (recomendado): 9:16, ≥540x960px. Horizontal: 16:9, ≥960x540px. Square: 1:1, ≥640x640px. Duração: até 10min. Foto de perfil (opcional): 98x98px, quadrada (se vazia, usa foto default). Nome da conta (App Ads): extraído automaticamente da App Store/Google Play; usado como título da landing page in-app. Download Card (só App Ads): gerado automaticamente, aparece logo após o CTA ou cor de fundo.</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>9:16 (recomendado), 16:9 ou 1:1</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Até 500 MB (reservation); limites podem variar em auction</t>
+          <t>≤500 MB; bitrate ≥516 kbps. Foto de perfil: &lt;50 KB.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>MP4, MOV, MPEG, 3GP</t>
+          <t>MP4, MOV, MPEG, 3GP, AVI. Foto de perfil: JPG, JPEG, PNG.</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Legenda: exibida em branco, fonte uniforme (não personalizável); não suporta links clicáveis, símbolo '@' nem hashtags. Nome da conta: 1 linha, máx. 10c (CN/JP/KR) ou 20c (outras línguas). Zonas seguras variam consoante orientação (vertical/horizontal/quadrado), idioma (LTR/RTL) e uso de anchors — ficheiros de referência disponíveis na TikTok Ads Help.</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -12365,22 +12375,22 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Usa vídeo orgânico; para push, ≥540x960 recomendado</t>
+          <t>Pull: usa o vídeo orgânico tal como publicado, sem restrição de duração; legenda extraída diretamente do vídeo, até 4 linhas visíveis. Push: sobe um novo vídeo, ≥540x960px.</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>9:16</t>
+          <t>9:16 (recomendado para Push); Pull usa o rácio do vídeo orgânico</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Até 500 MB para push</t>
+          <t>Push: até 500 MB</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Vídeo orgânico autorizado ou MP4/MOV/MPEG/3GP</t>
+          <t>Pull: .mp4 ou .mov (do vídeo orgânico). Push: MP4, MOV, MPEG, 3GP.</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -19197,8 +19207,6 @@
           <t>Combina os placements TopView (primeiro conteúdo ao abrir a app) e Top Feed (primeiro anúncio in-feed no For You), por 1 dia (24h). Sem dayparting. Frequência: 1 impressão por utilizador, por placement (alcance único garantido de frequência 1).</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr"/>
-      <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr">
         <is>
           <t>Suporta Spark Ads e Non-Spark Ads (recomendado 1-2 criativos por campanha); Duet/Stitch: Spark Ads segue os toggles do vídeo original, Non-Spark Ads não suportado.</t>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L359"/>
+  <dimension ref="A1:L296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -13741,9 +13741,34 @@
           <t>DV360</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Audio Ad</t>
+        </is>
+      </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Prog - App Install</t>
+          <t>Prog - Audio Ad</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Duração máxima: 30''.</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>1 MB</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>MP3; alternativa aceite: WAV 16-bit 44.1kHz. Áudio normalizado a -14 dB LUFS integrado; MP3 ≥192kbps; picos abaixo de -1 dB TP para evitar distorção na transcodificação.</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Nome do anunciante: máx. 45c.</t>
         </is>
       </c>
     </row>
@@ -13768,24 +13793,39 @@
           <t>DV360</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Prog - Audio Ad</t>
+          <t>Prog - Standard Banners</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>300x250, 300x600, 728x90, 320x50</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>1 MB</t>
+          <t>200 KB</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>MP3</t>
+          <t>ZIP com HTML5 e pastas de imagens/scripts, ou JPEG/GIF; enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Animação: máx. 30 segundos. Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK).</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>https://support.google.com/dcm/answer/3145300?hl=en</t>
         </is>
       </c>
     </row>
@@ -13807,12 +13847,42 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Open Door</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Prog - Audio Ingame</t>
+          <t>Prog - YouTube Masthead</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13834,27 +13904,42 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Prog - Banner</t>
+          <t>Prog - YouTube Select</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>300x250, 300x600, 728x90, 320x50</t>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>ZIP com HTML5 e pastas de imagens, scripts... ou JPEG/GIF. Enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13876,12 +13961,42 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Prog - Banner Ingame</t>
+          <t>Prog - YouTube VRC Ad Sequence</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13903,12 +14018,42 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Prog - Banner Mobile</t>
+          <t>Prog - YouTube VRC Non-Skippable</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13930,12 +14075,42 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Prog - Conversational Display</t>
+          <t>Prog - YouTube VVC</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>MP4, MOV (upload via YouTube)</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
@@ -13957,12 +14132,42 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Prog - Demand Gen</t>
+          <t>Prog - YouTube VRC Efficient Reach</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
@@ -13984,310 +14189,515 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DOOH</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Prog - DOOH</t>
+          <t>Prog - YouTube VRC Target Frequency</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
       </c>
     </row>
     <row r="260" ht="25" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Prog - Expositor</t>
+          <t>Imagem</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 4:5 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>5 MB</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google App Campaigns</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Prog - In Content</t>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>16:9 ou 9:16 ou 1:1</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
       </c>
     </row>
     <row r="262" ht="25" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Prog - inRead Carousel</t>
+          <t>Imagem</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>1.91:1 ou 1:1 ou 4:5</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>5120 KB</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Open Door</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Prog - YouTube Masthead</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
+          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>1:1 ou 4:1</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Alojado no YouTube</t>
+          <t>5120 KB</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
     <row r="264" ht="25" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Performance Max</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Prog - M-Rec</t>
+          <t>Vídeo</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>300x250</t>
+          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>16:9 ou 1:1 ou 9:16</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Alojado no YouTube</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
       </c>
     </row>
     <row r="265" ht="25" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Search</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Logo</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Prog - Native Ad</t>
+          <t>Business Information (Logo)</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>IMAGEM — Logo: 100x100 a 2000x2000px; Imagem: 1200x627 a 2000x1047px; Imagem quadrada (opcional, obrigatória em Programmatic Guaranteed): 627x627 a 2000x2000px. VÍDEO — Logo: 100x100 a 2000x2000px; Cover image: altura mín 627px, máx 2000x1047px (recomendado; para mais inventário, criar criativos adicionais com outros rácios); Vídeo: ficheiro fonte com a maior qualidade disponível.</t>
+          <t>Logo: 1200x1200 (mín. 128x128)</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Logo: 1:1; Imagem: 1.91:1; Imagem quadrada: 1:1; Cover image: 1.91:1 (recomendado), 16:9, 4:3 ou 1:1 (adicionais para mais inventário)</t>
+          <t>1:1</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Logo, Imagem, Imagem quadrada e Cover image: máx 1200 KB cada. Nome do ficheiro: ASCII, máx 50 caracteres.</t>
+          <t>não especificado</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Logo/Imagem/Imagem quadrada/Cover image: JPG, JPEG ou PNG (RGB ou CMYK). Vídeo: ficheiro de vídeo (specs à parte).</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>Igual para imagem e vídeo — Nome do anunciante: máx 25c; Headline: máx 25c (ou Long headline obrigatório se headline não usado); Long headline: máx 50c; Body text: máx 90c (ou Long body obrigatório se body não usado); Long body text: máx 150c; Landing page URL: máx 1024c; Caption URL: máx 30c; Call to action: máx 15c.</t>
+          <t>JPG, PNG</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>https://support.google.com/displayvideo/answer/7128458 | https://support.google.com/displayvideo/answer/7548780</t>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
     <row r="266" ht="25" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Search</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Ad Assets</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Prog - Rewarded Video</t>
+          <t>Ad Assets (Imagens)</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>1:1 ou 1.91:1</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>não especificado</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
       </c>
     </row>
     <row r="267" ht="25" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Search</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Search</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Responsive Search Ad</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Prog - Rich Media</t>
+          <t>Responsive Search Ads</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>N/A (só texto, sem imagem)</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>N/A (texto)</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/7684791</t>
         </is>
       </c>
     </row>
     <row r="268" ht="37.5" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -14302,49 +14712,54 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Prog - YouTube Select</t>
+          <t>Video Action Campaigns</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9 ou 9:16 ou 1:1</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Alojado no YouTube</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://support.google.com/google-ads/answer/12066387</t>
         </is>
       </c>
     </row>
     <row r="269" ht="37.5" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -14354,32 +14769,32 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Thumbnail</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Ad Sequence</t>
+          <t>Thumbnail (vídeo)</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>1280x720 (mín. 1280x640)</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>JPG, GIF ou PNG</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -14391,1193 +14806,1388 @@
     <row r="270" ht="37.5" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Google Vídeo/YouTube</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Prog - Skyscraper</t>
+          <t>Companion Banner</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>300x60 (só em desktop)</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>&lt; 150 KB</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>JPG, GIF ou PNG</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Prog - Social Display</t>
+          <t>Single Image</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>30 MB</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Non-Skippable</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre: BUMPER — recomendado 1920x1080, mín. 640x360; até 6 segundos; não saltável; NON-SKIPPABLE STANDARD — recomendado 1920x1080; 7 a 15 segundos; não saltável; NON-SKIPPABLE 30S — mesma especificação técnica do standard, mas com 30 segundos de duração.</t>
+          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Prog - Uber Journey Ad</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
+          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
+          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+          <t>Imagem: 30 MB por cartão</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Display: imagens. Video: MP4.</t>
+          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Prog - Spotify Video Takeover</t>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>JPG, PNG, MP4, MOV ou GIF</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Single Image</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Prog - Wallpaper</t>
+          <t>Single Image</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>30 MB</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>JPG, PNG</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Prog - YouTube VVC</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Recomendado 1920x1080; saltável a partir dos 5s; sem duração máxima fixa</t>
+          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16</t>
+          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>4 GB</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>MP4, MOV (upload via YouTube)</t>
+          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Efficient Reach</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); Vertical: 1080x1920, 6 a 60 segundos (Shorts); Square: 1080x1080, 6 a 60 segundos.</t>
+          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
+          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Imagem: 30 MB por cartão</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>In-Stream Video</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Prog - YouTube VRC Target Frequency</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>A equipa escolhe o(s) formato(s) mais adequado(s) de entre — Horizontal: 1920x1080 (15s para in-stream skippable/in-feed; 6s para bumper); usa também non-skippable in-stream, in-feed e Shorts (specs conforme cada formato individual).</t>
+          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>16:9</t>
+          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Alojado no YouTube (sem limite de peso do Google Ads)</t>
+          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>MP4, MOV</t>
+          <t>JPG, PNG, MP4 ou MOV</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
+          <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Impresa)</t>
+          <t>Idea Ad</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>970x250, 320x10</t>
+          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>9:16 (recomendado, sem restrição rígida)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Título: até 100c; Texto na página: até 250c.</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Media Capital)</t>
+          <t>Showcase Ad</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>980x250 ou 970x250</t>
+          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>100 KB</t>
+          <t>Até 32 MB</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>JPG, GIF ou PNG</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/billboard/</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Observador)</t>
+          <t>Quiz Ad</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>1200x220, 970x250</t>
+          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Title Pin: 2:3; Results Pin: 2:3</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>120 KB / 2 MB</t>
+          <t>Até 32 MB</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/manchete-desktop.html</t>
+          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Branded Effects</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Público)</t>
+          <t>AR Lenses</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Desktop: 1140x220px | 970x250px | 728x90px, Tablet: 728x90px, Smartphone: 320x100px</t>
+          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>120 KB</t>
+          <t>Varia por asset AR</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>Snapchat</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Billboard</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Prog - Billboard (Sapo)</t>
+          <t>Sponsored Snap</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>970x250</t>
+          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>9:16</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>200 KB</t>
+          <t>Varia; validar no Ads Manager</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>MP4, MOV, JPG ou PNG</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
+          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Vertical Video</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Impresa)</t>
+          <t>Vertical Video Ad</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>Recomendado até 1080x1920, mín. 720x1280. Duração recomendada &lt;15s (até 2:20 suportado). Frame rate máx. 60 fps. Bitrate máx. 25 Mbps (alvo 5-10 Mbps).</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>200 KB</t>
+          <t>9:16 (recomendado); também aceites 4:5, 2:3, 1:1, 1.91:1 ou 16:9</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
+          <t>https://business.x.com/en/products/vertical-video-ads</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Single Video</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Capital)</t>
+          <t>Amplify Pre-roll</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>Recomendado 1200x1200 (mín. 600x600 para 1:1); se não for 1:1, mín. 640x360. Duração recomendada ≤15s (máx. 2:20). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (superior aceite, não fazer upsample).</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>1:1 (recomendado — ocupa sempre espaço quadrado em desktop/mobile/timeline/perfil) ou 9:16 (vertical, ocupa o mesmo espaço); o anúncio é automaticamente combinado com conteúdo de rácio semelhante do publisher</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>Máx. 1 GB</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
+          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>URL (opcional): tem de começar por http:// ou https://. Branding e legendas/closed captions fortemente recomendados.</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
+          <t>https://business.x.com/en/advertising/campaign-types/amplify-pre-roll</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Media Livre)</t>
+          <t>X Live</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>1:2</t>
+          <t>Resolução: 1280x720 recomendado, 1920x1080 máximo. Frame rate: 30 fps recomendado, 60 fps máximo. Keyframe interval: OBS a cada 3s; Wirecast varia por frame rate (24fps→72 frames, 30fps→90, 50fps→150, 60fps→180).</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>80 KB / 2 MB</t>
+          <t>Bitrate de vídeo: 9 Mbps recomendado, 12 Mbps máximo. Bitrate de áudio: máx. 128 bps.</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>HTML, JPEG, PNG ou GIF / MP4</t>
+          <t>Protocolo RTMP; codec de vídeo H.264/AVC; codec de áudio AAC-LC. Encoders suportados: OBS, Wirecast, Restream, Golightstream, Socialive, Teradek, Elemental, Vmix, StreamYard, Streamlabs.</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Descrição da página do evento: até 280c (pode incluir links externos). Carousel do evento: até 5 vídeos (live, VOD, GIFs ou fotos — investimento adicional). Timeline post: até 5 termos específicos (palavras-chave, nomes).</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Observador)</t>
+          <t>Timeline Takeover</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>100 KB / 2 MB</t>
+          <t>Sem specs próprias — usa as specs do formato subjacente escolhido: Image Ads, Video Ads, Carousel Ads, X Live, Promoted Ads com Conversation Button/Polls, ou Branded Notifications.</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / HTML</t>
+          <t>Conforme o formato subjacente escolhido</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/halfpage-desktop.html</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Takeover</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Público)</t>
+          <t>Spotlight Takeover</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>300x600</t>
+          <t>Recomendado 1280x720. Companion Promoted Ads: 3 a 6 anúncios obrigatórios (imagem, vídeo, GIF, etc.) para apoiar o trend.</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>1:2</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>80 KB</t>
+          <t>Imagem: máx. 5 MB; GIF: máx. 15 MB</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
+          <t>Vídeo MP4 ou imagem estática (ou GIF); entrega via darkpost, só media (cartões não aceites)</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Nome do trend (obrigatório): máx. 20c; Descrição do trend (opcional, muito recomendado): máx. 30c — evitar frases tipo clickbait ('50% off', 'compre um leve dois').</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Sapo)</t>
+          <t>Branded Notifications</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>200 KB / 3.5 MB</t>
+          <t>Segue as specs standard dos formatos suportados: Standalone Image/Video Ads; Image/Video Ads com botão Web ou App; Image/Video Carousel Ads com botão Web ou App (destino único); Image/Video Ads com Conversation Button; Moment Ads.</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
+          <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow.</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
+          <t>https://business.x.com/en/advertising/branded-notifications</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Halfpage</t>
+          <t>Catalog Ad</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Prog - Half-Page (Google)</t>
+          <t>Dynamic Product Ads</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>300x600</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>1:2</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>150 KB</t>
+          <t>Criativo gerado dinamicamente a partir do catálogo de produtos (X Shopping Manager, até 1M produtos ou feed de 8GB, sincronização agendada).</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>JPG, PNG, GIF</t>
+          <t>Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters)</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Impresa)</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t>150 KB</t>
+          <t>Conversation Button</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>Feature adicionada a Image Ads ou Video Ads (tem de estar associada a media)</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Conversation Card (post original): texto até 280c, hashtag até 21c (incl. o caracter #). Post pré-preenchido (após clique no CTA): texto até 256c, título até 23c. Thank You post: texto até 23c, URL opcional até 23c.</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#conversation</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>X</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Media Livre</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Media Livre)</t>
+          <t>Polls</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>1240x220, 970x250, 1280x220 e 1280x600</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>150 KB</t>
+          <t>Duração: mín. 5 min, máx. 7 dias (conta a partir da criação do post, não da promoção). Pode ter ou não media associada (imagem ou vídeo).</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>HTML, JPG, PNG ou GIF</t>
+          <t>Feature adicionada a um post, com ou sem media</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Texto do post: até 280c; 2 a 4 opções de resposta, até 25c cada (não conta para os 280c do post).</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
+          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#polls</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PROGRAMÁTICO</t>
+          <t>INTERNET</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Programático</t>
+          <t>Paid Social</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>DV360</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Observador</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Native</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Observador)</t>
+          <t>TopReach</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>557x80, 273x80, 875x80, 1040x80, 1205x80, 1428x80, 1600x80, 400x239, 630x378x 950x286, 1112x334, 1280x383, 1500x462</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t>500 KB</t>
+          <t>Combina os placements TopView (primeiro conteúdo ao abrir a app) e Top Feed (primeiro anúncio in-feed no For You), por 1 dia (24h). Sem dayparting. Frequência: 1 impressão por utilizador, por placement (alcance único garantido de frequência 1).</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>JPG, PNG ou GIF</t>
+          <t>Suporta Spark Ads e Non-Spark Ads (recomendado 1-2 criativos por campanha); Duet/Stitch: Spark Ads segue os toggles do vídeo original, Non-Spark Ads não suportado.</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Objetivo: Reach. Targeting disponível: idade (18+) e localização (país). Tracking de terceiros suportado (impressões e cliques). Landing page: webview standard (HTTPS) ou páginas internas TikTok (Branded Hashtag Challenge, Effect, TikTok Shop) — não suporta redirecionamento automático para app store nem link de TopView para LIVE. Música: mesma política dos in-feed ads reservation (Commercial Music Library ou faixas próprias autorizadas). Permite desativar comentários e download do vídeo. Add-ons: só os disponíveis em ambos os placements (TopView + Top Feed). Som: sempre ativo. Watermark: pode pedir vídeo descarregável sem marca de água.</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>https://formatos.observador.pt/header_xl-desktop.html</t>
+          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
       </c>
     </row>
@@ -15599,19 +16209,41 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Sapo</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Header XL</t>
+          <t>Companion Banner</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Prog - Header XL (Sapo)</t>
-        </is>
-      </c>
+          <t>Prog - Companion Banner</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>640x640px</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>200 KB</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>JPEG ou PNG</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15631,44 +16263,41 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Impresa</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>Pre-Roll</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Prog - Intro (Impresa)</t>
+          <t>Prog - Pre-Roll</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>600x400, 320x480</t>
+          <t>Secundagem recomendada: 15''. Secundagem máxima: 30'' — vídeos com mais de 30'' têm skip ad.</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>3:2 ou 2:3</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
-        </is>
-      </c>
+          <t>Vídeo MP4</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15688,3540 +16317,41 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Media Capital</t>
+          <t>DV360</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Intro</t>
+          <t>CTV</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Prog - Intro (Media Capital)</t>
+          <t>Prog - Connected TV</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>800x600</t>
+          <t>Secundagem recomendada: 15''. Secundagem máxima: 30'' — vídeos com mais de 30'' têm skip ad.</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>4:3</t>
+          <t>16:9</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>150 KB</t>
+          <t>10 MB</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>HTML + Imagens</t>
-        </is>
-      </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Media Livre</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Prog - Intro (Media Livre)</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>120 KB / 1 MB</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>Observador</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Prog - Intro (Observador)</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>990x600, 300x480</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>120 KB, 75 KB / 2 MB</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF / HTML</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t>https://formatos.observador.pt/interstitial-desktop.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Prog - Intro (Público)</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>800x600, 768x1024</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:4</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>120 KB</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>HTML, JPG, PNG ou GIF / Video</t>
-        </is>
-      </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Sapo</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>Intro</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Prog - Intro (Sapo)</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>800x600px (600x400px recomendado)</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>4:3 ou 3:2</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF</t>
-        </is>
-      </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>Media Capital</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Prog - Leaderboard (Media Capital)</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>728x90</t>
-        </is>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>HTML + Imagens</t>
-        </is>
-      </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Media Livre</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Prog - Leaderboard (Media Livre)</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>728x90</t>
-        </is>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>80 KB</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>HTML, JPEG, PNG ou GIF</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Prog - Leaderboard (Público)</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>1140x50</t>
-        </is>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>HTML, JPG, PNG ou GIF</t>
-        </is>
-      </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>Sapo</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Prog - Leaderboard (Sapo)</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>728x90</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J304" t="inlineStr">
-        <is>
-          <t>WEBP</t>
-        </is>
-      </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>Leaderboard</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Prog - Leaderboard (Google)</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>728x90</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t>JPG, PNG, GIF</t>
-        </is>
-      </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/13676244</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>Impresa</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Prog - Open Door (Impresa)</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>1920x1080, 680x1520</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>200 KB, 150 KB</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>JPG</t>
-        </is>
-      </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>Media Capital</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Prog - Open Door (Media Capital)</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>1920x1080, 680x1520</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>100 KB</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>https://mediacapitalcomercial.pt/format/open-door/</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>Media Livre</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>Prog - Open Door (Media Livre)</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>950x700, 390x850 / 640x360</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>500 KB / 2 MB</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG / MP4</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>Observador</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Prog - Open Door (Observador)</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>Máxima resolução</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
-        </is>
-      </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t>https://formatos.observador.pt/opendoor-desktop.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Prog - Open Door (Público)</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>800x900</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>200 KB</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>JPG / Video</t>
-        </is>
-      </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>Open Door</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Prog - Open Door (Google)</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>Recomendado 1920x1080 ou superior; autoplay sem som até 30 segundos, depois miniatura clicável</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I311" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>Parallax</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Prog - Parallax (Público)</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>Landscape: 1280x720px, Portrait: 720x1280px</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16</t>
-        </is>
-      </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>120 KB</t>
-        </is>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF</t>
-        </is>
-      </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>Media Capital</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Prog - Peel off (Media Capital)</t>
-        </is>
-      </c>
-      <c r="I313" t="inlineStr">
-        <is>
-          <t>40 KB</t>
-        </is>
-      </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t>Imagens</t>
-        </is>
-      </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>Media Livre</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Prog - Peel off (Media Livre)</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>200x200, 850x650</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>260 KB</t>
-        </is>
-      </c>
-      <c r="L314" t="inlineStr">
-        <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>Observador</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>Peel Off</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Prog - Peel off (Observador)</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>200x200, 850x650px</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr">
-        <is>
-          <t>120 KB / 2 MB</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF</t>
-        </is>
-      </c>
-      <c r="L315" t="inlineStr">
-        <is>
-          <t>https://formatos.observador.pt/pell-off-desktop.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>Media Capital</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Prog - Pre-Roll (Media Capital)</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>1280x720</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t>6 MB</t>
-        </is>
-      </c>
-      <c r="J316" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="L316" t="inlineStr">
-        <is>
-          <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>Media Livre</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Prog - Pre-Roll (Media Livre)</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>640x360</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>15 MB</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>MP4 ou FLV</t>
-        </is>
-      </c>
-      <c r="L317" t="inlineStr">
-        <is>
-          <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>Observador</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>Prog - Pre-Roll (Observador)</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>640x360</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I318" t="inlineStr">
-        <is>
-          <t>10 MB</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>Prog - Pre-Roll (Público)</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>640x360px</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>10 MB</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t>MP4 ou WEBM</t>
-        </is>
-      </c>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>Sapo</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>Pre-Roll</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>Prog - Pre-Roll (Sapo)</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>640x360px</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>3.5 MB</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>MP4</t>
-        </is>
-      </c>
-      <c r="L320" t="inlineStr">
-        <is>
-          <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>Media Capital</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>Prog - Takeover (Media Capital)</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>650x350</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>150 KB</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>Prog - Takeover (Público)</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>630x80, 400x80, 950x80, 1112x80, 1500x80, 2300x80, 630x378, 400x240, 950x286, 1112x385, 1500x462, 2300x462</t>
-        </is>
-      </c>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>500 KB</t>
-        </is>
-      </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>JPG, PNG ou GIF / Video para a área expandida</t>
-        </is>
-      </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Sapo</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>Prog - Connected TV (Sapo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>Prog - Connected TV (Google)</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>16 a 30 segundos; formato específico para Connected TV</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/11462260</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>PROGRAMÁTICO</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Programático</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>DV360</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>Sapo</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>CTV</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>Prog - CTV First Screen (Sapo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Google App Campaigns</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Google App Campaigns</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>Imagem</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Vertical: 1200x1500 (mín. 320x400); Square: 1200x1200 (mín. 200x200) — até 20 imagens, opcionais mas recomendadas</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>1.91:1 ou 4:5 ou 1:1</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t>5 MB</t>
-        </is>
-      </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="L326" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Google App Campaigns</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>Google App Campaigns</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>Horizontal, Vertical, Square; 10 a 60 segundos — até 20 vídeos, opcionais mas recomendados</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L327" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091671</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Google Performance Max</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Google Performance Max</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>Imagem</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>Horizontal: 1200x628 (mín. 600x314); Square: 1200x1200 (mín. 300x300); Vertical: 960x1200 (mín. 480x600, opcional) — mín. 4 imagens de cada tipo obrigatório, até 20</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>1.91:1 ou 1:1 ou 4:5</t>
-        </is>
-      </c>
-      <c r="I328" t="inlineStr">
-        <is>
-          <t>5120 KB</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="L328" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Google Performance Max</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>Google Performance Max</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>Logo</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>Logo</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>Logo quadrado: 1200x1200 (mín. 128x128, obrigatório); Logo horizontal: 1200x300 (mín. 512x128, opcional) — até 5 de cada</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>1:1 ou 4:1</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>5120 KB</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Google Performance Max</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>Google Performance Max</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>Horizontal, Square, Vertical; mín. 10 segundos — até 15 vídeos de cada, opcional (gerado automaticamente se não for fornecido)</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>16:9 ou 1:1 ou 9:16</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/9748775</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>Logo</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>Business Information (Logo)</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>Logo: 1200x1200 (mín. 128x128)</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr">
-        <is>
-          <t>não especificado</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>Ad Assets</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Ad Assets (Imagens)</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>Square: 1200x1200 (mín. 300x300), obrigatório; Horizontal: 1200x628 (mín. 600x314), opcional</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>1:1 ou 1.91:1</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>não especificado</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/12437745</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>Google Search</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>Responsive Search Ad</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Responsive Search Ads</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>N/A (só texto, sem imagem)</t>
-        </is>
-      </c>
-      <c r="I333" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t>N/A (texto)</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
-        </is>
-      </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/7684791</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Google Vídeo/YouTube</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>In-Stream Video</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>Video Action Campaigns</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>Horizontal: 1920x1080; Vertical: 1080x1920; Square: 1080x1080; mín. 10 segundos.</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>16:9 ou 9:16 ou 1:1</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t>Alojado no YouTube</t>
-        </is>
-      </c>
-      <c r="J334" t="inlineStr">
-        <is>
-          <t>MP4, MOV</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
-        </is>
-      </c>
-      <c r="L334" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/12066387</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Google Vídeo/YouTube</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>Thumbnail</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>Thumbnail (vídeo)</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>1280x720 (mín. 1280x640)</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>&lt; 2 MB (vídeos); &lt; 10 MB (podcasts)</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Google Vídeo/YouTube</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Companion Banner</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>300x60 (só em desktop)</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>5:1</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t>&lt; 150 KB</t>
-        </is>
-      </c>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>JPG, GIF ou PNG</t>
-        </is>
-      </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t>https://support.google.com/google-ads/answer/17091270</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>Feed: 1440x1800 (mín. 600px largura, mín. 750px altura); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 600x600px).</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t>30 MB</t>
-        </is>
-      </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
-        </is>
-      </c>
-      <c r="L337" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>Feed: 1440x1800 (mín. 120x120px), 1s a 241min; Stories: 1440x2560 (mín. 250px largura), 1s a 3min; Reels: 1440x2560 recomendado, sem duração máxima.</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>4 GB</t>
-        </is>
-      </c>
-      <c r="J338" t="inlineStr">
-        <is>
-          <t>MP4, MOV ou GIF. Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
-        </is>
-      </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
-        </is>
-      </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>Feed: 1080x1080 mín. (imagem ou vídeo), 2 a 10 cartões; Stories: 1080x1920 mín. (só imagem, sem suporte a vídeo), 3 a 10 cartões, largura mín. 500px; Reels: 1080x1920 mín. (só imagem), 2 a 10 cartões, largura mín. 500px, altura mín. 262px.</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>Feed: 1:1; Stories: 1:1 (recomendado); Reels: 9:16</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>Imagem: 30 MB por cartão</t>
-        </is>
-      </c>
-      <c r="J339" t="inlineStr">
-        <is>
-          <t>JPG ou PNG (Feed também aceita MP4/MOV/GIF)</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
-        </is>
-      </c>
-      <c r="L339" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>Feed: 1080x1080 mín. (capa: imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Reels: 1080x1080 mín., requer Catálogo Advantage+ como fonte de conteúdo, Experiência Instantânea obrigatória.</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>Feed: 1.91:1 até 1:1; Reels: 9:16 até 1:1</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
-        </is>
-      </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t>JPG, PNG, MP4, MOV ou GIF</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
-        </is>
-      </c>
-      <c r="L340" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Single Image</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>Feed: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100); Stories: 1440x2560 (mín. 500px largura); Reels: 1440x2560 (mín. 500px largura); Explorar: 1440x1800 (mín. 500px largura; proporção mín. 400x500, máx. 191x100).</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>Feed: 4:5; Stories: 9:16; Reels: 9:16; Explorar: 4:5</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>30 MB</t>
-        </is>
-      </c>
-      <c r="J341" t="inlineStr">
-        <is>
-          <t>JPG, PNG</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>Feed: 1080x1920 (mín. 250px largura), 1s a 60min; Stories: 1440x2560 (mín. 250px largura), 1s a 60min; Reels: 1440x2560, 0 a 15min, mín. 250px largura (&lt;30s) ou 500px (≥30s).</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>Feed: 9:16; Stories: 9:16; Reels: 9:16</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>4 GB</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>MP4, MOV ou GIF (Reels: só MP4 ou MOV). Compressão H.264, píxeis quadrados, taxa de fotogramas fixa, áudio AAC estéreo ≥128 Kbps.</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
-        </is>
-      </c>
-      <c r="L342" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>Feed: 1080x1080 mín., 2 a 10 cartões; Stories: 1080x1920 mín. (imagem ou vídeo), 2 a 10 cartões; Reels: 1080x1080 mín. (só imagem), 2 a 10 cartões.</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>Feed: 4:5 (só imagem) ou 1:1 (com vídeo); Stories: 9:16; Reels: 9:16</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>Imagem: 30 MB por cartão</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>JPG ou PNG (Feed e Stories também aceitam MP4/MOV/GIF)</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
-        </is>
-      </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>Feed: 1080x1080 mín. (mín. 500x500), capa (imagem ou vídeo) + 3 imagens de produto, Experiência Instantânea obrigatória; Stories: 1080x1080 mín. (mín. 500x500), capa + 2 imagens de produto, Experiência Instantânea obrigatória; Reels: mín. 500x888, capa + até 3 imagens de produto (imagem de produto), Experiência Instantânea obrigatória.</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>Feed: 1.91:1 até 1:1; Stories: 1.91:1 até 1:1; Reels: 9:16 (imagem de produto: 1:1)</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>Imagem: 30 MB; Vídeo: 4 GB</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>JPG, PNG, MP4 ou MOV</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
-        </is>
-      </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/business/ads-guide/update</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>Idea Ad</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>Recomendado 1080x1920 para imagem/vídeo full-bleed. Duração de vídeo: máx. 5min. Zonas seguras: topo 270px, esquerda 65px, direita 195px, fundo 440px.</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>9:16 (recomendado, sem restrição rígida)</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>Recomendado 1 GB; Android/iOS: máx. 2 GB; Web: máx. 100 MB</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, M4V, MOV, codec H.264 ou H.265</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>Título: até 100c; Texto na página: até 250c.</t>
-        </is>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>Showcase Ad</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>Recomendado 1000x1500. Até 4 cartões além do title Pin principal; 1 a 3 features por cartão. Zona segura: 342x430px; evitar texto/logos nos últimos 80px do cartão.</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>Title Pin: 2:3; Cartão: 2:3; Feature: 1:1 estático</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>Até 32 MB</t>
-        </is>
-      </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
-        </is>
-      </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Quiz Ad</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>Recomendado 1000x1500. Até 3 results Pins com 1 title Pin. Zona segura: 342x376px.</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>Title Pin: 2:3; Results Pin: 2:3</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>Até 32 MB</t>
-        </is>
-      </c>
-      <c r="J347" t="inlineStr">
-        <is>
-          <t>Imagem: BMP, JPEG, PNG, TIFF, WEBP; Vídeo (só iOS/Android): MP4, MOV ou M4V, 3 a 60s</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
-        </is>
-      </c>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>Branded Effects</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>AR Lenses</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>Sem dimensão fixa — experiência AR criada via Lens Web Builder ou Lens Studio.</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>Varia por asset AR</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
-        </is>
-      </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>Snapchat</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>Sponsored Snap</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>720x1280; duração máx. 180 seg. (recomendado &lt;10 seg). Elementos opcionais de Message Design (até 3): fundo de chat personalizado 1080x1920; mensagem de chat até 500c; resposta automática até 500c (texto ou vídeo).</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>9:16</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr">
-        <is>
-          <t>Varia; validar no Ads Manager</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>MP4, MOV, JPG ou PNG</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
-        </is>
-      </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>Vertical Video</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>Vertical Video Ad</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>Recomendado até 1080x1920, mín. 720x1280. Duração recomendada &lt;15s (até 2:20 suportado). Frame rate máx. 60 fps. Bitrate máx. 25 Mbps (alvo 5-10 Mbps).</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>9:16 (recomendado); também aceites 4:5, 2:3, 1:1, 1.91:1 ou 16:9</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
-        </is>
-      </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/products/vertical-video-ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>Single Video</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>Amplify Pre-roll</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>Recomendado 1200x1200 (mín. 600x600 para 1:1); se não for 1:1, mín. 640x360. Duração recomendada ≤15s (máx. 2:20). Bitrate: 1080p 6.000-10.000k (recomendado 6.000k); 720p 5.000-8.000k (recomendado 5.000k). Frame rate: 29,97 ou 30 FPS (superior aceite, não fazer upsample).</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>1:1 (recomendado — ocupa sempre espaço quadrado em desktop/mobile/timeline/perfil) ou 9:16 (vertical, ocupa o mesmo espaço); o anúncio é automaticamente combinado com conteúdo de rácio semelhante do publisher</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>Máx. 1 GB</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>MP4 ou MOV; codec H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>URL (opcional): tem de começar por http:// ou https://. Branding e legendas/closed captions fortemente recomendados.</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/advertising/campaign-types/amplify-pre-roll</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>X Live</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>Resolução: 1280x720 recomendado, 1920x1080 máximo. Frame rate: 30 fps recomendado, 60 fps máximo. Keyframe interval: OBS a cada 3s; Wirecast varia por frame rate (24fps→72 frames, 30fps→90, 50fps→150, 60fps→180).</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t>Bitrate de vídeo: 9 Mbps recomendado, 12 Mbps máximo. Bitrate de áudio: máx. 128 bps.</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>Protocolo RTMP; codec de vídeo H.264/AVC; codec de áudio AAC-LC. Encoders suportados: OBS, Wirecast, Restream, Golightstream, Socialive, Teradek, Elemental, Vmix, StreamYard, Streamlabs.</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>Descrição da página do evento: até 280c (pode incluir links externos). Carousel do evento: até 5 vídeos (live, VOD, GIFs ou fotos — investimento adicional). Timeline post: até 5 termos específicos (palavras-chave, nomes).</t>
-        </is>
-      </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>Timeline Takeover</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>Sem specs próprias — usa as specs do formato subjacente escolhido: Image Ads, Video Ads, Carousel Ads, X Live, Promoted Ads com Conversation Button/Polls, ou Branded Notifications.</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>Conforme o formato subjacente escolhido</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>Takeover</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>Spotlight Takeover</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>Recomendado 1280x720. Companion Promoted Ads: 3 a 6 anúncios obrigatórios (imagem, vídeo, GIF, etc.) para apoiar o trend.</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>16:9</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t>Imagem: máx. 5 MB; GIF: máx. 15 MB</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>Vídeo MP4 ou imagem estática (ou GIF); entrega via darkpost, só media (cartões não aceites)</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t>Nome do trend (obrigatório): máx. 20c; Descrição do trend (opcional, muito recomendado): máx. 30c — evitar frases tipo clickbait ('50% off', 'compre um leve dois').</t>
-        </is>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>Branded Notifications</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>Segue as specs standard dos formatos suportados: Standalone Image/Video Ads; Image/Video Ads com botão Web ou App; Image/Video Carousel Ads com botão Web ou App (destino único); Image/Video Ads com Conversation Button; Moment Ads.</t>
-        </is>
-      </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow.</t>
-        </is>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/advertising/branded-notifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>Catalog Ad</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>Dynamic Product Ads</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>Criativo gerado dinamicamente a partir do catálogo de produtos (X Shopping Manager, até 1M produtos ou feed de 8GB, sincronização agendada).</t>
-        </is>
-      </c>
-      <c r="J356" t="inlineStr">
-        <is>
-          <t>Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters)</t>
-        </is>
-      </c>
-      <c r="L356" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>Conversation Button</t>
-        </is>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>Feature adicionada a Image Ads ou Video Ads (tem de estar associada a media)</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>Conversation Card (post original): texto até 280c, hashtag até 21c (incl. o caracter #). Post pré-preenchido (após clique no CTA): texto até 256c, título até 23c. Thank You post: texto até 23c, URL opcional até 23c.</t>
-        </is>
-      </c>
-      <c r="L357" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#conversation</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>Polls</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>Duração: mín. 5 min, máx. 7 dias (conta a partir da criação do post, não da promoção). Pode ter ou não media associada (imagem ou vídeo).</t>
-        </is>
-      </c>
-      <c r="J358" t="inlineStr">
-        <is>
-          <t>Feature adicionada a um post, com ou sem media</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>Texto do post: até 280c; 2 a 4 opções de resposta, até 25c cada (não conta para os 280c do post).</t>
-        </is>
-      </c>
-      <c r="L358" t="inlineStr">
-        <is>
-          <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#polls</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>INTERNET</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Paid Social</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>Native</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>TopReach</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>Combina os placements TopView (primeiro conteúdo ao abrir a app) e Top Feed (primeiro anúncio in-feed no For You), por 1 dia (24h). Sem dayparting. Frequência: 1 impressão por utilizador, por placement (alcance único garantido de frequência 1).</t>
-        </is>
-      </c>
-      <c r="J359" t="inlineStr">
-        <is>
-          <t>Suporta Spark Ads e Non-Spark Ads (recomendado 1-2 criativos por campanha); Duet/Stitch: Spark Ads segue os toggles do vídeo original, Non-Spark Ads não suportado.</t>
-        </is>
-      </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>Objetivo: Reach. Targeting disponível: idade (18+) e localização (país). Tracking de terceiros suportado (impressões e cliques). Landing page: webview standard (HTTPS) ou páginas internas TikTok (Branded Hashtag Challenge, Effect, TikTok Shop) — não suporta redirecionamento automático para app store nem link de TopView para LIVE. Música: mesma política dos in-feed ads reservation (Commercial Music Library ou faixas próprias autorizadas). Permite desativar comentários e download do vídeo. Add-ons: só os disponíveis em ambos os placements (TopView + Top Feed). Som: sempre ativo. Watermark: pode pedir vídeo descarregável sem marca de água.</t>
-        </is>
-      </c>
-      <c r="L359" t="inlineStr">
-        <is>
-          <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
-        </is>
-      </c>
+          <t>Vídeo MP4</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L296"/>
+  <dimension ref="A1:L297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Prog - Companion Banner</t>
+          <t>Prog - Companion Banner (Audio)</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -16242,8 +16242,6 @@
           <t>JPEG ou PNG</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16296,8 +16294,6 @@
           <t>Vídeo MP4</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16350,8 +16346,64 @@
           <t>Vídeo MP4</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Companion Banner</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Prog - Companion Banner (YouTube)</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>300x60 (só em desktop)</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>&lt; 150 KB</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>JPG, GIF ou PNG</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>https://support.google.com/google-ads/answer/17091270</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L297"/>
+  <dimension ref="A1:L301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -16398,12 +16398,171 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
       </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Prog - Uber Journey Ad</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: 975x861, mín 1/máx 5 imagens (todas com logo e diferentes); Espera: 420x420 ou 314x420, máx 1 imagem; Viagem: 1146x393, mín 1/máx 5 imagens (todas com logo e diferentes). VIDEO (MP4, altura mín 486px, largura mín 864px) — Pedido: 3 a 6 seg; Espera: 6 a 60 seg; Viagem: 6 a 60 seg.</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>1:1 ou 3:4 ou 16:9 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Display: máx 1 MB (todas as fases). Video: máx 1 MB (Pedido); máx 3 MB (Espera e Viagem).</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Display: imagens. Video: MP4.</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Prog - Rewarded Video</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Prog - Outstream</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>PROGRAMÁTICO</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Programático</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>DV360</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Prog - Rich Media</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Specs a definir</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -16425,7 +16425,6 @@
           <t>Uber</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>Prog - Uber Journey Ad</t>
@@ -16456,7 +16455,6 @@
           <t>DISPLAY — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. VIDEO — Pedido: título máx 25c, corpo máx 52c; Espera: título máx 25c, CTA máx 15c; Viagem: título máx 25c, corpo máx 52c, CTA máx 15c. URL — Display: parametrizado, não parametrizado ou Click Tag (só disponível nas fases de Espera e Viagem); Video: parametrizado, não parametrizado ou Click Tag (todas as fases).</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16479,18 +16477,36 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
       <c r="F299" t="inlineStr">
         <is>
           <t>Prog - Rewarded Video</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Aplica-se só a anúncios de vídeo — o utilizador recebe uma recompensa (ex.: moeda in-app, power-up) depois de ver o anúncio.</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Até 10 MB</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/9166157?hl=en</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16513,18 +16529,41 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>In-Feed Video</t>
+        </is>
+      </c>
       <c r="F300" t="inlineStr">
         <is>
           <t>Prog - Outstream</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
-      <c r="L300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Dimensões: mín. 256px no lado maior e no lado menor, exceto 300x250 e 320x180 (exceções aceites). Colocação: só no corpo principal da página (não em sidebar, cabeçalho ou rodapé).</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>4:3 ou 16:9 (horizontal); 3:4 ou 9:16 (vertical) — fora destes rácios o anúncio não serve</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Até 10 MB</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; só tags VAST (VPAID não suportado); áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>https://support.google.com/displayvideo/answer/3129957?hl=en</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16547,7 +16586,6 @@
           <t>DV360</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>Prog - Rich Media</t>
@@ -16558,11 +16596,6 @@
           <t>Specs a definir</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
-      <c r="L301" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L301"/>
+  <dimension ref="A1:L337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -16597,6 +16597,2018 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Window Splash Vídeo</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Imagem: 800x600px. Vídeo (opcional): duração máx. 15s; deixar espaço no centro da imagem para o vídeo.</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/window-splash-video/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Intro Full Vídeo</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Duração máx. 15s.</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>16:9 e 9:16</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/intro-full-video/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Splash/Intro</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Imagem: 1024x600px (ou 800x600px) + 480x640px; para campanhas programáticas: 800x600px + 320x480px; em HTML5, dimensões mobile 320x480px e 480x320px. Vídeo (opcional): duração máx. 15s; deixar espaço na imagem para o vídeo.</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>16:9 e 9:16 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/splash-intro/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Takeover</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Vídeo FullScreen TakeOver</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Imagem: Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px. Vídeo: duração máx. 15s (medidas recomendadas 1024x600 e 480x640).</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>16:9 e 9:16 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/video-fullscreen-takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Takeover</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>FullScreen TakeOver</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Imagem: Splash/Intro 1024x600px + 480x640px + 640x480px; Half Page 300x600px; Superboard 1260x200px + 728x150px + 320x100px; em HTML5 para a Intro, dimensões mobile 320x480px e 480x320px. Vídeo (opcional): duração máx. 15s; deixar espaço na imagem para o vídeo.</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>16:9 e 9:16 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/FullScreen-TakeOver/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Takeover</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>TakeOver</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>1260x200px + 728x150px + 320x100px, e também 300x600px ou 300x250px. Pode incluir vídeo (contactar para mais info).</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por ficheiro.</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5.</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/takeover/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Skin (Imagem)</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por imagem.</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF.</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/skin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Skin Vídeo</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px (deixar espaço na imagem de topo para o vídeo). Laterais não devem conter informação relevante. Vídeo: duração máx. 30s.</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/skin-video/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Skin Invertida</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2 imagens laterais 310x1080px + 1 imagem de fundo 1300x250px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por imagem.</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF.</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/skin-invertida/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Skin Mobile</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2 imagens 320x100px + 1 imagem 300x600px (pode ter vídeo, deixar espaço na imagem 300x600 para o vídeo). Vídeo (opcional): duração máx. recomendada 15s.</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>16:9 e 9:16 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/skin-mobile/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Parallax</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Parallax</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>320x600px</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB.</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF.</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/parallax/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Carousel</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Mín. 3 imagens, 320x320px cada; logótipo da marca 160x50px.</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Título: máx. 40c; Descrição: máx. 35c; Texto do botão CTA (ex.: Saber mais, Comprar agora, Reserve já, Entre em contacto).</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/carrossel/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>FlipBook Ad</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>2 imagens: 300x600px (versão colapsada) + 600x600px (versão expandida) — deixar espaço na imagem expandida para o vídeo. Vídeo (opcional): duração máx. 30s.</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 100 KB por imagem. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/flipbook/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Cubo</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Mrec Cubo 3D</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>4 a 6 imagens, 300x300px cada.</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB por imagem.</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>JPG ou PNG.</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/mrec-cubo-3d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Cubo</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Half Page Cubo 3D</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>3 a 6 imagens, 300x600px cada.</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB por imagem.</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>JPG ou PNG.</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/half-page-cubo-3d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Ticker Expandido</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>1260x300px + 728x300px + 320x200px (deixar espaço para vídeo, se aplicável). Vídeo (opcional): duração máx. 15s.</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/ticker/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>In-Stream Video</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Spot TV</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Duração máx. recomendada 15s.</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/spot-tv/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Flip Ad</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>1024x600px (ou 800x600px) + 480x640px (deixar espaço para vídeo, se aplicável). Vídeo (opcional): duração máx. 15s.</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>16:9 e 9:16 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB por imagem. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/flip-ad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Overslide</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2 imagens: 300x600px + 150x300px.</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por imagem.</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF.</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/overslide/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>600x500px. Vídeo (opcional): 600x500px, ou usar o rácio 16:9; duração máx. 15s; deixar espaço na imagem para o vídeo se usados em conjunto.</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo, alternativa às dimensões fixas)</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4.</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/layer/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Peel Off</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Peel Off</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Área fechada: 200x200px; área aberta: 850x650px. Não colocar informação no canto superior direito de nenhuma das duas imagens (fica coberto pela aba). Vídeo (opcional): duração máx. 20s; deixar espaço na imagem aberta para o vídeo.</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>16:9 (vídeo)</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 200 KB. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/peel-off/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Push Down</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>(1260x100px + 1260x370px) + (728x100px + 728x300px) + (320x100px + 320x250px).</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por ficheiro.</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF.</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/push-down/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Audio Ad</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Áudio Ad</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB.</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>MP3.</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/audio-ad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Pre-Roll</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Pre-Roll</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB.</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>MP4.</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/pre-roll/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>In-Feed Video</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>InContent Sticky</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Duração máx. recomendada 20s.</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB.</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/incontent-sticky/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>In-Feed Video</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>InContent</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Duração máx. recomendada 20s.</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>16:9</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Máx. 100 MB.</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>MP4, som off por defeito.</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/incontent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Superboard/Billboard</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>1260x200px + 728x150px + 320x100px, ou 970x250px + 728x90px + 320x50px.</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por ficheiro.</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5.</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/superboard/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Mrec</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Mrec</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>300x250px</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Máx. 150 KB.</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5.</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/mrec/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Halfpage</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Half Page</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>300x600px</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB.</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5.</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/half-page/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Header XL</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Megapub</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>1260x370px + 728x338px + 320x239px. Se tiver vídeo, deixar espaço nas imagens.</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por ficheiro.</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>JPG, PNG, GIF ou HTML5.</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/megapub/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Mrec</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Mrec Vídeo</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>300x250px, ou o rácio 16:9.</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>16:9 (alternativa a 300x250px)</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Máx. 3 MB.</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>MP4.</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/mrec-video/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Halfpage</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Half Page Vídeo (Imagem + Vídeo)</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>300x600px.</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Imagem: máx. 150 KB. Vídeo: máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/half-page-video/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Halfpage</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Half Page Full Vídeo</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>300x600px, ou o rácio 9:16.</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>9:16 (alternativa a 300x600px)</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Máx. 2 MB.</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>MP4.</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/half-page-full-video/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Social Card</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Sem dimensão fixa — usa o post/link social já publicado.</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Link social do Facebook, Instagram, X (Twitter) ou LinkedIn.</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/social-card/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Gallery</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Filmstrip</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2 a 5 imagens, 300x600px cada.</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Máx. 100 KB por imagem.</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>JPG, PNG ou GIF.</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/filmstrip/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Notícias Ilimitadas</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Newsletter Banner</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2 imagens: 300x250px + 640x124px.</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB por imagem.</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>JPG (formato estático).</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Só suporta tag de clicks (não é possível usar tag de impressões).</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>https://noticiasilimitadas.pt/digital/newsletter/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L337"/>
+  <dimension ref="A1:L340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -16648,7 +16648,6 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/window-splash-video/</t>
@@ -16706,7 +16705,6 @@
           <t>MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/intro-full-video/</t>
@@ -16764,7 +16762,6 @@
           <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/splash-intro/</t>
@@ -16822,7 +16819,6 @@
           <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/video-fullscreen-takeover/</t>
@@ -16880,7 +16876,6 @@
           <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/FullScreen-TakeOver/</t>
@@ -16923,7 +16918,6 @@
           <t>1260x200px + 728x150px + 320x100px, e também 300x600px ou 300x250px. Pode incluir vídeo (contactar para mais info).</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>Máx. 200 KB por ficheiro.</t>
@@ -16934,7 +16928,6 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/takeover/</t>
@@ -16977,7 +16970,6 @@
           <t>2 imagens laterais 330x1080px + 1 imagem de topo 1260x290px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
           <t>Máx. 200 KB por imagem.</t>
@@ -16988,7 +16980,6 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin/</t>
@@ -17046,7 +17037,6 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-video/</t>
@@ -17089,7 +17079,6 @@
           <t>2 imagens laterais 310x1080px + 1 imagem de fundo 1300x250px. Laterais não devem conter informação relevante (podem ficar cortadas em ecrãs mais pequenos).</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
           <t>Máx. 200 KB por imagem.</t>
@@ -17100,7 +17089,6 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-invertida/</t>
@@ -17158,7 +17146,6 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-mobile/</t>
@@ -17201,7 +17188,6 @@
           <t>320x600px</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
           <t>Máx. 200 KB.</t>
@@ -17212,7 +17198,6 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/parallax/</t>
@@ -17255,9 +17240,6 @@
           <t>Mín. 3 imagens, 320x320px cada; logótipo da marca 160x50px.</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
           <t>Título: máx. 40c; Descrição: máx. 35c; Texto do botão CTA (ex.: Saber mais, Comprar agora, Reserve já, Entre em contacto).</t>
@@ -17320,7 +17302,6 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/flipbook/</t>
@@ -17363,7 +17344,6 @@
           <t>4 a 6 imagens, 300x300px cada.</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
           <t>Máx. 100 KB por imagem.</t>
@@ -17374,7 +17354,6 @@
           <t>JPG ou PNG.</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/mrec-cubo-3d/</t>
@@ -17417,7 +17396,6 @@
           <t>3 a 6 imagens, 300x600px cada.</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
           <t>Máx. 100 KB por imagem.</t>
@@ -17428,7 +17406,6 @@
           <t>JPG ou PNG.</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/half-page-cubo-3d/</t>
@@ -17486,7 +17463,6 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/ticker/</t>
@@ -17544,7 +17520,6 @@
           <t>MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/spot-tv/</t>
@@ -17602,7 +17577,6 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/flip-ad/</t>
@@ -17645,7 +17619,6 @@
           <t>2 imagens: 300x600px + 150x300px.</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>Máx. 200 KB por imagem.</t>
@@ -17656,7 +17629,6 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/overslide/</t>
@@ -17714,7 +17686,6 @@
           <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/layer/</t>
@@ -17772,7 +17743,6 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/peel-off/</t>
@@ -17815,7 +17785,6 @@
           <t>(1260x100px + 1260x370px) + (728x100px + 728x300px) + (320x100px + 320x250px).</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr">
         <is>
           <t>Máx. 200 KB por ficheiro.</t>
@@ -17826,7 +17795,6 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/push-down/</t>
@@ -17869,7 +17837,6 @@
           <t>Duração máx. recomendada 20s (CPV contabilizado aos 20s em campanhas por visualizações).</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>Máx. 100 MB.</t>
@@ -17880,7 +17847,6 @@
           <t>MP3.</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/audio-ad/</t>
@@ -17938,7 +17904,6 @@
           <t>MP4.</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/pre-roll/</t>
@@ -17996,7 +17961,6 @@
           <t>MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/incontent-sticky/</t>
@@ -18054,7 +18018,6 @@
           <t>MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/incontent/</t>
@@ -18097,7 +18060,6 @@
           <t>1260x200px + 728x150px + 320x100px, ou 970x250px + 728x90px + 320x50px.</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
           <t>Máx. 200 KB por ficheiro.</t>
@@ -18108,7 +18070,6 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/superboard/</t>
@@ -18151,7 +18112,6 @@
           <t>300x250px</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
           <t>Máx. 150 KB.</t>
@@ -18162,7 +18122,6 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/mrec/</t>
@@ -18205,7 +18164,6 @@
           <t>300x600px</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
           <t>Máx. 200 KB.</t>
@@ -18216,7 +18174,6 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/half-page/</t>
@@ -18259,7 +18216,6 @@
           <t>1260x370px + 728x338px + 320x239px. Se tiver vídeo, deixar espaço nas imagens.</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>Máx. 200 KB por ficheiro.</t>
@@ -18270,7 +18226,6 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/megapub/</t>
@@ -18328,7 +18283,6 @@
           <t>MP4.</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/mrec-video/</t>
@@ -18371,7 +18325,6 @@
           <t>300x600px.</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>Imagem: máx. 150 KB. Vídeo: máx. 2 MB.</t>
@@ -18382,7 +18335,6 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/half-page-video/</t>
@@ -18440,7 +18392,6 @@
           <t>MP4.</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/half-page-full-video/</t>
@@ -18483,14 +18434,11 @@
           <t>Sem dimensão fixa — usa o post/link social já publicado.</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr">
         <is>
           <t>Link social do Facebook, Instagram, X (Twitter) ou LinkedIn.</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/social-card/</t>
@@ -18533,7 +18481,6 @@
           <t>2 a 5 imagens, 300x600px cada.</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
           <t>Máx. 100 KB por imagem.</t>
@@ -18544,7 +18491,6 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/filmstrip/</t>
@@ -18587,7 +18533,6 @@
           <t>2 imagens: 300x250px + 640x124px.</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>Máx. 200 KB por imagem.</t>
@@ -18608,6 +18553,164 @@
           <t>https://noticiasilimitadas.pt/digital/newsletter/</t>
         </is>
       </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Azerion</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>WeTransfer</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Takeover</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Static Starter</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Ficheiro PSD 2560x1600px (perfil de cores RGB). 3 elementos gráficos em layers: imagem de fundo; copy (em imagem ou texto); logo.</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>8:5</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Opções de layout: fundo com copy (base); + CTA à esquerda ou à direita (opcional); + logo no topo, à esquerda ou à direita.</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Anzu</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Display Ads</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>480x320px, 320x480px, 320x50px, 300x250px ou 640x360px. Máx. 1024px no lado maior; recomendado mín. 512px no lado maior, mantendo o aspect ratio.</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>3:2, 2:3, 6.4:1, 6:5 ou 16:9 (consoante o tamanho escolhido)</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>PNG, JPG ou BMP (também aceite em GIF, redimensionado automaticamente pela Anzu).</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox.</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>OLX</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Homepage Leaderboard</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>320x100px</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Máx. 1 MB</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>JPEG, JPG, PNG, GIF ou HTML5 (GWD)</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L340"/>
+  <dimension ref="A1:L355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -18595,7 +18595,6 @@
           <t>8:5</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr">
         <is>
           <t>PSD</t>
@@ -18603,10 +18602,9 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Opções de layout: fundo com copy (base); + CTA à esquerda ou à direita (opcional); + logo no topo, à esquerda ou à direita.</t>
-        </is>
-      </c>
-      <c r="L338" t="inlineStr"/>
+          <t>Opções de layout: fundo com copy (base); + CTA à esquerda ou à direita (opcional); + logo no topo, à esquerda ou à direita. Suporte com tracking DCM. Ver ficha técnica adicional fornecida pelo meio ("We Transfer", não disponibilizada aqui).</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -18621,7 +18619,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Anzu</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -18649,7 +18647,6 @@
           <t>3:2, 2:3, 6.4:1, 6:5 ou 16:9 (consoante o tamanho escolhido)</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr">
         <is>
           <t>PNG, JPG ou BMP (também aceite em GIF, redimensionado automaticamente pela Anzu).</t>
@@ -18657,10 +18654,9 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox.</t>
-        </is>
-      </c>
-      <c r="L339" t="inlineStr"/>
+          <t>Suporte com tracking DCM. Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox. Ver ficheiro técnico adicional fornecido pelo meio (não disponibilizado aqui).</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -18698,7 +18694,6 @@
           <t>320x100px</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
           <t>Máx. 1 MB</t>
@@ -18709,8 +18704,744 @@
           <t>JPEG, JPG, PNG, GIF ou HTML5 (GWD)</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Azerion</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Azerion</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Ficheiros de trabalho necessários: banners laterais em PSD, fontes (fonts), copies e color book/codes. As dimensões exatas dos banners laterais constam numa folha técnica adicional fornecida pelo meio (não disponibilizada aqui).</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>PSD</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Os banners laterais podem ser iguais ou diferentes, ao critério do cliente. Suporte com tracking DCM. O meio ajuda a produzir a versão final — se houver elementos extra com que possa trabalhar para enriquecer o formato, enviar os ficheiros editáveis.</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Azerion</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Azerion</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Native ad</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>1.91:1, 1.78:1, 1.5:1, 1.33:1 ou 1:1 (pelo menos um obrigatório)</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Máx. 200 KB</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Tag (Sizmek, DoubleClick, Weborama, etc.), Imagem (JPG, GIF) ou HTML5 (*)</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Suporte com tracking DCM. Copies (todos obrigatórios): Short Headline (x2) — máx. 30 caracteres; Long Headline — 90 caracteres; Descrição — 90 caracteres; Business/Brand Name — 25 caracteres.</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>728x90px (Desktop, Tablet)</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Leaderboard</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Mobile Leaderboard</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>320x50px (Mobile)</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Mrec</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>MREC (mpu)</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>300x250px (All)</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Máx. 150 KB</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>GIF, JPEG ou HTML5</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#mpu-h4</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Billboard (desktop)</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>970x250px (Desktop)</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>GIF, JPEG ou HTML5</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#bb-h4</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Billboard</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Mobile Billboard</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>320x100px (Mobile)</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Halfpage</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Halfpage (double mpu)</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>300x600px (All)</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Máx. 250 KB</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>GIF, JPEG ou HTML5</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr"/>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#dmpu-h4</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Native</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Responsive (All) — adapta-se ao layout do site.</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Formatos nativos personalizados, específicos por site. Consultar as specs próprias de cada site (ex.: Bauer Native — All Site) através do link fornecido pelo meio (não disponibilizado aqui).</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Interscroller</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Mobile Interscroller</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>300x600px (Mobile)</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Servido via tag de terceiros (Mobkoi).</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Rich Media</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Socially Inspired Rich Media</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Multi — formato construído internamente pela Illuminate (Mobile).</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Solução de rich media interativa, otimizada mobile-first, com formatos inspirados em redes sociais, para alcançar utilizadores durante a leitura de conteúdo editorial. Specs técnicas completas num documento à parte ("Social Display RMF Specifications"), não disponibilizado aqui.</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Takeover</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Standard Takeover</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Multi (All) — combinação de vários espaços publicitários na página.</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Skin/hero images em formato estático: JPG ou PNG.</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Takeover</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Hero Takeover</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Responsive (All).</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Skin/hero images em formato estático: JPG ou PNG.</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>In-Feed Video</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>In-Article Video</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Mín. 4 KB, máx. 4 MB</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Anúncio de vídeo autónomo entre parágrafos de conteúdo editorial (mobile, tablet e desktop). Reproduz automaticamente quando 50% do anúncio está visível; som desligado por defeito; botão "Learn More" no fundo do anúncio (único elemento clicável).</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>INTERNET</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Pre-Roll</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Radio Player Pre-Roll</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Mín. 4 KB, máx. 4 MB</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Pre-roll único, reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer.</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base-formatos.xlsx
+++ b/data/base-formatos.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L355"/>
+  <dimension ref="A1:M355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.08984375" customWidth="1" style="2" min="1" max="1"/>
@@ -516,7 +516,12 @@
           <t>Copies</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
@@ -568,7 +573,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/billboard.html</t>
         </is>
@@ -620,7 +625,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/cube.html</t>
         </is>
@@ -672,7 +677,7 @@
           <t>GIF, JPEG ou PNG</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/floorad.html</t>
         </is>
@@ -729,7 +734,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/halfpage.html</t>
         </is>
@@ -776,7 +781,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/headerxl.html</t>
         </is>
@@ -828,7 +833,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/hero.html</t>
         </is>
@@ -885,7 +890,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/in-article.html</t>
         </is>
@@ -942,7 +947,7 @@
           <t>HTML, JPG ou GIF</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/interscroller.html</t>
         </is>
@@ -999,7 +1004,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/interstitial.html</t>
         </is>
@@ -1051,7 +1056,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/mrec.html</t>
         </is>
@@ -1103,7 +1108,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/mrec_video.html</t>
         </is>
@@ -1160,7 +1165,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/pushdown.html</t>
         </is>
@@ -1217,7 +1222,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/opendoor.html</t>
         </is>
@@ -1274,7 +1279,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/video-instream.html</t>
         </is>
@@ -1331,7 +1336,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>https://publicidade.impresa.pt/onlinespecs/video-outstream.html</t>
         </is>
@@ -1383,7 +1388,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/billboard/</t>
         </is>
@@ -1440,7 +1445,7 @@
           <t>PNG</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/billboard-xl/</t>
         </is>
@@ -1497,7 +1502,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/carrossel-incontent/</t>
         </is>
@@ -1554,7 +1559,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/carrossel-top/</t>
         </is>
@@ -1611,7 +1616,7 @@
           <t>JPEG</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/dossier/</t>
         </is>
@@ -1668,7 +1673,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/full-frame/</t>
         </is>
@@ -1725,7 +1730,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/halfpage/</t>
         </is>
@@ -1782,7 +1787,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/interscroller/</t>
         </is>
@@ -1839,7 +1844,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/intro-desktop/</t>
         </is>
@@ -1891,7 +1896,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/intro-splash/</t>
         </is>
@@ -1948,7 +1953,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/l-frame/</t>
         </is>
@@ -2000,7 +2005,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/leaderboard/</t>
         </is>
@@ -2052,7 +2057,7 @@
           <t>Imagens (S, M, L e XL)</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/megabillboard/</t>
         </is>
@@ -2104,7 +2109,7 @@
           <t>HTML + Imagens</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/mrec/</t>
         </is>
@@ -2161,7 +2166,7 @@
           <t>JPEG</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/native/</t>
         </is>
@@ -2218,7 +2223,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/open-door/</t>
         </is>
@@ -2265,7 +2270,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/outstream/</t>
         </is>
@@ -2312,7 +2317,7 @@
           <t>Imagens</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pageflip/</t>
         </is>
@@ -2364,7 +2369,7 @@
           <t>JPEG, PNG ou GIF + Copies</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pop-in/</t>
         </is>
@@ -2416,7 +2421,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/post-social-media/</t>
         </is>
@@ -2473,7 +2478,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/pre-roll/</t>
         </is>
@@ -2530,7 +2535,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/7668/</t>
         </is>
@@ -2587,7 +2592,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/push-down/</t>
         </is>
@@ -2644,7 +2649,7 @@
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/reel-social-media/</t>
         </is>
@@ -2696,7 +2701,7 @@
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/side-frame/</t>
         </is>
@@ -2738,7 +2743,7 @@
           <t>Link post Facebook ou Instagram</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/social-card/</t>
         </is>
@@ -2790,7 +2795,7 @@
           <t>JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/splash/</t>
         </is>
@@ -2847,7 +2852,7 @@
           <t>MP4 ou MOV</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/story-social-media/</t>
         </is>
@@ -2899,7 +2904,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/brand-day-takeover/</t>
         </is>
@@ -2956,7 +2961,7 @@
           <t>PNG</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/ticker/</t>
         </is>
@@ -3013,7 +3018,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/vertical-video/</t>
         </is>
@@ -3060,7 +3065,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>https://mediacapitalcomercial.pt/format/videowall/</t>
         </is>
@@ -3112,7 +3117,7 @@
           <t>HTML / MP4</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/cornerad/</t>
         </is>
@@ -3164,7 +3169,7 @@
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/floorad/</t>
         </is>
@@ -3221,7 +3226,7 @@
           <t>HTML, JPEG, PNG ou GIF / MP4</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/half-page/</t>
         </is>
@@ -3278,7 +3283,7 @@
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/incontent/</t>
         </is>
@@ -3335,7 +3340,7 @@
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/intro/</t>
         </is>
@@ -3387,7 +3392,7 @@
           <t>JPEG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/layer/</t>
         </is>
@@ -3439,7 +3444,7 @@
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/leaderboard/</t>
         </is>
@@ -3491,7 +3496,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/masthead/</t>
         </is>
@@ -3543,7 +3548,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/masthead-sticky-companion/</t>
         </is>
@@ -3590,7 +3595,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/moldura/</t>
         </is>
@@ -3642,7 +3647,7 @@
           <t>HTML, JPEG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/m-rec/</t>
         </is>
@@ -3699,7 +3704,7 @@
           <t>JPG, GIF ou PNG / MP4</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/open-door/</t>
         </is>
@@ -3751,7 +3756,7 @@
           <t>260 KB</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/peel-off/</t>
         </is>
@@ -3808,7 +3813,7 @@
           <t>MP4 ou FLV</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/pre-roll/</t>
         </is>
@@ -3845,7 +3850,7 @@
           <t>Showcase Rich Media</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/showcase-richmedia/</t>
         </is>
@@ -3882,7 +3887,7 @@
           <t>Sideticker</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/sideticker/</t>
         </is>
@@ -3919,7 +3924,7 @@
           <t>Slash</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/slash/</t>
         </is>
@@ -3956,7 +3961,7 @@
           <t>Topo Extensivel</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>https://www.medialivreboostsolutions.pt/adspecs/topo-extensivel/</t>
         </is>
@@ -4003,7 +4008,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/audio-desktop.html</t>
         </is>
@@ -4055,7 +4060,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/nl-desktop.html</t>
         </is>
@@ -4112,7 +4117,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/carrossel-desktop.html</t>
         </is>
@@ -4169,7 +4174,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/compare-desktop.html</t>
         </is>
@@ -4226,7 +4231,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/flipper-desktop.html</t>
         </is>
@@ -4283,7 +4288,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/halfpage-desktop.html</t>
         </is>
@@ -4335,7 +4340,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/header_xl-desktop.html</t>
         </is>
@@ -4387,7 +4392,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/interstitial-desktop.html</t>
         </is>
@@ -4439,7 +4444,7 @@
           <t>GIF ou WEBM</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/intro-dinamic-desktop.html</t>
         </is>
@@ -4486,7 +4491,7 @@
           <t>PDF</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/intro-folheto-desktop.html</t>
         </is>
@@ -4538,7 +4543,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/manchete-desktop.html</t>
         </is>
@@ -4590,7 +4595,7 @@
           <t>JPG, PNG ou GIF / HTML</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/mrec-desktop.html</t>
         </is>
@@ -4637,7 +4642,7 @@
           <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/opendoor-desktop.html</t>
         </is>
@@ -4694,7 +4699,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/outstream-desktop.html</t>
         </is>
@@ -4751,7 +4756,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/pell-off-desktop.html</t>
         </is>
@@ -4808,7 +4813,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/pre-roll-desktop.html</t>
         </is>
@@ -4860,7 +4865,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/skin-desktop.html</t>
         </is>
@@ -4912,7 +4917,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-dynamic-mobile.html</t>
         </is>
@@ -4964,7 +4969,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-footer-desktop.html</t>
         </is>
@@ -5021,7 +5026,7 @@
           <t>JPG, PNG ou GIF / MP4</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/sticky-to-intro-desktop.html</t>
         </is>
@@ -5078,7 +5083,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>https://formatos.observador.pt/twinad-desktop.html</t>
         </is>
@@ -5135,7 +5140,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/ad-selector.html</t>
         </is>
@@ -5187,7 +5192,7 @@
           <t>HTML, JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/barra-topo.html</t>
         </is>
@@ -5239,7 +5244,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/barra-topo-extensivel.html</t>
         </is>
@@ -5291,7 +5296,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/billboard.html</t>
         </is>
@@ -5343,7 +5348,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/cubo-mrec.html</t>
         </is>
@@ -5395,7 +5400,7 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/floorad.html</t>
         </is>
@@ -5452,7 +5457,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/gallery-flip.html</t>
         </is>
@@ -5509,7 +5514,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/halfpage.html</t>
         </is>
@@ -5566,7 +5571,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/interstitial.html</t>
         </is>
@@ -5618,7 +5623,7 @@
           <t>HTML, JPG, PNG ou GIF / Video</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/mrec.html</t>
         </is>
@@ -5670,7 +5675,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/newsletter.html</t>
         </is>
@@ -5722,7 +5727,7 @@
           <t>JPG / Video</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/opendoor.html</t>
         </is>
@@ -5779,7 +5784,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/parallax.html</t>
         </is>
@@ -5836,7 +5841,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/prisma-halfpage.html</t>
         </is>
@@ -5893,7 +5898,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/scratch-.html</t>
         </is>
@@ -5950,7 +5955,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/shopping-ads-.html</t>
         </is>
@@ -6007,7 +6012,7 @@
           <t>JPG</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/slidedoorvideo.html</t>
         </is>
@@ -6054,7 +6059,7 @@
           <t>JPEG, JPG ou PNG</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/slidervideo.html</t>
         </is>
@@ -6106,7 +6111,7 @@
           <t>JPG, PNG ou GIF / Video para a área expandida</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/xxl.html</t>
         </is>
@@ -6153,7 +6158,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/galeria_header.html</t>
         </is>
@@ -6205,7 +6210,7 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/twinad.html</t>
         </is>
@@ -6262,7 +6267,7 @@
           <t>MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/incontent.html</t>
         </is>
@@ -6319,7 +6324,7 @@
           <t>MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>https://comunique.publico.pt/publicidade/formatos/pre-roll.html</t>
         </is>
@@ -6371,7 +6376,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278437-cube-3d-viewable-display</t>
         </is>
@@ -6428,7 +6433,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-app_install_native_outbrain</t>
         </is>
@@ -6475,7 +6480,7 @@
           <t>MPEG, MP3, WAV, ou OGG</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/audio-ad-specs/</t>
         </is>
@@ -6522,7 +6527,7 @@
           <t>MP3</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6569,7 +6574,7 @@
           <t>MP3</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6616,7 +6621,7 @@
           <t>MP3</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-audio_preroll_midroll_postroll</t>
         </is>
@@ -6668,7 +6673,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_1a_2a_posicao</t>
         </is>
@@ -6725,7 +6730,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_carousel</t>
         </is>
@@ -6772,7 +6777,7 @@
           <t>200 KB</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard_iab</t>
         </is>
@@ -6824,7 +6829,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-billboard</t>
         </is>
@@ -6861,7 +6866,7 @@
           <t>Branded Content</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-artigos_content_marketing</t>
         </is>
@@ -6918,7 +6923,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-capa_falsa</t>
         </is>
@@ -6970,7 +6975,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206459-carousel-square,  https://support.teads.tv/support/solutions/articles/36000206458-carousel-landscape, https://support.teads.tv/support/solutions/articles/36000552432-carousel-vertical-</t>
         </is>
@@ -7027,7 +7032,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t>https://www.outbrain.com/help/ads-specs/#carousel</t>
         </is>
@@ -7143,7 +7148,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-companion_banner_resumo_artigo</t>
         </is>
@@ -7200,7 +7205,7 @@
           <t>PNG</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-countdown</t>
         </is>
@@ -7353,7 +7358,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-display_standard_cpc_surf</t>
         </is>
@@ -7405,7 +7410,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278434-drag-drop-viewable-display</t>
         </is>
@@ -7457,7 +7462,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552435-flip-flow-viewable-display</t>
         </is>
@@ -7509,7 +7514,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206460-flow-square, https://support.teads.tv/support/solutions/articles/36000206461-flow-landscape</t>
         </is>
@@ -7566,7 +7571,7 @@
           <t>JPG, PNG ou GIF / MP4 ou WEBM</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage, https://saleshouse.sapo.pt/formatos.html#format-halfpage_video</t>
         </is>
@@ -7623,7 +7628,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-halfpage_flip</t>
         </is>
@@ -7904,7 +7909,7 @@
           <t>JPG / MOV ou MP4</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-SG/ad-experiences/display-homepage-takeover-ads-specs/</t>
         </is>
@@ -7961,7 +7966,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278440-hover-viewable-display</t>
         </is>
@@ -8018,7 +8023,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/display-ad-specs/</t>
         </is>
@@ -8055,7 +8060,7 @@
           <t>In-feed Video (Spotify)</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/in-feed-video-ad-specs/</t>
         </is>
@@ -8107,7 +8112,7 @@
           <t>JPG, PNG ou WEBP / MP4</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/inline-midscroll-template</t>
         </is>
@@ -8164,7 +8169,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552431-interscroller-display</t>
         </is>
@@ -8221,7 +8226,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000552411-interscroller-video</t>
         </is>
@@ -8278,7 +8283,7 @@
           <t>JPG, PNG ou GIF</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra</t>
         </is>
@@ -8330,7 +8335,7 @@
           <t>WEBP ou GIF</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_plus</t>
         </is>
@@ -8382,7 +8387,7 @@
           <t>HTML5 responsive com recursos em WEBP e MP4/WEBM, WEBP ou GIF (Leaderboard e Mobile)</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_plus_video</t>
         </is>
@@ -8439,7 +8444,7 @@
           <t>MP4 ou WEBP</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-intra_video</t>
         </is>
@@ -8496,7 +8501,7 @@
           <t>MP4, WebM, ou MOV</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t>https://ads.spotify.com/en-US/ad-specs/in-stream-video-ad-specs/</t>
         </is>
@@ -8533,7 +8538,7 @@
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-microsites_landing_pages</t>
         </is>
@@ -8585,7 +8590,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-leaderboard</t>
         </is>
@@ -8622,7 +8627,7 @@
           <t>Microsite</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-microsites_landing_pages</t>
         </is>
@@ -8674,7 +8679,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mobile_banner</t>
         </is>
@@ -8726,7 +8731,7 @@
           <t>JPG, PNG ou GIF / MP4 ou WEBP</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mrec, https://saleshouse.sapo.pt/formatos.html#format-mrec_video</t>
         </is>
@@ -8778,7 +8783,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-mrec_carousel</t>
         </is>
@@ -8835,7 +8840,7 @@
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206444-video-overlay</t>
         </is>
@@ -8892,7 +8897,7 @@
           <t>JPG, PNG ou WEBP / MP4</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/inline-expander-reel-template</t>
         </is>
@@ -8949,7 +8954,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278439-scratch-viewable-display</t>
         </is>
@@ -9001,7 +9006,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206455-scroller-square, https://support.teads.tv/support/solutions/articles/36000206453-scroller-landscape, https://support.teads.tv/support/solutions/articles/36000206456-scroller-vertical</t>
         </is>
@@ -9053,7 +9058,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000434238-shoppable-carousel</t>
         </is>
@@ -9105,7 +9110,7 @@
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000206452-shoppable-square, https://support.teads.tv/support/solutions/articles/36000206451-shoppable-landscape, https://support.teads.tv/support/solutions/articles/36000552430-shoppable-vertical</t>
         </is>
@@ -9157,7 +9162,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000208421-single-image</t>
         </is>
@@ -9204,7 +9209,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000297712-single-video</t>
         </is>
@@ -9246,7 +9251,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/fluid-skin-image-video</t>
         </is>
@@ -9303,7 +9308,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278442-slider-viewable-display</t>
         </is>
@@ -9360,7 +9365,7 @@
           <t>JPG ou PNG / MP4</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000366159-inread-smart6</t>
         </is>
@@ -9402,7 +9407,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000238201-social-video-image-layout-1-, https://support.teads.tv/support/solutions/articles/36000238202-social-video-image-layout-2-</t>
         </is>
@@ -9444,7 +9449,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000297713-social-layout-1-performance, https://support.teads.tv/support/solutions/articles/36000297714-social-layout-2-performance</t>
         </is>
@@ -9486,7 +9491,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000238201-social-video-image-layout-1-, https://support.teads.tv/support/solutions/articles/36000238202-social-video-image-layout-2-</t>
         </is>
@@ -9538,7 +9543,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278441-spin-card-viewable-display</t>
         </is>
@@ -9590,7 +9595,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-standard_green_ad</t>
         </is>
@@ -9647,7 +9652,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t>https://www.outbrain.com/help/ads-specs/#native-image</t>
         </is>
@@ -9689,7 +9694,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000245892-stories-display-square, https://support.teads.tv/support/solutions/articles/36000245899-stories-display-vertical</t>
         </is>
@@ -9731,7 +9736,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000245891-stories-video-square, https://support.teads.tv/support/solutions/articles/36000245901-stories-video-vertical</t>
         </is>
@@ -9788,7 +9793,7 @@
           <t>JPG ou PNG</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t>https://support.teads.tv/support/solutions/articles/36000278444-swipe-carousel-viewable-display</t>
         </is>
@@ -9845,7 +9850,7 @@
           <t>JPG, PNG ou WEBP</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-desktop-image</t>
         </is>
@@ -9887,7 +9892,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/fluid-product-carousel, https://www.adnami.io/specs/dynamic-hybrid-carousel, https://www.adnami.io/specs/product-lightbox</t>
         </is>
@@ -9939,7 +9944,7 @@
           <t>JPG ou WEBP</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-expand-template-image-desktop, https://www.adnami.io/specs/topscroll-expand-template-image-mobile</t>
         </is>
@@ -9991,7 +9996,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-expand-template-desktop, https://www.adnami.io/specs/topscroll-expand-template-mobile</t>
         </is>
@@ -10043,7 +10048,7 @@
           <t>JPG ou WEBP</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/prismo</t>
         </is>
@@ -10085,7 +10090,7 @@
           <t>Várias, consultar o link</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t>https://www.adnami.io/specs/topscroll-desktop-video, https://www.adnami.io/specs/topscroll-mobile-video</t>
         </is>
@@ -10137,7 +10142,7 @@
           <t>WEBP</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-twin_ad</t>
         </is>
@@ -10194,7 +10199,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
@@ -10251,7 +10256,7 @@
           <t>MP4</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t>https://saleshouse.sapo.pt/formatos.html#format-video_instream_preroll_midroll</t>
         </is>
@@ -10308,7 +10313,7 @@
           <t>Sem título/texto introdutório editável — o criativo é o artigo/newsletter orgânico original.</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/articles-and-newsletters-ads/specs</t>
         </is>
@@ -10370,7 +10375,7 @@
           <t>Nome do anúncio (opcional): 255c; Título do cartão: 45c; Texto introdutório: 255c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/carousel-ads/specs</t>
         </is>
@@ -10427,7 +10432,7 @@
           <t>MP4, codec H.264, bitrate mín. 12 Mbps (recomendado 15–40 Mbps), frame rate constante (23,98/24/25/29,97/30 fps), áudio 2 canais -23 LUFS integrado, PCM (16/24 bit) ou AAC ≥192 Kbps, 48 kHz, chroma 4:2:0 (recomendado 4:2:2).</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/connected-tv-ads/specs</t>
         </is>
@@ -10484,7 +10489,7 @@
           <t>Nome do anúncio (opcional): 255c; Texto da mensagem: máx. 8000c; Rodapé personalizado: máx. 20000c; CTA: máx. 25c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-messaging/conversation-ads/specs</t>
         </is>
@@ -10541,7 +10546,7 @@
           <t>Nome do anúncio (opcional): 255c; Título: 70c; Texto introdutório: 150c.</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/document-ads/specs</t>
         </is>
@@ -10603,7 +10608,7 @@
           <t>Nome do evento (opcional): 255c; Texto introdutório: 600c; Event URL: obrigatório, só páginas de Evento do LinkedIn.</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/event-ads/specs</t>
         </is>
@@ -10665,7 +10670,7 @@
           <t>Título: 50c; Descrição: 70c; Nome da empresa: 25c.</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/dynamic-ads/follower-ads</t>
         </is>
@@ -10722,7 +10727,7 @@
           <t>Texto introdutório: até 150c.</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/ads-guide</t>
         </is>
@@ -10779,7 +10784,7 @@
           <t>Nome do formulário: 256c; Título da oferta: 60c; Detalhe da oferta (opcional): 160c; Política de privacidade: 2000c; CTA: 20c; Mensagem de confirmação: 300c; Perguntas personalizadas: até 3, 100c cada; campos recomendados: 3-4 (máx. 12).</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/lead-gen-ads/specs</t>
         </is>
@@ -10836,7 +10841,7 @@
           <t>Nome do anúncio (opcional): 255c; Texto da mensagem: máx. 8000c; Rodapé personalizado: máx. 20000c; CTA: máx. 25c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-messaging/message-ads/specs</t>
         </is>
@@ -10898,7 +10903,7 @@
           <t>Nome do anúncio (opcional): 255c; Título: 70c; Texto introdutório: 150c (máx. 3000c); Descrição (só LAN): 70c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/single-image-ads-specs</t>
         </is>
@@ -10960,7 +10965,7 @@
           <t>Nome do anúncio (opcional): 255c; Título: 70c (máx. 200c); Texto introdutório: 150c (máx. 600c).</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/video-ads/specs</t>
         </is>
@@ -11022,7 +11027,7 @@
           <t>Título: 50c; Descrição: 70c; Nome da empresa: 25c; CTA: 18c; Landing page URL: máx. 500c.</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/dynamic-ads/spotlight-ads</t>
         </is>
@@ -11084,7 +11089,7 @@
           <t>Título: 25c; Descrição: 75c; Landing page URL: máx. 2000c.</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/text-ads/specs</t>
         </is>
@@ -11141,7 +11146,7 @@
           <t>Sem título/texto introdutório editável — o criativo é o post orgânico original; sem CTA.</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t>https://business.linkedin.com/advertise/ads/sponsored-content/thought-leader-ads/specs</t>
         </is>
@@ -11203,7 +11208,7 @@
           <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: até 800c.</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11265,7 +11270,7 @@
           <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: só aparece em Pins de Collection orgânicos vistos de perto, não em ads promovidos.</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11327,7 +11332,7 @@
           <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: até 800c.</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11389,7 +11394,7 @@
           <t>Título: até 100c (só os primeiros 40c podem mostrar no feed; 30c para chinês/japonês/coreano/árabe); Descrição: até 800c.</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -11451,7 +11456,7 @@
           <t>Título: até 300c, 1 (recomendado ≤100c, mais seguro ≤80c); URL de destino: até 268c, 1 por imagem; Legenda: até 50c, 1 por imagem; URL de exibição: até 100c, 1 por imagem (tem de corresponder ao domínio do destino); CTA: à escolha.</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t>https://business.reddithelp.com/s/article/carousel-ad-specifications</t>
         </is>
@@ -11513,7 +11518,7 @@
           <t>Título: até 300c, 1 (recomendado ≤100c, mais seguro ≤80c); Corpo: até 40.000c, 1 (recomendado 3-6 linhas em texto simples no feed); Legenda: até 50c, 1 por imagem/vídeo.</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t>https://business.reddithelp.com/s/article/free-form-ad-specifications</t>
         </is>
@@ -11575,7 +11580,7 @@
           <t>Título: até 300c (recomendado ≤100c, mais seguro ≤80c); URL de destino: até 268c; URL de exibição: até 100c (tem de corresponder ao domínio do destino); CTA: à escolha.</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t>https://business.reddithelp.com/s/article/image-ad-specifications</t>
         </is>
@@ -11627,7 +11632,7 @@
           <t>Catálogo de produtos + JPG/PNG ou vídeo conforme configuração</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t>https://www.business.reddit.com/advertise/ad-types</t>
         </is>
@@ -11689,7 +11694,7 @@
           <t>Título: até 300c (recomendado ≤100c, mais seguro ≤80c); URL de destino: até 268c; URL de exibição: até 100c (tem de corresponder ao domínio do destino); CTA: à escolha.</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t>https://business.reddithelp.com/s/article/video-ad-specifications</t>
         </is>
@@ -11741,7 +11746,7 @@
           <t>PNG (estático), GIF (animado)</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11803,7 +11808,7 @@
           <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11860,7 +11865,7 @@
           <t>MP4 ou MOV (H.264)</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11922,7 +11927,7 @@
           <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -11984,7 +11989,7 @@
           <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -12046,7 +12051,7 @@
           <t>Marca: até 25c com espaços; Título: até 34c com espaços.</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -12103,7 +12108,7 @@
           <t>PNG + assets de efeito conforme template</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/help/article/tiktok-branded-effect-asset-commercial-benefits-specs?lang=en</t>
         </is>
@@ -12162,10 +12167,15 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Nome do anunciante: até 24c (sem espaços/emojis/caracteres especiais, exceto '&amp;'). Nome da Mission: até 70c (recomendado ≤18c para caber numa linha; sem espaços/emojis/caracteres especiais como &lt; &gt; " &amp;). Descrição da Mission: até 300c (recomendado ≤150c). Legenda do vídeo de exemplo: até 150c (recomendado 4-60c, sem quebras de linha). Nome da música: até 60c (recomendado ≤12c); nome do artista sem limite (recomendado ≤12c). Nome do logo: até 20c. Nome de concorrente/marca (brand safety): até 20c cada. Requisitos: pelo menos 1 requisito geral obrigatório (música oficial, hashtag oficial, mencionar conta oficial, usar/acionar Branded Effect, ou Duet); até 3 requisitos específicos opcionais (dançar, lip-sync, mudar de roupa, mostrar a cara); requisitos de marca opcionais (revelar logo &gt;1s, usar Quick Effect).</t>
+          <t>Nome do anunciante: até 24c (sem espaços/emojis/caracteres especiais, exceto '&amp;'). Nome da Mission: até 70c (recomendado ≤18c para caber numa linha; sem espaços/emojis/caracteres especiais como &lt; &gt; " &amp;). Descrição da Mission: até 300c (recomendado ≤150c). Legenda do vídeo de exemplo: até 150c (recomendado 4-60c, sem quebras de linha). Nome da música: até 60c (recomendado ≤12c); nome do artista sem limite (recomendado ≤12c). Nome do logo: até 20c. Nome de concorrente/marca (brand safety): até 20c cada.</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t>Requisitos: pelo menos 1 requisito geral obrigatório (música oficial, hashtag oficial, mencionar conta oficial, usar/acionar Branded Effect, ou Duet); até 3 requisitos específicos opcionais (dançar, lip-sync, mudar de roupa, mostrar a cara); requisitos de marca opcionais (revelar logo &gt;1s, usar Quick Effect).</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/help/article/about-branded-mission</t>
         </is>
@@ -12222,7 +12232,7 @@
           <t>JPG/JPEG, PNG + MP3</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="M224" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/specifications-for-carousel-ads?lang=pt</t>
         </is>
@@ -12281,10 +12291,15 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Legenda: exibida em branco, fonte uniforme (não personalizável); não suporta links clicáveis, símbolo '@' nem hashtags. Nome da conta: 1 linha, máx. 10c (CN/JP/KR) ou 20c (outras línguas). Zonas seguras variam consoante orientação (vertical/horizontal/quadrado), idioma (LTR/RTL) e uso de anchors — ficheiros de referência disponíveis na TikTok Ads Help.</t>
+          <t>Legenda: exibida em branco, fonte uniforme (não personalizável); não suporta links clicáveis, símbolo '@' nem hashtags. Nome da conta: 1 linha, máx. 10c (CN/JP/KR) ou 20c (outras línguas).</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t>Zonas seguras variam consoante orientação (vertical/horizontal/quadrado), idioma (LTR/RTL) e uso de anchors — ficheiros de referência disponíveis na TikTok Ads Help.</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12336,7 +12351,7 @@
           <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/help/article/split-testing-variables?lang=en</t>
         </is>
@@ -12393,7 +12408,7 @@
           <t>Pull: .mp4 ou .mov (do vídeo orgânico). Push: MP4, MOV, MPEG, 3GP.</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="M227" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12450,7 +12465,7 @@
           <t>MP4, MOV / Spark Ads</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="M228" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
@@ -12509,10 +12524,15 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Foto de perfil: quadrada, 98x98px, &lt;50 KB, .jpg/.jpeg/.png (elemento-chave centrado numa área de 66x66px); em Spark Ads usa a foto de perfil da conta do vídeo. Nome da conta: 1 linha, máx. 10c (CN/JP/KR) ou 20c (outras línguas), sem emojis nem '{ }'. Legenda do anúncio: Spark Ads Pull até 100c (extraída do vídeo orgânico, pode ser vazia); Non-Spark/Spark Push até 100c, máx. 4 linhas visíveis (recomendado ≤50c CN/JP/KR ou ≤100c outras línguas para não ser coberta por 'Ver mais'), sem '{ }', emojis só a partir da versão 11. Máx. 20 anúncios por ad group.</t>
+          <t>Foto de perfil: quadrada, 98x98px, &lt;50 KB, .jpg/.jpeg/.png (elemento-chave centrado numa área de 66x66px); em Spark Ads usa a foto de perfil da conta do vídeo. Nome da conta: 1 linha, máx. 10c (CN/JP/KR) ou 20c (outras línguas), sem emojis nem '{ }'. Legenda do anúncio: Spark Ads Pull até 100c (extraída do vídeo orgânico, pode ser vazia); Non-Spark/Spark Push até 100c, máx. 4 linhas visíveis (recomendado ≤50c CN/JP/KR ou ≤100c outras línguas para não ser coberta por 'Ver mais'), sem '{ }', emojis só a partir da versão 11.</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t>Máx. 20 anúncios por ad group.</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/tiktok-reservation-topview?lang=pt</t>
         </is>
@@ -12574,7 +12594,7 @@
           <t>1 destino (Carousel de destino único) ou até 6 destinos únicos (Carousel multi-destino).</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12636,7 +12656,7 @@
           <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="M231" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12693,7 +12713,7 @@
           <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12755,7 +12775,7 @@
           <t>Texto do post: até 280c (cada link usado reduz 280c em 23c, ficando efetivamente 257c).</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -12807,7 +12827,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -12859,7 +12879,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -12911,7 +12931,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -12968,7 +12988,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
+      <c r="M237" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13020,7 +13040,7 @@
           <t>JPG, PNG, GIF</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
+      <c r="M238" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13077,7 +13097,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13134,7 +13154,7 @@
           <t>ZIP HTML5</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
+      <c r="M240" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13676244</t>
         </is>
@@ -13191,7 +13211,7 @@
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="M241" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13248,7 +13268,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13305,7 +13325,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="M243" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13362,7 +13382,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
+      <c r="M244" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -13424,7 +13444,7 @@
           <t>Título: 2 linhas, 40 caracteres cada; Descrição: 2 linhas, 35 caracteres cada.</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
+      <c r="M245" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13481,7 +13501,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
+      <c r="M246" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13538,7 +13558,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
+      <c r="M247" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13595,7 +13615,7 @@
           <t>JPG, PNG, GIF (não animado)</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
+      <c r="M248" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -13652,7 +13672,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -13714,7 +13734,7 @@
           <t>Título por cartão: até 40 caracteres</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
+      <c r="M250" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/13704860</t>
         </is>
@@ -13818,12 +13838,13 @@
           <t>ZIP com HTML5 e pastas de imagens/scripts, ou JPEG/GIF; enviar sempre uma imagem de backup incluída no ZIP da criatividade.</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
         <is>
           <t>Não há template para peças servidas em Google — inserir sempre a clicktag do Google (GWD: inserida no editor; outros programas: colocar no código, ver guidelines). Não pode ter vídeo (passaria a Rich Media, com specs diferentes). Animação: máx. 30 segundos. Fundo branco: usar border para destacar a peça. Validação: usar o validador de asset DCM (todos os pontos têm de estar OK).</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
+      <c r="M252" t="inlineStr">
         <is>
           <t>https://support.google.com/dcm/answer/3145300?hl=en</t>
         </is>
@@ -13880,7 +13901,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13937,7 +13958,7 @@
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
+      <c r="M254" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -13994,7 +14015,7 @@
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
+      <c r="M255" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -14051,7 +14072,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
+      <c r="M256" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -14108,7 +14129,7 @@
           <t>MP4, MOV (upload via YouTube)</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
+      <c r="M257" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -14165,7 +14186,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
+      <c r="M258" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -14222,7 +14243,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
+      <c r="M259" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/11462260</t>
         </is>
@@ -14279,7 +14300,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
+      <c r="M260" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
@@ -14336,7 +14357,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
+      <c r="M261" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091671</t>
         </is>
@@ -14393,7 +14414,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
+      <c r="M262" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
@@ -14450,7 +14471,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
+      <c r="M263" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
@@ -14507,7 +14528,7 @@
           <t>MP4, MOV</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
+      <c r="M264" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/9748775</t>
         </is>
@@ -14564,7 +14585,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
+      <c r="M265" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
@@ -14621,7 +14642,7 @@
           <t>JPG, PNG</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
+      <c r="M266" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/12437745</t>
         </is>
@@ -14678,7 +14699,7 @@
           <t>Títulos: até 30 caracteres, 1 a 15; Descrições: até 90 caracteres, 1 a 4</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
+      <c r="M267" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/7684791</t>
         </is>
@@ -14740,7 +14761,7 @@
           <t>Título: 30c; Título longo: 90c; Descrição: 90c; CTA: 10c.</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
+      <c r="M268" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/12066387</t>
         </is>
@@ -14797,7 +14818,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
+      <c r="M269" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -14854,7 +14875,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
+      <c r="M270" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -14916,7 +14937,7 @@
           <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c.</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
+      <c r="M271" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -14978,7 +14999,7 @@
           <t>Feed: texto principal 50-150c, título 27c; Stories: texto principal 125c, título 40c; Reels: texto principal 40c, título 55c (sem legendas automáticas).</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
+      <c r="M272" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -15040,7 +15061,7 @@
           <t>Feed: texto principal 80c, título 20c, descrição 18c, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 40c.</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
+      <c r="M273" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -15102,7 +15123,7 @@
           <t>Feed: texto principal 125c, título 40c, URL obrigatório; Reels: texto principal 72c, título 10c, URL obrigatório.</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
+      <c r="M274" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -15164,7 +15185,7 @@
           <t>Feed: texto principal 125c, título 40c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c; Explorar: texto principal 125c, título 40c, máx. 30 hashtags.</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
+      <c r="M275" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -15226,7 +15247,7 @@
           <t>Feed: texto principal 125c, máx. 30 hashtags; Stories: texto principal 125c; Reels: texto principal 44c.</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
+      <c r="M276" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -15288,7 +15309,7 @@
           <t>Feed: texto principal 125c, máx. 30 hashtags, URL obrigatório; Stories: texto principal 125c, título 40c, URL obrigatório.</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
+      <c r="M277" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -15350,7 +15371,7 @@
           <t>Feed: texto principal 125c, título 40c, URL obrigatório; Stories: texto principal 125c, URL obrigatório.</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
+      <c r="M278" t="inlineStr">
         <is>
           <t>https://www.facebook.com/business/ads-guide/update</t>
         </is>
@@ -15412,7 +15433,7 @@
           <t>Título: até 100c; Texto na página: até 250c.</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
+      <c r="M279" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -15474,7 +15495,7 @@
           <t>Texto sobreposto: máx. 10 palavras; Feature: até 50c (título cortado a partir dos 50c).</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
+      <c r="M280" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -15536,7 +15557,7 @@
           <t>Título: até 100c; Texto sobreposto: máx. 10 palavras; Perguntas: até 96c; Respostas: até 48c; Resultados: título até 100c, descrição até 800c.</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
+      <c r="M281" t="inlineStr">
         <is>
           <t>https://help.pinterest.com/en/business/article/pinterest-product-specs</t>
         </is>
@@ -15588,12 +15609,13 @@
           <t>Lens assets conforme Lens Studio/Lens Web Builder</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr">
         <is>
           <t>Logótipo ou nome da marca visível obrigatório em Face e World Lenses, de preferência no canto superior esquerdo ou direito, fora da zona coberta pela UI/carrossel; etiqueta 'SPONSORED' acrescentada automaticamente pelo Snapchat (visível 2 seg, não aparece no Snap do utilizador).</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
+      <c r="M282" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -15655,7 +15677,7 @@
           <t>Nome da marca: até 25c com espaços (retirado automaticamente do Perfil Público); Título: 25-28c ideal (máx. 34c).</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
+      <c r="M283" t="inlineStr">
         <is>
           <t>https://forbusiness.snapchat.com/advertising/ad-formats</t>
         </is>
@@ -15707,7 +15729,7 @@
           <t>Codec vídeo H.264 (Baseline, Main ou High Profile, espaço de cor 4:2:0); áudio AAC LC</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
+      <c r="M284" t="inlineStr">
         <is>
           <t>https://business.x.com/en/products/vertical-video-ads</t>
         </is>
@@ -15766,10 +15788,15 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>URL (opcional): tem de começar por http:// ou https://. Branding e legendas/closed captions fortemente recomendados.</t>
+          <t>URL (opcional): tem de começar por http:// ou https://.</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
+        <is>
+          <t>Branding e legendas/closed captions fortemente recomendados.</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
         <is>
           <t>https://business.x.com/en/advertising/campaign-types/amplify-pre-roll</t>
         </is>
@@ -15826,7 +15853,7 @@
           <t>Descrição da página do evento: até 280c (pode incluir links externos). Carousel do evento: até 5 vídeos (live, VOD, GIFs ou fotos — investimento adicional). Timeline post: até 5 termos específicos (palavras-chave, nomes).</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
+      <c r="M286" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -15873,7 +15900,7 @@
           <t>Conforme o formato subjacente escolhido</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="M287" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -15935,7 +15962,7 @@
           <t>Nome do trend (obrigatório): máx. 20c; Descrição do trend (opcional, muito recomendado): máx. 30c — evitar frases tipo clickbait ('50% off', 'compre um leve dois').</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
+      <c r="M288" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -15982,12 +16009,13 @@
           <t>Configurado e lançado via Arrow (plataforma de terceiros, IC Group + X Next)</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr">
         <is>
           <t>3 formatos de campanha: Scheduled (post de opt-in + 1 post agendado); Subscription (post de opt-in + vários posts agendados); Instant (1 post instantâneo por pessoa que fez opt-in). Requer conta X pública e verificada, e autorização via X OAuth à Arrow.</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
+      <c r="M289" t="inlineStr">
         <is>
           <t>https://business.x.com/en/advertising/branded-notifications</t>
         </is>
@@ -16034,7 +16062,7 @@
           <t>Requer X Pixel ou Conversion API configurado (eventos: Page View, Content View, Add to Cart, Purchase, com content parameters)</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
+      <c r="M290" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications</t>
         </is>
@@ -16081,7 +16109,7 @@
           <t>Conversation Card (post original): texto até 280c, hashtag até 21c (incl. o caracter #). Post pré-preenchido (após clique no CTA): texto até 256c, título até 23c. Thank You post: texto até 23c, URL opcional até 23c.</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
+      <c r="M291" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#conversation</t>
         </is>
@@ -16133,7 +16161,7 @@
           <t>Texto do post: até 280c; 2 a 4 opções de resposta, até 25c cada (não conta para os 280c do post).</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
+      <c r="M292" t="inlineStr">
         <is>
           <t>https://business.x.com/en/help/campaign-setup/creative-ad-specifications#polls</t>
         </is>
@@ -16180,12 +16208,13 @@
           <t>Suporta Spark Ads e Non-Spark Ads (recomendado 1-2 criativos por campanha); Duet/Stitch: Spark Ads segue os toggles do vídeo original, Non-Spark Ads não suportado.</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr">
         <is>
           <t>Objetivo: Reach. Targeting disponível: idade (18+) e localização (país). Tracking de terceiros suportado (impressões e cliques). Landing page: webview standard (HTTPS) ou páginas internas TikTok (Branded Hashtag Challenge, Effect, TikTok Shop) — não suporta redirecionamento automático para app store nem link de TopView para LIVE. Música: mesma política dos in-feed ads reservation (Commercial Music Library ou faixas próprias autorizadas). Permite desativar comentários e download do vídeo. Add-ons: só os disponíveis em ambos os placements (TopView + Top Feed). Som: sempre ativo. Watermark: pode pedir vídeo descarregável sem marca de água.</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
+      <c r="M293" t="inlineStr">
         <is>
           <t>https://ads.tiktok.com/resources/help/article/topreach-ad-specifications?lang=pt</t>
         </is>
@@ -16398,7 +16427,7 @@
           <t>JPG, GIF ou PNG</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
+      <c r="M297" t="inlineStr">
         <is>
           <t>https://support.google.com/google-ads/answer/17091270</t>
         </is>
@@ -16502,7 +16531,7 @@
           <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
+      <c r="M299" t="inlineStr">
         <is>
           <t>https://support.google.com/displayvideo/answer/9166157?hl=en</t>
         </is>
@@ -16559,7 +16588,7 @@
           <t>AVI, MOV, MP4, M4V, MPEG, MPG, WEBM ou WMV; só tags VAST (VPAID não suportado); áudio: loudness recomendado -24 LKFS ±2 LKFS</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
+      <c r="M300" t="inlineStr">
         <is>
           <t>https://support.google.com/displayvideo/answer/3129957?hl=en</t>
         </is>
@@ -16648,7 +16677,7 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
+      <c r="M302" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/window-splash-video/</t>
         </is>
@@ -16705,7 +16734,7 @@
           <t>MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
+      <c r="M303" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/intro-full-video/</t>
         </is>
@@ -16762,7 +16791,7 @@
           <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
+      <c r="M304" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/splash-intro/</t>
         </is>
@@ -16819,7 +16848,7 @@
           <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
+      <c r="M305" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/video-fullscreen-takeover/</t>
         </is>
@@ -16876,7 +16905,7 @@
           <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
+      <c r="M306" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/FullScreen-TakeOver/</t>
         </is>
@@ -16928,7 +16957,7 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
+      <c r="M307" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/takeover/</t>
         </is>
@@ -16980,7 +17009,7 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
+      <c r="M308" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin/</t>
         </is>
@@ -17037,7 +17066,7 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
+      <c r="M309" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-video/</t>
         </is>
@@ -17089,7 +17118,7 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
+      <c r="M310" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-invertida/</t>
         </is>
@@ -17146,7 +17175,7 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
+      <c r="M311" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/skin-mobile/</t>
         </is>
@@ -17198,7 +17227,7 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
+      <c r="M312" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/parallax/</t>
         </is>
@@ -17245,7 +17274,7 @@
           <t>Título: máx. 40c; Descrição: máx. 35c; Texto do botão CTA (ex.: Saber mais, Comprar agora, Reserve já, Entre em contacto).</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
+      <c r="M313" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/carrossel/</t>
         </is>
@@ -17302,7 +17331,7 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
+      <c r="M314" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/flipbook/</t>
         </is>
@@ -17354,7 +17383,7 @@
           <t>JPG ou PNG.</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
+      <c r="M315" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/mrec-cubo-3d/</t>
         </is>
@@ -17406,7 +17435,7 @@
           <t>JPG ou PNG.</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
+      <c r="M316" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/half-page-cubo-3d/</t>
         </is>
@@ -17463,7 +17492,7 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
+      <c r="M317" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/ticker/</t>
         </is>
@@ -17520,7 +17549,7 @@
           <t>MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
+      <c r="M318" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/spot-tv/</t>
         </is>
@@ -17577,7 +17606,7 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
+      <c r="M319" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/flip-ad/</t>
         </is>
@@ -17629,7 +17658,7 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
+      <c r="M320" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/overslide/</t>
         </is>
@@ -17686,7 +17715,7 @@
           <t>Imagem: JPG, PNG, GIF ou HTML5. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
+      <c r="M321" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/layer/</t>
         </is>
@@ -17743,7 +17772,7 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
+      <c r="M322" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/peel-off/</t>
         </is>
@@ -17795,7 +17824,7 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
+      <c r="M323" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/push-down/</t>
         </is>
@@ -17847,7 +17876,7 @@
           <t>MP3.</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
+      <c r="M324" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/audio-ad/</t>
         </is>
@@ -17904,7 +17933,7 @@
           <t>MP4.</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
+      <c r="M325" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/pre-roll/</t>
         </is>
@@ -17961,7 +17990,7 @@
           <t>MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
+      <c r="M326" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/incontent-sticky/</t>
         </is>
@@ -18018,7 +18047,7 @@
           <t>MP4, som off por defeito.</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
+      <c r="M327" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/incontent/</t>
         </is>
@@ -18070,7 +18099,7 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr">
+      <c r="M328" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/superboard/</t>
         </is>
@@ -18122,7 +18151,7 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr">
+      <c r="M329" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/mrec/</t>
         </is>
@@ -18174,7 +18203,7 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
+      <c r="M330" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/half-page/</t>
         </is>
@@ -18226,7 +18255,7 @@
           <t>JPG, PNG, GIF ou HTML5.</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
+      <c r="M331" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/megapub/</t>
         </is>
@@ -18283,7 +18312,7 @@
           <t>MP4.</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
+      <c r="M332" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/mrec-video/</t>
         </is>
@@ -18335,7 +18364,7 @@
           <t>Imagem: JPG, PNG ou GIF. Vídeo: MP4.</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
+      <c r="M333" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/half-page-video/</t>
         </is>
@@ -18392,7 +18421,7 @@
           <t>MP4.</t>
         </is>
       </c>
-      <c r="L334" t="inlineStr">
+      <c r="M334" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/half-page-full-video/</t>
         </is>
@@ -18439,7 +18468,7 @@
           <t>Link social do Facebook, Instagram, X (Twitter) ou LinkedIn.</t>
         </is>
       </c>
-      <c r="L335" t="inlineStr">
+      <c r="M335" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/social-card/</t>
         </is>
@@ -18491,7 +18520,7 @@
           <t>JPG, PNG ou GIF.</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
+      <c r="M336" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/filmstrip/</t>
         </is>
@@ -18543,12 +18572,13 @@
           <t>JPG (formato estático).</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr">
         <is>
           <t>Só suporta tag de clicks (não é possível usar tag de impressões).</t>
         </is>
       </c>
-      <c r="L337" t="inlineStr">
+      <c r="M337" t="inlineStr">
         <is>
           <t>https://noticiasilimitadas.pt/digital/newsletter/</t>
         </is>
@@ -18600,7 +18630,8 @@
           <t>PSD</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr">
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr">
         <is>
           <t>Opções de layout: fundo com copy (base); + CTA à esquerda ou à direita (opcional); + logo no topo, à esquerda ou à direita. Suporte com tracking DCM. Ver ficha técnica adicional fornecida pelo meio ("We Transfer", não disponibilizada aqui).</t>
         </is>
@@ -18652,7 +18683,8 @@
           <t>PNG, JPG ou BMP (também aceite em GIF, redimensionado automaticamente pela Anzu).</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr">
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr">
         <is>
           <t>Suporte com tracking DCM. Até 10 criativos por deal. Todos os criativos são moderados pela equipa Roblox e podem sofrer alterações para cumprir as regras de compliance da Roblox. Ver ficheiro técnico adicional fornecido pelo meio (não disponibilizado aqui).</t>
         </is>
@@ -18738,22 +18770,20 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Ficheiros de trabalho necessários: banners laterais em PSD, fontes (fonts), copies e color book/codes. As dimensões exatas dos banners laterais constam numa folha técnica adicional fornecida pelo meio (não disponibilizada aqui).</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr"/>
+          <t>Ficheiros de trabalho necessários: banners laterais em PSD, fontes (fonts), copies e color book/codes.</t>
+        </is>
+      </c>
       <c r="J341" t="inlineStr">
         <is>
           <t>PSD</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>Os banners laterais podem ser iguais ou diferentes, ao critério do cliente. Suporte com tracking DCM. O meio ajuda a produzir a versão final — se houver elementos extra com que possa trabalhar para enriquecer o formato, enviar os ficheiros editáveis.</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Os banners laterais podem ser iguais ou diferentes, ao critério do cliente. Suporte com tracking DCM. O meio ajuda a produzir a versão final — se houver elementos extra com que possa trabalhar para enriquecer o formato, enviar os ficheiros editáveis. As dimensões exatas dos banners laterais constam numa folha técnica adicional fornecida pelo meio (não disponibilizada aqui).</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -18786,7 +18816,6 @@
           <t>Native ad</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr">
         <is>
           <t>1.91:1, 1.78:1, 1.5:1, 1.33:1 ou 1:1 (pelo menos um obrigatório)</t>
@@ -18804,10 +18833,14 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Suporte com tracking DCM. Copies (todos obrigatórios): Short Headline (x2) — máx. 30 caracteres; Long Headline — 90 caracteres; Descrição — 90 caracteres; Business/Brand Name — 25 caracteres.</t>
-        </is>
-      </c>
-      <c r="L342" t="inlineStr"/>
+          <t>Todos obrigatórios: Short Headline (x2) — máx. 30 caracteres; Long Headline — 90 caracteres; Descrição — 90 caracteres; Business/Brand Name — 25 caracteres.</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Suporte com tracking DCM.</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -18845,11 +18878,6 @@
           <t>728x90px (Desktop, Tablet)</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
-      <c r="L343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -18887,11 +18915,6 @@
           <t>320x50px (Mobile)</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -18929,7 +18952,6 @@
           <t>300x250px (All)</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
           <t>Máx. 150 KB</t>
@@ -18940,8 +18962,7 @@
           <t>GIF, JPEG ou HTML5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr">
+      <c r="M345" t="inlineStr">
         <is>
           <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#mpu-h4</t>
         </is>
@@ -18983,7 +19004,6 @@
           <t>970x250px (Desktop)</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
           <t>Máx. 250 KB</t>
@@ -18994,8 +19014,7 @@
           <t>GIF, JPEG ou HTML5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
-      <c r="L346" t="inlineStr">
+      <c r="M346" t="inlineStr">
         <is>
           <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#bb-h4</t>
         </is>
@@ -19037,11 +19056,6 @@
           <t>320x100px (Mobile)</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr"/>
-      <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -19079,7 +19093,6 @@
           <t>300x600px (All)</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
           <t>Máx. 250 KB</t>
@@ -19090,8 +19103,7 @@
           <t>GIF, JPEG ou HTML5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr">
+      <c r="M348" t="inlineStr">
         <is>
           <t>https://www.bauermedia.co.uk/advertise/advertising-services/ad-specs/display-ad-specs/#dmpu-h4</t>
         </is>
@@ -19133,15 +19145,12 @@
           <t>Responsive (All) — adapta-se ao layout do site.</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr">
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr">
         <is>
           <t>Formatos nativos personalizados, específicos por site. Consultar as specs próprias de cada site (ex.: Bauer Native — All Site) através do link fornecido pelo meio (não disponibilizado aqui).</t>
         </is>
       </c>
-      <c r="L349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -19179,15 +19188,12 @@
           <t>300x600px (Mobile)</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
-      <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr">
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr">
         <is>
           <t>Servido via tag de terceiros (Mobkoi).</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -19225,15 +19231,12 @@
           <t>Multi — formato construído internamente pela Illuminate (Mobile).</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
-      <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr">
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr">
         <is>
           <t>Solução de rich media interativa, otimizada mobile-first, com formatos inspirados em redes sociais, para alcançar utilizadores durante a leitura de conteúdo editorial. Specs técnicas completas num documento à parte ("Social Display RMF Specifications"), não disponibilizado aqui.</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -19271,19 +19274,17 @@
           <t>Multi (All) — combinação de vários espaços publicitários na página.</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr">
         <is>
           <t>Skin/hero images em formato estático: JPG ou PNG.</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr">
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr">
         <is>
           <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
         </is>
       </c>
-      <c r="L352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -19321,19 +19322,17 @@
           <t>Responsive (All).</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
-      <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr">
         <is>
           <t>Skin/hero images em formato estático: JPG ou PNG.</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr">
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr">
         <is>
           <t>Não são aceites tags de criativos de terceiros (viewability, conversão, engagement) — apenas trackers de impressão e clique.</t>
         </is>
       </c>
-      <c r="L353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -19366,7 +19365,6 @@
           <t>In-Article Video</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
           <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
@@ -19382,12 +19380,12 @@
           <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr">
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr">
         <is>
           <t>Anúncio de vídeo autónomo entre parágrafos de conteúdo editorial (mobile, tablet e desktop). Reproduz automaticamente quando 50% do anúncio está visível; som desligado por defeito; botão "Learn More" no fundo do anúncio (único elemento clicável).</t>
         </is>
       </c>
-      <c r="L354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -19420,7 +19418,6 @@
           <t>Radio Player Pre-Roll</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
       <c r="H355" t="inlineStr">
         <is>
           <t>16:9 ou 4:3 (horizontal, mín. 1280x720 ou 1280x960); 9:16 (vertical, mín. 720x1280) — recomenda-se pelo menos 1 vídeo horizontal para entrega em todos os dispositivos.</t>
@@ -19436,12 +19433,12 @@
           <t>MP4, 3GPP ou MOV (H264, vídeo MPEG4, áudio AAC); AVI (vídeo MJPEG, áudio PCM); MPEG-PS (vídeo MPEG2, áudio MP2); WMV. Bitrate mín. 1500 kbit/s. Duração máx. 30s. Sem autoplay de áudio (som off por defeito). Tags VAST 2.0 a 4.2 (sem suporte a VPAID).</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr">
         <is>
           <t>Pre-roll único, reproduzido no arranque do stream de áudio iniciado pelo utilizador (ex.: Radio Players como Kiss). Vendido como parte do Radio Player Takeover ou via programática. Não disponível atualmente nos canais de YouTube da Bauer.</t>
         </is>
       </c>
-      <c r="L355" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
